--- a/docs/planning/05_상세기능명세서.xlsx
+++ b/docs/planning/05_상세기능명세서.xlsx
@@ -604,22 +604,22 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>게스트 모드</t>
+          <t>게스트 모드 (프로토타입 전용)</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>가입 없이 샘플 데이터로 즉시 체험</t>
+          <t>프로토타입 검토용. 출시 시 제거</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>MVP</t>
+          <t>프로토타입</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Won't</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -1645,7 +1645,7 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>시스템·다크·라이트 + 4색</t>
+          <t>다크/라이트 + 강조색 3종(핑크/블루/그레이)</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -2165,7 +2165,7 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>TBD: 인증 방식 — 6자리 코드 vs 메일 링크 클릭. 인우님 결정 필요</t>
+          <t>결정: 이메일 6자리 코드. SMS는 v1.x 검토</t>
         </is>
       </c>
     </row>
@@ -2417,7 +2417,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>게스트 모드</t>
+          <t>게스트 모드 (프로토타입 전용)</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -2427,22 +2427,22 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>가입 없이 샘플 데이터로 모든 기능 체험. 폴더 4개 + 공유 폴더 2개 + 링크 ~14개 시드. 로컬스토리지에만 저장. 가입 시 데이터 마이그레이션 옵션 제공</t>
+          <t>(프로토타입 전용) 가입 없이 샘플 데이터로 기능 체험. 출시 빌드에서는 "둘러보기" 버튼 자체 비노출 (feature flag로 제어)</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Won't</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>(클라이언트 처리)</t>
+          <t>(클라이언트, feature flag)</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>MVP</t>
+          <t>프로토타입</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>TBD: 가입 시 게스트 데이터 마이그레이션 — 자동 vs 모달 선택. 일단 모달로</t>
+          <t>결정: 출시 시 제거. 마이그레이션 로직 구현 불필요(게스트 데이터 폐기)</t>
         </is>
       </c>
     </row>
@@ -2462,12 +2462,12 @@
       <c r="C14" s="3" t="inlineStr"/>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>입력</t>
+          <t>정책</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>"가입 없이 둘러보기" 버튼 클릭</t>
+          <t>[활성 조건] feature flag GUEST_MODE=true 일 때만 노출 / [출시] GUEST_MODE=false 빌드로 배포</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr"/>
@@ -2477,24 +2477,52 @@
       <c r="J14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr"/>
-      <c r="B15" s="3" t="inlineStr"/>
-      <c r="C15" s="3" t="inlineStr"/>
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>AUTH-004
+#SPLASH</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>인증</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>자동 로그인 / 토큰 갱신</t>
+        </is>
+      </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>출력</t>
+          <t>설명</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>- 시드 데이터가 #HOME에 표시
-- 헤더에 "게스트 모드" 배지 + "가입하기" 버튼</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr"/>
-      <c r="G15" s="3" t="inlineStr"/>
-      <c r="H15" s="3" t="inlineStr"/>
-      <c r="I15" s="3" t="inlineStr"/>
+          <t>앱·웹 진입 시 저장된 토큰으로 자동 로그인. 액세스 토큰 만료 시 리프레시 토큰으로 갱신, 둘 다 만료 시 로그아웃</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>토큰 갱신 API</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>기획완료</t>
+        </is>
+      </c>
       <c r="J15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
@@ -2503,14 +2531,12 @@
       <c r="C16" s="3" t="inlineStr"/>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>정책</t>
+          <t>입력</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>[로컬 저장 대상] 모든 데이터 (POLICY-LOCAL 참고)
-[동기화 비활성] SYNC-001 비활성 (가입 후 마이그레이션)
-[기능 차단] 공유 폴더 만들기/초대 수락은 가입 유도 모달</t>
+          <t>(자동) 저장된 액세스·리프레시 토큰</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr"/>
@@ -2525,14 +2551,14 @@
       <c r="C17" s="3" t="inlineStr"/>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>예외</t>
+          <t>출력</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>- 게스트에서 공유 폴더 시도: '가입하면 친구와 함께 큐레이션할 수 있어요'
-- 게스트에서 동기화 시도: '가입하면 모든 디바이스에서 이어볼 수 있어요'
-- 로컬스토리지 한도 초과(5MB): '둘러보기 데이터가 가득 찼어요. 가입하면 안 차요'</t>
+          <t>- 토큰 유효: #HOME 즉시
+- 액세스 만료 + 리프레시 OK: 새 토큰 저장 후 #HOME
+- 리프레시 만료: #AUTH-LOGIN</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr"/>
@@ -2542,52 +2568,25 @@
       <c r="J17" s="3" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>AUTH-004
-#SPLASH</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>인증</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>자동 로그인 / 토큰 갱신</t>
-        </is>
-      </c>
+      <c r="A18" s="3" t="inlineStr"/>
+      <c r="B18" s="3" t="inlineStr"/>
+      <c r="C18" s="3" t="inlineStr"/>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>설명</t>
+          <t>정책</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>앱·웹 진입 시 저장된 토큰으로 자동 로그인. 액세스 토큰 만료 시 리프레시 토큰으로 갱신, 둘 다 만료 시 로그아웃</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>토큰 갱신 API</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="inlineStr">
-        <is>
-          <t>기획완료</t>
-        </is>
-      </c>
+          <t>POLICY-AUTH 참고
+[처리 순서] 401 응답 시 자동 1회 갱신 후 원래 요청 재시도
+[동기화] 갱신은 모든 활성 디바이스가 독립적으로 처리</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr"/>
+      <c r="G18" s="3" t="inlineStr"/>
+      <c r="H18" s="3" t="inlineStr"/>
+      <c r="I18" s="3" t="inlineStr"/>
       <c r="J18" s="3" t="inlineStr"/>
     </row>
     <row r="19">
@@ -2596,12 +2595,13 @@
       <c r="C19" s="3" t="inlineStr"/>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>입력</t>
+          <t>예외</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>(자동) 저장된 액세스·리프레시 토큰</t>
+          <t>- 갱신 API 실패 (네트워크): 캐시된 #HOME 표시 + "곧 다시 연결할게요" 토스트
+- 리프레시 토큰 무효(서버 invalidate): 강제 로그아웃 + #AUTH-LOGIN</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr"/>
@@ -2611,168 +2611,171 @@
       <c r="J19" s="3" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr"/>
-      <c r="B20" s="3" t="inlineStr"/>
-      <c r="C20" s="3" t="inlineStr"/>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>출력</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>- 토큰 유효: #HOME 즉시
-- 액세스 만료 + 리프레시 OK: 새 토큰 저장 후 #HOME
-- 리프레시 만료: #AUTH-LOGIN</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr"/>
-      <c r="G20" s="3" t="inlineStr"/>
-      <c r="H20" s="3" t="inlineStr"/>
-      <c r="I20" s="3" t="inlineStr"/>
-      <c r="J20" s="3" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr"/>
-      <c r="B21" s="3" t="inlineStr"/>
-      <c r="C21" s="3" t="inlineStr"/>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>정책</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>POLICY-AUTH 참고
-[처리 순서] 401 응답 시 자동 1회 갱신 후 원래 요청 재시도
-[동기화] 갱신은 모든 활성 디바이스가 독립적으로 처리</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr"/>
-      <c r="G21" s="3" t="inlineStr"/>
-      <c r="H21" s="3" t="inlineStr"/>
-      <c r="I21" s="3" t="inlineStr"/>
-      <c r="J21" s="3" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr"/>
-      <c r="B22" s="3" t="inlineStr"/>
-      <c r="C22" s="3" t="inlineStr"/>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>예외</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>- 갱신 API 실패 (네트워크): 캐시된 #HOME 표시 + "곧 다시 연결할게요" 토스트
-- 리프레시 토큰 무효(서버 invalidate): 강제 로그아웃 + #AUTH-LOGIN</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr"/>
-      <c r="G22" s="3" t="inlineStr"/>
-      <c r="H22" s="3" t="inlineStr"/>
-      <c r="I22" s="3" t="inlineStr"/>
-      <c r="J22" s="3" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>AUTH-005
 #AUTH-LOGIN</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>인증</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>소셜 로그인</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>Google/Apple/Kakao OAuth 가입/로그인. v1.x 추가 예정 — 보류</t>
         </is>
       </c>
-      <c r="F23" s="4" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>Should</t>
         </is>
       </c>
-      <c r="G23" s="4" t="inlineStr"/>
-      <c r="H23" s="4" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr"/>
+      <c r="H20" s="4" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="I23" s="4" t="inlineStr">
+      <c r="I20" s="4" t="inlineStr">
         <is>
           <t>기획중</t>
         </is>
       </c>
-      <c r="J23" s="4" t="inlineStr">
+      <c r="J20" s="4" t="inlineStr">
         <is>
           <t>MVP 이후 v1.x 추가</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>LINK-001
 #HOME
 #LINK-ADD</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>링크</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>URL 직접 입력 추가</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="E27" s="3" t="inlineStr">
+      <c r="E24" s="3" t="inlineStr">
         <is>
           <t>사용자가 URL을 직접 입력 또는 붙여넣어 저장하는 1차 진입 경로. + 버튼 → 시트 슬라이드 업 → 입력 → 저장. 저장 직후 LINK-004(AI 요약) 자동 트리거</t>
         </is>
       </c>
-      <c r="F27" s="3" t="inlineStr">
+      <c r="F24" s="3" t="inlineStr">
         <is>
           <t>Must</t>
         </is>
       </c>
-      <c r="G27" s="3" t="inlineStr">
+      <c r="G24" s="3" t="inlineStr">
         <is>
           <t>링크 생성 API
 AI 요약 큐 publish</t>
         </is>
       </c>
-      <c r="H27" s="3" t="inlineStr">
+      <c r="H24" s="3" t="inlineStr">
         <is>
           <t>MVP</t>
         </is>
       </c>
-      <c r="I27" s="3" t="inlineStr">
+      <c r="I24" s="3" t="inlineStr">
         <is>
           <t>기획완료</t>
         </is>
       </c>
+      <c r="J24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr"/>
+      <c r="B25" s="3" t="inlineStr"/>
+      <c r="C25" s="3" t="inlineStr"/>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>입력</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>- URL (필수, 2048자 이하, http/https)
+- 폴더 (선택, 기본=미분류)
+- 메모 (선택, 200자)
+- (자동) source_type='url', owner_id</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr"/>
+      <c r="G25" s="3" t="inlineStr"/>
+      <c r="H25" s="3" t="inlineStr"/>
+      <c r="I25" s="3" t="inlineStr"/>
+      <c r="J25" s="3" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr"/>
+      <c r="B26" s="3" t="inlineStr"/>
+      <c r="C26" s="3" t="inlineStr"/>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>출력</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>- links INSERT → 홈 피드 최상단에 카드 fade-in
+- 토스트 "저장됐어요"
+- LINK-004 비동기 트리거</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr"/>
+      <c r="G26" s="3" t="inlineStr"/>
+      <c r="H26" s="3" t="inlineStr"/>
+      <c r="I26" s="3" t="inlineStr"/>
+      <c r="J26" s="3" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr"/>
+      <c r="B27" s="3" t="inlineStr"/>
+      <c r="C27" s="3" t="inlineStr"/>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>정책</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>[기본값] 폴더=미분류
+[제약] URL 길이 ≤ 2048자, 한 유저당 ≤ 10,000개
+[중복 처리] 동일 owner의 동일 URL은 INSERT 차단
+[동기화] INSERT 직후 SYNC-001로 다른 디바이스에 1~2초 내 반영</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr"/>
+      <c r="G27" s="3" t="inlineStr"/>
+      <c r="H27" s="3" t="inlineStr"/>
+      <c r="I27" s="3" t="inlineStr"/>
       <c r="J27" s="3" t="inlineStr"/>
     </row>
     <row r="28">
@@ -2781,15 +2784,15 @@
       <c r="C28" s="3" t="inlineStr"/>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>입력</t>
+          <t>예외</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>- URL (필수, 2048자 이하, http/https)
-- 폴더 (선택, 기본=미분류)
-- 메모 (선택, 200자)
-- (자동) source_type='url', owner_id</t>
+          <t>- URL 형식 오류: '올바른 URL 형식이 아니에요' + 저장 버튼 비활성
+- 중복 URL: 모달 "이미 저장된 링크예요. 상세로 이동할까요?" → "이동" 또는 "취소"
+- 한도 초과 (10,000개): '저장 한도에 도달했어요. 오래된 링크를 정리해주세요'
+- 네트워크 오류: 로컬 큐잉 + '곧 다시 시도할게요' (POLICY-LOCAL 참고)</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr"/>
@@ -2799,25 +2802,52 @@
       <c r="J28" s="3" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr"/>
-      <c r="B29" s="3" t="inlineStr"/>
-      <c r="C29" s="3" t="inlineStr"/>
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>LINK-002
+#LINK-ADD</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>링크</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>클립보드 자동 감지</t>
+        </is>
+      </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>출력</t>
+          <t>설명</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>- links INSERT → 홈 피드 최상단에 카드 fade-in
-- 토스트 "저장됐어요"
-- LINK-004 비동기 트리거</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="inlineStr"/>
-      <c r="G29" s="3" t="inlineStr"/>
-      <c r="H29" s="3" t="inlineStr"/>
-      <c r="I29" s="3" t="inlineStr"/>
+          <t>링크 추가 시트 진입 즉시 navigator.clipboard로 텍스트 읽고, URL이면 입력창에 자동 채움</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>(클라이언트)</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>기획완료</t>
+        </is>
+      </c>
       <c r="J29" s="3" t="inlineStr"/>
     </row>
     <row r="30">
@@ -2826,15 +2856,12 @@
       <c r="C30" s="3" t="inlineStr"/>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>정책</t>
+          <t>입력</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>[기본값] 폴더=미분류
-[제약] URL 길이 ≤ 2048자, 한 유저당 ≤ 10,000개
-[중복 처리] 동일 owner의 동일 URL은 INSERT 차단
-[동기화] INSERT 직후 SYNC-001로 다른 디바이스에 1~2초 내 반영</t>
+          <t>(자동) 클립보드 텍스트</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr"/>
@@ -2849,15 +2876,13 @@
       <c r="C31" s="3" t="inlineStr"/>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>예외</t>
+          <t>출력</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>- URL 형식 오류: '올바른 URL 형식이 아니에요' + 저장 버튼 비활성
-- 중복 URL: 모달 "이미 저장된 링크예요. 상세로 이동할까요?" → "이동" 또는 "취소"
-- 한도 초과 (10,000개): '저장 한도에 도달했어요. 오래된 링크를 정리해주세요'
-- 네트워크 오류: 로컬 큐잉 + '곧 다시 시도할게요' (POLICY-LOCAL 참고)</t>
+          <t>- URL이면 입력창 자동 채움 + "클립보드에서 가져왔어요" 미세 안내
+- 아니면 빈 입력창</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr"/>
@@ -2867,52 +2892,24 @@
       <c r="J31" s="3" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>LINK-002
-#LINK-ADD</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>링크</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>클립보드 자동 감지</t>
-        </is>
-      </c>
+      <c r="A32" s="3" t="inlineStr"/>
+      <c r="B32" s="3" t="inlineStr"/>
+      <c r="C32" s="3" t="inlineStr"/>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>설명</t>
+          <t>정책</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>링크 추가 시트 진입 즉시 navigator.clipboard로 텍스트 읽고, URL이면 입력창에 자동 채움</t>
-        </is>
-      </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t>(클라이언트)</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="I32" s="3" t="inlineStr">
-        <is>
-          <t>기획완료</t>
-        </is>
-      </c>
+          <t>[권한] 권한 거부 시 자동 채움 영구 비활성
+[정규식] http(s):// 시작 또는 도메인 패턴 인식</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr"/>
+      <c r="G32" s="3" t="inlineStr"/>
+      <c r="H32" s="3" t="inlineStr"/>
+      <c r="I32" s="3" t="inlineStr"/>
       <c r="J32" s="3" t="inlineStr"/>
     </row>
     <row r="33">
@@ -2921,12 +2918,14 @@
       <c r="C33" s="3" t="inlineStr"/>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>입력</t>
+          <t>예외</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>(자동) 클립보드 텍스트</t>
+          <t>- 권한 미허용: 자동 채움 생략, 안내 없음
+- 클립보드 비어있음/텍스트 아님: 빈 상태
+- 매우 긴 텍스트(2000자+): URL 추출 실패, 빈 상태</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr"/>
@@ -2936,24 +2935,53 @@
       <c r="J33" s="3" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="inlineStr"/>
-      <c r="B34" s="3" t="inlineStr"/>
-      <c r="C34" s="3" t="inlineStr"/>
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>LINK-003
+#SHARE-RECEIVE
+#LINK-ADD</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>링크</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>시스템 공유 시트 수신</t>
+        </is>
+      </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>출력</t>
+          <t>설명</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>- URL이면 입력창 자동 채움 + "클립보드에서 가져왔어요" 미세 안내
-- 아니면 빈 입력창</t>
-        </is>
-      </c>
-      <c r="F34" s="3" t="inlineStr"/>
-      <c r="G34" s="3" t="inlineStr"/>
-      <c r="H34" s="3" t="inlineStr"/>
-      <c r="I34" s="3" t="inlineStr"/>
+          <t>manifest.json의 share_target으로 외부 앱(카톡/인스타/사파리/크롬)이 OS 공유 메뉴에 "QLINK" 노출. 사용자가 선택 시 PWA가 URL 받아 #LINK-ADD에 자동 채움</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>(manifest 설정)</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>기획완료</t>
+        </is>
+      </c>
       <c r="J34" s="3" t="inlineStr"/>
     </row>
     <row r="35">
@@ -2962,13 +2990,12 @@
       <c r="C35" s="3" t="inlineStr"/>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>정책</t>
+          <t>입력</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>[권한] 권한 거부 시 자동 채움 영구 비활성
-[정규식] http(s):// 시작 또는 도메인 패턴 인식</t>
+          <t>(외부) URL 또는 텍스트 (text/plain, text/url)</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr"/>
@@ -2983,14 +3010,12 @@
       <c r="C36" s="3" t="inlineStr"/>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>예외</t>
+          <t>출력</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>- 권한 미허용: 자동 채움 생략, 안내 없음
-- 클립보드 비어있음/텍스트 아님: 빈 상태
-- 매우 긴 텍스트(2000자+): URL 추출 실패, 빈 상태</t>
+          <t>- URL 자동 채움 → 사용자가 "저장" 누르면 LINK-001 진행</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr"/>
@@ -3000,53 +3025,24 @@
       <c r="J36" s="3" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>LINK-003
-#SHARE-RECEIVE
-#LINK-ADD</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>링크</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>시스템 공유 시트 수신</t>
-        </is>
-      </c>
+      <c r="A37" s="3" t="inlineStr"/>
+      <c r="B37" s="3" t="inlineStr"/>
+      <c r="C37" s="3" t="inlineStr"/>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>설명</t>
+          <t>정책</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>manifest.json의 share_target으로 외부 앱(카톡/인스타/사파리/크롬)이 OS 공유 메뉴에 "QLINK" 노출. 사용자가 선택 시 PWA가 URL 받아 #LINK-ADD에 자동 채움</t>
-        </is>
-      </c>
-      <c r="F37" s="3" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G37" s="3" t="inlineStr">
-        <is>
-          <t>(manifest 설정)</t>
-        </is>
-      </c>
-      <c r="H37" s="3" t="inlineStr">
-        <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="I37" s="3" t="inlineStr">
-        <is>
-          <t>기획완료</t>
-        </is>
-      </c>
+          <t>[처리 순서] 미로그인 시 토큰 임시 보관 → 로그인 후 자동 #LINK-ADD 진입
+[정규식] 텍스트 페이로드에서 URL 정규식 추출</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr"/>
+      <c r="G37" s="3" t="inlineStr"/>
+      <c r="H37" s="3" t="inlineStr"/>
+      <c r="I37" s="3" t="inlineStr"/>
       <c r="J37" s="3" t="inlineStr"/>
     </row>
     <row r="38">
@@ -3055,12 +3051,14 @@
       <c r="C38" s="3" t="inlineStr"/>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>입력</t>
+          <t>예외</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>(외부) URL 또는 텍스트 (text/plain, text/url)</t>
+          <t>- URL 없음: 빈 #LINK-ADD 진입 + "공유받은 텍스트에서 링크를 못 찾았어요"
+- 게스트: 로컬 저장 + "가입하면 영구 보관돼요" 배너
+- 중복 URL: LINK-001 분기 동일</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr"/>
@@ -3070,24 +3068,59 @@
       <c r="J38" s="3" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="inlineStr"/>
-      <c r="B39" s="3" t="inlineStr"/>
-      <c r="C39" s="3" t="inlineStr"/>
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>LINK-004
+#LINK-ADD
+#LINK-DETAIL</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>링크</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>AI 한 줄 요약 + 자동 태그</t>
+        </is>
+      </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>출력</t>
+          <t>설명</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>- URL 자동 채움 → 사용자가 "저장" 누르면 LINK-001 진행</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="inlineStr"/>
-      <c r="G39" s="3" t="inlineStr"/>
-      <c r="H39" s="3" t="inlineStr"/>
-      <c r="I39" s="3" t="inlineStr"/>
-      <c r="J39" s="3" t="inlineStr"/>
+          <t>링크 저장 직후 비동기로 AI 요약 호출. 사다리 폴백: (1) Chrome 확장 외부 세션(Could) → (2) 사용자 본인 API 키 → (3) 서버 mock. 응답 받으면 links UPDATE + Realtime publish. POLICY-AI 참고</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>AI 요약 API (provider별 어댑터)
+ai_jobs INSERT/UPDATE</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>기획완료</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>결정: MVP=mock+사용자 API키 / v1.x=외부 세션 도입. 단건은 외부 세션 미사용, 일괄 import만 외부 세션 우선 검토</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr"/>
@@ -3095,13 +3128,15 @@
       <c r="C40" s="3" t="inlineStr"/>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>정책</t>
+          <t>입력</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>[처리 순서] 미로그인 시 토큰 임시 보관 → 로그인 후 자동 #LINK-ADD 진입
-[정규식] 텍스트 페이로드에서 URL 정규식 추출</t>
+          <t>- link_id
+- URL
+- (옵션) 페이지 메타(og:title, og:description)
+- 사용자 선택 provider (SETTINGS-001)</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr"/>
@@ -3116,14 +3151,15 @@
       <c r="C41" s="3" t="inlineStr"/>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>예외</t>
+          <t>출력</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>- URL 없음: 빈 #LINK-ADD 진입 + "공유받은 텍스트에서 링크를 못 찾았어요"
-- 게스트: 로컬 저장 + "가입하면 영구 보관돼요" 배너
-- 중복 URL: LINK-001 분기 동일</t>
+          <t>- one_liner: 한 줄 요약 (200자 이내)
+- tags: 자동 태그 3개
+- links UPDATE + ai_jobs 레코드
+- UI에 요약 텍스트 fade-in</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr"/>
@@ -3133,59 +3169,28 @@
       <c r="J41" s="3" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>LINK-004
-#LINK-ADD
-#LINK-DETAIL</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>링크</t>
-        </is>
-      </c>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t>AI 한 줄 요약 + 자동 태그</t>
-        </is>
-      </c>
+      <c r="A42" s="3" t="inlineStr"/>
+      <c r="B42" s="3" t="inlineStr"/>
+      <c r="C42" s="3" t="inlineStr"/>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>설명</t>
+          <t>정책</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>링크 저장 직후 비동기로 AI 요약 호출. 사다리 폴백: (1) Chrome 확장 외부 세션(Could) → (2) 사용자 본인 API 키 → (3) 서버 mock. 응답 받으면 links UPDATE + Realtime publish. POLICY-AI 참고</t>
-        </is>
-      </c>
-      <c r="F42" s="3" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G42" s="3" t="inlineStr">
-        <is>
-          <t>AI 요약 API (provider별 어댑터)
-ai_jobs INSERT/UPDATE</t>
-        </is>
-      </c>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="I42" s="3" t="inlineStr">
-        <is>
-          <t>기획완료</t>
-        </is>
-      </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>TBD: 외부 세션 우선 vs 사용자 API 키 우선 — 인우님 결정 필요</t>
-        </is>
-      </c>
+          <t>[기본값] provider=SETTINGS-001 사용자 선택값, 미설정 시 'mock'
+[시간] 응답 1.4초 이내 (timeout 후 fallback)
+[재시도] 1회 자동 재시도(2초 후), 실패 시 빈 요약으로 저장
+[데이터·채점] 응답 raw는 ai_jobs.raw_response에 jsonb로 보존
+[동기화] 요약 완료 즉시 SYNC-001로 다른 디바이스 반영</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr"/>
+      <c r="G42" s="3" t="inlineStr"/>
+      <c r="H42" s="3" t="inlineStr"/>
+      <c r="I42" s="3" t="inlineStr"/>
+      <c r="J42" s="3" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr"/>
@@ -3193,15 +3198,15 @@
       <c r="C43" s="3" t="inlineStr"/>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>입력</t>
+          <t>예외</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>- link_id
-- URL
-- (옵션) 페이지 메타(og:title, og:description)
-- 사용자 선택 provider (SETTINGS-001)</t>
+          <t>- 모든 폴백 실패: 빈 요약 + 상세에 "다시 요약" 버튼
+- 응답 스키마 불일치(JSON 파싱 실패): 'AI 응답을 이해하지 못했어요' + 재시도 옵션
+- URL 비공개/메타 없음: URL 자체로 추측 요약
+- 한도 초과(외부 API quota): provider 자동 폴백 + 사용자 안내</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr"/>
@@ -3211,26 +3216,54 @@
       <c r="J43" s="3" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="inlineStr"/>
-      <c r="B44" s="3" t="inlineStr"/>
-      <c r="C44" s="3" t="inlineStr"/>
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>LINK-005
+#LINK-DETAIL</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>링크</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>링크 상세 (열기·공유·이동·삭제)</t>
+        </is>
+      </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>출력</t>
+          <t>설명</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>- one_liner: 한 줄 요약 (200자 이내)
-- tags: 자동 태그 3개
-- links UPDATE + ai_jobs 레코드
-- UI에 요약 텍스트 fade-in</t>
-        </is>
-      </c>
-      <c r="F44" s="3" t="inlineStr"/>
-      <c r="G44" s="3" t="inlineStr"/>
-      <c r="H44" s="3" t="inlineStr"/>
-      <c r="I44" s="3" t="inlineStr"/>
+          <t>링크 카드 탭 → 시트(모바일)·사이드패널(웹)으로 상세 노출. 액션 5개: 열기 / 공유 / 폴더 이동 / 알림 설정 / 삭제</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>링크 조회 API
+링크 삭제 API
+링크 폴더 이동 API</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>기획완료</t>
+        </is>
+      </c>
       <c r="J44" s="3" t="inlineStr"/>
     </row>
     <row r="45">
@@ -3239,16 +3272,13 @@
       <c r="C45" s="3" t="inlineStr"/>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>정책</t>
+          <t>입력</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>[기본값] provider=SETTINGS-001 사용자 선택값, 미설정 시 'mock'
-[시간] 응답 1.4초 이내 (timeout 후 fallback)
-[재시도] 1회 자동 재시도(2초 후), 실패 시 빈 요약으로 저장
-[데이터·채점] 응답 raw는 ai_jobs.raw_response에 jsonb로 보존
-[동기화] 요약 완료 즉시 SYNC-001로 다른 디바이스 반영</t>
+          <t>(탭) link_id
+(액션) 사용자 선택</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr"/>
@@ -3263,15 +3293,16 @@
       <c r="C46" s="3" t="inlineStr"/>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>예외</t>
+          <t>출력</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>- 모든 폴백 실패: 빈 요약 + 상세에 "다시 요약" 버튼
-- 응답 스키마 불일치(JSON 파싱 실패): 'AI 응답을 이해하지 못했어요' + 재시도 옵션
-- URL 비공개/메타 없음: URL 자체로 추측 요약
-- 한도 초과(외부 API quota): provider 자동 폴백 + 사용자 안내</t>
+          <t>- 열기: 새 탭/외부 브라우저로 URL 열기
+- 공유: OS 공유 시트
+- 폴더 이동: 폴더 픽커 → UPDATE
+- 알림: LINK-007
+- 삭제: 확인 모달 → DELETE</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr"/>
@@ -3281,54 +3312,25 @@
       <c r="J46" s="3" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>LINK-005
-#LINK-DETAIL</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>링크</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="inlineStr">
-        <is>
-          <t>링크 상세 (열기·공유·이동·삭제)</t>
-        </is>
-      </c>
+      <c r="A47" s="3" t="inlineStr"/>
+      <c r="B47" s="3" t="inlineStr"/>
+      <c r="C47" s="3" t="inlineStr"/>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>설명</t>
+          <t>정책</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>링크 카드 탭 → 시트(모바일)·사이드패널(웹)으로 상세 노출. 액션 5개: 열기 / 공유 / 폴더 이동 / 알림 설정 / 삭제</t>
-        </is>
-      </c>
-      <c r="F47" s="3" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G47" s="3" t="inlineStr">
-        <is>
-          <t>링크 조회 API
-링크 삭제 API
-링크 폴더 이동 API</t>
-        </is>
-      </c>
-      <c r="H47" s="3" t="inlineStr">
-        <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="I47" s="3" t="inlineStr">
-        <is>
-          <t>기획완료</t>
-        </is>
-      </c>
+          <t>[차별 인터랙션] 모바일=시트 슬라이드 업, 웹=우측 사이드패널 (WEB-001)
+[확인] 삭제는 항상 모달 한 번
+[동기화] 모든 액션은 SYNC-001로 즉시 반영</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr"/>
+      <c r="G47" s="3" t="inlineStr"/>
+      <c r="H47" s="3" t="inlineStr"/>
+      <c r="I47" s="3" t="inlineStr"/>
       <c r="J47" s="3" t="inlineStr"/>
     </row>
     <row r="48">
@@ -3337,13 +3339,13 @@
       <c r="C48" s="3" t="inlineStr"/>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>입력</t>
+          <t>예외</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>(탭) link_id
-(액션) 사용자 선택</t>
+          <t>- 삭제 후 다른 디바이스에서 같은 링크 보는 중: Realtime으로 카드 fade-out + "다른 디바이스에서 삭제됐어요"
+- 권한 없음(공유 폴더 viewer): 삭제 버튼 비활성, 툴팁 "읽기 권한이에요"</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr"/>
@@ -3353,27 +3355,52 @@
       <c r="J48" s="3" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="inlineStr"/>
-      <c r="B49" s="3" t="inlineStr"/>
-      <c r="C49" s="3" t="inlineStr"/>
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>LINK-006
+#LINK-EDIT</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>링크</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>링크 메모/제목 수정</t>
+        </is>
+      </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>출력</t>
+          <t>설명</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>- 열기: 새 탭/외부 브라우저로 URL 열기
-- 공유: OS 공유 시트
-- 폴더 이동: 폴더 픽커 → UPDATE
-- 알림: LINK-007
-- 삭제: 확인 모달 → DELETE</t>
-        </is>
-      </c>
-      <c r="F49" s="3" t="inlineStr"/>
-      <c r="G49" s="3" t="inlineStr"/>
-      <c r="H49" s="3" t="inlineStr"/>
-      <c r="I49" s="3" t="inlineStr"/>
+          <t>사용자가 제목·요약·태그를 직접 편집. AI 요약이 마음에 안 들 때 수동 수정</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>링크 수정 API</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>기획완료</t>
+        </is>
+      </c>
       <c r="J49" s="3" t="inlineStr"/>
     </row>
     <row r="50">
@@ -3382,14 +3409,14 @@
       <c r="C50" s="3" t="inlineStr"/>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>정책</t>
+          <t>입력</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>[차별 인터랙션] 모바일=시트 슬라이드 업, 웹=우측 사이드패널 (WEB-001)
-[확인] 삭제는 항상 모달 한 번
-[동기화] 모든 액션은 SYNC-001로 즉시 반영</t>
+          <t>- 제목 (200자)
+- 요약 (500자)
+- 태그 (5개, 각 20자)</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr"/>
@@ -3404,13 +3431,12 @@
       <c r="C51" s="3" t="inlineStr"/>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>예외</t>
+          <t>출력</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>- 삭제 후 다른 디바이스에서 같은 링크 보는 중: Realtime으로 카드 fade-out + "다른 디바이스에서 삭제됐어요"
-- 권한 없음(공유 폴더 viewer): 삭제 버튼 비활성, 툴팁 "읽기 권한이에요"</t>
+          <t>- links UPDATE + Realtime publish</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr"/>
@@ -3420,52 +3446,24 @@
       <c r="J51" s="3" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t>LINK-006
-#LINK-EDIT</t>
-        </is>
-      </c>
-      <c r="B52" s="3" t="inlineStr">
-        <is>
-          <t>링크</t>
-        </is>
-      </c>
-      <c r="C52" s="3" t="inlineStr">
-        <is>
-          <t>링크 메모/제목 수정</t>
-        </is>
-      </c>
+      <c r="A52" s="3" t="inlineStr"/>
+      <c r="B52" s="3" t="inlineStr"/>
+      <c r="C52" s="3" t="inlineStr"/>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>설명</t>
+          <t>정책</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>사용자가 제목·요약·태그를 직접 편집. AI 요약이 마음에 안 들 때 수동 수정</t>
-        </is>
-      </c>
-      <c r="F52" s="3" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G52" s="3" t="inlineStr">
-        <is>
-          <t>링크 수정 API</t>
-        </is>
-      </c>
-      <c r="H52" s="3" t="inlineStr">
-        <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="I52" s="3" t="inlineStr">
-        <is>
-          <t>기획완료</t>
-        </is>
-      </c>
+          <t>[제약] 길이 한도 초과 시 인풋 카운터 빨간색 + 저장 비활성
+[동시 편집] last-write-wins (POLICY-LOCAL 참고)</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr"/>
+      <c r="G52" s="3" t="inlineStr"/>
+      <c r="H52" s="3" t="inlineStr"/>
+      <c r="I52" s="3" t="inlineStr"/>
       <c r="J52" s="3" t="inlineStr"/>
     </row>
     <row r="53">
@@ -3474,14 +3472,14 @@
       <c r="C53" s="3" t="inlineStr"/>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>입력</t>
+          <t>예외</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>- 제목 (200자)
-- 요약 (500자)
-- 태그 (5개, 각 20자)</t>
+          <t>- 빈 제목 저장 시도: '제목을 입력해주세요'
+- 태그 6개 이상: 입력 자체 차단
+- 다른 디바이스에서 같은 링크 동시 편집: 저장 시 서버 timestamp 비교, 충돌 시 토스트 "다른 디바이스에서 먼저 저장됐어요. 다시 확인해주세요"</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr"/>
@@ -3491,24 +3489,59 @@
       <c r="J53" s="3" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="inlineStr"/>
-      <c r="B54" s="3" t="inlineStr"/>
-      <c r="C54" s="3" t="inlineStr"/>
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>LINK-007
+#LINK-DETAIL
+#SETTINGS-NOTIFICATION</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>링크</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>알림 예약</t>
+        </is>
+      </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>출력</t>
+          <t>설명</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>- links UPDATE + Realtime publish</t>
-        </is>
-      </c>
-      <c r="F54" s="3" t="inlineStr"/>
-      <c r="G54" s="3" t="inlineStr"/>
-      <c r="H54" s="3" t="inlineStr"/>
-      <c r="I54" s="3" t="inlineStr"/>
-      <c r="J54" s="3" t="inlineStr"/>
+          <t>링크별 reminder_at 설정. EventBridge가 시간에 Lambda 트리거 → FCM Topic으로 사용자의 모든 활성 디바이스에 푸시 발송</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>예약 알림 API
+FCM Topic 발송</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>일부포함</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>기획완료</t>
+        </is>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>결정: FCM Topic으로 모든 디바이스 발송 + 모바일/PC 채널 분리 옵션. 중복은 사용자 토글로 회피</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr"/>
@@ -3516,13 +3549,12 @@
       <c r="C55" s="3" t="inlineStr"/>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>정책</t>
+          <t>입력</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>[제약] 길이 한도 초과 시 인풋 카운터 빨간색 + 저장 비활성
-[동시 편집] last-write-wins (POLICY-LOCAL 참고)</t>
+          <t>reminder_at (datetime, 미래)</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr"/>
@@ -3537,14 +3569,12 @@
       <c r="C56" s="3" t="inlineStr"/>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>예외</t>
+          <t>출력</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>- 빈 제목 저장 시도: '제목을 입력해주세요'
-- 태그 6개 이상: 입력 자체 차단
-- 다른 디바이스에서 같은 링크 동시 편집: 저장 시 서버 timestamp 비교, 충돌 시 토스트 "다른 디바이스에서 먼저 저장됐어요. 다시 확인해주세요"</t>
+          <t>links UPDATE + 예약 등록 + 시간에 푸시</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr"/>
@@ -3554,58 +3584,26 @@
       <c r="J56" s="3" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="inlineStr">
-        <is>
-          <t>LINK-007
-#LINK-DETAIL</t>
-        </is>
-      </c>
-      <c r="B57" s="3" t="inlineStr">
-        <is>
-          <t>링크</t>
-        </is>
-      </c>
-      <c r="C57" s="3" t="inlineStr">
-        <is>
-          <t>알림 예약</t>
-        </is>
-      </c>
+      <c r="A57" s="3" t="inlineStr"/>
+      <c r="B57" s="3" t="inlineStr"/>
+      <c r="C57" s="3" t="inlineStr"/>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>설명</t>
+          <t>정책</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>링크별 reminder_at 설정. EventBridge가 시간에 Lambda 트리거 → FCM/APNs 푸시 발송</t>
-        </is>
-      </c>
-      <c r="F57" s="3" t="inlineStr">
-        <is>
-          <t>Should</t>
-        </is>
-      </c>
-      <c r="G57" s="3" t="inlineStr">
-        <is>
-          <t>예약 알림 API
-FCM/APNs 발송</t>
-        </is>
-      </c>
-      <c r="H57" s="3" t="inlineStr">
-        <is>
-          <t>일부포함</t>
-        </is>
-      </c>
-      <c r="I57" s="3" t="inlineStr">
-        <is>
-          <t>기획완료</t>
-        </is>
-      </c>
-      <c r="J57" s="3" t="inlineStr">
-        <is>
-          <t>TBD: 멀티 디바이스에서 같은 알림이 중복 노출될 위험 — FCM topic 또는 device_id 단위 분배</t>
-        </is>
-      </c>
+          <t>[권한] 푸시 권한 미허용 시 인앱 토스트로 폴백
+[분배] FCM Topic으로 모든 활성 디바이스에 푸시
+[채널 분리] 설정에 "모바일 알림 받기" / "데스크톱 알림 받기" 토글 — 사용자가 채널별 ON/OFF</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr"/>
+      <c r="G57" s="3" t="inlineStr"/>
+      <c r="H57" s="3" t="inlineStr"/>
+      <c r="I57" s="3" t="inlineStr"/>
+      <c r="J57" s="3" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr"/>
@@ -3613,12 +3611,15 @@
       <c r="C58" s="3" t="inlineStr"/>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>입력</t>
+          <t>예외</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>reminder_at (datetime, 미래)</t>
+          <t>- 과거 시각: 픽커 차단
+- 링크 삭제됨: 발송 안 함
+- 푸시 발송 실패: 24시간 후 1회 재시도
+- 같은 알림 중복 노출: 사용자가 한쪽 채널 OFF로 회피</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr"/>
@@ -3628,23 +3629,53 @@
       <c r="J58" s="3" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="inlineStr"/>
-      <c r="B59" s="3" t="inlineStr"/>
-      <c r="C59" s="3" t="inlineStr"/>
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>QR-001
+#LINK-ADD
+#QR-SCAN</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>링크</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>카메라 QR 스캔 (모바일)</t>
+        </is>
+      </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>출력</t>
+          <t>설명</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>links UPDATE + 예약 등록 + 시간에 푸시</t>
-        </is>
-      </c>
-      <c r="F59" s="3" t="inlineStr"/>
-      <c r="G59" s="3" t="inlineStr"/>
-      <c r="H59" s="3" t="inlineStr"/>
-      <c r="I59" s="3" t="inlineStr"/>
+          <t>html5-qrcode로 카메라 스트림 인식. URL 형태의 QR이면 #LINK-ADD에 자동 채움. 데스크톱 웹에서는 비활성</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t>(클라이언트, html5-qrcode)</t>
+        </is>
+      </c>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="I59" s="3" t="inlineStr">
+        <is>
+          <t>기획완료</t>
+        </is>
+      </c>
       <c r="J59" s="3" t="inlineStr"/>
     </row>
     <row r="60">
@@ -3653,13 +3684,13 @@
       <c r="C60" s="3" t="inlineStr"/>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>정책</t>
+          <t>입력</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>[권한] 푸시 권한 미허용 시 인앱 토스트로 폴백
-[동기화] 알림 시각은 모든 디바이스에 발송</t>
+          <t>(자동) MediaStream
+사용자: QR 비추기</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr"/>
@@ -3674,14 +3705,12 @@
       <c r="C61" s="3" t="inlineStr"/>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>예외</t>
+          <t>출력</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>- 과거 시각: 픽커 차단
-- 링크 삭제됨: 발송 안 함
-- 푸시 발송 실패: 24시간 후 1회 재시도</t>
+          <t>- URL 추출 → #LINK-ADD 입력창 채움</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr"/>
@@ -3691,53 +3720,25 @@
       <c r="J61" s="3" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="inlineStr">
-        <is>
-          <t>QR-001
-#LINK-ADD
-#QR-SCAN</t>
-        </is>
-      </c>
-      <c r="B62" s="3" t="inlineStr">
-        <is>
-          <t>링크</t>
-        </is>
-      </c>
-      <c r="C62" s="3" t="inlineStr">
-        <is>
-          <t>카메라 QR 스캔 (모바일)</t>
-        </is>
-      </c>
+      <c r="A62" s="3" t="inlineStr"/>
+      <c r="B62" s="3" t="inlineStr"/>
+      <c r="C62" s="3" t="inlineStr"/>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>설명</t>
+          <t>정책</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>html5-qrcode로 카메라 스트림 인식. URL 형태의 QR이면 #LINK-ADD에 자동 채움. 데스크톱 웹에서는 비활성</t>
-        </is>
-      </c>
-      <c r="F62" s="3" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G62" s="3" t="inlineStr">
-        <is>
-          <t>(클라이언트, html5-qrcode)</t>
-        </is>
-      </c>
-      <c r="H62" s="3" t="inlineStr">
-        <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="I62" s="3" t="inlineStr">
-        <is>
-          <t>기획완료</t>
-        </is>
-      </c>
+          <t>[권한] 카메라 권한 거부 시 URL 직접 입력 폴백 + 안내
+[환경] HTTPS 또는 localhost 필수
+[차별 인터랙션] 모바일 전용. 웹에서는 QR 탭 비활성 + 툴팁 "모바일에서 사용 가능해요"</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="inlineStr"/>
+      <c r="G62" s="3" t="inlineStr"/>
+      <c r="H62" s="3" t="inlineStr"/>
+      <c r="I62" s="3" t="inlineStr"/>
       <c r="J62" s="3" t="inlineStr"/>
     </row>
     <row r="63">
@@ -3746,13 +3747,15 @@
       <c r="C63" s="3" t="inlineStr"/>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>입력</t>
+          <t>예외</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>(자동) MediaStream
-사용자: QR 비추기</t>
+          <t>- 권한 거부: '카메라 권한이 필요해요. 설정에서 허용해주세요'
+- HTTPS 아님: 'QR 스캔은 보안 연결에서만 동작해요'
+- 인식 실패 10초: '다시 비춰주세요' + Mock 입력(개발용)
+- URL이 아닌 QR: 'URL이 아닌 QR이에요'</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr"/>
@@ -3762,120 +3765,55 @@
       <c r="J63" s="3" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="inlineStr"/>
-      <c r="B64" s="3" t="inlineStr"/>
-      <c r="C64" s="3" t="inlineStr"/>
-      <c r="D64" s="3" t="inlineStr">
-        <is>
-          <t>출력</t>
-        </is>
-      </c>
-      <c r="E64" s="3" t="inlineStr">
-        <is>
-          <t>- URL 추출 → #LINK-ADD 입력창 채움</t>
-        </is>
-      </c>
-      <c r="F64" s="3" t="inlineStr"/>
-      <c r="G64" s="3" t="inlineStr"/>
-      <c r="H64" s="3" t="inlineStr"/>
-      <c r="I64" s="3" t="inlineStr"/>
-      <c r="J64" s="3" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="3" t="inlineStr"/>
-      <c r="B65" s="3" t="inlineStr"/>
-      <c r="C65" s="3" t="inlineStr"/>
-      <c r="D65" s="3" t="inlineStr">
-        <is>
-          <t>정책</t>
-        </is>
-      </c>
-      <c r="E65" s="3" t="inlineStr">
-        <is>
-          <t>[권한] 카메라 권한 거부 시 URL 직접 입력 폴백 + 안내
-[환경] HTTPS 또는 localhost 필수
-[차별 인터랙션] 모바일 전용. 웹에서는 QR 탭 비활성 + 툴팁 "모바일에서 사용 가능해요"</t>
-        </is>
-      </c>
-      <c r="F65" s="3" t="inlineStr"/>
-      <c r="G65" s="3" t="inlineStr"/>
-      <c r="H65" s="3" t="inlineStr"/>
-      <c r="I65" s="3" t="inlineStr"/>
-      <c r="J65" s="3" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="3" t="inlineStr"/>
-      <c r="B66" s="3" t="inlineStr"/>
-      <c r="C66" s="3" t="inlineStr"/>
-      <c r="D66" s="3" t="inlineStr">
-        <is>
-          <t>예외</t>
-        </is>
-      </c>
-      <c r="E66" s="3" t="inlineStr">
-        <is>
-          <t>- 권한 거부: '카메라 권한이 필요해요. 설정에서 허용해주세요'
-- HTTPS 아님: 'QR 스캔은 보안 연결에서만 동작해요'
-- 인식 실패 10초: '다시 비춰주세요' + Mock 입력(개발용)
-- URL이 아닌 QR: 'URL이 아닌 QR이에요'</t>
-        </is>
-      </c>
-      <c r="F66" s="3" t="inlineStr"/>
-      <c r="G66" s="3" t="inlineStr"/>
-      <c r="H66" s="3" t="inlineStr"/>
-      <c r="I66" s="3" t="inlineStr"/>
-      <c r="J66" s="3" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="4" t="inlineStr">
+      <c r="A64" s="4" t="inlineStr">
         <is>
           <t>QR-002</t>
         </is>
       </c>
-      <c r="B67" s="4" t="inlineStr">
+      <c r="B64" s="4" t="inlineStr">
         <is>
           <t>링크</t>
         </is>
       </c>
-      <c r="C67" s="4" t="inlineStr">
+      <c r="C64" s="4" t="inlineStr">
         <is>
           <t>갤러리 QR 인식</t>
         </is>
       </c>
-      <c r="D67" s="4" t="inlineStr">
+      <c r="D64" s="4" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="E67" s="4" t="inlineStr">
+      <c r="E64" s="4" t="inlineStr">
         <is>
           <t>사진첩 이미지에서 QR 추출 (Media Capture + jsQR)</t>
         </is>
       </c>
-      <c r="F67" s="4" t="inlineStr">
+      <c r="F64" s="4" t="inlineStr">
         <is>
           <t>Could</t>
         </is>
       </c>
-      <c r="G67" s="4" t="inlineStr"/>
-      <c r="H67" s="4" t="inlineStr">
+      <c r="G64" s="4" t="inlineStr"/>
+      <c r="H64" s="4" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="I67" s="4" t="inlineStr">
+      <c r="I64" s="4" t="inlineStr">
         <is>
           <t>기획중</t>
         </is>
       </c>
-      <c r="J67" s="4" t="inlineStr">
+      <c r="J64" s="4" t="inlineStr">
         <is>
           <t>v1.x 추가 예정</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="3" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
         <is>
           <t>FOLDER-001
 #FOLDER-LIST
@@ -3883,46 +3821,111 @@
 #FOLDER-DETAIL</t>
         </is>
       </c>
-      <c r="B71" s="3" t="inlineStr">
+      <c r="B68" s="3" t="inlineStr">
         <is>
           <t>폴더</t>
         </is>
       </c>
-      <c r="C71" s="3" t="inlineStr">
+      <c r="C68" s="3" t="inlineStr">
         <is>
           <t>폴더 생성/수정/삭제</t>
         </is>
       </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>이모지 + 이름으로 폴더 관리. 시스템 폴더 "미분류"는 삭제 불가. 공유 폴더는 SHARE-001 참고</t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G68" s="3" t="inlineStr">
+        <is>
+          <t>폴더 CRUD API</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="I68" s="3" t="inlineStr">
+        <is>
+          <t>기획완료</t>
+        </is>
+      </c>
+      <c r="J68" s="3" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr"/>
+      <c r="B69" s="3" t="inlineStr"/>
+      <c r="C69" s="3" t="inlineStr"/>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>입력</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>(생성) 이름 1~30자, 이모지
+(수정) 이름·이모지 변경
+(삭제) 폴더 ID + 확인</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="inlineStr"/>
+      <c r="G69" s="3" t="inlineStr"/>
+      <c r="H69" s="3" t="inlineStr"/>
+      <c r="I69" s="3" t="inlineStr"/>
+      <c r="J69" s="3" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr"/>
+      <c r="B70" s="3" t="inlineStr"/>
+      <c r="C70" s="3" t="inlineStr"/>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>출력</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>folders INSERT/UPDATE/DELETE + Realtime</t>
+        </is>
+      </c>
+      <c r="F70" s="3" t="inlineStr"/>
+      <c r="G70" s="3" t="inlineStr"/>
+      <c r="H70" s="3" t="inlineStr"/>
+      <c r="I70" s="3" t="inlineStr"/>
+      <c r="J70" s="3" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr"/>
+      <c r="B71" s="3" t="inlineStr"/>
+      <c r="C71" s="3" t="inlineStr"/>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>설명</t>
+          <t>정책</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>이모지 + 이름으로 폴더 관리. 시스템 폴더 "미분류"는 삭제 불가. 공유 폴더는 SHARE-001 참고</t>
-        </is>
-      </c>
-      <c r="F71" s="3" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G71" s="3" t="inlineStr">
-        <is>
-          <t>폴더 CRUD API</t>
-        </is>
-      </c>
-      <c r="H71" s="3" t="inlineStr">
-        <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="I71" s="3" t="inlineStr">
-        <is>
-          <t>기획완료</t>
-        </is>
-      </c>
+          <t>[기본값] 이모지=📁
+[제약] 폴더 100개 한도
+[삭제 처리] 폴더 삭제 시 소속 링크는 folder_id=NULL (미분류로 자동 이동)
+[공유 폴더] owner만 이름·이모지 변경 가능</t>
+        </is>
+      </c>
+      <c r="F71" s="3" t="inlineStr"/>
+      <c r="G71" s="3" t="inlineStr"/>
+      <c r="H71" s="3" t="inlineStr"/>
+      <c r="I71" s="3" t="inlineStr"/>
       <c r="J71" s="3" t="inlineStr"/>
     </row>
     <row r="72">
@@ -3931,14 +3934,16 @@
       <c r="C72" s="3" t="inlineStr"/>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>입력</t>
+          <t>예외</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>(생성) 이름 1~30자, 이모지
-(수정) 이름·이모지 변경
-(삭제) 폴더 ID + 확인</t>
+          <t>- 빈 이름: '폴더 이름을 입력해주세요'
+- 30자 초과: 입력 자체 차단
+- 공유 폴더 멤버가 삭제 시도: '오너만 삭제할 수 있어요' + "나가기" 버튼
+- 미분류 삭제 시도: 메뉴에 삭제 노출 안 함
+- 100개 한도: '폴더는 최대 100개까지'</t>
         </is>
       </c>
       <c r="F72" s="3" t="inlineStr"/>
@@ -3948,23 +3953,53 @@
       <c r="J72" s="3" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="3" t="inlineStr"/>
-      <c r="B73" s="3" t="inlineStr"/>
-      <c r="C73" s="3" t="inlineStr"/>
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>FOLDER-002
+#LINK-DETAIL
+#FOLDER-PICKER</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>폴더</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>폴더 이동</t>
+        </is>
+      </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>출력</t>
+          <t>설명</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>folders INSERT/UPDATE/DELETE + Realtime</t>
-        </is>
-      </c>
-      <c r="F73" s="3" t="inlineStr"/>
-      <c r="G73" s="3" t="inlineStr"/>
-      <c r="H73" s="3" t="inlineStr"/>
-      <c r="I73" s="3" t="inlineStr"/>
+          <t>링크 상세에서 폴더 변경. 픽커 모달에 사용자 폴더 + 미분류 노출</t>
+        </is>
+      </c>
+      <c r="F73" s="3" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G73" s="3" t="inlineStr">
+        <is>
+          <t>링크 폴더 이동 API</t>
+        </is>
+      </c>
+      <c r="H73" s="3" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="I73" s="3" t="inlineStr">
+        <is>
+          <t>기획완료</t>
+        </is>
+      </c>
       <c r="J73" s="3" t="inlineStr"/>
     </row>
     <row r="74">
@@ -3973,15 +4008,12 @@
       <c r="C74" s="3" t="inlineStr"/>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>정책</t>
+          <t>입력</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>[기본값] 이모지=📁
-[제약] 폴더 100개 한도
-[삭제 처리] 폴더 삭제 시 소속 링크는 folder_id=NULL (미분류로 자동 이동)
-[공유 폴더] owner만 이름·이모지 변경 가능</t>
+          <t>link_id, target_folder_id</t>
         </is>
       </c>
       <c r="F74" s="3" t="inlineStr"/>
@@ -3996,16 +4028,12 @@
       <c r="C75" s="3" t="inlineStr"/>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>예외</t>
+          <t>출력</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>- 빈 이름: '폴더 이름을 입력해주세요'
-- 30자 초과: 입력 자체 차단
-- 공유 폴더 멤버가 삭제 시도: '오너만 삭제할 수 있어요' + "나가기" 버튼
-- 미분류 삭제 시도: 메뉴에 삭제 노출 안 함
-- 100개 한도: '폴더는 최대 100개까지'</t>
+          <t>links.folder_id UPDATE + Realtime</t>
         </is>
       </c>
       <c r="F75" s="3" t="inlineStr"/>
@@ -4015,53 +4043,23 @@
       <c r="J75" s="3" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="3" t="inlineStr">
-        <is>
-          <t>FOLDER-002
-#LINK-DETAIL
-#FOLDER-PICKER</t>
-        </is>
-      </c>
-      <c r="B76" s="3" t="inlineStr">
-        <is>
-          <t>폴더</t>
-        </is>
-      </c>
-      <c r="C76" s="3" t="inlineStr">
-        <is>
-          <t>폴더 이동</t>
-        </is>
-      </c>
+      <c r="A76" s="3" t="inlineStr"/>
+      <c r="B76" s="3" t="inlineStr"/>
+      <c r="C76" s="3" t="inlineStr"/>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>설명</t>
+          <t>정책</t>
         </is>
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>링크 상세에서 폴더 변경. 픽커 모달에 사용자 폴더 + 미분류 노출</t>
-        </is>
-      </c>
-      <c r="F76" s="3" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G76" s="3" t="inlineStr">
-        <is>
-          <t>링크 폴더 이동 API</t>
-        </is>
-      </c>
-      <c r="H76" s="3" t="inlineStr">
-        <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="I76" s="3" t="inlineStr">
-        <is>
-          <t>기획완료</t>
-        </is>
-      </c>
+          <t>[동기화] 다른 디바이스에서 카드가 다른 폴더로 부드럽게 이동</t>
+        </is>
+      </c>
+      <c r="F76" s="3" t="inlineStr"/>
+      <c r="G76" s="3" t="inlineStr"/>
+      <c r="H76" s="3" t="inlineStr"/>
+      <c r="I76" s="3" t="inlineStr"/>
       <c r="J76" s="3" t="inlineStr"/>
     </row>
     <row r="77">
@@ -4070,12 +4068,13 @@
       <c r="C77" s="3" t="inlineStr"/>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>입력</t>
+          <t>예외</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>link_id, target_folder_id</t>
+          <t>- 공유 폴더(viewer 권한)로 이동 시도: '읽기 권한 폴더에는 옮길 수 없어요'
+- 삭제된 폴더 ID: 미분류로 자동 fallback</t>
         </is>
       </c>
       <c r="F77" s="3" t="inlineStr"/>
@@ -4085,24 +4084,58 @@
       <c r="J77" s="3" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="3" t="inlineStr"/>
-      <c r="B78" s="3" t="inlineStr"/>
-      <c r="C78" s="3" t="inlineStr"/>
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>HOME-001
+#HOME
+#HOME-EMPTY</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>홈</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>홈 피드</t>
+        </is>
+      </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>출력</t>
+          <t>설명</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>links.folder_id UPDATE + Realtime</t>
-        </is>
-      </c>
-      <c r="F78" s="3" t="inlineStr"/>
-      <c r="G78" s="3" t="inlineStr"/>
-      <c r="H78" s="3" t="inlineStr"/>
-      <c r="I78" s="3" t="inlineStr"/>
-      <c r="J78" s="3" t="inlineStr"/>
+          <t>사용자의 모든 링크를 created_at desc로 무한 스크롤. 페이지당 30개. 게스트 시드 데이터 또는 Empty State</t>
+        </is>
+      </c>
+      <c r="F78" s="3" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G78" s="3" t="inlineStr">
+        <is>
+          <t>링크 목록 API (cursor)</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="I78" s="3" t="inlineStr">
+        <is>
+          <t>기획완료</t>
+        </is>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>TBD: 사용자 설정으로 인기/오래된순 추가?</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr"/>
@@ -4110,12 +4143,12 @@
       <c r="C79" s="3" t="inlineStr"/>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>정책</t>
+          <t>입력</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>[동기화] 다른 디바이스에서 카드가 다른 폴더로 부드럽게 이동</t>
+          <t>(자동) cursor (last_created_at)</t>
         </is>
       </c>
       <c r="F79" s="3" t="inlineStr"/>
@@ -4130,13 +4163,12 @@
       <c r="C80" s="3" t="inlineStr"/>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>예외</t>
+          <t>출력</t>
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>- 공유 폴더(viewer 권한)로 이동 시도: '읽기 권한 폴더에는 옮길 수 없어요'
-- 삭제된 폴더 ID: 미분류로 자동 fallback</t>
+          <t>링크 카드 리스트 / Empty State 일러스트+CTA</t>
         </is>
       </c>
       <c r="F80" s="3" t="inlineStr"/>
@@ -4146,58 +4178,26 @@
       <c r="J80" s="3" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="3" t="inlineStr">
-        <is>
-          <t>HOME-001
-#HOME
-#HOME-EMPTY</t>
-        </is>
-      </c>
-      <c r="B81" s="3" t="inlineStr">
-        <is>
-          <t>홈</t>
-        </is>
-      </c>
-      <c r="C81" s="3" t="inlineStr">
-        <is>
-          <t>홈 피드</t>
-        </is>
-      </c>
+      <c r="A81" s="3" t="inlineStr"/>
+      <c r="B81" s="3" t="inlineStr"/>
+      <c r="C81" s="3" t="inlineStr"/>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>설명</t>
+          <t>정책</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>사용자의 모든 링크를 created_at desc로 무한 스크롤. 페이지당 30개. 게스트 시드 데이터 또는 Empty State</t>
-        </is>
-      </c>
-      <c r="F81" s="3" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G81" s="3" t="inlineStr">
-        <is>
-          <t>링크 목록 API (cursor)</t>
-        </is>
-      </c>
-      <c r="H81" s="3" t="inlineStr">
-        <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="I81" s="3" t="inlineStr">
-        <is>
-          <t>기획완료</t>
-        </is>
-      </c>
-      <c r="J81" s="3" t="inlineStr">
-        <is>
-          <t>TBD: 사용자 설정으로 인기/오래된순 추가?</t>
-        </is>
-      </c>
+          <t>[기본값] 정렬: 최신순
+[페이지네이션] cursor 기반 30개
+[차별 인터랙션] 모바일=1열, 웹 1024px+=2열, 1440px+=3열, 1920px+=4열 (WEB-001)</t>
+        </is>
+      </c>
+      <c r="F81" s="3" t="inlineStr"/>
+      <c r="G81" s="3" t="inlineStr"/>
+      <c r="H81" s="3" t="inlineStr"/>
+      <c r="I81" s="3" t="inlineStr"/>
+      <c r="J81" s="3" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr"/>
@@ -4205,12 +4205,13 @@
       <c r="C82" s="3" t="inlineStr"/>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>입력</t>
+          <t>예외</t>
         </is>
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>(자동) cursor (last_created_at)</t>
+          <t>- 첫 진입 + 데이터 0개: Empty State "+ 버튼으로 첫 링크를 저장해보세요"
+- 네트워크 오류: 캐시된 마지막 페이지 + "오프라인이에요" 배너</t>
         </is>
       </c>
       <c r="F82" s="3" t="inlineStr"/>
@@ -4220,23 +4221,53 @@
       <c r="J82" s="3" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="3" t="inlineStr"/>
-      <c r="B83" s="3" t="inlineStr"/>
-      <c r="C83" s="3" t="inlineStr"/>
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>SEARCH-001
+#SEARCH
+#SEARCH-EMPTY</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>검색</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>키워드 검색</t>
+        </is>
+      </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>출력</t>
+          <t>설명</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>링크 카드 리스트 / Empty State 일러스트+CTA</t>
-        </is>
-      </c>
-      <c r="F83" s="3" t="inlineStr"/>
-      <c r="G83" s="3" t="inlineStr"/>
-      <c r="H83" s="3" t="inlineStr"/>
-      <c r="I83" s="3" t="inlineStr"/>
+          <t>제목·요약·태그 통합 검색. 디바운스 200ms. 결과 카드에 키워드 하이라이트. 데스크톱 웹은 ⌘K/Ctrl+K 단축키</t>
+        </is>
+      </c>
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G83" s="3" t="inlineStr">
+        <is>
+          <t>검색 API (ILIKE → tsvector)</t>
+        </is>
+      </c>
+      <c r="H83" s="3" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="I83" s="3" t="inlineStr">
+        <is>
+          <t>기획완료</t>
+        </is>
+      </c>
       <c r="J83" s="3" t="inlineStr"/>
     </row>
     <row r="84">
@@ -4245,14 +4276,12 @@
       <c r="C84" s="3" t="inlineStr"/>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>정책</t>
+          <t>입력</t>
         </is>
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>[기본값] 정렬: 최신순
-[페이지네이션] cursor 기반 30개
-[차별 인터랙션] 모바일=1열, 웹 1024px+=2열, 1440px+=3열, 1920px+=4열 (WEB-001)</t>
+          <t>키워드 (2자 이상)</t>
         </is>
       </c>
       <c r="F84" s="3" t="inlineStr"/>
@@ -4267,13 +4296,12 @@
       <c r="C85" s="3" t="inlineStr"/>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>예외</t>
+          <t>출력</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>- 첫 진입 + 데이터 0개: Empty State "+ 버튼으로 첫 링크를 저장해보세요"
-- 네트워크 오류: 캐시된 마지막 페이지 + "오프라인이에요" 배너</t>
+          <t>매칭 링크 카드 리스트 + 키워드 강조</t>
         </is>
       </c>
       <c r="F85" s="3" t="inlineStr"/>
@@ -4283,53 +4311,25 @@
       <c r="J85" s="3" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="3" t="inlineStr">
-        <is>
-          <t>SEARCH-001
-#SEARCH
-#SEARCH-EMPTY</t>
-        </is>
-      </c>
-      <c r="B86" s="3" t="inlineStr">
-        <is>
-          <t>검색</t>
-        </is>
-      </c>
-      <c r="C86" s="3" t="inlineStr">
-        <is>
-          <t>키워드 검색</t>
-        </is>
-      </c>
+      <c r="A86" s="3" t="inlineStr"/>
+      <c r="B86" s="3" t="inlineStr"/>
+      <c r="C86" s="3" t="inlineStr"/>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>설명</t>
+          <t>정책</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>제목·요약·태그 통합 검색. 디바운스 200ms. 결과 카드에 키워드 하이라이트. 데스크톱 웹은 ⌘K/Ctrl+K 단축키</t>
-        </is>
-      </c>
-      <c r="F86" s="3" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G86" s="3" t="inlineStr">
-        <is>
-          <t>검색 API (ILIKE → tsvector)</t>
-        </is>
-      </c>
-      <c r="H86" s="3" t="inlineStr">
-        <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="I86" s="3" t="inlineStr">
-        <is>
-          <t>기획완료</t>
-        </is>
-      </c>
+          <t>[기본값] 검색 대상=제목/요약/태그 동시
+[구현] v1: ILIKE '%kw%' (Postgres) / v2: tsvector + gin 인덱스
+[동기화] 새로 저장된 링크도 즉시 검색 가능</t>
+        </is>
+      </c>
+      <c r="F86" s="3" t="inlineStr"/>
+      <c r="G86" s="3" t="inlineStr"/>
+      <c r="H86" s="3" t="inlineStr"/>
+      <c r="I86" s="3" t="inlineStr"/>
       <c r="J86" s="3" t="inlineStr"/>
     </row>
     <row r="87">
@@ -4338,12 +4338,14 @@
       <c r="C87" s="3" t="inlineStr"/>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>입력</t>
+          <t>예외</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>키워드 (2자 이상)</t>
+          <t>- 1자: 트리거 안 함, '2자 이상 입력해주세요'
+- 결과 0개: "'{키워드}' 결과가 없어요" + 최근 검색어 추천
+- 네트워크 오류: 로컬 캐시 결과 + '오프라인 결과를 보여드려요'</t>
         </is>
       </c>
       <c r="F87" s="3" t="inlineStr"/>
@@ -4353,24 +4355,57 @@
       <c r="J87" s="3" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="3" t="inlineStr"/>
-      <c r="B88" s="3" t="inlineStr"/>
-      <c r="C88" s="3" t="inlineStr"/>
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t>WEB-001
+(전 화면 반응형)</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>플랫폼</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>데스크톱 웹 레이아웃 (반응형 PWA)</t>
+        </is>
+      </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>출력</t>
+          <t>설명</t>
         </is>
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
-          <t>매칭 링크 카드 리스트 + 키워드 강조</t>
-        </is>
-      </c>
-      <c r="F88" s="3" t="inlineStr"/>
-      <c r="G88" s="3" t="inlineStr"/>
-      <c r="H88" s="3" t="inlineStr"/>
-      <c r="I88" s="3" t="inlineStr"/>
-      <c r="J88" s="3" t="inlineStr"/>
+          <t>단일 React PWA 코드베이스가 화면 폭에 따라 모바일·태블릿·데스크톱 레이아웃을 자동 전환. 데스크톱은 좌측 사이드바(폴더 트리) + 메인 그리드(2~4컬럼) + 우측 상세 패널 구조</t>
+        </is>
+      </c>
+      <c r="F88" s="3" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G88" s="3" t="inlineStr">
+        <is>
+          <t>(클라이언트 레이아웃)</t>
+        </is>
+      </c>
+      <c r="H88" s="3" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="I88" s="3" t="inlineStr">
+        <is>
+          <t>기획완료</t>
+        </is>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>TBD: 사이드바 폭(고정 240px vs 가변), 다크모드 색상 토큰은 THEME-001과 연동</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="inlineStr"/>
@@ -4378,14 +4413,12 @@
       <c r="C89" s="3" t="inlineStr"/>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>정책</t>
+          <t>입력</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>[기본값] 검색 대상=제목/요약/태그 동시
-[구현] v1: ILIKE '%kw%' (Postgres) / v2: tsvector + gin 인덱스
-[동기화] 새로 저장된 링크도 즉시 검색 가능</t>
+          <t>window.innerWidth (브레이크포인트 매칭)</t>
         </is>
       </c>
       <c r="F89" s="3" t="inlineStr"/>
@@ -4400,14 +4433,15 @@
       <c r="C90" s="3" t="inlineStr"/>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>예외</t>
+          <t>출력</t>
         </is>
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>- 1자: 트리거 안 함, '2자 이상 입력해주세요'
-- 결과 0개: "'{키워드}' 결과가 없어요" + 최근 검색어 추천
-- 네트워크 오류: 로컬 캐시 결과 + '오프라인 결과를 보여드려요'</t>
+          <t>- &lt;1024px: 모바일 레이아웃(단일 컬럼 + 하단 탭바)
+- 1024~1439px: 사이드바 + 2컬럼 그리드
+- 1440~1919px: 사이드바 + 3컬럼
+- 1920px+: 사이드바 + 4컬럼 + 우측 상세 패널</t>
         </is>
       </c>
       <c r="F90" s="3" t="inlineStr"/>
@@ -4417,57 +4451,26 @@
       <c r="J90" s="3" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="3" t="inlineStr">
-        <is>
-          <t>WEB-001
-(전 화면 반응형)</t>
-        </is>
-      </c>
-      <c r="B91" s="3" t="inlineStr">
-        <is>
-          <t>플랫폼</t>
-        </is>
-      </c>
-      <c r="C91" s="3" t="inlineStr">
-        <is>
-          <t>데스크톱 웹 레이아웃 (반응형 PWA)</t>
-        </is>
-      </c>
+      <c r="A91" s="3" t="inlineStr"/>
+      <c r="B91" s="3" t="inlineStr"/>
+      <c r="C91" s="3" t="inlineStr"/>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>설명</t>
+          <t>정책</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>단일 React PWA 코드베이스가 화면 폭에 따라 모바일·태블릿·데스크톱 레이아웃을 자동 전환. 데스크톱은 좌측 사이드바(폴더 트리) + 메인 그리드(2~4컬럼) + 우측 상세 패널 구조</t>
-        </is>
-      </c>
-      <c r="F91" s="3" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G91" s="3" t="inlineStr">
-        <is>
-          <t>(클라이언트 레이아웃)</t>
-        </is>
-      </c>
-      <c r="H91" s="3" t="inlineStr">
-        <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="I91" s="3" t="inlineStr">
-        <is>
-          <t>기획완료</t>
-        </is>
-      </c>
-      <c r="J91" s="3" t="inlineStr">
-        <is>
-          <t>TBD: 사이드바 폭(고정 240px vs 가변), 다크모드 색상 토큰은 THEME-001과 연동</t>
-        </is>
-      </c>
+          <t>[차별 인터랙션] 데스크톱: 키보드 단축키 ⌘K(검색) / N(새 링크) / J·K(카드 이동) / Enter(상세) / Del(삭제)
+[차별 인터랙션] 데스크톱: 카드 hover 시 액션 버튼 노출
+[모바일 전용] QR-001은 데스크톱에서 비활성</t>
+        </is>
+      </c>
+      <c r="F91" s="3" t="inlineStr"/>
+      <c r="G91" s="3" t="inlineStr"/>
+      <c r="H91" s="3" t="inlineStr"/>
+      <c r="I91" s="3" t="inlineStr"/>
+      <c r="J91" s="3" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="3" t="inlineStr"/>
@@ -4475,12 +4478,13 @@
       <c r="C92" s="3" t="inlineStr"/>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>입력</t>
+          <t>예외</t>
         </is>
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>window.innerWidth (브레이크포인트 매칭)</t>
+          <t>- 화면 폭 변경(창 리사이즈): 즉시 레이아웃 재계산, 스크롤 위치 보존
+- PWA 설치 데스크톱: 단축키 충돌 회피(브라우저 단축키 존중)</t>
         </is>
       </c>
       <c r="F92" s="3" t="inlineStr"/>
@@ -4490,27 +4494,58 @@
       <c r="J92" s="3" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" s="3" t="inlineStr"/>
-      <c r="B93" s="3" t="inlineStr"/>
-      <c r="C93" s="3" t="inlineStr"/>
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t>SYNC-001
+(전 화면 백그라운드)</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>플랫폼</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t>모바일↔웹 자동 동기화</t>
+        </is>
+      </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>출력</t>
+          <t>설명</t>
         </is>
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>- &lt;1024px: 모바일 레이아웃(단일 컬럼 + 하단 탭바)
-- 1024~1439px: 사이드바 + 2컬럼 그리드
-- 1440~1919px: 사이드바 + 3컬럼
-- 1920px+: 사이드바 + 4컬럼 + 우측 상세 패널</t>
-        </is>
-      </c>
-      <c r="F93" s="3" t="inlineStr"/>
-      <c r="G93" s="3" t="inlineStr"/>
-      <c r="H93" s="3" t="inlineStr"/>
-      <c r="I93" s="3" t="inlineStr"/>
-      <c r="J93" s="3" t="inlineStr"/>
+          <t>한 계정 = 단일 백엔드(AWS RDS) → 디바이스 간 데이터 자동 동기화. AWS API Gateway WebSocket으로 1~2초 내 반영. 멀티탭/멀티디바이스 동시 사용 가정</t>
+        </is>
+      </c>
+      <c r="F93" s="3" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G93" s="3" t="inlineStr">
+        <is>
+          <t>AWS API Gateway WebSocket
+sync delta API</t>
+        </is>
+      </c>
+      <c r="H93" s="3" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="I93" s="3" t="inlineStr">
+        <is>
+          <t>기획완료</t>
+        </is>
+      </c>
+      <c r="J93" s="3" t="inlineStr">
+        <is>
+          <t>결정: AWS API Gateway WebSocket 채택 (단순·비용 효율). 끊김 시 5s polling 폴백. last-write-wins. CRDT는 v2 백로그</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr"/>
@@ -4518,14 +4553,12 @@
       <c r="C94" s="3" t="inlineStr"/>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>정책</t>
+          <t>입력</t>
         </is>
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t>[차별 인터랙션] 데스크톱: 키보드 단축키 ⌘K(검색) / N(새 링크) / J·K(카드 이동) / Enter(상세) / Del(삭제)
-[차별 인터랙션] 데스크톱: 카드 hover 시 액션 버튼 노출
-[모바일 전용] QR-001은 데스크톱에서 비활성</t>
+          <t>(자동) 사용자 인증 + 활성 세션</t>
         </is>
       </c>
       <c r="F94" s="3" t="inlineStr"/>
@@ -4540,13 +4573,13 @@
       <c r="C95" s="3" t="inlineStr"/>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>예외</t>
+          <t>출력</t>
         </is>
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>- 화면 폭 변경(창 리사이즈): 즉시 레이아웃 재계산, 스크롤 위치 보존
-- PWA 설치 데스크톱: 단축키 충돌 회피(브라우저 단축키 존중)</t>
+          <t>- 각 디바이스가 links/folders/folder_members 변경 이벤트 구독
+- 변경 발생 → 모든 활성 디바이스에 publish → UI에 fade 애니메이션</t>
         </is>
       </c>
       <c r="F95" s="3" t="inlineStr"/>
@@ -4556,58 +4589,28 @@
       <c r="J95" s="3" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" s="3" t="inlineStr">
-        <is>
-          <t>SYNC-001
-(전 화면 백그라운드)</t>
-        </is>
-      </c>
-      <c r="B96" s="3" t="inlineStr">
-        <is>
-          <t>플랫폼</t>
-        </is>
-      </c>
-      <c r="C96" s="3" t="inlineStr">
-        <is>
-          <t>모바일↔웹 자동 동기화</t>
-        </is>
-      </c>
+      <c r="A96" s="3" t="inlineStr"/>
+      <c r="B96" s="3" t="inlineStr"/>
+      <c r="C96" s="3" t="inlineStr"/>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>설명</t>
+          <t>정책</t>
         </is>
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>한 계정 = 단일 백엔드(AWS RDS) → 디바이스 간 데이터 자동 동기화. WebSocket Realtime 또는 polling으로 1~2초 내 반영. 멀티탭/멀티디바이스 동시 사용 가정</t>
-        </is>
-      </c>
-      <c r="F96" s="3" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G96" s="3" t="inlineStr">
-        <is>
-          <t>Realtime 구독
-sync delta API</t>
-        </is>
-      </c>
-      <c r="H96" s="3" t="inlineStr">
-        <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="I96" s="3" t="inlineStr">
-        <is>
-          <t>기획완료</t>
-        </is>
-      </c>
-      <c r="J96" s="3" t="inlineStr">
-        <is>
-          <t>TBD: WebSocket vs SSE vs polling. AWS API Gateway WebSocket 또는 AppSync Subscriptions 검토. CRDT 도입 여부</t>
-        </is>
-      </c>
+          <t>[기본] AWS API Gateway WebSocket (재연결 시 backoff 1s,2s,4s,8s,30s)
+[폴백] 1차 5s polling, 2차 60s polling
+[충돌] last-write-wins by `updated_at` (CRDT는 v2 백로그)
+[낙관적 UI] 클라이언트는 즉시 적용, 서버 응답으로 검증
+[동시 편집] 같은 필드 동시 편집 시 토스트 알림</t>
+        </is>
+      </c>
+      <c r="F96" s="3" t="inlineStr"/>
+      <c r="G96" s="3" t="inlineStr"/>
+      <c r="H96" s="3" t="inlineStr"/>
+      <c r="I96" s="3" t="inlineStr"/>
+      <c r="J96" s="3" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="3" t="inlineStr"/>
@@ -4615,12 +4618,15 @@
       <c r="C97" s="3" t="inlineStr"/>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>입력</t>
+          <t>예외</t>
         </is>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>(자동) 사용자 인증 + 활성 세션</t>
+          <t>- WebSocket 끊김: 자동 재연결 + 마지막 sync timestamp 이후 변경분 일괄 fetch
+- 디바이스 시계 어긋남: 서버 timestamp만 사용
+- 게스트 모드(프로토타입): SYNC 비활성
+- 데이터 초기화(SETTINGS-004): 모든 디바이스에서 즉시 빈 상태</t>
         </is>
       </c>
       <c r="F97" s="3" t="inlineStr"/>
@@ -4630,25 +4636,61 @@
       <c r="J97" s="3" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" s="3" t="inlineStr"/>
-      <c r="B98" s="3" t="inlineStr"/>
-      <c r="C98" s="3" t="inlineStr"/>
+      <c r="A98" s="3" t="inlineStr">
+        <is>
+          <t>IMPORT-001
+#SETTINGS-IMPORT
+#IMPORT-UPLOAD
+#IMPORT-PREVIEW
+#IMPORT-PROGRESS</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>플랫폼</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="inlineStr">
+        <is>
+          <t>크롬 즐겨찾기 가져오기 (웹 전용)</t>
+        </is>
+      </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>출력</t>
+          <t>설명</t>
         </is>
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>- 각 디바이스가 links/folders/folder_members 변경 이벤트 구독
-- 변경 발생 → 모든 활성 디바이스에 publish → UI에 fade 애니메이션</t>
-        </is>
-      </c>
-      <c r="F98" s="3" t="inlineStr"/>
-      <c r="G98" s="3" t="inlineStr"/>
-      <c r="H98" s="3" t="inlineStr"/>
-      <c r="I98" s="3" t="inlineStr"/>
-      <c r="J98" s="3" t="inlineStr"/>
+          <t>크롬 북마크 관리자 → 내보내기 → bookmarks.html 파일 업로드. 파싱 후 폴더 구조와 함께 미리보기 → 사용자가 폴더 선택/제외 → 일괄 INSERT + AI 요약 SQS 큐잉</t>
+        </is>
+      </c>
+      <c r="F98" s="3" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G98" s="3" t="inlineStr">
+        <is>
+          <t>북마크 import API (배치)
+AI 요약 큐 publish</t>
+        </is>
+      </c>
+      <c r="H98" s="3" t="inlineStr">
+        <is>
+          <t>일부포함</t>
+        </is>
+      </c>
+      <c r="I98" s="3" t="inlineStr">
+        <is>
+          <t>기획완료</t>
+        </is>
+      </c>
+      <c r="J98" s="3" t="inlineStr">
+        <is>
+          <t>결정: MVP는 비용 동의 모달 미표시 (mock·API키만 가정, 사용자가 본인 API 키 사용 시 본인 부담). 외부 세션 도입(v1.x) 시 모달 추가</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="inlineStr"/>
@@ -4656,16 +4698,12 @@
       <c r="C99" s="3" t="inlineStr"/>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>정책</t>
+          <t>플로우</t>
         </is>
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>[기본] WebSocket 연결 (재연결 시 backoff 1s,2s,4s,8s,30s)
-[폴백] 1차 5s polling, 2차 60s polling
-[충돌] last-write-wins by `updated_at`
-[낙관적 UI] 클라이언트는 즉시 적용, 서버 응답으로 검증
-[동시 편집] 같은 필드 동시 편집 시 토스트 알림</t>
+          <t>(1) 안내(크롬 메뉴 → 북마크 관리자 → ⋮ → 북마크 내보내기) → (2) bookmarks.html 업로드 → (3) 파싱 + 미리보기(폴더 트리 + 링크 카운트) → (4) 폴더 선택/제외 → (5) "가져오기" → (6) 진행률 + 백그라운드 AI 요약</t>
         </is>
       </c>
       <c r="F99" s="3" t="inlineStr"/>
@@ -4680,15 +4718,12 @@
       <c r="C100" s="3" t="inlineStr"/>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>예외</t>
+          <t>입력</t>
         </is>
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t>- WebSocket 끊김: 자동 재연결 + 마지막 sync timestamp 이후 변경분 일괄 fetch
-- 디바이스 시계 어긋남: 서버 timestamp만 사용
-- 게스트 모드: SYNC 비활성, 가입 시 마이그레이션 모달
-- 데이터 초기화(SETTINGS-004): 모든 디바이스에서 즉시 빈 상태</t>
+          <t>- bookmarks.html (≤5MB, Netscape Bookmark Format)</t>
         </is>
       </c>
       <c r="F100" s="3" t="inlineStr"/>
@@ -4698,61 +4733,27 @@
       <c r="J100" s="3" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" s="3" t="inlineStr">
-        <is>
-          <t>IMPORT-001
-#SETTINGS-IMPORT
-#IMPORT-UPLOAD
-#IMPORT-PREVIEW
-#IMPORT-PROGRESS</t>
-        </is>
-      </c>
-      <c r="B101" s="3" t="inlineStr">
-        <is>
-          <t>플랫폼</t>
-        </is>
-      </c>
-      <c r="C101" s="3" t="inlineStr">
-        <is>
-          <t>크롬 즐겨찾기 가져오기 (웹 전용)</t>
-        </is>
-      </c>
+      <c r="A101" s="3" t="inlineStr"/>
+      <c r="B101" s="3" t="inlineStr"/>
+      <c r="C101" s="3" t="inlineStr"/>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>설명</t>
+          <t>출력</t>
         </is>
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>크롬 북마크 관리자 → 내보내기 → bookmarks.html 파일 업로드. 파싱 후 폴더 구조와 함께 미리보기 → 사용자가 폴더 선택/제외 → 일괄 INSERT + AI 요약 SQS 큐잉</t>
-        </is>
-      </c>
-      <c r="F101" s="3" t="inlineStr">
-        <is>
-          <t>Should</t>
-        </is>
-      </c>
-      <c r="G101" s="3" t="inlineStr">
-        <is>
-          <t>북마크 import API (배치)
-AI 요약 큐 publish</t>
-        </is>
-      </c>
-      <c r="H101" s="3" t="inlineStr">
-        <is>
-          <t>일부포함</t>
-        </is>
-      </c>
-      <c r="I101" s="3" t="inlineStr">
-        <is>
-          <t>기획완료</t>
-        </is>
-      </c>
-      <c r="J101" s="3" t="inlineStr">
-        <is>
-          <t>TBD: AI 일괄 요약 비용 — 외부 세션이면 사용자 부담 0, API면 큰 비용. 사용자 동의 모달 필요</t>
-        </is>
-      </c>
+          <t>- 폴더 N개 INSERT
+- 링크 M개 INSERT
+- SQS에 AI 요약 작업 M개 publish
+- "N개 가져왔어요. AI 요약은 백그라운드에서 진행 중이에요"</t>
+        </is>
+      </c>
+      <c r="F101" s="3" t="inlineStr"/>
+      <c r="G101" s="3" t="inlineStr"/>
+      <c r="H101" s="3" t="inlineStr"/>
+      <c r="I101" s="3" t="inlineStr"/>
+      <c r="J101" s="3" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="3" t="inlineStr"/>
@@ -4760,12 +4761,15 @@
       <c r="C102" s="3" t="inlineStr"/>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t>플로우</t>
+          <t>정책</t>
         </is>
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>(1) 안내(크롬 메뉴 → 북마크 관리자 → ⋮ → 북마크 내보내기) → (2) bookmarks.html 업로드 → (3) 파싱 + 미리보기(폴더 트리 + 링크 카운트) → (4) 폴더 선택/제외 → (5) "가져오기" → (6) 진행률 + 백그라운드 AI 요약</t>
+          <t>[차별 인터랙션] 데스크톱 웹 전용 (모바일은 안내만)
+[중복 처리] 기본=스킵, 옵션=덮어쓰기
+[요약 전략] 일괄 import 시 요약은 백그라운드 (홈 피드는 빈 요약으로 즉시 노출, 요약 도착 시 fade-in)
+[한도] 폴더 100개·링크 10000개 한도 사전 검증, 초과 시 일부 선택 강제</t>
         </is>
       </c>
       <c r="F102" s="3" t="inlineStr"/>
@@ -4780,12 +4784,16 @@
       <c r="C103" s="3" t="inlineStr"/>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t>입력</t>
+          <t>예외</t>
         </is>
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>- bookmarks.html (≤5MB, Netscape Bookmark Format)</t>
+          <t>- 형식 오류: '크롬 즐겨찾기 HTML 파일만 가능해요'
+- 5MB 초과: '파일이 너무 커요. 5MB 이하로 잘라서 다시 시도해주세요'
+- 파싱 실패: '북마크 구조를 읽지 못했어요' + 다시 내보내기 안내
+- 한도 초과: 부분 선택 강제 + 안내
+- 모바일 진입: '데스크톱 웹에서 사용 가능한 기능이에요'</t>
         </is>
       </c>
       <c r="F103" s="3" t="inlineStr"/>
@@ -4795,171 +4803,164 @@
       <c r="J103" s="3" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" s="3" t="inlineStr"/>
-      <c r="B104" s="3" t="inlineStr"/>
-      <c r="C104" s="3" t="inlineStr"/>
-      <c r="D104" s="3" t="inlineStr">
-        <is>
-          <t>출력</t>
-        </is>
-      </c>
-      <c r="E104" s="3" t="inlineStr">
-        <is>
-          <t>- 폴더 N개 INSERT
-- 링크 M개 INSERT
-- SQS에 AI 요약 작업 M개 publish
-- "N개 가져왔어요. AI 요약은 백그라운드에서 진행 중이에요"</t>
-        </is>
-      </c>
-      <c r="F104" s="3" t="inlineStr"/>
-      <c r="G104" s="3" t="inlineStr"/>
-      <c r="H104" s="3" t="inlineStr"/>
-      <c r="I104" s="3" t="inlineStr"/>
-      <c r="J104" s="3" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="3" t="inlineStr"/>
-      <c r="B105" s="3" t="inlineStr"/>
-      <c r="C105" s="3" t="inlineStr"/>
-      <c r="D105" s="3" t="inlineStr">
-        <is>
-          <t>정책</t>
-        </is>
-      </c>
-      <c r="E105" s="3" t="inlineStr">
-        <is>
-          <t>[차별 인터랙션] 데스크톱 웹 전용 (모바일은 안내만)
-[중복 처리] 기본=스킵, 옵션=덮어쓰기
-[요약 전략] 일괄 import 시 요약은 백그라운드 (홈 피드는 빈 요약으로 즉시 노출, 요약 도착 시 fade-in)
-[한도] 폴더 100개·링크 10000개 한도 사전 검증, 초과 시 일부 선택 강제</t>
-        </is>
-      </c>
-      <c r="F105" s="3" t="inlineStr"/>
-      <c r="G105" s="3" t="inlineStr"/>
-      <c r="H105" s="3" t="inlineStr"/>
-      <c r="I105" s="3" t="inlineStr"/>
-      <c r="J105" s="3" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="3" t="inlineStr"/>
-      <c r="B106" s="3" t="inlineStr"/>
-      <c r="C106" s="3" t="inlineStr"/>
-      <c r="D106" s="3" t="inlineStr">
-        <is>
-          <t>예외</t>
-        </is>
-      </c>
-      <c r="E106" s="3" t="inlineStr">
-        <is>
-          <t>- 형식 오류: '크롬 즐겨찾기 HTML 파일만 가능해요'
-- 5MB 초과: '파일이 너무 커요. 5MB 이하로 잘라서 다시 시도해주세요'
-- 파싱 실패: '북마크 구조를 읽지 못했어요' + 다시 내보내기 안내
-- 한도 초과: 부분 선택 강제 + 안내
-- 모바일 진입: '데스크톱 웹에서 사용 가능한 기능이에요'</t>
-        </is>
-      </c>
-      <c r="F106" s="3" t="inlineStr"/>
-      <c r="G106" s="3" t="inlineStr"/>
-      <c r="H106" s="3" t="inlineStr"/>
-      <c r="I106" s="3" t="inlineStr"/>
-      <c r="J106" s="3" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="4" t="inlineStr">
+      <c r="A104" s="4" t="inlineStr">
         <is>
           <t>IMPORT-002</t>
         </is>
       </c>
-      <c r="B107" s="4" t="inlineStr">
+      <c r="B104" s="4" t="inlineStr">
         <is>
           <t>플랫폼</t>
         </is>
       </c>
-      <c r="C107" s="4" t="inlineStr">
+      <c r="C104" s="4" t="inlineStr">
         <is>
           <t>Pocket/Raindrop import</t>
         </is>
       </c>
-      <c r="D107" s="4" t="inlineStr">
+      <c r="D104" s="4" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="E107" s="4" t="inlineStr">
+      <c r="E104" s="4" t="inlineStr">
         <is>
           <t>Pocket·Raindrop·Goodlinks 등 export 파일 import</t>
         </is>
       </c>
-      <c r="F107" s="4" t="inlineStr">
+      <c r="F104" s="4" t="inlineStr">
         <is>
           <t>Could</t>
         </is>
       </c>
-      <c r="G107" s="4" t="inlineStr"/>
-      <c r="H107" s="4" t="inlineStr">
+      <c r="G104" s="4" t="inlineStr"/>
+      <c r="H104" s="4" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="I107" s="4" t="inlineStr">
+      <c r="I104" s="4" t="inlineStr">
         <is>
           <t>기획중</t>
         </is>
       </c>
-      <c r="J107" s="4" t="inlineStr">
+      <c r="J104" s="4" t="inlineStr">
         <is>
           <t>v1.x 추가 예정</t>
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="3" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="3" t="inlineStr">
         <is>
           <t>SHARE-001
 #FOLDER-DETAIL
 #SHARE-INVITE</t>
         </is>
       </c>
-      <c r="B111" s="3" t="inlineStr">
+      <c r="B108" s="3" t="inlineStr">
         <is>
           <t>공유 폴더</t>
         </is>
       </c>
-      <c r="C111" s="3" t="inlineStr">
+      <c r="C108" s="3" t="inlineStr">
         <is>
           <t>공유 폴더 만들기</t>
         </is>
       </c>
+      <c r="D108" s="3" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+      <c r="E108" s="3" t="inlineStr">
+        <is>
+          <t>폴더의 shared 플래그를 true로 전환 → folder_invites에 토큰 INSERT → OS 공유 시트로 링크 발송</t>
+        </is>
+      </c>
+      <c r="F108" s="3" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G108" s="3" t="inlineStr">
+        <is>
+          <t>초대 토큰 생성 API</t>
+        </is>
+      </c>
+      <c r="H108" s="3" t="inlineStr">
+        <is>
+          <t>일부포함</t>
+        </is>
+      </c>
+      <c r="I108" s="3" t="inlineStr">
+        <is>
+          <t>기획완료</t>
+        </is>
+      </c>
+      <c r="J108" s="3" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="3" t="inlineStr"/>
+      <c r="B109" s="3" t="inlineStr"/>
+      <c r="C109" s="3" t="inlineStr"/>
+      <c r="D109" s="3" t="inlineStr">
+        <is>
+          <t>입력</t>
+        </is>
+      </c>
+      <c r="E109" s="3" t="inlineStr">
+        <is>
+          <t>folder_id (오너만)</t>
+        </is>
+      </c>
+      <c r="F109" s="3" t="inlineStr"/>
+      <c r="G109" s="3" t="inlineStr"/>
+      <c r="H109" s="3" t="inlineStr"/>
+      <c r="I109" s="3" t="inlineStr"/>
+      <c r="J109" s="3" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="3" t="inlineStr"/>
+      <c r="B110" s="3" t="inlineStr"/>
+      <c r="C110" s="3" t="inlineStr"/>
+      <c r="D110" s="3" t="inlineStr">
+        <is>
+          <t>출력</t>
+        </is>
+      </c>
+      <c r="E110" s="3" t="inlineStr">
+        <is>
+          <t>folders.shared=true / folder_invites INSERT / 공유 URL 생성 (https://qlink.app/invite/{token})</t>
+        </is>
+      </c>
+      <c r="F110" s="3" t="inlineStr"/>
+      <c r="G110" s="3" t="inlineStr"/>
+      <c r="H110" s="3" t="inlineStr"/>
+      <c r="I110" s="3" t="inlineStr"/>
+      <c r="J110" s="3" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="3" t="inlineStr"/>
+      <c r="B111" s="3" t="inlineStr"/>
+      <c r="C111" s="3" t="inlineStr"/>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>설명</t>
+          <t>정책</t>
         </is>
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>폴더의 shared 플래그를 true로 전환 → folder_invites에 토큰 INSERT → OS 공유 시트로 링크 발송</t>
-        </is>
-      </c>
-      <c r="F111" s="3" t="inlineStr">
-        <is>
-          <t>Should</t>
-        </is>
-      </c>
-      <c r="G111" s="3" t="inlineStr">
-        <is>
-          <t>초대 토큰 생성 API</t>
-        </is>
-      </c>
-      <c r="H111" s="3" t="inlineStr">
-        <is>
-          <t>일부포함</t>
-        </is>
-      </c>
-      <c r="I111" s="3" t="inlineStr">
-        <is>
-          <t>기획완료</t>
-        </is>
-      </c>
+          <t>POLICY-SHARED 참고
+[기본값] 토큰 유효 7일
+[권한] 오너만 발급
+[재발급] 새 토큰 발급 시 이전 토큰은 만료 전까지 유효</t>
+        </is>
+      </c>
+      <c r="F111" s="3" t="inlineStr"/>
+      <c r="G111" s="3" t="inlineStr"/>
+      <c r="H111" s="3" t="inlineStr"/>
+      <c r="I111" s="3" t="inlineStr"/>
       <c r="J111" s="3" t="inlineStr"/>
     </row>
     <row r="112">
@@ -4968,12 +4969,13 @@
       <c r="C112" s="3" t="inlineStr"/>
       <c r="D112" s="3" t="inlineStr">
         <is>
-          <t>입력</t>
+          <t>예외</t>
         </is>
       </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
-          <t>folder_id (오너만)</t>
+          <t>- 비오너 시도: '오너만 공유할 수 있어요'
+- 미분류 폴더 공유 시도: '미분류 폴더는 공유할 수 없어요'</t>
         </is>
       </c>
       <c r="F112" s="3" t="inlineStr"/>
@@ -4983,23 +4985,52 @@
       <c r="J112" s="3" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" s="3" t="inlineStr"/>
-      <c r="B113" s="3" t="inlineStr"/>
-      <c r="C113" s="3" t="inlineStr"/>
+      <c r="A113" s="3" t="inlineStr">
+        <is>
+          <t>SHARE-002
+#SHARE-ACCEPT</t>
+        </is>
+      </c>
+      <c r="B113" s="3" t="inlineStr">
+        <is>
+          <t>공유 폴더</t>
+        </is>
+      </c>
+      <c r="C113" s="3" t="inlineStr">
+        <is>
+          <t>공유 폴더 초대 수락</t>
+        </is>
+      </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>출력</t>
+          <t>설명</t>
         </is>
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>folders.shared=true / folder_invites INSERT / 공유 URL 생성 (https://qlink.app/invite/{token})</t>
-        </is>
-      </c>
-      <c r="F113" s="3" t="inlineStr"/>
-      <c r="G113" s="3" t="inlineStr"/>
-      <c r="H113" s="3" t="inlineStr"/>
-      <c r="I113" s="3" t="inlineStr"/>
+          <t>초대 링크 클릭 → 토큰 검증 → 사용자가 "참여" 클릭 → folder_members INSERT</t>
+        </is>
+      </c>
+      <c r="F113" s="3" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G113" s="3" t="inlineStr">
+        <is>
+          <t>accept_folder_invite RPC</t>
+        </is>
+      </c>
+      <c r="H113" s="3" t="inlineStr">
+        <is>
+          <t>일부포함</t>
+        </is>
+      </c>
+      <c r="I113" s="3" t="inlineStr">
+        <is>
+          <t>기획완료</t>
+        </is>
+      </c>
       <c r="J113" s="3" t="inlineStr"/>
     </row>
     <row r="114">
@@ -5008,15 +5039,12 @@
       <c r="C114" s="3" t="inlineStr"/>
       <c r="D114" s="3" t="inlineStr">
         <is>
-          <t>정책</t>
+          <t>입력</t>
         </is>
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
-          <t>POLICY-SHARED 참고
-[기본값] 토큰 유효 7일
-[권한] 오너만 발급
-[재발급] 새 토큰 발급 시 이전 토큰은 만료 전까지 유효</t>
+          <t>invite_token (URL 파라미터)</t>
         </is>
       </c>
       <c r="F114" s="3" t="inlineStr"/>
@@ -5031,13 +5059,12 @@
       <c r="C115" s="3" t="inlineStr"/>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t>예외</t>
+          <t>출력</t>
         </is>
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>- 비오너 시도: '오너만 공유할 수 있어요'
-- 미분류 폴더 공유 시도: '미분류 폴더는 공유할 수 없어요'</t>
+          <t>folder_members INSERT (role='member') / 폴더 진입</t>
         </is>
       </c>
       <c r="F115" s="3" t="inlineStr"/>
@@ -5047,52 +5074,25 @@
       <c r="J115" s="3" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="A116" s="3" t="inlineStr">
-        <is>
-          <t>SHARE-002
-#SHARE-ACCEPT</t>
-        </is>
-      </c>
-      <c r="B116" s="3" t="inlineStr">
-        <is>
-          <t>공유 폴더</t>
-        </is>
-      </c>
-      <c r="C116" s="3" t="inlineStr">
-        <is>
-          <t>공유 폴더 초대 수락</t>
-        </is>
-      </c>
+      <c r="A116" s="3" t="inlineStr"/>
+      <c r="B116" s="3" t="inlineStr"/>
+      <c r="C116" s="3" t="inlineStr"/>
       <c r="D116" s="3" t="inlineStr">
         <is>
-          <t>설명</t>
+          <t>정책</t>
         </is>
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
-          <t>초대 링크 클릭 → 토큰 검증 → 사용자가 "참여" 클릭 → folder_members INSERT</t>
-        </is>
-      </c>
-      <c r="F116" s="3" t="inlineStr">
-        <is>
-          <t>Should</t>
-        </is>
-      </c>
-      <c r="G116" s="3" t="inlineStr">
-        <is>
-          <t>accept_folder_invite RPC</t>
-        </is>
-      </c>
-      <c r="H116" s="3" t="inlineStr">
-        <is>
-          <t>일부포함</t>
-        </is>
-      </c>
-      <c r="I116" s="3" t="inlineStr">
-        <is>
-          <t>기획완료</t>
-        </is>
-      </c>
+          <t>POLICY-SHARED 참고
+[처리 순서] 미로그인 시 토큰 임시 보관 → 로그인 후 자동 수락 화면
+[멤버 한도] 50명</t>
+        </is>
+      </c>
+      <c r="F116" s="3" t="inlineStr"/>
+      <c r="G116" s="3" t="inlineStr"/>
+      <c r="H116" s="3" t="inlineStr"/>
+      <c r="I116" s="3" t="inlineStr"/>
       <c r="J116" s="3" t="inlineStr"/>
     </row>
     <row r="117">
@@ -5101,12 +5101,15 @@
       <c r="C117" s="3" t="inlineStr"/>
       <c r="D117" s="3" t="inlineStr">
         <is>
-          <t>입력</t>
+          <t>예외</t>
         </is>
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
-          <t>invite_token (URL 파라미터)</t>
+          <t>- 토큰 만료: '유효하지 않거나 만료된 초대 링크입니다'
+- 이미 멤버: 토스트 + 폴더 이동
+- 본인이 오너: '본인의 폴더예요'
+- 멤버 한도 50명 초과: '이 폴더는 50명까지만 참여할 수 있어요. 오너에게 문의하세요'</t>
         </is>
       </c>
       <c r="F117" s="3" t="inlineStr"/>
@@ -5116,218 +5119,216 @@
       <c r="J117" s="3" t="inlineStr"/>
     </row>
     <row r="118">
-      <c r="A118" s="3" t="inlineStr"/>
-      <c r="B118" s="3" t="inlineStr"/>
-      <c r="C118" s="3" t="inlineStr"/>
-      <c r="D118" s="3" t="inlineStr">
-        <is>
-          <t>출력</t>
-        </is>
-      </c>
-      <c r="E118" s="3" t="inlineStr">
-        <is>
-          <t>folder_members INSERT (role='member') / 폴더 진입</t>
-        </is>
-      </c>
-      <c r="F118" s="3" t="inlineStr"/>
-      <c r="G118" s="3" t="inlineStr"/>
-      <c r="H118" s="3" t="inlineStr"/>
-      <c r="I118" s="3" t="inlineStr"/>
-      <c r="J118" s="3" t="inlineStr"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="3" t="inlineStr"/>
-      <c r="B119" s="3" t="inlineStr"/>
-      <c r="C119" s="3" t="inlineStr"/>
-      <c r="D119" s="3" t="inlineStr">
-        <is>
-          <t>정책</t>
-        </is>
-      </c>
-      <c r="E119" s="3" t="inlineStr">
-        <is>
-          <t>POLICY-SHARED 참고
-[처리 순서] 미로그인 시 토큰 임시 보관 → 로그인 후 자동 수락 화면</t>
-        </is>
-      </c>
-      <c r="F119" s="3" t="inlineStr"/>
-      <c r="G119" s="3" t="inlineStr"/>
-      <c r="H119" s="3" t="inlineStr"/>
-      <c r="I119" s="3" t="inlineStr"/>
-      <c r="J119" s="3" t="inlineStr"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="3" t="inlineStr"/>
-      <c r="B120" s="3" t="inlineStr"/>
-      <c r="C120" s="3" t="inlineStr"/>
-      <c r="D120" s="3" t="inlineStr">
-        <is>
-          <t>예외</t>
-        </is>
-      </c>
-      <c r="E120" s="3" t="inlineStr">
-        <is>
-          <t>- 토큰 만료: '유효하지 않거나 만료된 초대 링크입니다'
-- 이미 멤버: 토스트 + 폴더 이동
-- 본인이 오너: '본인의 폴더예요'
-- 멤버 한도(TBD): '참여할 수 없어요. 오너에게 문의하세요'</t>
-        </is>
-      </c>
-      <c r="F120" s="3" t="inlineStr"/>
-      <c r="G120" s="3" t="inlineStr"/>
-      <c r="H120" s="3" t="inlineStr"/>
-      <c r="I120" s="3" t="inlineStr"/>
-      <c r="J120" s="3" t="inlineStr"/>
-    </row>
-    <row r="121">
-      <c r="A121" s="3" t="inlineStr">
+      <c r="A118" s="3" t="inlineStr">
         <is>
           <t>SHARE-003
 #FOLDER-MEMBERS</t>
         </is>
       </c>
-      <c r="B121" s="3" t="inlineStr">
+      <c r="B118" s="3" t="inlineStr">
         <is>
           <t>공유 폴더</t>
         </is>
       </c>
-      <c r="C121" s="3" t="inlineStr">
+      <c r="C118" s="3" t="inlineStr">
         <is>
           <t>공유 폴더 멤버 관리</t>
         </is>
       </c>
-      <c r="D121" s="3" t="inlineStr">
+      <c r="D118" s="3" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="E121" s="3" t="inlineStr">
+      <c r="E118" s="3" t="inlineStr">
         <is>
           <t>멤버 목록 + 역할 변경(owner만) + 제거(owner) / 나가기(self)</t>
         </is>
       </c>
-      <c r="F121" s="3" t="inlineStr">
+      <c r="F118" s="3" t="inlineStr">
         <is>
           <t>Should</t>
         </is>
       </c>
-      <c r="G121" s="3" t="inlineStr">
+      <c r="G118" s="3" t="inlineStr">
         <is>
           <t>멤버 조회/수정/삭제 API</t>
         </is>
       </c>
-      <c r="H121" s="3" t="inlineStr">
+      <c r="H118" s="3" t="inlineStr">
         <is>
           <t>일부포함</t>
         </is>
       </c>
-      <c r="I121" s="3" t="inlineStr">
+      <c r="I118" s="3" t="inlineStr">
         <is>
           <t>기획중</t>
         </is>
       </c>
-      <c r="J121" s="3" t="inlineStr">
+      <c r="J118" s="3" t="inlineStr">
         <is>
           <t>v1.0 가벼운 형태로</t>
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="3" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="3" t="inlineStr">
         <is>
           <t>VIEW-001
 #LINK-DETAIL</t>
         </is>
       </c>
-      <c r="B122" s="3" t="inlineStr">
+      <c r="B119" s="3" t="inlineStr">
         <is>
           <t>콘텐츠</t>
         </is>
       </c>
-      <c r="C122" s="3" t="inlineStr">
+      <c r="C119" s="3" t="inlineStr">
         <is>
           <t>YouTube 임베드 미리보기</t>
         </is>
       </c>
-      <c r="D122" s="3" t="inlineStr">
+      <c r="D119" s="3" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="E122" s="3" t="inlineStr">
+      <c r="E119" s="3" t="inlineStr">
         <is>
           <t>URL이 youtube.com/youtu.be 도메인이면 상세 화면에서 iframe 임베드. 자동재생 X, 사용자 클릭 시 재생</t>
         </is>
       </c>
-      <c r="F122" s="3" t="inlineStr">
+      <c r="F119" s="3" t="inlineStr">
         <is>
           <t>Should</t>
         </is>
       </c>
-      <c r="G122" s="3" t="inlineStr">
+      <c r="G119" s="3" t="inlineStr">
         <is>
           <t>(클라이언트, iframe)</t>
         </is>
       </c>
-      <c r="H122" s="3" t="inlineStr">
+      <c r="H119" s="3" t="inlineStr">
         <is>
           <t>일부포함</t>
         </is>
       </c>
-      <c r="I122" s="3" t="inlineStr">
+      <c r="I119" s="3" t="inlineStr">
         <is>
           <t>기획중</t>
         </is>
       </c>
-      <c r="J122" s="3" t="inlineStr"/>
-    </row>
-    <row r="123">
-      <c r="A123" s="3" t="inlineStr">
+      <c r="J119" s="3" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="3" t="inlineStr">
         <is>
           <t>SETTINGS-001
 #SETTINGS-AI</t>
         </is>
       </c>
-      <c r="B123" s="3" t="inlineStr">
+      <c r="B120" s="3" t="inlineStr">
         <is>
           <t>설정</t>
         </is>
       </c>
-      <c r="C123" s="3" t="inlineStr">
+      <c r="C120" s="3" t="inlineStr">
         <is>
           <t>AI 제공자 선택</t>
         </is>
       </c>
+      <c r="D120" s="3" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+      <c r="E120" s="3" t="inlineStr">
+        <is>
+          <t>6종 중 선택: ChatGPT / Gemini / Claude / Perplexity / 큐링크 기본(mock) / 사용자 API 키. SETTINGS-001 변경은 LINK-004의 provider 입력으로 즉시 반영</t>
+        </is>
+      </c>
+      <c r="F120" s="3" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G120" s="3" t="inlineStr">
+        <is>
+          <t>프로필 업데이트 API</t>
+        </is>
+      </c>
+      <c r="H120" s="3" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="I120" s="3" t="inlineStr">
+        <is>
+          <t>기획완료</t>
+        </is>
+      </c>
+      <c r="J120" s="3" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="3" t="inlineStr"/>
+      <c r="B121" s="3" t="inlineStr"/>
+      <c r="C121" s="3" t="inlineStr"/>
+      <c r="D121" s="3" t="inlineStr">
+        <is>
+          <t>입력</t>
+        </is>
+      </c>
+      <c r="E121" s="3" t="inlineStr">
+        <is>
+          <t>provider 식별자</t>
+        </is>
+      </c>
+      <c r="F121" s="3" t="inlineStr"/>
+      <c r="G121" s="3" t="inlineStr"/>
+      <c r="H121" s="3" t="inlineStr"/>
+      <c r="I121" s="3" t="inlineStr"/>
+      <c r="J121" s="3" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="3" t="inlineStr"/>
+      <c r="B122" s="3" t="inlineStr"/>
+      <c r="C122" s="3" t="inlineStr"/>
+      <c r="D122" s="3" t="inlineStr">
+        <is>
+          <t>출력</t>
+        </is>
+      </c>
+      <c r="E122" s="3" t="inlineStr">
+        <is>
+          <t>profiles.ai_provider UPDATE + 토스트</t>
+        </is>
+      </c>
+      <c r="F122" s="3" t="inlineStr"/>
+      <c r="G122" s="3" t="inlineStr"/>
+      <c r="H122" s="3" t="inlineStr"/>
+      <c r="I122" s="3" t="inlineStr"/>
+      <c r="J122" s="3" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="3" t="inlineStr"/>
+      <c r="B123" s="3" t="inlineStr"/>
+      <c r="C123" s="3" t="inlineStr"/>
       <c r="D123" s="3" t="inlineStr">
         <is>
-          <t>설명</t>
+          <t>정책</t>
         </is>
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>6종 중 선택: ChatGPT / Gemini / Claude / Perplexity / 큐링크 기본(mock) / 사용자 API 키. SETTINGS-001 변경은 LINK-004의 provider 입력으로 즉시 반영</t>
-        </is>
-      </c>
-      <c r="F123" s="3" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G123" s="3" t="inlineStr">
-        <is>
-          <t>프로필 업데이트 API</t>
-        </is>
-      </c>
-      <c r="H123" s="3" t="inlineStr">
-        <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="I123" s="3" t="inlineStr">
-        <is>
-          <t>기획완료</t>
-        </is>
-      </c>
+          <t>[기본값] 'mock' (앱 진입 시)
+[동기화] 모든 디바이스에 SYNC-001로 반영
+[API 키] 사용자 API 키 선택 시 키 입력 화면 추가 노출, 서버 KMS 암호화 저장</t>
+        </is>
+      </c>
+      <c r="F123" s="3" t="inlineStr"/>
+      <c r="G123" s="3" t="inlineStr"/>
+      <c r="H123" s="3" t="inlineStr"/>
+      <c r="I123" s="3" t="inlineStr"/>
       <c r="J123" s="3" t="inlineStr"/>
     </row>
     <row r="124">
@@ -5336,12 +5337,13 @@
       <c r="C124" s="3" t="inlineStr"/>
       <c r="D124" s="3" t="inlineStr">
         <is>
-          <t>입력</t>
+          <t>예외</t>
         </is>
       </c>
       <c r="E124" s="3" t="inlineStr">
         <is>
-          <t>provider 식별자</t>
+          <t>- 외부 세션 provider 선택했지만 Chrome 확장 미설치: '확장 프로그램 설치가 필요해요' + 안내 링크
+- API 키 무효: 다음 호출 시 '키를 확인해주세요' 안내</t>
         </is>
       </c>
       <c r="F124" s="3" t="inlineStr"/>
@@ -5351,23 +5353,52 @@
       <c r="J124" s="3" t="inlineStr"/>
     </row>
     <row r="125">
-      <c r="A125" s="3" t="inlineStr"/>
-      <c r="B125" s="3" t="inlineStr"/>
-      <c r="C125" s="3" t="inlineStr"/>
+      <c r="A125" s="3" t="inlineStr">
+        <is>
+          <t>SETTINGS-002
+#SETTINGS-PROFILE</t>
+        </is>
+      </c>
+      <c r="B125" s="3" t="inlineStr">
+        <is>
+          <t>설정</t>
+        </is>
+      </c>
+      <c r="C125" s="3" t="inlineStr">
+        <is>
+          <t>프로필 변경</t>
+        </is>
+      </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
-          <t>출력</t>
+          <t>설명</t>
         </is>
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>profiles.ai_provider UPDATE + 토스트</t>
-        </is>
-      </c>
-      <c r="F125" s="3" t="inlineStr"/>
-      <c r="G125" s="3" t="inlineStr"/>
-      <c r="H125" s="3" t="inlineStr"/>
-      <c r="I125" s="3" t="inlineStr"/>
+          <t>닉네임·아바타 이모지 변경</t>
+        </is>
+      </c>
+      <c r="F125" s="3" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G125" s="3" t="inlineStr">
+        <is>
+          <t>프로필 업데이트 API</t>
+        </is>
+      </c>
+      <c r="H125" s="3" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="I125" s="3" t="inlineStr">
+        <is>
+          <t>기획완료</t>
+        </is>
+      </c>
       <c r="J125" s="3" t="inlineStr"/>
     </row>
     <row r="126">
@@ -5376,14 +5407,12 @@
       <c r="C126" s="3" t="inlineStr"/>
       <c r="D126" s="3" t="inlineStr">
         <is>
-          <t>정책</t>
+          <t>입력</t>
         </is>
       </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
-          <t>[기본값] 'mock' (앱 진입 시)
-[동기화] 모든 디바이스에 SYNC-001로 반영
-[API 키] 사용자 API 키 선택 시 키 입력 화면 추가 노출, 서버 KMS 암호화 저장</t>
+          <t>display_name (1~20자), avatar (이모지 단일 문자)</t>
         </is>
       </c>
       <c r="F126" s="3" t="inlineStr"/>
@@ -5398,13 +5427,12 @@
       <c r="C127" s="3" t="inlineStr"/>
       <c r="D127" s="3" t="inlineStr">
         <is>
-          <t>예외</t>
+          <t>출력</t>
         </is>
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>- 외부 세션 provider 선택했지만 Chrome 확장 미설치: '확장 프로그램 설치가 필요해요' + 안내 링크
-- API 키 무효: 다음 호출 시 '키를 확인해주세요' 안내</t>
+          <t>profiles UPDATE + 헤더 즉시 반영</t>
         </is>
       </c>
       <c r="F127" s="3" t="inlineStr"/>
@@ -5414,52 +5442,23 @@
       <c r="J127" s="3" t="inlineStr"/>
     </row>
     <row r="128">
-      <c r="A128" s="3" t="inlineStr">
-        <is>
-          <t>SETTINGS-002
-#SETTINGS-PROFILE</t>
-        </is>
-      </c>
-      <c r="B128" s="3" t="inlineStr">
-        <is>
-          <t>설정</t>
-        </is>
-      </c>
-      <c r="C128" s="3" t="inlineStr">
-        <is>
-          <t>프로필 변경</t>
-        </is>
-      </c>
+      <c r="A128" s="3" t="inlineStr"/>
+      <c r="B128" s="3" t="inlineStr"/>
+      <c r="C128" s="3" t="inlineStr"/>
       <c r="D128" s="3" t="inlineStr">
         <is>
-          <t>설명</t>
+          <t>정책</t>
         </is>
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
-          <t>닉네임·아바타 이모지 변경</t>
-        </is>
-      </c>
-      <c r="F128" s="3" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G128" s="3" t="inlineStr">
-        <is>
-          <t>프로필 업데이트 API</t>
-        </is>
-      </c>
-      <c r="H128" s="3" t="inlineStr">
-        <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="I128" s="3" t="inlineStr">
-        <is>
-          <t>기획완료</t>
-        </is>
-      </c>
+          <t>[동기화] 즉시 모든 디바이스 반영</t>
+        </is>
+      </c>
+      <c r="F128" s="3" t="inlineStr"/>
+      <c r="G128" s="3" t="inlineStr"/>
+      <c r="H128" s="3" t="inlineStr"/>
+      <c r="I128" s="3" t="inlineStr"/>
       <c r="J128" s="3" t="inlineStr"/>
     </row>
     <row r="129">
@@ -5468,12 +5467,13 @@
       <c r="C129" s="3" t="inlineStr"/>
       <c r="D129" s="3" t="inlineStr">
         <is>
-          <t>입력</t>
+          <t>예외</t>
         </is>
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>display_name (1~20자), avatar (이모지 단일 문자)</t>
+          <t>- 빈 닉네임: '닉네임을 입력해주세요'
+- 20자 초과: 입력 차단</t>
         </is>
       </c>
       <c r="F129" s="3" t="inlineStr"/>
@@ -5483,24 +5483,58 @@
       <c r="J129" s="3" t="inlineStr"/>
     </row>
     <row r="130">
-      <c r="A130" s="3" t="inlineStr"/>
-      <c r="B130" s="3" t="inlineStr"/>
-      <c r="C130" s="3" t="inlineStr"/>
+      <c r="A130" s="3" t="inlineStr">
+        <is>
+          <t>SETTINGS-003
+#SETTINGS-PASSWORD</t>
+        </is>
+      </c>
+      <c r="B130" s="3" t="inlineStr">
+        <is>
+          <t>설정</t>
+        </is>
+      </c>
+      <c r="C130" s="3" t="inlineStr">
+        <is>
+          <t>비밀번호 변경</t>
+        </is>
+      </c>
       <c r="D130" s="3" t="inlineStr">
         <is>
-          <t>출력</t>
+          <t>설명</t>
         </is>
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>profiles UPDATE + 헤더 즉시 반영</t>
-        </is>
-      </c>
-      <c r="F130" s="3" t="inlineStr"/>
-      <c r="G130" s="3" t="inlineStr"/>
-      <c r="H130" s="3" t="inlineStr"/>
-      <c r="I130" s="3" t="inlineStr"/>
-      <c r="J130" s="3" t="inlineStr"/>
+          <t>현재 비밀번호 검증 → 새 비밀번호 변경. 변경 후 다른 디바이스는 강제 로그아웃 (보안 우선)</t>
+        </is>
+      </c>
+      <c r="F130" s="3" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G130" s="3" t="inlineStr">
+        <is>
+          <t>비밀번호 변경 API
+리프레시 토큰 무효화 API</t>
+        </is>
+      </c>
+      <c r="H130" s="3" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="I130" s="3" t="inlineStr">
+        <is>
+          <t>기획완료</t>
+        </is>
+      </c>
+      <c r="J130" s="3" t="inlineStr">
+        <is>
+          <t>결정: 변경 시 다른 디바이스 강제 로그아웃 + 화면 안내 문구 추가</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="3" t="inlineStr"/>
@@ -5508,12 +5542,12 @@
       <c r="C131" s="3" t="inlineStr"/>
       <c r="D131" s="3" t="inlineStr">
         <is>
-          <t>정책</t>
+          <t>입력</t>
         </is>
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>[동기화] 즉시 모든 디바이스 반영</t>
+          <t>current_password, new_password (8~64자, 영문+숫자)</t>
         </is>
       </c>
       <c r="F131" s="3" t="inlineStr"/>
@@ -5528,13 +5562,12 @@
       <c r="C132" s="3" t="inlineStr"/>
       <c r="D132" s="3" t="inlineStr">
         <is>
-          <t>예외</t>
+          <t>출력</t>
         </is>
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>- 빈 닉네임: '닉네임을 입력해주세요'
-- 20자 초과: 입력 차단</t>
+          <t>비밀번호 변경 + 모든 다른 디바이스 리프레시 토큰 invalidate + 토스트 "변경됐어요. 다른 기기에서는 다시 로그인해주세요"</t>
         </is>
       </c>
       <c r="F132" s="3" t="inlineStr"/>
@@ -5544,57 +5577,26 @@
       <c r="J132" s="3" t="inlineStr"/>
     </row>
     <row r="133">
-      <c r="A133" s="3" t="inlineStr">
-        <is>
-          <t>SETTINGS-003
-#SETTINGS-PASSWORD</t>
-        </is>
-      </c>
-      <c r="B133" s="3" t="inlineStr">
-        <is>
-          <t>설정</t>
-        </is>
-      </c>
-      <c r="C133" s="3" t="inlineStr">
-        <is>
-          <t>비밀번호 변경</t>
-        </is>
-      </c>
+      <c r="A133" s="3" t="inlineStr"/>
+      <c r="B133" s="3" t="inlineStr"/>
+      <c r="C133" s="3" t="inlineStr"/>
       <c r="D133" s="3" t="inlineStr">
         <is>
-          <t>설명</t>
+          <t>정책</t>
         </is>
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>현재 비밀번호 검증 → 새 비밀번호 변경. 변경 후 다른 디바이스 로그아웃 (선택, TBD)</t>
-        </is>
-      </c>
-      <c r="F133" s="3" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G133" s="3" t="inlineStr">
-        <is>
-          <t>비밀번호 변경 API</t>
-        </is>
-      </c>
-      <c r="H133" s="3" t="inlineStr">
-        <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="I133" s="3" t="inlineStr">
-        <is>
-          <t>기획완료</t>
-        </is>
-      </c>
-      <c r="J133" s="3" t="inlineStr">
-        <is>
-          <t>TBD: 변경 후 다른 디바이스 강제 로그아웃 여부</t>
-        </is>
-      </c>
+          <t>[보안] 현재 비밀번호 검증 필수
+[강제 로그아웃] 변경 즉시 서버에서 모든 다른 활성 리프레시 토큰 invalidate
+[화면 안내] 비밀번호 변경 화면 상단에 안내 카피: "비밀번호를 바꾸면 로그인된 다른 기기들에서 자동으로 로그아웃돼요. 보안을 위한 조치예요."</t>
+        </is>
+      </c>
+      <c r="F133" s="3" t="inlineStr"/>
+      <c r="G133" s="3" t="inlineStr"/>
+      <c r="H133" s="3" t="inlineStr"/>
+      <c r="I133" s="3" t="inlineStr"/>
+      <c r="J133" s="3" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="3" t="inlineStr"/>
@@ -5602,12 +5604,14 @@
       <c r="C134" s="3" t="inlineStr"/>
       <c r="D134" s="3" t="inlineStr">
         <is>
-          <t>입력</t>
+          <t>예외</t>
         </is>
       </c>
       <c r="E134" s="3" t="inlineStr">
         <is>
-          <t>current_password, new_password (8~64자, 영문+숫자)</t>
+          <t>- 현재 PW 불일치: '현재 비밀번호가 일치하지 않아요'
+- 새 PW 정책 미충족: 안내
+- 5회 실패: 잠시 차단</t>
         </is>
       </c>
       <c r="F134" s="3" t="inlineStr"/>
@@ -5617,24 +5621,57 @@
       <c r="J134" s="3" t="inlineStr"/>
     </row>
     <row r="135">
-      <c r="A135" s="3" t="inlineStr"/>
-      <c r="B135" s="3" t="inlineStr"/>
-      <c r="C135" s="3" t="inlineStr"/>
+      <c r="A135" s="3" t="inlineStr">
+        <is>
+          <t>SETTINGS-004
+#SETTINGS-RESET</t>
+        </is>
+      </c>
+      <c r="B135" s="3" t="inlineStr">
+        <is>
+          <t>설정</t>
+        </is>
+      </c>
+      <c r="C135" s="3" t="inlineStr">
+        <is>
+          <t>데이터 초기화</t>
+        </is>
+      </c>
       <c r="D135" s="3" t="inlineStr">
         <is>
-          <t>출력</t>
+          <t>설명</t>
         </is>
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>비밀번호 변경 + 토스트 "변경됐어요"</t>
-        </is>
-      </c>
-      <c r="F135" s="3" t="inlineStr"/>
-      <c r="G135" s="3" t="inlineStr"/>
-      <c r="H135" s="3" t="inlineStr"/>
-      <c r="I135" s="3" t="inlineStr"/>
-      <c r="J135" s="3" t="inlineStr"/>
+          <t>본인 데이터(폴더·링크·공유 멤버십) 전체 영구 삭제. 이중 확인 모달. 모든 디바이스에서 즉시 빈 상태</t>
+        </is>
+      </c>
+      <c r="F135" s="3" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G135" s="3" t="inlineStr">
+        <is>
+          <t>데이터 일괄 삭제 API (트랜잭션)</t>
+        </is>
+      </c>
+      <c r="H135" s="3" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="I135" s="3" t="inlineStr">
+        <is>
+          <t>기획완료</t>
+        </is>
+      </c>
+      <c r="J135" s="3" t="inlineStr">
+        <is>
+          <t>결정: 즉시 hard delete (개인정보보호법 OK, 사용자 의도 그대로 존중)</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="3" t="inlineStr"/>
@@ -5642,13 +5679,12 @@
       <c r="C136" s="3" t="inlineStr"/>
       <c r="D136" s="3" t="inlineStr">
         <is>
-          <t>정책</t>
+          <t>입력</t>
         </is>
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
-          <t>[보안] 현재 비밀번호 검증 필수
-[선택] 변경 후 다른 디바이스 강제 로그아웃 옵션 (TBD)</t>
+          <t>"초기화" 버튼 → 모달 1 → "정말 삭제" → 모달 2 → 사용자 비밀번호 재입력</t>
         </is>
       </c>
       <c r="F136" s="3" t="inlineStr"/>
@@ -5663,14 +5699,12 @@
       <c r="C137" s="3" t="inlineStr"/>
       <c r="D137" s="3" t="inlineStr">
         <is>
-          <t>예외</t>
+          <t>출력</t>
         </is>
       </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>- 현재 PW 불일치: '현재 비밀번호가 일치하지 않아요'
-- 새 PW 정책 미충족: 안내
-- 5회 실패: 잠시 차단</t>
+          <t>DELETE folders/links/folder_members(self) + 모든 디바이스 SYNC</t>
         </is>
       </c>
       <c r="F137" s="3" t="inlineStr"/>
@@ -5680,57 +5714,27 @@
       <c r="J137" s="3" t="inlineStr"/>
     </row>
     <row r="138">
-      <c r="A138" s="3" t="inlineStr">
-        <is>
-          <t>SETTINGS-004
-#SETTINGS-RESET</t>
-        </is>
-      </c>
-      <c r="B138" s="3" t="inlineStr">
-        <is>
-          <t>설정</t>
-        </is>
-      </c>
-      <c r="C138" s="3" t="inlineStr">
-        <is>
-          <t>데이터 초기화</t>
-        </is>
-      </c>
+      <c r="A138" s="3" t="inlineStr"/>
+      <c r="B138" s="3" t="inlineStr"/>
+      <c r="C138" s="3" t="inlineStr"/>
       <c r="D138" s="3" t="inlineStr">
         <is>
-          <t>설명</t>
+          <t>정책</t>
         </is>
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>본인 데이터(폴더·링크·공유 멤버십) 전체 삭제. 이중 확인 모달. 모든 디바이스에서 즉시 빈 상태</t>
-        </is>
-      </c>
-      <c r="F138" s="3" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G138" s="3" t="inlineStr">
-        <is>
-          <t>데이터 일괄 삭제 API</t>
-        </is>
-      </c>
-      <c r="H138" s="3" t="inlineStr">
-        <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="I138" s="3" t="inlineStr">
-        <is>
-          <t>기획완료</t>
-        </is>
-      </c>
-      <c r="J138" s="3" t="inlineStr">
-        <is>
-          <t>TBD: 30일 soft delete vs 즉시 hard delete (개인정보보호법 검토)</t>
-        </is>
-      </c>
+          <t>[위험 액션] 이중 확인 + 비밀번호 재입력
+[복구 불가] 즉시 hard delete — DB에서 본인 데이터 영구 삭제, 복구 불가
+[고지] 모달 2에 명시: "삭제하면 복구할 수 없어요. 그래도 진행할까요?"
+[동기화] 즉시 모든 디바이스에서 빈 상태</t>
+        </is>
+      </c>
+      <c r="F138" s="3" t="inlineStr"/>
+      <c r="G138" s="3" t="inlineStr"/>
+      <c r="H138" s="3" t="inlineStr"/>
+      <c r="I138" s="3" t="inlineStr"/>
+      <c r="J138" s="3" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="3" t="inlineStr"/>
@@ -5738,12 +5742,13 @@
       <c r="C139" s="3" t="inlineStr"/>
       <c r="D139" s="3" t="inlineStr">
         <is>
-          <t>입력</t>
+          <t>예외</t>
         </is>
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>"초기화" 버튼 → 모달 1 → "정말 삭제" → 모달 2 → 사용자 비밀번호 재입력</t>
+          <t>- 비밀번호 불일치: 모달 안에서 '비밀번호가 일치하지 않아요'
+- 처리 중 네트워크 오류: 트랜잭션으로 서버 측 부분 삭제 방지 (전부 실패하거나 전부 성공)</t>
         </is>
       </c>
       <c r="F139" s="3" t="inlineStr"/>
@@ -5753,24 +5758,57 @@
       <c r="J139" s="3" t="inlineStr"/>
     </row>
     <row r="140">
-      <c r="A140" s="3" t="inlineStr"/>
-      <c r="B140" s="3" t="inlineStr"/>
-      <c r="C140" s="3" t="inlineStr"/>
+      <c r="A140" s="3" t="inlineStr">
+        <is>
+          <t>THEME-001
+#SETTINGS-THEME</t>
+        </is>
+      </c>
+      <c r="B140" s="3" t="inlineStr">
+        <is>
+          <t>설정</t>
+        </is>
+      </c>
+      <c r="C140" s="3" t="inlineStr">
+        <is>
+          <t>다크/라이트 + 강조색</t>
+        </is>
+      </c>
       <c r="D140" s="3" t="inlineStr">
         <is>
-          <t>출력</t>
+          <t>설명</t>
         </is>
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>DELETE folders/links/folder_members(self) + 모든 디바이스 SYNC</t>
-        </is>
-      </c>
-      <c r="F140" s="3" t="inlineStr"/>
-      <c r="G140" s="3" t="inlineStr"/>
-      <c r="H140" s="3" t="inlineStr"/>
-      <c r="I140" s="3" t="inlineStr"/>
-      <c r="J140" s="3" t="inlineStr"/>
+          <t>다크/라이트 모드 + 강조색 3종(핑크·블루·그레이). 사용자별 저장. 로그인 화면은 항상 라이트+핑크(브랜드)</t>
+        </is>
+      </c>
+      <c r="F140" s="3" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G140" s="3" t="inlineStr">
+        <is>
+          <t>프로필 업데이트 API</t>
+        </is>
+      </c>
+      <c r="H140" s="3" t="inlineStr">
+        <is>
+          <t>일부포함</t>
+        </is>
+      </c>
+      <c r="I140" s="3" t="inlineStr">
+        <is>
+          <t>기획완료</t>
+        </is>
+      </c>
+      <c r="J140" s="3" t="inlineStr">
+        <is>
+          <t>결정: 다크/라이트 모드 + 강조색 3종(핑크/블루/그레이)</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="3" t="inlineStr"/>
@@ -5778,14 +5816,12 @@
       <c r="C141" s="3" t="inlineStr"/>
       <c r="D141" s="3" t="inlineStr">
         <is>
-          <t>정책</t>
+          <t>입력</t>
         </is>
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>[위험 액션] 이중 확인 + 비밀번호 재입력
-[복구 불가] 'soft delete + 30일 후 hard delete' (POLICY-LOCAL 참고, TBD)
-[동기화] 즉시 모든 디바이스에서 빈 상태</t>
+          <t>mode (`light`/`dark`), accent (`pink`/`blue`/`gray`)</t>
         </is>
       </c>
       <c r="F141" s="3" t="inlineStr"/>
@@ -5800,13 +5836,12 @@
       <c r="C142" s="3" t="inlineStr"/>
       <c r="D142" s="3" t="inlineStr">
         <is>
-          <t>예외</t>
+          <t>출력</t>
         </is>
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
-          <t>- 비밀번호 불일치: 모달 안에서 '비밀번호가 일치하지 않아요'
-- 처리 중 네트워크 오류: 부분 삭제 위험 → 서버는 트랜잭션 보장</t>
+          <t>profiles.theme UPDATE + CSS 변수 즉시 반영 + SYNC</t>
         </is>
       </c>
       <c r="F142" s="3" t="inlineStr"/>
@@ -5816,52 +5851,24 @@
       <c r="J142" s="3" t="inlineStr"/>
     </row>
     <row r="143">
-      <c r="A143" s="3" t="inlineStr">
-        <is>
-          <t>THEME-001
-#SETTINGS-THEME</t>
-        </is>
-      </c>
-      <c r="B143" s="3" t="inlineStr">
-        <is>
-          <t>설정</t>
-        </is>
-      </c>
-      <c r="C143" s="3" t="inlineStr">
-        <is>
-          <t>다크/라이트 + 강조색</t>
-        </is>
-      </c>
+      <c r="A143" s="3" t="inlineStr"/>
+      <c r="B143" s="3" t="inlineStr"/>
+      <c r="C143" s="3" t="inlineStr"/>
       <c r="D143" s="3" t="inlineStr">
         <is>
-          <t>설명</t>
+          <t>정책</t>
         </is>
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>시스템·다크·라이트 + 강조색 4종(핑크·블루·퍼플·그린). 사용자별 저장. 로그인 화면은 항상 라이트+핑크(브랜드)</t>
-        </is>
-      </c>
-      <c r="F143" s="3" t="inlineStr">
-        <is>
-          <t>Should</t>
-        </is>
-      </c>
-      <c r="G143" s="3" t="inlineStr">
-        <is>
-          <t>프로필 업데이트 API</t>
-        </is>
-      </c>
-      <c r="H143" s="3" t="inlineStr">
-        <is>
-          <t>일부포함</t>
-        </is>
-      </c>
-      <c r="I143" s="3" t="inlineStr">
-        <is>
-          <t>기획중</t>
-        </is>
-      </c>
+          <t>[동기화] SYNC-001로 모든 디바이스 즉시 반영
+[기본값] 신규 가입자 light + pink</t>
+        </is>
+      </c>
+      <c r="F143" s="3" t="inlineStr"/>
+      <c r="G143" s="3" t="inlineStr"/>
+      <c r="H143" s="3" t="inlineStr"/>
+      <c r="I143" s="3" t="inlineStr"/>
       <c r="J143" s="3" t="inlineStr"/>
     </row>
     <row r="144">
@@ -6479,7 +6486,7 @@
           <t>[역할] owner: 폴더·링크·멤버 전체 권한 / member: 링크 추가·읽기·자기 추가한 링크 삭제 / viewer: 읽기만
 [기본] 초대 수락 시 role='member'
 [토큰] 유효 7일, 1회용 아님(여러 명 사용 가능)
-[멤버 한도] TBD (50명 가정)</t>
+[멤버 한도] 50명</t>
         </is>
       </c>
       <c r="F178" s="3" t="inlineStr"/>
@@ -6844,7 +6851,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6888,10 +6895,32 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>최초 작성. 40개 기능(Must 19 / Should 8 / Could 5 / Won't 3 / Policy 4 / 보류 1). 모바일·웹 동시 PWA + 모바일↔웹 동기화 + 크롬 즐겨찾기 import 포함</t>
+          <t>최초 작성. 40개 기능. 모바일·웹 동시 PWA + 모바일↔웹 동기화 + 크롬 즐겨찾기 import 포함</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>인우</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>v1.0.1</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>결정 12건 반영: 이메일 6자리·게스트 출시 제거(Won't)·AI 폴백(MVP=mock+API키, v1.x=외부세션)·FCM Topic 분배+모바일/PC 채널 분리·비밀번호 변경 시 강제 로그아웃·즉시 hard delete·AWS API Gateway WebSocket·last-write-wins·공유멤버 50명·강조색 3색(핑크/블루/그레이)·단건 외부세션 미사용</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>인우</t>
         </is>

--- a/docs/planning/05_상세기능명세서.xlsx
+++ b/docs/planning/05_상세기능명세서.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -925,61 +925,57 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>LINK-007</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>링크</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>알림 예약</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>링크별 알림 시간 설정</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>일부포함</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>Should</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>US-010</t>
-        </is>
-      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>(DEPRECATED) 단일 알림 예약</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>TODO-001~005에 통합</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>미포함</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>Won't</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>QR-001</t>
+          <t>TODO-001</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>링크</t>
+          <t>할일</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>카메라 QR 스캔 (모바일)</t>
+          <t>링크당 다중 할 일</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>카메라로 QR 인식 → URL 추출</t>
+          <t>한 링크에 N개(≤20). 제목+3가지 알림 모드(없음/시간선택/반복)</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -994,66 +990,66 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>US-005</t>
+          <t>US-007, US-009</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>QR-002</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>링크</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>갤러리 QR 인식</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>사진첩 이미지에서 QR 추출</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>Could</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>US-005</t>
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>TODO-002</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>할일</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>반복 알림 (요일 기반)</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>일~토 체크박스(default 매일) + 시간 + 종료일</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>US-008</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>FOLDER-001</t>
+          <t>TODO-003</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>폴더</t>
+          <t>할일</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>폴더 생성/수정/삭제</t>
+          <t>할 일 완료 체크</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>이모지+이름. 삭제 시 링크 미분류로</t>
+          <t>개별 토글, 낙관적 UI</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -1068,29 +1064,29 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>US-003</t>
+          <t>US-011</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>FOLDER-002</t>
+          <t>TODO-004</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>폴더</t>
+          <t>할일</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>폴더 이동</t>
+          <t>할일 통합 화면</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>링크 상세에서 폴더 변경</t>
+          <t>모든 할 일 평탄화. 필터 5종</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -1105,29 +1101,29 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>US-003</t>
+          <t>US-010</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>HOME-001</t>
+          <t>TODO-005</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>홈</t>
+          <t>할일</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>홈 피드</t>
+          <t>할 일 알림 발송 (FCM)</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>최신순 무한 스크롤, Empty State</t>
+          <t>EventBridge → Lambda → FCM Topic. 반복 자동 스케줄</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -1142,177 +1138,177 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>US-001</t>
+          <t>US-008</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>SEARCH-001</t>
+          <t>TODO-006</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>검색</t>
+          <t>할일</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>키워드 검색</t>
+          <t>캘린더 .ics 내보내기</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>제목·요약·태그 통합 검색, 디바운스</t>
+          <t>외부 캘린더 앱 연동</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>MVP</t>
+          <t>일부포함</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>US-004</t>
+          <t>US-008</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>WEB-001</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>플랫폼</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>데스크톱 웹 레이아웃</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>1024px+ 사이드바·다중컬럼·키보드 단축키</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>US-006</t>
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>TODO-007</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>할일</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>채용 마감일 자동 추출</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>AI가 채용 공고 마감일 파싱 → 할 일 제안</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>Could</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>US-009</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>SYNC-001</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>플랫폼</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>모바일↔웹 자동 동기화</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>한 계정 = 한 데이터, Realtime 1~2초</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>US-006</t>
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>TODO-008</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>할일</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>AI 할 일 추천</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>본문 분석 → 할 일 제안</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>Could</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>US-007</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>IMPORT-001</t>
+          <t>QR-001</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>플랫폼</t>
+          <t>링크</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>크롬 즐겨찾기 가져오기</t>
+          <t>카메라 QR 스캔 (모바일)</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>bookmarks.html 업로드 → 일괄 import + AI 요약</t>
+          <t>카메라로 QR 인식 → URL 추출</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>일부포함</t>
+          <t>MVP</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>US-007</t>
+          <t>US-005</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>IMPORT-002</t>
+          <t>QR-002</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>플랫폼</t>
+          <t>링크</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Pocket/Raindrop import</t>
+          <t>갤러리 QR 인식</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>타 서비스 export 파일 import</t>
+          <t>사진첩 이미지에서 QR 추출</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
@@ -1327,177 +1323,177 @@
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>US-007</t>
+          <t>US-005</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>SHARE-001</t>
+          <t>FOLDER-001</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>공유 폴더</t>
+          <t>폴더</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>공유 폴더 만들기</t>
+          <t>폴더 생성/수정/삭제</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>shared 모드 + 초대 토큰</t>
+          <t>이모지+이름. 삭제 시 링크 미분류로</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>일부포함</t>
+          <t>MVP</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>US-008</t>
+          <t>US-003</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>SHARE-002</t>
+          <t>FOLDER-002</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>공유 폴더</t>
+          <t>폴더</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>공유 폴더 초대 수락</t>
+          <t>폴더 이동</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>토큰 검증 + 멤버 가입</t>
+          <t>링크 상세에서 폴더 변경</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>일부포함</t>
+          <t>MVP</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>US-008</t>
+          <t>US-003</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>SHARE-003</t>
+          <t>HOME-001</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>공유 폴더</t>
+          <t>홈</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>공유 폴더 멤버 관리</t>
+          <t>홈 피드</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>역할·제거·나가기</t>
+          <t>최신순 무한 스크롤, Empty State</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>일부포함</t>
+          <t>MVP</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>US-008</t>
+          <t>US-001</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>VIEW-001</t>
+          <t>SEARCH-001</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>콘텐츠</t>
+          <t>검색</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>YouTube 임베드 미리보기</t>
+          <t>키워드 검색</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>URL 자동 인식 → 상세 임베드</t>
+          <t>제목·요약·태그 통합 검색, 디바운스</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>일부포함</t>
+          <t>MVP</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>US-009</t>
+          <t>US-004</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>SETTINGS-001</t>
+          <t>WEB-001</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>설정</t>
+          <t>플랫폼</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>AI 제공자 선택</t>
+          <t>데스크톱 웹 레이아웃</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Gemini/ChatGPT/Claude/Perplexity 등</t>
+          <t>1024px+ 사이드바·다중컬럼·키보드 단축키</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -1512,29 +1508,29 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>US-002</t>
+          <t>US-006</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>SETTINGS-002</t>
+          <t>SYNC-001</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>설정</t>
+          <t>플랫폼</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>프로필 변경</t>
+          <t>모바일↔웹 자동 동기화</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>닉네임·아바타 이모지</t>
+          <t>한 계정 = 한 데이터, Realtime 1~2초</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -1549,354 +1545,362 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>US-001</t>
+          <t>US-006</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>SETTINGS-003</t>
+          <t>IMPORT-001</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>설정</t>
+          <t>플랫폼</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>비밀번호 변경</t>
+          <t>크롬 즐겨찾기 가져오기</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>현재 PW 검증 후 변경</t>
+          <t>bookmarks.html 업로드 → 일괄 import + AI 요약</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>MVP</t>
+          <t>일부포함</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>US-001</t>
+          <t>US-007</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>SETTINGS-004</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>설정</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>데이터 초기화</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>본인 데이터 전체 삭제</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t>US-001</t>
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>IMPORT-002</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>플랫폼</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>Pocket/Raindrop import</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>타 서비스 export 파일 import</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>Could</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>US-007</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>THEME-001</t>
+          <t>SHARE-001</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
+          <t>공유 폴더</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>공유 폴더 만들기</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>shared 모드 + 초대 토큰</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>일부포함</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>US-008</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>SHARE-002</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>공유 폴더</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>공유 폴더 초대 수락</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>토큰 검증 + 멤버 가입</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>일부포함</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>US-008</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>SHARE-003</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>공유 폴더</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>공유 폴더 멤버 관리</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>역할·제거·나가기</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>일부포함</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>US-008</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>VIEW-001</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>콘텐츠</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>YouTube 임베드 미리보기</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>URL 자동 인식 → 상세 임베드</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>일부포함</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>US-009</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>SETTINGS-001</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
           <t>설정</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>다크/라이트 + 강조색</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>다크/라이트 + 강조색 3종(핑크/블루/그레이)</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>일부포함</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>Should</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t>US-012</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>AI-001</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>Chrome 확장 (외부 AI 세션)</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="inlineStr">
-        <is>
-          <t>사용자 웹 AI 세션 활용</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>Could</t>
-        </is>
-      </c>
-      <c r="G34" s="4" t="inlineStr">
-        <is>
-          <t>US-013</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>BACKUP-001</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>AI 제공자 선택</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>Gemini/ChatGPT/Claude/Perplexity 등</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>US-002</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>SETTINGS-002</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
         <is>
           <t>설정</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>데이터 내보내기</t>
-        </is>
-      </c>
-      <c r="D35" s="4" t="inlineStr">
-        <is>
-          <t>JSON/CSV 다운로드</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t>Could</t>
-        </is>
-      </c>
-      <c r="G35" s="4" t="inlineStr">
-        <is>
-          <t>US-014</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>HIGHLIGHT-001</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>콘텐츠</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>본문 하이라이트</t>
-        </is>
-      </c>
-      <c r="D36" s="4" t="inlineStr">
-        <is>
-          <t>텍스트 일부 강조 저장</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>Could</t>
-        </is>
-      </c>
-      <c r="G36" s="4" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="4" t="inlineStr">
-        <is>
-          <t>OFFLINE-001</t>
-        </is>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>PWA</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t>풀 오프라인 모드</t>
-        </is>
-      </c>
-      <c r="D37" s="4" t="inlineStr">
-        <is>
-          <t>네트워크 없이 모든 기능</t>
-        </is>
-      </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>미포함</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="inlineStr">
-        <is>
-          <t>Won't</t>
-        </is>
-      </c>
-      <c r="G37" s="4" t="inlineStr">
-        <is>
-          <t>US-015</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>NATIVE-001</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>PWA</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="inlineStr">
-        <is>
-          <t>네이티브 앱</t>
-        </is>
-      </c>
-      <c r="D38" s="4" t="inlineStr">
-        <is>
-          <t>iOS/Android 스토어</t>
-        </is>
-      </c>
-      <c r="E38" s="4" t="inlineStr">
-        <is>
-          <t>미포함</t>
-        </is>
-      </c>
-      <c r="F38" s="4" t="inlineStr">
-        <is>
-          <t>Won't</t>
-        </is>
-      </c>
-      <c r="G38" s="4" t="inlineStr">
-        <is>
-          <t>US-016</t>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>프로필 변경</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>닉네임·아바타 이모지</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>US-001</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>BILLING-001</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>계정</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="inlineStr">
-        <is>
-          <t>유료 플랜</t>
-        </is>
-      </c>
-      <c r="D39" s="4" t="inlineStr">
-        <is>
-          <t>결제·구독</t>
-        </is>
-      </c>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>미포함</t>
-        </is>
-      </c>
-      <c r="F39" s="4" t="inlineStr">
-        <is>
-          <t>Won't</t>
-        </is>
-      </c>
-      <c r="G39" s="4" t="inlineStr"/>
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>SETTINGS-003</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>설정</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>비밀번호 변경</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>현재 PW 검증 후 변경</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>US-001</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>POLICY-AUTH</t>
+          <t>SETTINGS-004</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>정책</t>
+          <t>설정</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>토큰 만료/갱신</t>
+          <t>데이터 초기화</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>JWT 액세스 15분 + 리프레시 30일</t>
+          <t>본인 데이터 전체 삭제</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
@@ -1909,106 +1913,394 @@
           <t>Must</t>
         </is>
       </c>
-      <c r="G40" s="3" t="inlineStr"/>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>US-001</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
+          <t>THEME-001</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>설정</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>다크/라이트 + 강조색</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>다크/라이트 + 강조색 3종(핑크/블루/그레이)</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>일부포함</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>US-012</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>AI-001</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>Chrome 확장 (외부 AI 세션)</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>사용자 웹 AI 세션 활용</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>Could</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t>US-013</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>BACKUP-001</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>설정</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>데이터 내보내기</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>JSON/CSV 다운로드</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>Could</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="inlineStr">
+        <is>
+          <t>US-014</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>HIGHLIGHT-001</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>콘텐츠</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>본문 하이라이트</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>텍스트 일부 강조 저장</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>Could</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>OFFLINE-001</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>PWA</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>풀 오프라인 모드</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>네트워크 없이 모든 기능</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>미포함</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>Won't</t>
+        </is>
+      </c>
+      <c r="G45" s="4" t="inlineStr">
+        <is>
+          <t>US-015</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>NATIVE-001</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>PWA</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>네이티브 앱</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>iOS/Android 스토어</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>미포함</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>Won't</t>
+        </is>
+      </c>
+      <c r="G46" s="4" t="inlineStr">
+        <is>
+          <t>US-016</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>BILLING-001</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>계정</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>유료 플랜</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>결제·구독</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>미포함</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>Won't</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>POLICY-AUTH</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>정책</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>토큰 만료/갱신</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>JWT 액세스 15분 + 리프레시 30일</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
           <t>POLICY-AI</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B49" s="3" t="inlineStr">
         <is>
           <t>정책</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr">
+      <c r="C49" s="3" t="inlineStr">
         <is>
           <t>AI 요약 호출</t>
         </is>
       </c>
-      <c r="D41" s="3" t="inlineStr">
+      <c r="D49" s="3" t="inlineStr">
         <is>
           <t>외부 세션→API→mock 폴백 사다리</t>
         </is>
       </c>
-      <c r="E41" s="3" t="inlineStr">
+      <c r="E49" s="3" t="inlineStr">
         <is>
           <t>MVP</t>
         </is>
       </c>
-      <c r="F41" s="3" t="inlineStr">
+      <c r="F49" s="3" t="inlineStr">
         <is>
           <t>Must</t>
         </is>
       </c>
-      <c r="G41" s="3" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="inlineStr">
+      <c r="G49" s="3" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
         <is>
           <t>POLICY-LOCAL</t>
         </is>
       </c>
-      <c r="B42" s="3" t="inlineStr">
+      <c r="B50" s="3" t="inlineStr">
         <is>
           <t>정책</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
+      <c r="C50" s="3" t="inlineStr">
         <is>
           <t>로컬·서버 저장 분리</t>
         </is>
       </c>
-      <c r="D42" s="3" t="inlineStr">
+      <c r="D50" s="3" t="inlineStr">
         <is>
           <t>게스트 로컬 / 정식 서버+캐시, 오프라인 큐잉</t>
         </is>
       </c>
-      <c r="E42" s="3" t="inlineStr">
+      <c r="E50" s="3" t="inlineStr">
         <is>
           <t>MVP</t>
         </is>
       </c>
-      <c r="F42" s="3" t="inlineStr">
+      <c r="F50" s="3" t="inlineStr">
         <is>
           <t>Must</t>
         </is>
       </c>
-      <c r="G42" s="3" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="inlineStr">
+      <c r="G50" s="3" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
         <is>
           <t>POLICY-SHARED</t>
         </is>
       </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="B51" s="3" t="inlineStr">
         <is>
           <t>정책</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="C51" s="3" t="inlineStr">
         <is>
           <t>공유 폴더 권한</t>
         </is>
       </c>
-      <c r="D43" s="3" t="inlineStr">
+      <c r="D51" s="3" t="inlineStr">
         <is>
           <t>owner/member/viewer + 토큰 7일</t>
         </is>
       </c>
-      <c r="E43" s="3" t="inlineStr">
+      <c r="E51" s="3" t="inlineStr">
         <is>
           <t>일부포함</t>
         </is>
       </c>
-      <c r="F43" s="3" t="inlineStr">
+      <c r="F51" s="3" t="inlineStr">
         <is>
           <t>Should</t>
         </is>
       </c>
-      <c r="G43" s="3" t="inlineStr"/>
+      <c r="G51" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2024,7 +2316,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J179"/>
+  <dimension ref="A1:J212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3489,193 +3781,129 @@
       <c r="J53" s="3" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>LINK-007
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>LINK-007</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>링크</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>(DEPRECATED) 단일 알림 예약</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>기존 단일 reminder_at 모델은 TODO-001~005에 통합되어 폐기됨</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>Won't</t>
+        </is>
+      </c>
+      <c r="G54" s="4" t="inlineStr"/>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t>미포함</t>
+        </is>
+      </c>
+      <c r="I54" s="4" t="inlineStr">
+        <is>
+          <t>기획중</t>
+        </is>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>v1.1에서 TODO-001~005로 통합. 단일 reminder_at 모델 폐기, 다중 todos 모델 채택</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>TODO-001
 #LINK-DETAIL
-#SETTINGS-NOTIFICATION</t>
-        </is>
-      </c>
-      <c r="B54" s="3" t="inlineStr">
-        <is>
-          <t>링크</t>
-        </is>
-      </c>
-      <c r="C54" s="3" t="inlineStr">
-        <is>
-          <t>알림 예약</t>
-        </is>
-      </c>
-      <c r="D54" s="3" t="inlineStr">
+#TODO-CREATE
+#TODO-EDIT</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>할일</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>링크당 다중 할 일</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="E54" s="3" t="inlineStr">
-        <is>
-          <t>링크별 reminder_at 설정. EventBridge가 시간에 Lambda 트리거 → FCM Topic으로 사용자의 모든 활성 디바이스에 푸시 발송</t>
-        </is>
-      </c>
-      <c r="F54" s="3" t="inlineStr">
-        <is>
-          <t>Should</t>
-        </is>
-      </c>
-      <c r="G54" s="3" t="inlineStr">
-        <is>
-          <t>예약 알림 API
-FCM Topic 발송</t>
-        </is>
-      </c>
-      <c r="H54" s="3" t="inlineStr">
-        <is>
-          <t>일부포함</t>
-        </is>
-      </c>
-      <c r="I54" s="3" t="inlineStr">
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>한 링크에 여러 개 할 일을 매달 수 있다. 각 할 일은 제목 + 3가지 알림 모드(없음/시간선택/반복알림) 중 하나. 링크당 최대 20개. UI: 편집 시트에 할 일 행 N개 + "＋ 할 일 추가" 버튼</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>POST/PATCH/DELETE /links/:id/todos</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="inlineStr">
         <is>
           <t>기획완료</t>
         </is>
       </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>결정: FCM Topic으로 모든 디바이스 발송 + 모바일/PC 채널 분리 옵션. 중복은 사용자 토글로 회피</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="3" t="inlineStr"/>
-      <c r="B55" s="3" t="inlineStr"/>
-      <c r="C55" s="3" t="inlineStr"/>
-      <c r="D55" s="3" t="inlineStr">
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>링크당 ≤20. 추가 시 EventBridge Rule 등록</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr"/>
+      <c r="B59" s="3" t="inlineStr"/>
+      <c r="C59" s="3" t="inlineStr"/>
+      <c r="D59" s="3" t="inlineStr">
         <is>
           <t>입력</t>
         </is>
       </c>
-      <c r="E55" s="3" t="inlineStr">
-        <is>
-          <t>reminder_at (datetime, 미래)</t>
-        </is>
-      </c>
-      <c r="F55" s="3" t="inlineStr"/>
-      <c r="G55" s="3" t="inlineStr"/>
-      <c r="H55" s="3" t="inlineStr"/>
-      <c r="I55" s="3" t="inlineStr"/>
-      <c r="J55" s="3" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="3" t="inlineStr"/>
-      <c r="B56" s="3" t="inlineStr"/>
-      <c r="C56" s="3" t="inlineStr"/>
-      <c r="D56" s="3" t="inlineStr">
-        <is>
-          <t>출력</t>
-        </is>
-      </c>
-      <c r="E56" s="3" t="inlineStr">
-        <is>
-          <t>links UPDATE + 예약 등록 + 시간에 푸시</t>
-        </is>
-      </c>
-      <c r="F56" s="3" t="inlineStr"/>
-      <c r="G56" s="3" t="inlineStr"/>
-      <c r="H56" s="3" t="inlineStr"/>
-      <c r="I56" s="3" t="inlineStr"/>
-      <c r="J56" s="3" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="3" t="inlineStr"/>
-      <c r="B57" s="3" t="inlineStr"/>
-      <c r="C57" s="3" t="inlineStr"/>
-      <c r="D57" s="3" t="inlineStr">
-        <is>
-          <t>정책</t>
-        </is>
-      </c>
-      <c r="E57" s="3" t="inlineStr">
-        <is>
-          <t>[권한] 푸시 권한 미허용 시 인앱 토스트로 폴백
-[분배] FCM Topic으로 모든 활성 디바이스에 푸시
-[채널 분리] 설정에 "모바일 알림 받기" / "데스크톱 알림 받기" 토글 — 사용자가 채널별 ON/OFF</t>
-        </is>
-      </c>
-      <c r="F57" s="3" t="inlineStr"/>
-      <c r="G57" s="3" t="inlineStr"/>
-      <c r="H57" s="3" t="inlineStr"/>
-      <c r="I57" s="3" t="inlineStr"/>
-      <c r="J57" s="3" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="3" t="inlineStr"/>
-      <c r="B58" s="3" t="inlineStr"/>
-      <c r="C58" s="3" t="inlineStr"/>
-      <c r="D58" s="3" t="inlineStr">
-        <is>
-          <t>예외</t>
-        </is>
-      </c>
-      <c r="E58" s="3" t="inlineStr">
-        <is>
-          <t>- 과거 시각: 픽커 차단
-- 링크 삭제됨: 발송 안 함
-- 푸시 발송 실패: 24시간 후 1회 재시도
-- 같은 알림 중복 노출: 사용자가 한쪽 채널 OFF로 회피</t>
-        </is>
-      </c>
-      <c r="F58" s="3" t="inlineStr"/>
-      <c r="G58" s="3" t="inlineStr"/>
-      <c r="H58" s="3" t="inlineStr"/>
-      <c r="I58" s="3" t="inlineStr"/>
-      <c r="J58" s="3" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="3" t="inlineStr">
-        <is>
-          <t>QR-001
-#LINK-ADD
-#QR-SCAN</t>
-        </is>
-      </c>
-      <c r="B59" s="3" t="inlineStr">
-        <is>
-          <t>링크</t>
-        </is>
-      </c>
-      <c r="C59" s="3" t="inlineStr">
-        <is>
-          <t>카메라 QR 스캔 (모바일)</t>
-        </is>
-      </c>
-      <c r="D59" s="3" t="inlineStr">
-        <is>
-          <t>설명</t>
-        </is>
-      </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>html5-qrcode로 카메라 스트림 인식. URL 형태의 QR이면 #LINK-ADD에 자동 채움. 데스크톱 웹에서는 비활성</t>
-        </is>
-      </c>
-      <c r="F59" s="3" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G59" s="3" t="inlineStr">
-        <is>
-          <t>(클라이언트, html5-qrcode)</t>
-        </is>
-      </c>
-      <c r="H59" s="3" t="inlineStr">
-        <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="I59" s="3" t="inlineStr">
-        <is>
-          <t>기획완료</t>
-        </is>
-      </c>
+          <t>- 제목 (1~50자, 필수)
+- 알림 모드: 없음 / 시간선택 / 반복알림 (chip 3개 중 1개)
+- 시간선택: 캘린더 picker(날짜) + 시간 picker(HH:MM, KST)
+- 반복알림: 요일 체크박스(일·월·화·수·목·금·토, default 모두 선택=매일) + 시간 + 종료일(선택)</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr"/>
+      <c r="G59" s="3" t="inlineStr"/>
+      <c r="H59" s="3" t="inlineStr"/>
+      <c r="I59" s="3" t="inlineStr"/>
       <c r="J59" s="3" t="inlineStr"/>
     </row>
     <row r="60">
@@ -3684,13 +3912,12 @@
       <c r="C60" s="3" t="inlineStr"/>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>입력</t>
+          <t>출력</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>(자동) MediaStream
-사용자: QR 비추기</t>
+          <t>link_todos INSERT/UPDATE/DELETE + Realtime publish (TODO_CREATED/UPDATED/DELETED)</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr"/>
@@ -3705,12 +3932,15 @@
       <c r="C61" s="3" t="inlineStr"/>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>출력</t>
+          <t>정책</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>- URL 추출 → #LINK-ADD 입력창 채움</t>
+          <t>[기본값] 알림 모드=없음, 반복 요일=매일(7개)
+[제약] 링크당 20개, 제목 50자, 반복 종료일 ≤ 시작+365일
+[정렬] sort_order 기준
+[동기화] SYNC-001 즉시 반영</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr"/>
@@ -3725,14 +3955,17 @@
       <c r="C62" s="3" t="inlineStr"/>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>정책</t>
+          <t>예외</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>[권한] 카메라 권한 거부 시 URL 직접 입력 폴백 + 안내
-[환경] HTTPS 또는 localhost 필수
-[차별 인터랙션] 모바일 전용. 웹에서는 QR 탭 비활성 + 툴팁 "모바일에서 사용 가능해요"</t>
+          <t>- 빈 제목: '할 일 제목을 입력해주세요'
+- 50자 초과: 입력 차단
+- 한도 20개 초과: '한 링크에 할 일은 20개까지 만들 수 있어요'
+- 시간선택 모드 + 과거 시각: picker 차단
+- 반복 모드 + 요일 0개: '하나 이상의 요일을 선택해주세요'
+- 권한 미허용: '인앱 토스트로만 알려드려요'</t>
         </is>
       </c>
       <c r="F62" s="3" t="inlineStr"/>
@@ -3742,93 +3975,160 @@
       <c r="J62" s="3" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="inlineStr"/>
-      <c r="B63" s="3" t="inlineStr"/>
-      <c r="C63" s="3" t="inlineStr"/>
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>TODO-002
+#TODO-CREATE
+#TODO-EDIT</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>할일</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>반복 알림 (요일 기반)</t>
+        </is>
+      </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
+          <t>설명</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>매일/평일/주말/사용자 정의 요일 + 시간으로 반복 알림. 요일 체크박스 7개 (일·월·화·수·목·금·토). default 모두 체크(매일). 사용자가 해제해서 패턴 만들기</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="inlineStr">
+        <is>
+          <t>POST /links/:id/todos (notifyMode='recurring')</t>
+        </is>
+      </c>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="I63" s="3" t="inlineStr">
+        <is>
+          <t>기획완료</t>
+        </is>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>default 매일=7개 모두 선택</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr"/>
+      <c r="B64" s="3" t="inlineStr"/>
+      <c r="C64" s="3" t="inlineStr"/>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>입력</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>weekdays: int[](0=일~6=토), notifyTime: HH:MM(KST), endDate: YYYY-MM-DD(선택)</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="inlineStr"/>
+      <c r="G64" s="3" t="inlineStr"/>
+      <c r="H64" s="3" t="inlineStr"/>
+      <c r="I64" s="3" t="inlineStr"/>
+      <c r="J64" s="3" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr"/>
+      <c r="B65" s="3" t="inlineStr"/>
+      <c r="C65" s="3" t="inlineStr"/>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>출력</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>EventBridge Rule 등록 (다음 회차 트리거)</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="inlineStr"/>
+      <c r="G65" s="3" t="inlineStr"/>
+      <c r="H65" s="3" t="inlineStr"/>
+      <c r="I65" s="3" t="inlineStr"/>
+      <c r="J65" s="3" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr"/>
+      <c r="B66" s="3" t="inlineStr"/>
+      <c r="C66" s="3" t="inlineStr"/>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>정책</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>[기본값] weekdays=[0,1,2,3,4,5,6], endDate=null(시스템 365일 cap)
+[표시] '매일 21:00' / '평일 21:00' / '주말 10:00' / '월수금 21:00' 자연 한국어
+[다음 회차] 현재 시각 이후 weekdays 중 가장 가까운 시각
+[발송] FCM Topic + 사용자 채널 토글 적용</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="inlineStr"/>
+      <c r="G66" s="3" t="inlineStr"/>
+      <c r="H66" s="3" t="inlineStr"/>
+      <c r="I66" s="3" t="inlineStr"/>
+      <c r="J66" s="3" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr"/>
+      <c r="B67" s="3" t="inlineStr"/>
+      <c r="C67" s="3" t="inlineStr"/>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
           <t>예외</t>
         </is>
       </c>
-      <c r="E63" s="3" t="inlineStr">
-        <is>
-          <t>- 권한 거부: '카메라 권한이 필요해요. 설정에서 허용해주세요'
-- HTTPS 아님: 'QR 스캔은 보안 연결에서만 동작해요'
-- 인식 실패 10초: '다시 비춰주세요' + Mock 입력(개발용)
-- URL이 아닌 QR: 'URL이 아닌 QR이에요'</t>
-        </is>
-      </c>
-      <c r="F63" s="3" t="inlineStr"/>
-      <c r="G63" s="3" t="inlineStr"/>
-      <c r="H63" s="3" t="inlineStr"/>
-      <c r="I63" s="3" t="inlineStr"/>
-      <c r="J63" s="3" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="4" t="inlineStr">
-        <is>
-          <t>QR-002</t>
-        </is>
-      </c>
-      <c r="B64" s="4" t="inlineStr">
-        <is>
-          <t>링크</t>
-        </is>
-      </c>
-      <c r="C64" s="4" t="inlineStr">
-        <is>
-          <t>갤러리 QR 인식</t>
-        </is>
-      </c>
-      <c r="D64" s="4" t="inlineStr">
-        <is>
-          <t>설명</t>
-        </is>
-      </c>
-      <c r="E64" s="4" t="inlineStr">
-        <is>
-          <t>사진첩 이미지에서 QR 추출 (Media Capture + jsQR)</t>
-        </is>
-      </c>
-      <c r="F64" s="4" t="inlineStr">
-        <is>
-          <t>Could</t>
-        </is>
-      </c>
-      <c r="G64" s="4" t="inlineStr"/>
-      <c r="H64" s="4" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="I64" s="4" t="inlineStr">
-        <is>
-          <t>기획중</t>
-        </is>
-      </c>
-      <c r="J64" s="4" t="inlineStr">
-        <is>
-          <t>v1.x 추가 예정</t>
-        </is>
-      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>- 요일 0개: '하나 이상의 요일을 선택해주세요'
+- 시간 미입력: '시간을 입력해주세요'
+- endDate 도달: Rule 자동 삭제, 할 일 status='완료'</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="inlineStr"/>
+      <c r="G67" s="3" t="inlineStr"/>
+      <c r="H67" s="3" t="inlineStr"/>
+      <c r="I67" s="3" t="inlineStr"/>
+      <c r="J67" s="3" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>FOLDER-001
-#FOLDER-LIST
-#FOLDER-CREATE
-#FOLDER-DETAIL</t>
+          <t>TODO-003
+#TODO-LIST
+#LINK-DETAIL</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>폴더</t>
+          <t>할일</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>폴더 생성/수정/삭제</t>
+          <t>할 일 완료 체크</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
@@ -3838,7 +4138,7 @@
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>이모지 + 이름으로 폴더 관리. 시스템 폴더 "미분류"는 삭제 불가. 공유 폴더는 SHARE-001 참고</t>
+          <t>할 일 카드 좌측 체크박스 또는 상세에서 토글. 낙관적 UI로 즉시 ✓ 표시 후 서버 UPDATE</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
@@ -3848,7 +4148,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>폴더 CRUD API</t>
+          <t>POST /todos/:id/complete</t>
         </is>
       </c>
       <c r="H68" s="3" t="inlineStr">
@@ -3861,7 +4161,11 @@
           <t>기획완료</t>
         </is>
       </c>
-      <c r="J68" s="3" t="inlineStr"/>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>낙관적 UI</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr"/>
@@ -3874,9 +4178,7 @@
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>(생성) 이름 1~30자, 이모지
-(수정) 이름·이모지 변경
-(삭제) 폴더 ID + 확인</t>
+          <t>todoId, completed: boolean</t>
         </is>
       </c>
       <c r="F69" s="3" t="inlineStr"/>
@@ -3896,7 +4198,7 @@
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>folders INSERT/UPDATE/DELETE + Realtime</t>
+          <t>link_todos.completed_at UPDATE + Realtime</t>
         </is>
       </c>
       <c r="F70" s="3" t="inlineStr"/>
@@ -3916,10 +4218,8 @@
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>[기본값] 이모지=📁
-[제약] 폴더 100개 한도
-[삭제 처리] 폴더 삭제 시 소속 링크는 folder_id=NULL (미분류로 자동 이동)
-[공유 폴더] owner만 이름·이모지 변경 가능</t>
+          <t>[낙관적 UI] 즉시 ✓ 후 UPDATE 호출, 실패 시 롤백
+[반복 알림] MVP는 "전체 종료"만(EventBridge Rule 일괄 제거). 회차별 완료는 v1.x</t>
         </is>
       </c>
       <c r="F71" s="3" t="inlineStr"/>
@@ -3939,6 +4239,742 @@
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
+          <t>- 네트워크 오류: 로컬 큐잉, 재연결 시 동기화
+- 동시 토글: last-write-wins</t>
+        </is>
+      </c>
+      <c r="F72" s="3" t="inlineStr"/>
+      <c r="G72" s="3" t="inlineStr"/>
+      <c r="H72" s="3" t="inlineStr"/>
+      <c r="I72" s="3" t="inlineStr"/>
+      <c r="J72" s="3" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>TODO-004
+#TODO-LIST</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>할일</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>할일 통합 화면</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>모바일 탭바 "할일" / 데스크톱 사이드바. 모든 link_todos 평탄화 노출. 카드=체크박스+제목+알림 시각/반복 배지+원본 링크 미리보기</t>
+        </is>
+      </c>
+      <c r="F73" s="3" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G73" s="3" t="inlineStr">
+        <is>
+          <t>GET /todos?filter=...</t>
+        </is>
+      </c>
+      <c r="H73" s="3" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="I73" s="3" t="inlineStr">
+        <is>
+          <t>기획완료</t>
+        </is>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>탭바 5번째</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr"/>
+      <c r="B74" s="3" t="inlineStr"/>
+      <c r="C74" s="3" t="inlineStr"/>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>입력</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>필터 chip(전체/미완료/알림예정/기간지남/완료) + 정렬</t>
+        </is>
+      </c>
+      <c r="F74" s="3" t="inlineStr"/>
+      <c r="G74" s="3" t="inlineStr"/>
+      <c r="H74" s="3" t="inlineStr"/>
+      <c r="I74" s="3" t="inlineStr"/>
+      <c r="J74" s="3" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr"/>
+      <c r="B75" s="3" t="inlineStr"/>
+      <c r="C75" s="3" t="inlineStr"/>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>출력</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>할 일 카드 리스트</t>
+        </is>
+      </c>
+      <c r="F75" s="3" t="inlineStr"/>
+      <c r="G75" s="3" t="inlineStr"/>
+      <c r="H75" s="3" t="inlineStr"/>
+      <c r="I75" s="3" t="inlineStr"/>
+      <c r="J75" s="3" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr"/>
+      <c r="B76" s="3" t="inlineStr"/>
+      <c r="C76" s="3" t="inlineStr"/>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>정책</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>[정렬] 미완료 우선 → 알림 임박순 → 최신 추가순. 완료는 맨 아래
+[페이지네이션] cursor 기반 30개
+[차별 인터랙션] 데스크톱 단축키 J/K/X/Enter</t>
+        </is>
+      </c>
+      <c r="F76" s="3" t="inlineStr"/>
+      <c r="G76" s="3" t="inlineStr"/>
+      <c r="H76" s="3" t="inlineStr"/>
+      <c r="I76" s="3" t="inlineStr"/>
+      <c r="J76" s="3" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr"/>
+      <c r="B77" s="3" t="inlineStr"/>
+      <c r="C77" s="3" t="inlineStr"/>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>- 빈 결과: '이 필터에 해당하는 할 일이 없어요' Empty State</t>
+        </is>
+      </c>
+      <c r="F77" s="3" t="inlineStr"/>
+      <c r="G77" s="3" t="inlineStr"/>
+      <c r="H77" s="3" t="inlineStr"/>
+      <c r="I77" s="3" t="inlineStr"/>
+      <c r="J77" s="3" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>TODO-005</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>할일</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>할 일 알림 발송 (FCM)</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="inlineStr">
+        <is>
+          <t>알림 시각에 EventBridge Rule이 Lambda 트리거 → FCM Topic 발송. 사용자 활성 디바이스 모두에 푸시 (모바일/PC 채널 토글 적용)</t>
+        </is>
+      </c>
+      <c r="F78" s="3" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G78" s="3" t="inlineStr">
+        <is>
+          <t>EventBridge Rule + Lambda + FCM</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="I78" s="3" t="inlineStr">
+        <is>
+          <t>기획완료</t>
+        </is>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>DLQ 모니터링, 24h 재시도</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr"/>
+      <c r="B79" s="3" t="inlineStr"/>
+      <c r="C79" s="3" t="inlineStr"/>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>입력</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="inlineStr">
+        <is>
+          <t>(시스템) Rule 발화</t>
+        </is>
+      </c>
+      <c r="F79" s="3" t="inlineStr"/>
+      <c r="G79" s="3" t="inlineStr"/>
+      <c r="H79" s="3" t="inlineStr"/>
+      <c r="I79" s="3" t="inlineStr"/>
+      <c r="J79" s="3" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr"/>
+      <c r="B80" s="3" t="inlineStr"/>
+      <c r="C80" s="3" t="inlineStr"/>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>출력</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="inlineStr">
+        <is>
+          <t>FCM 발송 + WebSocket TODO_FIRED 이벤트</t>
+        </is>
+      </c>
+      <c r="F80" s="3" t="inlineStr"/>
+      <c r="G80" s="3" t="inlineStr"/>
+      <c r="H80" s="3" t="inlineStr"/>
+      <c r="I80" s="3" t="inlineStr"/>
+      <c r="J80" s="3" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr"/>
+      <c r="B81" s="3" t="inlineStr"/>
+      <c r="C81" s="3" t="inlineStr"/>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>정책</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="inlineStr">
+        <is>
+          <t>[신뢰성] DLQ 모니터링, 24시간 후 1회 재시도
+[반복 알림] 발송 직후 다음 회차 Rule 등록 (재귀 스케줄)
+[종료] endDate 또는 완료 시 Rule 자동 삭제</t>
+        </is>
+      </c>
+      <c r="F81" s="3" t="inlineStr"/>
+      <c r="G81" s="3" t="inlineStr"/>
+      <c r="H81" s="3" t="inlineStr"/>
+      <c r="I81" s="3" t="inlineStr"/>
+      <c r="J81" s="3" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="inlineStr"/>
+      <c r="B82" s="3" t="inlineStr"/>
+      <c r="C82" s="3" t="inlineStr"/>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="inlineStr">
+        <is>
+          <t>- 권한 미허용: 인앱 토스트 폴백
+- 두 채널 모두 OFF: 발송 스킵
+- 링크 삭제됨: 발송 안 함</t>
+        </is>
+      </c>
+      <c r="F82" s="3" t="inlineStr"/>
+      <c r="G82" s="3" t="inlineStr"/>
+      <c r="H82" s="3" t="inlineStr"/>
+      <c r="I82" s="3" t="inlineStr"/>
+      <c r="J82" s="3" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>TODO-006</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>할일</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>캘린더 .ics 내보내기</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="inlineStr">
+        <is>
+          <t>할 일 → .ics 파일로 다운로드. 외부 캘린더 import. 반복 알림은 RRULE로 변환</t>
+        </is>
+      </c>
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G83" s="3" t="inlineStr"/>
+      <c r="H83" s="3" t="inlineStr">
+        <is>
+          <t>일부포함</t>
+        </is>
+      </c>
+      <c r="I83" s="3" t="inlineStr">
+        <is>
+          <t>기획중</t>
+        </is>
+      </c>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>외부 캘린더(Google/Apple/네이버) 연동</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="inlineStr">
+        <is>
+          <t>TODO-007</t>
+        </is>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t>할일</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="inlineStr">
+        <is>
+          <t>채용 마감일 자동 추출</t>
+        </is>
+      </c>
+      <c r="D84" s="4" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+      <c r="E84" s="4" t="inlineStr">
+        <is>
+          <t>채용 공고 도메인 인식 → AI가 마감일 파싱 → 할 일 제안 (D-3 자소서, D-1 포트폴리오, 당일 지원)</t>
+        </is>
+      </c>
+      <c r="F84" s="4" t="inlineStr">
+        <is>
+          <t>Could</t>
+        </is>
+      </c>
+      <c r="G84" s="4" t="inlineStr"/>
+      <c r="H84" s="4" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="I84" s="4" t="inlineStr">
+        <is>
+          <t>기획중</t>
+        </is>
+      </c>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>v1.x — 채용 도메인(잡코리아/사람인/원티드/링커리어) 패턴 학습</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="4" t="inlineStr">
+        <is>
+          <t>TODO-008</t>
+        </is>
+      </c>
+      <c r="B88" s="4" t="inlineStr">
+        <is>
+          <t>할일</t>
+        </is>
+      </c>
+      <c r="C88" s="4" t="inlineStr">
+        <is>
+          <t>AI 할 일 추천</t>
+        </is>
+      </c>
+      <c r="D88" s="4" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+      <c r="E88" s="4" t="inlineStr">
+        <is>
+          <t>링크 본문 분석 → 액션 아이템 추출 → 할 일 후보로 사용자에게 제안</t>
+        </is>
+      </c>
+      <c r="F88" s="4" t="inlineStr">
+        <is>
+          <t>Could</t>
+        </is>
+      </c>
+      <c r="G88" s="4" t="inlineStr"/>
+      <c r="H88" s="4" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="I88" s="4" t="inlineStr">
+        <is>
+          <t>기획중</t>
+        </is>
+      </c>
+      <c r="J88" s="4" t="inlineStr">
+        <is>
+          <t>본문 요약 → 할 일 후보 추출</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>QR-001
+#LINK-ADD
+#QR-SCAN</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>링크</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>카메라 QR 스캔 (모바일)</t>
+        </is>
+      </c>
+      <c r="D92" s="3" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="inlineStr">
+        <is>
+          <t>html5-qrcode로 카메라 스트림 인식. URL 형태의 QR이면 #LINK-ADD에 자동 채움. 데스크톱 웹에서는 비활성</t>
+        </is>
+      </c>
+      <c r="F92" s="3" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G92" s="3" t="inlineStr">
+        <is>
+          <t>(클라이언트, html5-qrcode)</t>
+        </is>
+      </c>
+      <c r="H92" s="3" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="I92" s="3" t="inlineStr">
+        <is>
+          <t>기획완료</t>
+        </is>
+      </c>
+      <c r="J92" s="3" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="inlineStr"/>
+      <c r="B93" s="3" t="inlineStr"/>
+      <c r="C93" s="3" t="inlineStr"/>
+      <c r="D93" s="3" t="inlineStr">
+        <is>
+          <t>입력</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="inlineStr">
+        <is>
+          <t>(자동) MediaStream
+사용자: QR 비추기</t>
+        </is>
+      </c>
+      <c r="F93" s="3" t="inlineStr"/>
+      <c r="G93" s="3" t="inlineStr"/>
+      <c r="H93" s="3" t="inlineStr"/>
+      <c r="I93" s="3" t="inlineStr"/>
+      <c r="J93" s="3" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="inlineStr"/>
+      <c r="B94" s="3" t="inlineStr"/>
+      <c r="C94" s="3" t="inlineStr"/>
+      <c r="D94" s="3" t="inlineStr">
+        <is>
+          <t>출력</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="inlineStr">
+        <is>
+          <t>- URL 추출 → #LINK-ADD 입력창 채움</t>
+        </is>
+      </c>
+      <c r="F94" s="3" t="inlineStr"/>
+      <c r="G94" s="3" t="inlineStr"/>
+      <c r="H94" s="3" t="inlineStr"/>
+      <c r="I94" s="3" t="inlineStr"/>
+      <c r="J94" s="3" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="inlineStr"/>
+      <c r="B95" s="3" t="inlineStr"/>
+      <c r="C95" s="3" t="inlineStr"/>
+      <c r="D95" s="3" t="inlineStr">
+        <is>
+          <t>정책</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="inlineStr">
+        <is>
+          <t>[권한] 카메라 권한 거부 시 URL 직접 입력 폴백 + 안내
+[환경] HTTPS 또는 localhost 필수
+[차별 인터랙션] 모바일 전용. 웹에서는 QR 탭 비활성 + 툴팁 "모바일에서 사용 가능해요"</t>
+        </is>
+      </c>
+      <c r="F95" s="3" t="inlineStr"/>
+      <c r="G95" s="3" t="inlineStr"/>
+      <c r="H95" s="3" t="inlineStr"/>
+      <c r="I95" s="3" t="inlineStr"/>
+      <c r="J95" s="3" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="inlineStr"/>
+      <c r="B96" s="3" t="inlineStr"/>
+      <c r="C96" s="3" t="inlineStr"/>
+      <c r="D96" s="3" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="inlineStr">
+        <is>
+          <t>- 권한 거부: '카메라 권한이 필요해요. 설정에서 허용해주세요'
+- HTTPS 아님: 'QR 스캔은 보안 연결에서만 동작해요'
+- 인식 실패 10초: '다시 비춰주세요' + Mock 입력(개발용)
+- URL이 아닌 QR: 'URL이 아닌 QR이에요'</t>
+        </is>
+      </c>
+      <c r="F96" s="3" t="inlineStr"/>
+      <c r="G96" s="3" t="inlineStr"/>
+      <c r="H96" s="3" t="inlineStr"/>
+      <c r="I96" s="3" t="inlineStr"/>
+      <c r="J96" s="3" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t>QR-002</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>링크</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="inlineStr">
+        <is>
+          <t>갤러리 QR 인식</t>
+        </is>
+      </c>
+      <c r="D97" s="4" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+      <c r="E97" s="4" t="inlineStr">
+        <is>
+          <t>사진첩 이미지에서 QR 추출 (Media Capture + jsQR)</t>
+        </is>
+      </c>
+      <c r="F97" s="4" t="inlineStr">
+        <is>
+          <t>Could</t>
+        </is>
+      </c>
+      <c r="G97" s="4" t="inlineStr"/>
+      <c r="H97" s="4" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="I97" s="4" t="inlineStr">
+        <is>
+          <t>기획중</t>
+        </is>
+      </c>
+      <c r="J97" s="4" t="inlineStr">
+        <is>
+          <t>v1.x 추가 예정</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="inlineStr">
+        <is>
+          <t>FOLDER-001
+#FOLDER-LIST
+#FOLDER-CREATE
+#FOLDER-DETAIL</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t>폴더</t>
+        </is>
+      </c>
+      <c r="C101" s="3" t="inlineStr">
+        <is>
+          <t>폴더 생성/수정/삭제</t>
+        </is>
+      </c>
+      <c r="D101" s="3" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+      <c r="E101" s="3" t="inlineStr">
+        <is>
+          <t>이모지 + 이름으로 폴더 관리. 시스템 폴더 "미분류"는 삭제 불가. 공유 폴더는 SHARE-001 참고</t>
+        </is>
+      </c>
+      <c r="F101" s="3" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G101" s="3" t="inlineStr">
+        <is>
+          <t>폴더 CRUD API</t>
+        </is>
+      </c>
+      <c r="H101" s="3" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="I101" s="3" t="inlineStr">
+        <is>
+          <t>기획완료</t>
+        </is>
+      </c>
+      <c r="J101" s="3" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="3" t="inlineStr"/>
+      <c r="B102" s="3" t="inlineStr"/>
+      <c r="C102" s="3" t="inlineStr"/>
+      <c r="D102" s="3" t="inlineStr">
+        <is>
+          <t>입력</t>
+        </is>
+      </c>
+      <c r="E102" s="3" t="inlineStr">
+        <is>
+          <t>(생성) 이름 1~30자, 이모지
+(수정) 이름·이모지 변경
+(삭제) 폴더 ID + 확인</t>
+        </is>
+      </c>
+      <c r="F102" s="3" t="inlineStr"/>
+      <c r="G102" s="3" t="inlineStr"/>
+      <c r="H102" s="3" t="inlineStr"/>
+      <c r="I102" s="3" t="inlineStr"/>
+      <c r="J102" s="3" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="inlineStr"/>
+      <c r="B103" s="3" t="inlineStr"/>
+      <c r="C103" s="3" t="inlineStr"/>
+      <c r="D103" s="3" t="inlineStr">
+        <is>
+          <t>출력</t>
+        </is>
+      </c>
+      <c r="E103" s="3" t="inlineStr">
+        <is>
+          <t>folders INSERT/UPDATE/DELETE + Realtime</t>
+        </is>
+      </c>
+      <c r="F103" s="3" t="inlineStr"/>
+      <c r="G103" s="3" t="inlineStr"/>
+      <c r="H103" s="3" t="inlineStr"/>
+      <c r="I103" s="3" t="inlineStr"/>
+      <c r="J103" s="3" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="3" t="inlineStr"/>
+      <c r="B104" s="3" t="inlineStr"/>
+      <c r="C104" s="3" t="inlineStr"/>
+      <c r="D104" s="3" t="inlineStr">
+        <is>
+          <t>정책</t>
+        </is>
+      </c>
+      <c r="E104" s="3" t="inlineStr">
+        <is>
+          <t>[기본값] 이모지=📁
+[제약] 폴더 100개 한도
+[삭제 처리] 폴더 삭제 시 소속 링크는 folder_id=NULL (미분류로 자동 이동)
+[공유 폴더] owner만 이름·이모지 변경 가능</t>
+        </is>
+      </c>
+      <c r="F104" s="3" t="inlineStr"/>
+      <c r="G104" s="3" t="inlineStr"/>
+      <c r="H104" s="3" t="inlineStr"/>
+      <c r="I104" s="3" t="inlineStr"/>
+      <c r="J104" s="3" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="3" t="inlineStr"/>
+      <c r="B105" s="3" t="inlineStr"/>
+      <c r="C105" s="3" t="inlineStr"/>
+      <c r="D105" s="3" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="E105" s="3" t="inlineStr">
+        <is>
           <t>- 빈 이름: '폴더 이름을 입력해주세요'
 - 30자 초과: 입력 자체 차단
 - 공유 폴더 멤버가 삭제 시도: '오너만 삭제할 수 있어요' + "나가기" 버튼
@@ -3946,497 +4982,497 @@
 - 100개 한도: '폴더는 최대 100개까지'</t>
         </is>
       </c>
-      <c r="F72" s="3" t="inlineStr"/>
-      <c r="G72" s="3" t="inlineStr"/>
-      <c r="H72" s="3" t="inlineStr"/>
-      <c r="I72" s="3" t="inlineStr"/>
-      <c r="J72" s="3" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="3" t="inlineStr">
+      <c r="F105" s="3" t="inlineStr"/>
+      <c r="G105" s="3" t="inlineStr"/>
+      <c r="H105" s="3" t="inlineStr"/>
+      <c r="I105" s="3" t="inlineStr"/>
+      <c r="J105" s="3" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="3" t="inlineStr">
         <is>
           <t>FOLDER-002
 #LINK-DETAIL
 #FOLDER-PICKER</t>
         </is>
       </c>
-      <c r="B73" s="3" t="inlineStr">
+      <c r="B106" s="3" t="inlineStr">
         <is>
           <t>폴더</t>
         </is>
       </c>
-      <c r="C73" s="3" t="inlineStr">
+      <c r="C106" s="3" t="inlineStr">
         <is>
           <t>폴더 이동</t>
         </is>
       </c>
-      <c r="D73" s="3" t="inlineStr">
+      <c r="D106" s="3" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="E73" s="3" t="inlineStr">
+      <c r="E106" s="3" t="inlineStr">
         <is>
           <t>링크 상세에서 폴더 변경. 픽커 모달에 사용자 폴더 + 미분류 노출</t>
         </is>
       </c>
-      <c r="F73" s="3" t="inlineStr">
+      <c r="F106" s="3" t="inlineStr">
         <is>
           <t>Must</t>
         </is>
       </c>
-      <c r="G73" s="3" t="inlineStr">
+      <c r="G106" s="3" t="inlineStr">
         <is>
           <t>링크 폴더 이동 API</t>
         </is>
       </c>
-      <c r="H73" s="3" t="inlineStr">
+      <c r="H106" s="3" t="inlineStr">
         <is>
           <t>MVP</t>
         </is>
       </c>
-      <c r="I73" s="3" t="inlineStr">
+      <c r="I106" s="3" t="inlineStr">
         <is>
           <t>기획완료</t>
         </is>
       </c>
-      <c r="J73" s="3" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="3" t="inlineStr"/>
-      <c r="B74" s="3" t="inlineStr"/>
-      <c r="C74" s="3" t="inlineStr"/>
-      <c r="D74" s="3" t="inlineStr">
+      <c r="J106" s="3" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="3" t="inlineStr"/>
+      <c r="B107" s="3" t="inlineStr"/>
+      <c r="C107" s="3" t="inlineStr"/>
+      <c r="D107" s="3" t="inlineStr">
         <is>
           <t>입력</t>
         </is>
       </c>
-      <c r="E74" s="3" t="inlineStr">
+      <c r="E107" s="3" t="inlineStr">
         <is>
           <t>link_id, target_folder_id</t>
         </is>
       </c>
-      <c r="F74" s="3" t="inlineStr"/>
-      <c r="G74" s="3" t="inlineStr"/>
-      <c r="H74" s="3" t="inlineStr"/>
-      <c r="I74" s="3" t="inlineStr"/>
-      <c r="J74" s="3" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="3" t="inlineStr"/>
-      <c r="B75" s="3" t="inlineStr"/>
-      <c r="C75" s="3" t="inlineStr"/>
-      <c r="D75" s="3" t="inlineStr">
+      <c r="F107" s="3" t="inlineStr"/>
+      <c r="G107" s="3" t="inlineStr"/>
+      <c r="H107" s="3" t="inlineStr"/>
+      <c r="I107" s="3" t="inlineStr"/>
+      <c r="J107" s="3" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="3" t="inlineStr"/>
+      <c r="B108" s="3" t="inlineStr"/>
+      <c r="C108" s="3" t="inlineStr"/>
+      <c r="D108" s="3" t="inlineStr">
         <is>
           <t>출력</t>
         </is>
       </c>
-      <c r="E75" s="3" t="inlineStr">
+      <c r="E108" s="3" t="inlineStr">
         <is>
           <t>links.folder_id UPDATE + Realtime</t>
         </is>
       </c>
-      <c r="F75" s="3" t="inlineStr"/>
-      <c r="G75" s="3" t="inlineStr"/>
-      <c r="H75" s="3" t="inlineStr"/>
-      <c r="I75" s="3" t="inlineStr"/>
-      <c r="J75" s="3" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="3" t="inlineStr"/>
-      <c r="B76" s="3" t="inlineStr"/>
-      <c r="C76" s="3" t="inlineStr"/>
-      <c r="D76" s="3" t="inlineStr">
+      <c r="F108" s="3" t="inlineStr"/>
+      <c r="G108" s="3" t="inlineStr"/>
+      <c r="H108" s="3" t="inlineStr"/>
+      <c r="I108" s="3" t="inlineStr"/>
+      <c r="J108" s="3" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="3" t="inlineStr"/>
+      <c r="B109" s="3" t="inlineStr"/>
+      <c r="C109" s="3" t="inlineStr"/>
+      <c r="D109" s="3" t="inlineStr">
         <is>
           <t>정책</t>
         </is>
       </c>
-      <c r="E76" s="3" t="inlineStr">
+      <c r="E109" s="3" t="inlineStr">
         <is>
           <t>[동기화] 다른 디바이스에서 카드가 다른 폴더로 부드럽게 이동</t>
         </is>
       </c>
-      <c r="F76" s="3" t="inlineStr"/>
-      <c r="G76" s="3" t="inlineStr"/>
-      <c r="H76" s="3" t="inlineStr"/>
-      <c r="I76" s="3" t="inlineStr"/>
-      <c r="J76" s="3" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="3" t="inlineStr"/>
-      <c r="B77" s="3" t="inlineStr"/>
-      <c r="C77" s="3" t="inlineStr"/>
-      <c r="D77" s="3" t="inlineStr">
+      <c r="F109" s="3" t="inlineStr"/>
+      <c r="G109" s="3" t="inlineStr"/>
+      <c r="H109" s="3" t="inlineStr"/>
+      <c r="I109" s="3" t="inlineStr"/>
+      <c r="J109" s="3" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="3" t="inlineStr"/>
+      <c r="B110" s="3" t="inlineStr"/>
+      <c r="C110" s="3" t="inlineStr"/>
+      <c r="D110" s="3" t="inlineStr">
         <is>
           <t>예외</t>
         </is>
       </c>
-      <c r="E77" s="3" t="inlineStr">
+      <c r="E110" s="3" t="inlineStr">
         <is>
           <t>- 공유 폴더(viewer 권한)로 이동 시도: '읽기 권한 폴더에는 옮길 수 없어요'
 - 삭제된 폴더 ID: 미분류로 자동 fallback</t>
         </is>
       </c>
-      <c r="F77" s="3" t="inlineStr"/>
-      <c r="G77" s="3" t="inlineStr"/>
-      <c r="H77" s="3" t="inlineStr"/>
-      <c r="I77" s="3" t="inlineStr"/>
-      <c r="J77" s="3" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="3" t="inlineStr">
+      <c r="F110" s="3" t="inlineStr"/>
+      <c r="G110" s="3" t="inlineStr"/>
+      <c r="H110" s="3" t="inlineStr"/>
+      <c r="I110" s="3" t="inlineStr"/>
+      <c r="J110" s="3" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="3" t="inlineStr">
         <is>
           <t>HOME-001
 #HOME
 #HOME-EMPTY</t>
         </is>
       </c>
-      <c r="B78" s="3" t="inlineStr">
+      <c r="B111" s="3" t="inlineStr">
         <is>
           <t>홈</t>
         </is>
       </c>
-      <c r="C78" s="3" t="inlineStr">
+      <c r="C111" s="3" t="inlineStr">
         <is>
           <t>홈 피드</t>
         </is>
       </c>
-      <c r="D78" s="3" t="inlineStr">
+      <c r="D111" s="3" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="E78" s="3" t="inlineStr">
+      <c r="E111" s="3" t="inlineStr">
         <is>
           <t>사용자의 모든 링크를 created_at desc로 무한 스크롤. 페이지당 30개. 게스트 시드 데이터 또는 Empty State</t>
         </is>
       </c>
-      <c r="F78" s="3" t="inlineStr">
+      <c r="F111" s="3" t="inlineStr">
         <is>
           <t>Must</t>
         </is>
       </c>
-      <c r="G78" s="3" t="inlineStr">
+      <c r="G111" s="3" t="inlineStr">
         <is>
           <t>링크 목록 API (cursor)</t>
         </is>
       </c>
-      <c r="H78" s="3" t="inlineStr">
+      <c r="H111" s="3" t="inlineStr">
         <is>
           <t>MVP</t>
         </is>
       </c>
-      <c r="I78" s="3" t="inlineStr">
+      <c r="I111" s="3" t="inlineStr">
         <is>
           <t>기획완료</t>
         </is>
       </c>
-      <c r="J78" s="3" t="inlineStr">
+      <c r="J111" s="3" t="inlineStr">
         <is>
           <t>TBD: 사용자 설정으로 인기/오래된순 추가?</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="3" t="inlineStr"/>
-      <c r="B79" s="3" t="inlineStr"/>
-      <c r="C79" s="3" t="inlineStr"/>
-      <c r="D79" s="3" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="3" t="inlineStr"/>
+      <c r="B112" s="3" t="inlineStr"/>
+      <c r="C112" s="3" t="inlineStr"/>
+      <c r="D112" s="3" t="inlineStr">
         <is>
           <t>입력</t>
         </is>
       </c>
-      <c r="E79" s="3" t="inlineStr">
+      <c r="E112" s="3" t="inlineStr">
         <is>
           <t>(자동) cursor (last_created_at)</t>
         </is>
       </c>
-      <c r="F79" s="3" t="inlineStr"/>
-      <c r="G79" s="3" t="inlineStr"/>
-      <c r="H79" s="3" t="inlineStr"/>
-      <c r="I79" s="3" t="inlineStr"/>
-      <c r="J79" s="3" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="3" t="inlineStr"/>
-      <c r="B80" s="3" t="inlineStr"/>
-      <c r="C80" s="3" t="inlineStr"/>
-      <c r="D80" s="3" t="inlineStr">
+      <c r="F112" s="3" t="inlineStr"/>
+      <c r="G112" s="3" t="inlineStr"/>
+      <c r="H112" s="3" t="inlineStr"/>
+      <c r="I112" s="3" t="inlineStr"/>
+      <c r="J112" s="3" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="3" t="inlineStr"/>
+      <c r="B113" s="3" t="inlineStr"/>
+      <c r="C113" s="3" t="inlineStr"/>
+      <c r="D113" s="3" t="inlineStr">
         <is>
           <t>출력</t>
         </is>
       </c>
-      <c r="E80" s="3" t="inlineStr">
+      <c r="E113" s="3" t="inlineStr">
         <is>
           <t>링크 카드 리스트 / Empty State 일러스트+CTA</t>
         </is>
       </c>
-      <c r="F80" s="3" t="inlineStr"/>
-      <c r="G80" s="3" t="inlineStr"/>
-      <c r="H80" s="3" t="inlineStr"/>
-      <c r="I80" s="3" t="inlineStr"/>
-      <c r="J80" s="3" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="3" t="inlineStr"/>
-      <c r="B81" s="3" t="inlineStr"/>
-      <c r="C81" s="3" t="inlineStr"/>
-      <c r="D81" s="3" t="inlineStr">
+      <c r="F113" s="3" t="inlineStr"/>
+      <c r="G113" s="3" t="inlineStr"/>
+      <c r="H113" s="3" t="inlineStr"/>
+      <c r="I113" s="3" t="inlineStr"/>
+      <c r="J113" s="3" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="3" t="inlineStr"/>
+      <c r="B114" s="3" t="inlineStr"/>
+      <c r="C114" s="3" t="inlineStr"/>
+      <c r="D114" s="3" t="inlineStr">
         <is>
           <t>정책</t>
         </is>
       </c>
-      <c r="E81" s="3" t="inlineStr">
+      <c r="E114" s="3" t="inlineStr">
         <is>
           <t>[기본값] 정렬: 최신순
 [페이지네이션] cursor 기반 30개
 [차별 인터랙션] 모바일=1열, 웹 1024px+=2열, 1440px+=3열, 1920px+=4열 (WEB-001)</t>
         </is>
       </c>
-      <c r="F81" s="3" t="inlineStr"/>
-      <c r="G81" s="3" t="inlineStr"/>
-      <c r="H81" s="3" t="inlineStr"/>
-      <c r="I81" s="3" t="inlineStr"/>
-      <c r="J81" s="3" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="3" t="inlineStr"/>
-      <c r="B82" s="3" t="inlineStr"/>
-      <c r="C82" s="3" t="inlineStr"/>
-      <c r="D82" s="3" t="inlineStr">
+      <c r="F114" s="3" t="inlineStr"/>
+      <c r="G114" s="3" t="inlineStr"/>
+      <c r="H114" s="3" t="inlineStr"/>
+      <c r="I114" s="3" t="inlineStr"/>
+      <c r="J114" s="3" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="3" t="inlineStr"/>
+      <c r="B115" s="3" t="inlineStr"/>
+      <c r="C115" s="3" t="inlineStr"/>
+      <c r="D115" s="3" t="inlineStr">
         <is>
           <t>예외</t>
         </is>
       </c>
-      <c r="E82" s="3" t="inlineStr">
+      <c r="E115" s="3" t="inlineStr">
         <is>
           <t>- 첫 진입 + 데이터 0개: Empty State "+ 버튼으로 첫 링크를 저장해보세요"
 - 네트워크 오류: 캐시된 마지막 페이지 + "오프라인이에요" 배너</t>
         </is>
       </c>
-      <c r="F82" s="3" t="inlineStr"/>
-      <c r="G82" s="3" t="inlineStr"/>
-      <c r="H82" s="3" t="inlineStr"/>
-      <c r="I82" s="3" t="inlineStr"/>
-      <c r="J82" s="3" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="3" t="inlineStr">
+      <c r="F115" s="3" t="inlineStr"/>
+      <c r="G115" s="3" t="inlineStr"/>
+      <c r="H115" s="3" t="inlineStr"/>
+      <c r="I115" s="3" t="inlineStr"/>
+      <c r="J115" s="3" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="3" t="inlineStr">
         <is>
           <t>SEARCH-001
 #SEARCH
 #SEARCH-EMPTY</t>
         </is>
       </c>
-      <c r="B83" s="3" t="inlineStr">
+      <c r="B116" s="3" t="inlineStr">
         <is>
           <t>검색</t>
         </is>
       </c>
-      <c r="C83" s="3" t="inlineStr">
+      <c r="C116" s="3" t="inlineStr">
         <is>
           <t>키워드 검색</t>
         </is>
       </c>
-      <c r="D83" s="3" t="inlineStr">
+      <c r="D116" s="3" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="E83" s="3" t="inlineStr">
+      <c r="E116" s="3" t="inlineStr">
         <is>
           <t>제목·요약·태그 통합 검색. 디바운스 200ms. 결과 카드에 키워드 하이라이트. 데스크톱 웹은 ⌘K/Ctrl+K 단축키</t>
         </is>
       </c>
-      <c r="F83" s="3" t="inlineStr">
+      <c r="F116" s="3" t="inlineStr">
         <is>
           <t>Must</t>
         </is>
       </c>
-      <c r="G83" s="3" t="inlineStr">
+      <c r="G116" s="3" t="inlineStr">
         <is>
           <t>검색 API (ILIKE → tsvector)</t>
         </is>
       </c>
-      <c r="H83" s="3" t="inlineStr">
+      <c r="H116" s="3" t="inlineStr">
         <is>
           <t>MVP</t>
         </is>
       </c>
-      <c r="I83" s="3" t="inlineStr">
+      <c r="I116" s="3" t="inlineStr">
         <is>
           <t>기획완료</t>
         </is>
       </c>
-      <c r="J83" s="3" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="3" t="inlineStr"/>
-      <c r="B84" s="3" t="inlineStr"/>
-      <c r="C84" s="3" t="inlineStr"/>
-      <c r="D84" s="3" t="inlineStr">
+      <c r="J116" s="3" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="3" t="inlineStr"/>
+      <c r="B117" s="3" t="inlineStr"/>
+      <c r="C117" s="3" t="inlineStr"/>
+      <c r="D117" s="3" t="inlineStr">
         <is>
           <t>입력</t>
         </is>
       </c>
-      <c r="E84" s="3" t="inlineStr">
+      <c r="E117" s="3" t="inlineStr">
         <is>
           <t>키워드 (2자 이상)</t>
         </is>
       </c>
-      <c r="F84" s="3" t="inlineStr"/>
-      <c r="G84" s="3" t="inlineStr"/>
-      <c r="H84" s="3" t="inlineStr"/>
-      <c r="I84" s="3" t="inlineStr"/>
-      <c r="J84" s="3" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="3" t="inlineStr"/>
-      <c r="B85" s="3" t="inlineStr"/>
-      <c r="C85" s="3" t="inlineStr"/>
-      <c r="D85" s="3" t="inlineStr">
+      <c r="F117" s="3" t="inlineStr"/>
+      <c r="G117" s="3" t="inlineStr"/>
+      <c r="H117" s="3" t="inlineStr"/>
+      <c r="I117" s="3" t="inlineStr"/>
+      <c r="J117" s="3" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="3" t="inlineStr"/>
+      <c r="B118" s="3" t="inlineStr"/>
+      <c r="C118" s="3" t="inlineStr"/>
+      <c r="D118" s="3" t="inlineStr">
         <is>
           <t>출력</t>
         </is>
       </c>
-      <c r="E85" s="3" t="inlineStr">
+      <c r="E118" s="3" t="inlineStr">
         <is>
           <t>매칭 링크 카드 리스트 + 키워드 강조</t>
         </is>
       </c>
-      <c r="F85" s="3" t="inlineStr"/>
-      <c r="G85" s="3" t="inlineStr"/>
-      <c r="H85" s="3" t="inlineStr"/>
-      <c r="I85" s="3" t="inlineStr"/>
-      <c r="J85" s="3" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="3" t="inlineStr"/>
-      <c r="B86" s="3" t="inlineStr"/>
-      <c r="C86" s="3" t="inlineStr"/>
-      <c r="D86" s="3" t="inlineStr">
+      <c r="F118" s="3" t="inlineStr"/>
+      <c r="G118" s="3" t="inlineStr"/>
+      <c r="H118" s="3" t="inlineStr"/>
+      <c r="I118" s="3" t="inlineStr"/>
+      <c r="J118" s="3" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="3" t="inlineStr"/>
+      <c r="B119" s="3" t="inlineStr"/>
+      <c r="C119" s="3" t="inlineStr"/>
+      <c r="D119" s="3" t="inlineStr">
         <is>
           <t>정책</t>
         </is>
       </c>
-      <c r="E86" s="3" t="inlineStr">
+      <c r="E119" s="3" t="inlineStr">
         <is>
           <t>[기본값] 검색 대상=제목/요약/태그 동시
 [구현] v1: ILIKE '%kw%' (Postgres) / v2: tsvector + gin 인덱스
 [동기화] 새로 저장된 링크도 즉시 검색 가능</t>
         </is>
       </c>
-      <c r="F86" s="3" t="inlineStr"/>
-      <c r="G86" s="3" t="inlineStr"/>
-      <c r="H86" s="3" t="inlineStr"/>
-      <c r="I86" s="3" t="inlineStr"/>
-      <c r="J86" s="3" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="3" t="inlineStr"/>
-      <c r="B87" s="3" t="inlineStr"/>
-      <c r="C87" s="3" t="inlineStr"/>
-      <c r="D87" s="3" t="inlineStr">
+      <c r="F119" s="3" t="inlineStr"/>
+      <c r="G119" s="3" t="inlineStr"/>
+      <c r="H119" s="3" t="inlineStr"/>
+      <c r="I119" s="3" t="inlineStr"/>
+      <c r="J119" s="3" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="3" t="inlineStr"/>
+      <c r="B120" s="3" t="inlineStr"/>
+      <c r="C120" s="3" t="inlineStr"/>
+      <c r="D120" s="3" t="inlineStr">
         <is>
           <t>예외</t>
         </is>
       </c>
-      <c r="E87" s="3" t="inlineStr">
+      <c r="E120" s="3" t="inlineStr">
         <is>
           <t>- 1자: 트리거 안 함, '2자 이상 입력해주세요'
 - 결과 0개: "'{키워드}' 결과가 없어요" + 최근 검색어 추천
 - 네트워크 오류: 로컬 캐시 결과 + '오프라인 결과를 보여드려요'</t>
         </is>
       </c>
-      <c r="F87" s="3" t="inlineStr"/>
-      <c r="G87" s="3" t="inlineStr"/>
-      <c r="H87" s="3" t="inlineStr"/>
-      <c r="I87" s="3" t="inlineStr"/>
-      <c r="J87" s="3" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="3" t="inlineStr">
+      <c r="F120" s="3" t="inlineStr"/>
+      <c r="G120" s="3" t="inlineStr"/>
+      <c r="H120" s="3" t="inlineStr"/>
+      <c r="I120" s="3" t="inlineStr"/>
+      <c r="J120" s="3" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="3" t="inlineStr">
         <is>
           <t>WEB-001
 (전 화면 반응형)</t>
         </is>
       </c>
-      <c r="B88" s="3" t="inlineStr">
+      <c r="B121" s="3" t="inlineStr">
         <is>
           <t>플랫폼</t>
         </is>
       </c>
-      <c r="C88" s="3" t="inlineStr">
+      <c r="C121" s="3" t="inlineStr">
         <is>
           <t>데스크톱 웹 레이아웃 (반응형 PWA)</t>
         </is>
       </c>
-      <c r="D88" s="3" t="inlineStr">
+      <c r="D121" s="3" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="E88" s="3" t="inlineStr">
+      <c r="E121" s="3" t="inlineStr">
         <is>
           <t>단일 React PWA 코드베이스가 화면 폭에 따라 모바일·태블릿·데스크톱 레이아웃을 자동 전환. 데스크톱은 좌측 사이드바(폴더 트리) + 메인 그리드(2~4컬럼) + 우측 상세 패널 구조</t>
         </is>
       </c>
-      <c r="F88" s="3" t="inlineStr">
+      <c r="F121" s="3" t="inlineStr">
         <is>
           <t>Must</t>
         </is>
       </c>
-      <c r="G88" s="3" t="inlineStr">
+      <c r="G121" s="3" t="inlineStr">
         <is>
           <t>(클라이언트 레이아웃)</t>
         </is>
       </c>
-      <c r="H88" s="3" t="inlineStr">
+      <c r="H121" s="3" t="inlineStr">
         <is>
           <t>MVP</t>
         </is>
       </c>
-      <c r="I88" s="3" t="inlineStr">
+      <c r="I121" s="3" t="inlineStr">
         <is>
           <t>기획완료</t>
         </is>
       </c>
-      <c r="J88" s="3" t="inlineStr">
+      <c r="J121" s="3" t="inlineStr">
         <is>
           <t>TBD: 사이드바 폭(고정 240px vs 가변), 다크모드 색상 토큰은 THEME-001과 연동</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="3" t="inlineStr"/>
-      <c r="B89" s="3" t="inlineStr"/>
-      <c r="C89" s="3" t="inlineStr"/>
-      <c r="D89" s="3" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="3" t="inlineStr"/>
+      <c r="B122" s="3" t="inlineStr"/>
+      <c r="C122" s="3" t="inlineStr"/>
+      <c r="D122" s="3" t="inlineStr">
         <is>
           <t>입력</t>
         </is>
       </c>
-      <c r="E89" s="3" t="inlineStr">
+      <c r="E122" s="3" t="inlineStr">
         <is>
           <t>window.innerWidth (브레이크포인트 매칭)</t>
         </is>
       </c>
-      <c r="F89" s="3" t="inlineStr"/>
-      <c r="G89" s="3" t="inlineStr"/>
-      <c r="H89" s="3" t="inlineStr"/>
-      <c r="I89" s="3" t="inlineStr"/>
-      <c r="J89" s="3" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="3" t="inlineStr"/>
-      <c r="B90" s="3" t="inlineStr"/>
-      <c r="C90" s="3" t="inlineStr"/>
-      <c r="D90" s="3" t="inlineStr">
+      <c r="F122" s="3" t="inlineStr"/>
+      <c r="G122" s="3" t="inlineStr"/>
+      <c r="H122" s="3" t="inlineStr"/>
+      <c r="I122" s="3" t="inlineStr"/>
+      <c r="J122" s="3" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="3" t="inlineStr"/>
+      <c r="B123" s="3" t="inlineStr"/>
+      <c r="C123" s="3" t="inlineStr"/>
+      <c r="D123" s="3" t="inlineStr">
         <is>
           <t>출력</t>
         </is>
       </c>
-      <c r="E90" s="3" t="inlineStr">
+      <c r="E123" s="3" t="inlineStr">
         <is>
           <t>- &lt;1024px: 모바일 레이아웃(단일 컬럼 + 하단 탭바)
 - 1024~1439px: 사이드바 + 2컬럼 그리드
@@ -4444,160 +5480,160 @@
 - 1920px+: 사이드바 + 4컬럼 + 우측 상세 패널</t>
         </is>
       </c>
-      <c r="F90" s="3" t="inlineStr"/>
-      <c r="G90" s="3" t="inlineStr"/>
-      <c r="H90" s="3" t="inlineStr"/>
-      <c r="I90" s="3" t="inlineStr"/>
-      <c r="J90" s="3" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="3" t="inlineStr"/>
-      <c r="B91" s="3" t="inlineStr"/>
-      <c r="C91" s="3" t="inlineStr"/>
-      <c r="D91" s="3" t="inlineStr">
+      <c r="F123" s="3" t="inlineStr"/>
+      <c r="G123" s="3" t="inlineStr"/>
+      <c r="H123" s="3" t="inlineStr"/>
+      <c r="I123" s="3" t="inlineStr"/>
+      <c r="J123" s="3" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="3" t="inlineStr"/>
+      <c r="B124" s="3" t="inlineStr"/>
+      <c r="C124" s="3" t="inlineStr"/>
+      <c r="D124" s="3" t="inlineStr">
         <is>
           <t>정책</t>
         </is>
       </c>
-      <c r="E91" s="3" t="inlineStr">
+      <c r="E124" s="3" t="inlineStr">
         <is>
           <t>[차별 인터랙션] 데스크톱: 키보드 단축키 ⌘K(검색) / N(새 링크) / J·K(카드 이동) / Enter(상세) / Del(삭제)
 [차별 인터랙션] 데스크톱: 카드 hover 시 액션 버튼 노출
 [모바일 전용] QR-001은 데스크톱에서 비활성</t>
         </is>
       </c>
-      <c r="F91" s="3" t="inlineStr"/>
-      <c r="G91" s="3" t="inlineStr"/>
-      <c r="H91" s="3" t="inlineStr"/>
-      <c r="I91" s="3" t="inlineStr"/>
-      <c r="J91" s="3" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="3" t="inlineStr"/>
-      <c r="B92" s="3" t="inlineStr"/>
-      <c r="C92" s="3" t="inlineStr"/>
-      <c r="D92" s="3" t="inlineStr">
+      <c r="F124" s="3" t="inlineStr"/>
+      <c r="G124" s="3" t="inlineStr"/>
+      <c r="H124" s="3" t="inlineStr"/>
+      <c r="I124" s="3" t="inlineStr"/>
+      <c r="J124" s="3" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="3" t="inlineStr"/>
+      <c r="B125" s="3" t="inlineStr"/>
+      <c r="C125" s="3" t="inlineStr"/>
+      <c r="D125" s="3" t="inlineStr">
         <is>
           <t>예외</t>
         </is>
       </c>
-      <c r="E92" s="3" t="inlineStr">
+      <c r="E125" s="3" t="inlineStr">
         <is>
           <t>- 화면 폭 변경(창 리사이즈): 즉시 레이아웃 재계산, 스크롤 위치 보존
 - PWA 설치 데스크톱: 단축키 충돌 회피(브라우저 단축키 존중)</t>
         </is>
       </c>
-      <c r="F92" s="3" t="inlineStr"/>
-      <c r="G92" s="3" t="inlineStr"/>
-      <c r="H92" s="3" t="inlineStr"/>
-      <c r="I92" s="3" t="inlineStr"/>
-      <c r="J92" s="3" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="3" t="inlineStr">
+      <c r="F125" s="3" t="inlineStr"/>
+      <c r="G125" s="3" t="inlineStr"/>
+      <c r="H125" s="3" t="inlineStr"/>
+      <c r="I125" s="3" t="inlineStr"/>
+      <c r="J125" s="3" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="3" t="inlineStr">
         <is>
           <t>SYNC-001
 (전 화면 백그라운드)</t>
         </is>
       </c>
-      <c r="B93" s="3" t="inlineStr">
+      <c r="B126" s="3" t="inlineStr">
         <is>
           <t>플랫폼</t>
         </is>
       </c>
-      <c r="C93" s="3" t="inlineStr">
+      <c r="C126" s="3" t="inlineStr">
         <is>
           <t>모바일↔웹 자동 동기화</t>
         </is>
       </c>
-      <c r="D93" s="3" t="inlineStr">
+      <c r="D126" s="3" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="E93" s="3" t="inlineStr">
+      <c r="E126" s="3" t="inlineStr">
         <is>
           <t>한 계정 = 단일 백엔드(AWS RDS) → 디바이스 간 데이터 자동 동기화. AWS API Gateway WebSocket으로 1~2초 내 반영. 멀티탭/멀티디바이스 동시 사용 가정</t>
         </is>
       </c>
-      <c r="F93" s="3" t="inlineStr">
+      <c r="F126" s="3" t="inlineStr">
         <is>
           <t>Must</t>
         </is>
       </c>
-      <c r="G93" s="3" t="inlineStr">
+      <c r="G126" s="3" t="inlineStr">
         <is>
           <t>AWS API Gateway WebSocket
 sync delta API</t>
         </is>
       </c>
-      <c r="H93" s="3" t="inlineStr">
+      <c r="H126" s="3" t="inlineStr">
         <is>
           <t>MVP</t>
         </is>
       </c>
-      <c r="I93" s="3" t="inlineStr">
+      <c r="I126" s="3" t="inlineStr">
         <is>
           <t>기획완료</t>
         </is>
       </c>
-      <c r="J93" s="3" t="inlineStr">
+      <c r="J126" s="3" t="inlineStr">
         <is>
           <t>결정: AWS API Gateway WebSocket 채택 (단순·비용 효율). 끊김 시 5s polling 폴백. last-write-wins. CRDT는 v2 백로그</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="3" t="inlineStr"/>
-      <c r="B94" s="3" t="inlineStr"/>
-      <c r="C94" s="3" t="inlineStr"/>
-      <c r="D94" s="3" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="3" t="inlineStr"/>
+      <c r="B127" s="3" t="inlineStr"/>
+      <c r="C127" s="3" t="inlineStr"/>
+      <c r="D127" s="3" t="inlineStr">
         <is>
           <t>입력</t>
         </is>
       </c>
-      <c r="E94" s="3" t="inlineStr">
+      <c r="E127" s="3" t="inlineStr">
         <is>
           <t>(자동) 사용자 인증 + 활성 세션</t>
         </is>
       </c>
-      <c r="F94" s="3" t="inlineStr"/>
-      <c r="G94" s="3" t="inlineStr"/>
-      <c r="H94" s="3" t="inlineStr"/>
-      <c r="I94" s="3" t="inlineStr"/>
-      <c r="J94" s="3" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="3" t="inlineStr"/>
-      <c r="B95" s="3" t="inlineStr"/>
-      <c r="C95" s="3" t="inlineStr"/>
-      <c r="D95" s="3" t="inlineStr">
+      <c r="F127" s="3" t="inlineStr"/>
+      <c r="G127" s="3" t="inlineStr"/>
+      <c r="H127" s="3" t="inlineStr"/>
+      <c r="I127" s="3" t="inlineStr"/>
+      <c r="J127" s="3" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="3" t="inlineStr"/>
+      <c r="B128" s="3" t="inlineStr"/>
+      <c r="C128" s="3" t="inlineStr"/>
+      <c r="D128" s="3" t="inlineStr">
         <is>
           <t>출력</t>
         </is>
       </c>
-      <c r="E95" s="3" t="inlineStr">
+      <c r="E128" s="3" t="inlineStr">
         <is>
           <t>- 각 디바이스가 links/folders/folder_members 변경 이벤트 구독
 - 변경 발생 → 모든 활성 디바이스에 publish → UI에 fade 애니메이션</t>
         </is>
       </c>
-      <c r="F95" s="3" t="inlineStr"/>
-      <c r="G95" s="3" t="inlineStr"/>
-      <c r="H95" s="3" t="inlineStr"/>
-      <c r="I95" s="3" t="inlineStr"/>
-      <c r="J95" s="3" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="3" t="inlineStr"/>
-      <c r="B96" s="3" t="inlineStr"/>
-      <c r="C96" s="3" t="inlineStr"/>
-      <c r="D96" s="3" t="inlineStr">
+      <c r="F128" s="3" t="inlineStr"/>
+      <c r="G128" s="3" t="inlineStr"/>
+      <c r="H128" s="3" t="inlineStr"/>
+      <c r="I128" s="3" t="inlineStr"/>
+      <c r="J128" s="3" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="3" t="inlineStr"/>
+      <c r="B129" s="3" t="inlineStr"/>
+      <c r="C129" s="3" t="inlineStr"/>
+      <c r="D129" s="3" t="inlineStr">
         <is>
           <t>정책</t>
         </is>
       </c>
-      <c r="E96" s="3" t="inlineStr">
+      <c r="E129" s="3" t="inlineStr">
         <is>
           <t>[기본] AWS API Gateway WebSocket (재연결 시 backoff 1s,2s,4s,8s,30s)
 [폴백] 1차 5s polling, 2차 60s polling
@@ -4606,22 +5642,22 @@
 [동시 편집] 같은 필드 동시 편집 시 토스트 알림</t>
         </is>
       </c>
-      <c r="F96" s="3" t="inlineStr"/>
-      <c r="G96" s="3" t="inlineStr"/>
-      <c r="H96" s="3" t="inlineStr"/>
-      <c r="I96" s="3" t="inlineStr"/>
-      <c r="J96" s="3" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="3" t="inlineStr"/>
-      <c r="B97" s="3" t="inlineStr"/>
-      <c r="C97" s="3" t="inlineStr"/>
-      <c r="D97" s="3" t="inlineStr">
+      <c r="F129" s="3" t="inlineStr"/>
+      <c r="G129" s="3" t="inlineStr"/>
+      <c r="H129" s="3" t="inlineStr"/>
+      <c r="I129" s="3" t="inlineStr"/>
+      <c r="J129" s="3" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="3" t="inlineStr"/>
+      <c r="B130" s="3" t="inlineStr"/>
+      <c r="C130" s="3" t="inlineStr"/>
+      <c r="D130" s="3" t="inlineStr">
         <is>
           <t>예외</t>
         </is>
       </c>
-      <c r="E97" s="3" t="inlineStr">
+      <c r="E130" s="3" t="inlineStr">
         <is>
           <t>- WebSocket 끊김: 자동 재연결 + 마지막 sync timestamp 이후 변경분 일괄 fetch
 - 디바이스 시계 어긋남: 서버 timestamp만 사용
@@ -4629,14 +5665,14 @@
 - 데이터 초기화(SETTINGS-004): 모든 디바이스에서 즉시 빈 상태</t>
         </is>
       </c>
-      <c r="F97" s="3" t="inlineStr"/>
-      <c r="G97" s="3" t="inlineStr"/>
-      <c r="H97" s="3" t="inlineStr"/>
-      <c r="I97" s="3" t="inlineStr"/>
-      <c r="J97" s="3" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="3" t="inlineStr">
+      <c r="F130" s="3" t="inlineStr"/>
+      <c r="G130" s="3" t="inlineStr"/>
+      <c r="H130" s="3" t="inlineStr"/>
+      <c r="I130" s="3" t="inlineStr"/>
+      <c r="J130" s="3" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="3" t="inlineStr">
         <is>
           <t>IMPORT-001
 #SETTINGS-IMPORT
@@ -4645,103 +5681,103 @@
 #IMPORT-PROGRESS</t>
         </is>
       </c>
-      <c r="B98" s="3" t="inlineStr">
+      <c r="B131" s="3" t="inlineStr">
         <is>
           <t>플랫폼</t>
         </is>
       </c>
-      <c r="C98" s="3" t="inlineStr">
+      <c r="C131" s="3" t="inlineStr">
         <is>
           <t>크롬 즐겨찾기 가져오기 (웹 전용)</t>
         </is>
       </c>
-      <c r="D98" s="3" t="inlineStr">
+      <c r="D131" s="3" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="E98" s="3" t="inlineStr">
+      <c r="E131" s="3" t="inlineStr">
         <is>
           <t>크롬 북마크 관리자 → 내보내기 → bookmarks.html 파일 업로드. 파싱 후 폴더 구조와 함께 미리보기 → 사용자가 폴더 선택/제외 → 일괄 INSERT + AI 요약 SQS 큐잉</t>
         </is>
       </c>
-      <c r="F98" s="3" t="inlineStr">
+      <c r="F131" s="3" t="inlineStr">
         <is>
           <t>Should</t>
         </is>
       </c>
-      <c r="G98" s="3" t="inlineStr">
+      <c r="G131" s="3" t="inlineStr">
         <is>
           <t>북마크 import API (배치)
 AI 요약 큐 publish</t>
         </is>
       </c>
-      <c r="H98" s="3" t="inlineStr">
+      <c r="H131" s="3" t="inlineStr">
         <is>
           <t>일부포함</t>
         </is>
       </c>
-      <c r="I98" s="3" t="inlineStr">
+      <c r="I131" s="3" t="inlineStr">
         <is>
           <t>기획완료</t>
         </is>
       </c>
-      <c r="J98" s="3" t="inlineStr">
+      <c r="J131" s="3" t="inlineStr">
         <is>
           <t>결정: MVP는 비용 동의 모달 미표시 (mock·API키만 가정, 사용자가 본인 API 키 사용 시 본인 부담). 외부 세션 도입(v1.x) 시 모달 추가</t>
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="3" t="inlineStr"/>
-      <c r="B99" s="3" t="inlineStr"/>
-      <c r="C99" s="3" t="inlineStr"/>
-      <c r="D99" s="3" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="3" t="inlineStr"/>
+      <c r="B132" s="3" t="inlineStr"/>
+      <c r="C132" s="3" t="inlineStr"/>
+      <c r="D132" s="3" t="inlineStr">
         <is>
           <t>플로우</t>
         </is>
       </c>
-      <c r="E99" s="3" t="inlineStr">
+      <c r="E132" s="3" t="inlineStr">
         <is>
           <t>(1) 안내(크롬 메뉴 → 북마크 관리자 → ⋮ → 북마크 내보내기) → (2) bookmarks.html 업로드 → (3) 파싱 + 미리보기(폴더 트리 + 링크 카운트) → (4) 폴더 선택/제외 → (5) "가져오기" → (6) 진행률 + 백그라운드 AI 요약</t>
         </is>
       </c>
-      <c r="F99" s="3" t="inlineStr"/>
-      <c r="G99" s="3" t="inlineStr"/>
-      <c r="H99" s="3" t="inlineStr"/>
-      <c r="I99" s="3" t="inlineStr"/>
-      <c r="J99" s="3" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="3" t="inlineStr"/>
-      <c r="B100" s="3" t="inlineStr"/>
-      <c r="C100" s="3" t="inlineStr"/>
-      <c r="D100" s="3" t="inlineStr">
+      <c r="F132" s="3" t="inlineStr"/>
+      <c r="G132" s="3" t="inlineStr"/>
+      <c r="H132" s="3" t="inlineStr"/>
+      <c r="I132" s="3" t="inlineStr"/>
+      <c r="J132" s="3" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="3" t="inlineStr"/>
+      <c r="B133" s="3" t="inlineStr"/>
+      <c r="C133" s="3" t="inlineStr"/>
+      <c r="D133" s="3" t="inlineStr">
         <is>
           <t>입력</t>
         </is>
       </c>
-      <c r="E100" s="3" t="inlineStr">
+      <c r="E133" s="3" t="inlineStr">
         <is>
           <t>- bookmarks.html (≤5MB, Netscape Bookmark Format)</t>
         </is>
       </c>
-      <c r="F100" s="3" t="inlineStr"/>
-      <c r="G100" s="3" t="inlineStr"/>
-      <c r="H100" s="3" t="inlineStr"/>
-      <c r="I100" s="3" t="inlineStr"/>
-      <c r="J100" s="3" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="3" t="inlineStr"/>
-      <c r="B101" s="3" t="inlineStr"/>
-      <c r="C101" s="3" t="inlineStr"/>
-      <c r="D101" s="3" t="inlineStr">
+      <c r="F133" s="3" t="inlineStr"/>
+      <c r="G133" s="3" t="inlineStr"/>
+      <c r="H133" s="3" t="inlineStr"/>
+      <c r="I133" s="3" t="inlineStr"/>
+      <c r="J133" s="3" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="3" t="inlineStr"/>
+      <c r="B134" s="3" t="inlineStr"/>
+      <c r="C134" s="3" t="inlineStr"/>
+      <c r="D134" s="3" t="inlineStr">
         <is>
           <t>출력</t>
         </is>
       </c>
-      <c r="E101" s="3" t="inlineStr">
+      <c r="E134" s="3" t="inlineStr">
         <is>
           <t>- 폴더 N개 INSERT
 - 링크 M개 INSERT
@@ -4749,22 +5785,22 @@
 - "N개 가져왔어요. AI 요약은 백그라운드에서 진행 중이에요"</t>
         </is>
       </c>
-      <c r="F101" s="3" t="inlineStr"/>
-      <c r="G101" s="3" t="inlineStr"/>
-      <c r="H101" s="3" t="inlineStr"/>
-      <c r="I101" s="3" t="inlineStr"/>
-      <c r="J101" s="3" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="3" t="inlineStr"/>
-      <c r="B102" s="3" t="inlineStr"/>
-      <c r="C102" s="3" t="inlineStr"/>
-      <c r="D102" s="3" t="inlineStr">
+      <c r="F134" s="3" t="inlineStr"/>
+      <c r="G134" s="3" t="inlineStr"/>
+      <c r="H134" s="3" t="inlineStr"/>
+      <c r="I134" s="3" t="inlineStr"/>
+      <c r="J134" s="3" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="3" t="inlineStr"/>
+      <c r="B135" s="3" t="inlineStr"/>
+      <c r="C135" s="3" t="inlineStr"/>
+      <c r="D135" s="3" t="inlineStr">
         <is>
           <t>정책</t>
         </is>
       </c>
-      <c r="E102" s="3" t="inlineStr">
+      <c r="E135" s="3" t="inlineStr">
         <is>
           <t>[차별 인터랙션] 데스크톱 웹 전용 (모바일은 안내만)
 [중복 처리] 기본=스킵, 옵션=덮어쓰기
@@ -4772,22 +5808,22 @@
 [한도] 폴더 100개·링크 10000개 한도 사전 검증, 초과 시 일부 선택 강제</t>
         </is>
       </c>
-      <c r="F102" s="3" t="inlineStr"/>
-      <c r="G102" s="3" t="inlineStr"/>
-      <c r="H102" s="3" t="inlineStr"/>
-      <c r="I102" s="3" t="inlineStr"/>
-      <c r="J102" s="3" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="3" t="inlineStr"/>
-      <c r="B103" s="3" t="inlineStr"/>
-      <c r="C103" s="3" t="inlineStr"/>
-      <c r="D103" s="3" t="inlineStr">
+      <c r="F135" s="3" t="inlineStr"/>
+      <c r="G135" s="3" t="inlineStr"/>
+      <c r="H135" s="3" t="inlineStr"/>
+      <c r="I135" s="3" t="inlineStr"/>
+      <c r="J135" s="3" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="3" t="inlineStr"/>
+      <c r="B136" s="3" t="inlineStr"/>
+      <c r="C136" s="3" t="inlineStr"/>
+      <c r="D136" s="3" t="inlineStr">
         <is>
           <t>예외</t>
         </is>
       </c>
-      <c r="E103" s="3" t="inlineStr">
+      <c r="E136" s="3" t="inlineStr">
         <is>
           <t>- 형식 오류: '크롬 즐겨찾기 HTML 파일만 가능해요'
 - 5MB 초과: '파일이 너무 커요. 5MB 이하로 잘라서 다시 시도해주세요'
@@ -4796,897 +5832,6 @@
 - 모바일 진입: '데스크톱 웹에서 사용 가능한 기능이에요'</t>
         </is>
       </c>
-      <c r="F103" s="3" t="inlineStr"/>
-      <c r="G103" s="3" t="inlineStr"/>
-      <c r="H103" s="3" t="inlineStr"/>
-      <c r="I103" s="3" t="inlineStr"/>
-      <c r="J103" s="3" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="4" t="inlineStr">
-        <is>
-          <t>IMPORT-002</t>
-        </is>
-      </c>
-      <c r="B104" s="4" t="inlineStr">
-        <is>
-          <t>플랫폼</t>
-        </is>
-      </c>
-      <c r="C104" s="4" t="inlineStr">
-        <is>
-          <t>Pocket/Raindrop import</t>
-        </is>
-      </c>
-      <c r="D104" s="4" t="inlineStr">
-        <is>
-          <t>설명</t>
-        </is>
-      </c>
-      <c r="E104" s="4" t="inlineStr">
-        <is>
-          <t>Pocket·Raindrop·Goodlinks 등 export 파일 import</t>
-        </is>
-      </c>
-      <c r="F104" s="4" t="inlineStr">
-        <is>
-          <t>Could</t>
-        </is>
-      </c>
-      <c r="G104" s="4" t="inlineStr"/>
-      <c r="H104" s="4" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="I104" s="4" t="inlineStr">
-        <is>
-          <t>기획중</t>
-        </is>
-      </c>
-      <c r="J104" s="4" t="inlineStr">
-        <is>
-          <t>v1.x 추가 예정</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="3" t="inlineStr">
-        <is>
-          <t>SHARE-001
-#FOLDER-DETAIL
-#SHARE-INVITE</t>
-        </is>
-      </c>
-      <c r="B108" s="3" t="inlineStr">
-        <is>
-          <t>공유 폴더</t>
-        </is>
-      </c>
-      <c r="C108" s="3" t="inlineStr">
-        <is>
-          <t>공유 폴더 만들기</t>
-        </is>
-      </c>
-      <c r="D108" s="3" t="inlineStr">
-        <is>
-          <t>설명</t>
-        </is>
-      </c>
-      <c r="E108" s="3" t="inlineStr">
-        <is>
-          <t>폴더의 shared 플래그를 true로 전환 → folder_invites에 토큰 INSERT → OS 공유 시트로 링크 발송</t>
-        </is>
-      </c>
-      <c r="F108" s="3" t="inlineStr">
-        <is>
-          <t>Should</t>
-        </is>
-      </c>
-      <c r="G108" s="3" t="inlineStr">
-        <is>
-          <t>초대 토큰 생성 API</t>
-        </is>
-      </c>
-      <c r="H108" s="3" t="inlineStr">
-        <is>
-          <t>일부포함</t>
-        </is>
-      </c>
-      <c r="I108" s="3" t="inlineStr">
-        <is>
-          <t>기획완료</t>
-        </is>
-      </c>
-      <c r="J108" s="3" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="3" t="inlineStr"/>
-      <c r="B109" s="3" t="inlineStr"/>
-      <c r="C109" s="3" t="inlineStr"/>
-      <c r="D109" s="3" t="inlineStr">
-        <is>
-          <t>입력</t>
-        </is>
-      </c>
-      <c r="E109" s="3" t="inlineStr">
-        <is>
-          <t>folder_id (오너만)</t>
-        </is>
-      </c>
-      <c r="F109" s="3" t="inlineStr"/>
-      <c r="G109" s="3" t="inlineStr"/>
-      <c r="H109" s="3" t="inlineStr"/>
-      <c r="I109" s="3" t="inlineStr"/>
-      <c r="J109" s="3" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="3" t="inlineStr"/>
-      <c r="B110" s="3" t="inlineStr"/>
-      <c r="C110" s="3" t="inlineStr"/>
-      <c r="D110" s="3" t="inlineStr">
-        <is>
-          <t>출력</t>
-        </is>
-      </c>
-      <c r="E110" s="3" t="inlineStr">
-        <is>
-          <t>folders.shared=true / folder_invites INSERT / 공유 URL 생성 (https://qlink.app/invite/{token})</t>
-        </is>
-      </c>
-      <c r="F110" s="3" t="inlineStr"/>
-      <c r="G110" s="3" t="inlineStr"/>
-      <c r="H110" s="3" t="inlineStr"/>
-      <c r="I110" s="3" t="inlineStr"/>
-      <c r="J110" s="3" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="3" t="inlineStr"/>
-      <c r="B111" s="3" t="inlineStr"/>
-      <c r="C111" s="3" t="inlineStr"/>
-      <c r="D111" s="3" t="inlineStr">
-        <is>
-          <t>정책</t>
-        </is>
-      </c>
-      <c r="E111" s="3" t="inlineStr">
-        <is>
-          <t>POLICY-SHARED 참고
-[기본값] 토큰 유효 7일
-[권한] 오너만 발급
-[재발급] 새 토큰 발급 시 이전 토큰은 만료 전까지 유효</t>
-        </is>
-      </c>
-      <c r="F111" s="3" t="inlineStr"/>
-      <c r="G111" s="3" t="inlineStr"/>
-      <c r="H111" s="3" t="inlineStr"/>
-      <c r="I111" s="3" t="inlineStr"/>
-      <c r="J111" s="3" t="inlineStr"/>
-    </row>
-    <row r="112">
-      <c r="A112" s="3" t="inlineStr"/>
-      <c r="B112" s="3" t="inlineStr"/>
-      <c r="C112" s="3" t="inlineStr"/>
-      <c r="D112" s="3" t="inlineStr">
-        <is>
-          <t>예외</t>
-        </is>
-      </c>
-      <c r="E112" s="3" t="inlineStr">
-        <is>
-          <t>- 비오너 시도: '오너만 공유할 수 있어요'
-- 미분류 폴더 공유 시도: '미분류 폴더는 공유할 수 없어요'</t>
-        </is>
-      </c>
-      <c r="F112" s="3" t="inlineStr"/>
-      <c r="G112" s="3" t="inlineStr"/>
-      <c r="H112" s="3" t="inlineStr"/>
-      <c r="I112" s="3" t="inlineStr"/>
-      <c r="J112" s="3" t="inlineStr"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="3" t="inlineStr">
-        <is>
-          <t>SHARE-002
-#SHARE-ACCEPT</t>
-        </is>
-      </c>
-      <c r="B113" s="3" t="inlineStr">
-        <is>
-          <t>공유 폴더</t>
-        </is>
-      </c>
-      <c r="C113" s="3" t="inlineStr">
-        <is>
-          <t>공유 폴더 초대 수락</t>
-        </is>
-      </c>
-      <c r="D113" s="3" t="inlineStr">
-        <is>
-          <t>설명</t>
-        </is>
-      </c>
-      <c r="E113" s="3" t="inlineStr">
-        <is>
-          <t>초대 링크 클릭 → 토큰 검증 → 사용자가 "참여" 클릭 → folder_members INSERT</t>
-        </is>
-      </c>
-      <c r="F113" s="3" t="inlineStr">
-        <is>
-          <t>Should</t>
-        </is>
-      </c>
-      <c r="G113" s="3" t="inlineStr">
-        <is>
-          <t>accept_folder_invite RPC</t>
-        </is>
-      </c>
-      <c r="H113" s="3" t="inlineStr">
-        <is>
-          <t>일부포함</t>
-        </is>
-      </c>
-      <c r="I113" s="3" t="inlineStr">
-        <is>
-          <t>기획완료</t>
-        </is>
-      </c>
-      <c r="J113" s="3" t="inlineStr"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="3" t="inlineStr"/>
-      <c r="B114" s="3" t="inlineStr"/>
-      <c r="C114" s="3" t="inlineStr"/>
-      <c r="D114" s="3" t="inlineStr">
-        <is>
-          <t>입력</t>
-        </is>
-      </c>
-      <c r="E114" s="3" t="inlineStr">
-        <is>
-          <t>invite_token (URL 파라미터)</t>
-        </is>
-      </c>
-      <c r="F114" s="3" t="inlineStr"/>
-      <c r="G114" s="3" t="inlineStr"/>
-      <c r="H114" s="3" t="inlineStr"/>
-      <c r="I114" s="3" t="inlineStr"/>
-      <c r="J114" s="3" t="inlineStr"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="3" t="inlineStr"/>
-      <c r="B115" s="3" t="inlineStr"/>
-      <c r="C115" s="3" t="inlineStr"/>
-      <c r="D115" s="3" t="inlineStr">
-        <is>
-          <t>출력</t>
-        </is>
-      </c>
-      <c r="E115" s="3" t="inlineStr">
-        <is>
-          <t>folder_members INSERT (role='member') / 폴더 진입</t>
-        </is>
-      </c>
-      <c r="F115" s="3" t="inlineStr"/>
-      <c r="G115" s="3" t="inlineStr"/>
-      <c r="H115" s="3" t="inlineStr"/>
-      <c r="I115" s="3" t="inlineStr"/>
-      <c r="J115" s="3" t="inlineStr"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="3" t="inlineStr"/>
-      <c r="B116" s="3" t="inlineStr"/>
-      <c r="C116" s="3" t="inlineStr"/>
-      <c r="D116" s="3" t="inlineStr">
-        <is>
-          <t>정책</t>
-        </is>
-      </c>
-      <c r="E116" s="3" t="inlineStr">
-        <is>
-          <t>POLICY-SHARED 참고
-[처리 순서] 미로그인 시 토큰 임시 보관 → 로그인 후 자동 수락 화면
-[멤버 한도] 50명</t>
-        </is>
-      </c>
-      <c r="F116" s="3" t="inlineStr"/>
-      <c r="G116" s="3" t="inlineStr"/>
-      <c r="H116" s="3" t="inlineStr"/>
-      <c r="I116" s="3" t="inlineStr"/>
-      <c r="J116" s="3" t="inlineStr"/>
-    </row>
-    <row r="117">
-      <c r="A117" s="3" t="inlineStr"/>
-      <c r="B117" s="3" t="inlineStr"/>
-      <c r="C117" s="3" t="inlineStr"/>
-      <c r="D117" s="3" t="inlineStr">
-        <is>
-          <t>예외</t>
-        </is>
-      </c>
-      <c r="E117" s="3" t="inlineStr">
-        <is>
-          <t>- 토큰 만료: '유효하지 않거나 만료된 초대 링크입니다'
-- 이미 멤버: 토스트 + 폴더 이동
-- 본인이 오너: '본인의 폴더예요'
-- 멤버 한도 50명 초과: '이 폴더는 50명까지만 참여할 수 있어요. 오너에게 문의하세요'</t>
-        </is>
-      </c>
-      <c r="F117" s="3" t="inlineStr"/>
-      <c r="G117" s="3" t="inlineStr"/>
-      <c r="H117" s="3" t="inlineStr"/>
-      <c r="I117" s="3" t="inlineStr"/>
-      <c r="J117" s="3" t="inlineStr"/>
-    </row>
-    <row r="118">
-      <c r="A118" s="3" t="inlineStr">
-        <is>
-          <t>SHARE-003
-#FOLDER-MEMBERS</t>
-        </is>
-      </c>
-      <c r="B118" s="3" t="inlineStr">
-        <is>
-          <t>공유 폴더</t>
-        </is>
-      </c>
-      <c r="C118" s="3" t="inlineStr">
-        <is>
-          <t>공유 폴더 멤버 관리</t>
-        </is>
-      </c>
-      <c r="D118" s="3" t="inlineStr">
-        <is>
-          <t>설명</t>
-        </is>
-      </c>
-      <c r="E118" s="3" t="inlineStr">
-        <is>
-          <t>멤버 목록 + 역할 변경(owner만) + 제거(owner) / 나가기(self)</t>
-        </is>
-      </c>
-      <c r="F118" s="3" t="inlineStr">
-        <is>
-          <t>Should</t>
-        </is>
-      </c>
-      <c r="G118" s="3" t="inlineStr">
-        <is>
-          <t>멤버 조회/수정/삭제 API</t>
-        </is>
-      </c>
-      <c r="H118" s="3" t="inlineStr">
-        <is>
-          <t>일부포함</t>
-        </is>
-      </c>
-      <c r="I118" s="3" t="inlineStr">
-        <is>
-          <t>기획중</t>
-        </is>
-      </c>
-      <c r="J118" s="3" t="inlineStr">
-        <is>
-          <t>v1.0 가벼운 형태로</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="3" t="inlineStr">
-        <is>
-          <t>VIEW-001
-#LINK-DETAIL</t>
-        </is>
-      </c>
-      <c r="B119" s="3" t="inlineStr">
-        <is>
-          <t>콘텐츠</t>
-        </is>
-      </c>
-      <c r="C119" s="3" t="inlineStr">
-        <is>
-          <t>YouTube 임베드 미리보기</t>
-        </is>
-      </c>
-      <c r="D119" s="3" t="inlineStr">
-        <is>
-          <t>설명</t>
-        </is>
-      </c>
-      <c r="E119" s="3" t="inlineStr">
-        <is>
-          <t>URL이 youtube.com/youtu.be 도메인이면 상세 화면에서 iframe 임베드. 자동재생 X, 사용자 클릭 시 재생</t>
-        </is>
-      </c>
-      <c r="F119" s="3" t="inlineStr">
-        <is>
-          <t>Should</t>
-        </is>
-      </c>
-      <c r="G119" s="3" t="inlineStr">
-        <is>
-          <t>(클라이언트, iframe)</t>
-        </is>
-      </c>
-      <c r="H119" s="3" t="inlineStr">
-        <is>
-          <t>일부포함</t>
-        </is>
-      </c>
-      <c r="I119" s="3" t="inlineStr">
-        <is>
-          <t>기획중</t>
-        </is>
-      </c>
-      <c r="J119" s="3" t="inlineStr"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="3" t="inlineStr">
-        <is>
-          <t>SETTINGS-001
-#SETTINGS-AI</t>
-        </is>
-      </c>
-      <c r="B120" s="3" t="inlineStr">
-        <is>
-          <t>설정</t>
-        </is>
-      </c>
-      <c r="C120" s="3" t="inlineStr">
-        <is>
-          <t>AI 제공자 선택</t>
-        </is>
-      </c>
-      <c r="D120" s="3" t="inlineStr">
-        <is>
-          <t>설명</t>
-        </is>
-      </c>
-      <c r="E120" s="3" t="inlineStr">
-        <is>
-          <t>6종 중 선택: ChatGPT / Gemini / Claude / Perplexity / 큐링크 기본(mock) / 사용자 API 키. SETTINGS-001 변경은 LINK-004의 provider 입력으로 즉시 반영</t>
-        </is>
-      </c>
-      <c r="F120" s="3" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G120" s="3" t="inlineStr">
-        <is>
-          <t>프로필 업데이트 API</t>
-        </is>
-      </c>
-      <c r="H120" s="3" t="inlineStr">
-        <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="I120" s="3" t="inlineStr">
-        <is>
-          <t>기획완료</t>
-        </is>
-      </c>
-      <c r="J120" s="3" t="inlineStr"/>
-    </row>
-    <row r="121">
-      <c r="A121" s="3" t="inlineStr"/>
-      <c r="B121" s="3" t="inlineStr"/>
-      <c r="C121" s="3" t="inlineStr"/>
-      <c r="D121" s="3" t="inlineStr">
-        <is>
-          <t>입력</t>
-        </is>
-      </c>
-      <c r="E121" s="3" t="inlineStr">
-        <is>
-          <t>provider 식별자</t>
-        </is>
-      </c>
-      <c r="F121" s="3" t="inlineStr"/>
-      <c r="G121" s="3" t="inlineStr"/>
-      <c r="H121" s="3" t="inlineStr"/>
-      <c r="I121" s="3" t="inlineStr"/>
-      <c r="J121" s="3" t="inlineStr"/>
-    </row>
-    <row r="122">
-      <c r="A122" s="3" t="inlineStr"/>
-      <c r="B122" s="3" t="inlineStr"/>
-      <c r="C122" s="3" t="inlineStr"/>
-      <c r="D122" s="3" t="inlineStr">
-        <is>
-          <t>출력</t>
-        </is>
-      </c>
-      <c r="E122" s="3" t="inlineStr">
-        <is>
-          <t>profiles.ai_provider UPDATE + 토스트</t>
-        </is>
-      </c>
-      <c r="F122" s="3" t="inlineStr"/>
-      <c r="G122" s="3" t="inlineStr"/>
-      <c r="H122" s="3" t="inlineStr"/>
-      <c r="I122" s="3" t="inlineStr"/>
-      <c r="J122" s="3" t="inlineStr"/>
-    </row>
-    <row r="123">
-      <c r="A123" s="3" t="inlineStr"/>
-      <c r="B123" s="3" t="inlineStr"/>
-      <c r="C123" s="3" t="inlineStr"/>
-      <c r="D123" s="3" t="inlineStr">
-        <is>
-          <t>정책</t>
-        </is>
-      </c>
-      <c r="E123" s="3" t="inlineStr">
-        <is>
-          <t>[기본값] 'mock' (앱 진입 시)
-[동기화] 모든 디바이스에 SYNC-001로 반영
-[API 키] 사용자 API 키 선택 시 키 입력 화면 추가 노출, 서버 KMS 암호화 저장</t>
-        </is>
-      </c>
-      <c r="F123" s="3" t="inlineStr"/>
-      <c r="G123" s="3" t="inlineStr"/>
-      <c r="H123" s="3" t="inlineStr"/>
-      <c r="I123" s="3" t="inlineStr"/>
-      <c r="J123" s="3" t="inlineStr"/>
-    </row>
-    <row r="124">
-      <c r="A124" s="3" t="inlineStr"/>
-      <c r="B124" s="3" t="inlineStr"/>
-      <c r="C124" s="3" t="inlineStr"/>
-      <c r="D124" s="3" t="inlineStr">
-        <is>
-          <t>예외</t>
-        </is>
-      </c>
-      <c r="E124" s="3" t="inlineStr">
-        <is>
-          <t>- 외부 세션 provider 선택했지만 Chrome 확장 미설치: '확장 프로그램 설치가 필요해요' + 안내 링크
-- API 키 무효: 다음 호출 시 '키를 확인해주세요' 안내</t>
-        </is>
-      </c>
-      <c r="F124" s="3" t="inlineStr"/>
-      <c r="G124" s="3" t="inlineStr"/>
-      <c r="H124" s="3" t="inlineStr"/>
-      <c r="I124" s="3" t="inlineStr"/>
-      <c r="J124" s="3" t="inlineStr"/>
-    </row>
-    <row r="125">
-      <c r="A125" s="3" t="inlineStr">
-        <is>
-          <t>SETTINGS-002
-#SETTINGS-PROFILE</t>
-        </is>
-      </c>
-      <c r="B125" s="3" t="inlineStr">
-        <is>
-          <t>설정</t>
-        </is>
-      </c>
-      <c r="C125" s="3" t="inlineStr">
-        <is>
-          <t>프로필 변경</t>
-        </is>
-      </c>
-      <c r="D125" s="3" t="inlineStr">
-        <is>
-          <t>설명</t>
-        </is>
-      </c>
-      <c r="E125" s="3" t="inlineStr">
-        <is>
-          <t>닉네임·아바타 이모지 변경</t>
-        </is>
-      </c>
-      <c r="F125" s="3" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G125" s="3" t="inlineStr">
-        <is>
-          <t>프로필 업데이트 API</t>
-        </is>
-      </c>
-      <c r="H125" s="3" t="inlineStr">
-        <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="I125" s="3" t="inlineStr">
-        <is>
-          <t>기획완료</t>
-        </is>
-      </c>
-      <c r="J125" s="3" t="inlineStr"/>
-    </row>
-    <row r="126">
-      <c r="A126" s="3" t="inlineStr"/>
-      <c r="B126" s="3" t="inlineStr"/>
-      <c r="C126" s="3" t="inlineStr"/>
-      <c r="D126" s="3" t="inlineStr">
-        <is>
-          <t>입력</t>
-        </is>
-      </c>
-      <c r="E126" s="3" t="inlineStr">
-        <is>
-          <t>display_name (1~20자), avatar (이모지 단일 문자)</t>
-        </is>
-      </c>
-      <c r="F126" s="3" t="inlineStr"/>
-      <c r="G126" s="3" t="inlineStr"/>
-      <c r="H126" s="3" t="inlineStr"/>
-      <c r="I126" s="3" t="inlineStr"/>
-      <c r="J126" s="3" t="inlineStr"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="3" t="inlineStr"/>
-      <c r="B127" s="3" t="inlineStr"/>
-      <c r="C127" s="3" t="inlineStr"/>
-      <c r="D127" s="3" t="inlineStr">
-        <is>
-          <t>출력</t>
-        </is>
-      </c>
-      <c r="E127" s="3" t="inlineStr">
-        <is>
-          <t>profiles UPDATE + 헤더 즉시 반영</t>
-        </is>
-      </c>
-      <c r="F127" s="3" t="inlineStr"/>
-      <c r="G127" s="3" t="inlineStr"/>
-      <c r="H127" s="3" t="inlineStr"/>
-      <c r="I127" s="3" t="inlineStr"/>
-      <c r="J127" s="3" t="inlineStr"/>
-    </row>
-    <row r="128">
-      <c r="A128" s="3" t="inlineStr"/>
-      <c r="B128" s="3" t="inlineStr"/>
-      <c r="C128" s="3" t="inlineStr"/>
-      <c r="D128" s="3" t="inlineStr">
-        <is>
-          <t>정책</t>
-        </is>
-      </c>
-      <c r="E128" s="3" t="inlineStr">
-        <is>
-          <t>[동기화] 즉시 모든 디바이스 반영</t>
-        </is>
-      </c>
-      <c r="F128" s="3" t="inlineStr"/>
-      <c r="G128" s="3" t="inlineStr"/>
-      <c r="H128" s="3" t="inlineStr"/>
-      <c r="I128" s="3" t="inlineStr"/>
-      <c r="J128" s="3" t="inlineStr"/>
-    </row>
-    <row r="129">
-      <c r="A129" s="3" t="inlineStr"/>
-      <c r="B129" s="3" t="inlineStr"/>
-      <c r="C129" s="3" t="inlineStr"/>
-      <c r="D129" s="3" t="inlineStr">
-        <is>
-          <t>예외</t>
-        </is>
-      </c>
-      <c r="E129" s="3" t="inlineStr">
-        <is>
-          <t>- 빈 닉네임: '닉네임을 입력해주세요'
-- 20자 초과: 입력 차단</t>
-        </is>
-      </c>
-      <c r="F129" s="3" t="inlineStr"/>
-      <c r="G129" s="3" t="inlineStr"/>
-      <c r="H129" s="3" t="inlineStr"/>
-      <c r="I129" s="3" t="inlineStr"/>
-      <c r="J129" s="3" t="inlineStr"/>
-    </row>
-    <row r="130">
-      <c r="A130" s="3" t="inlineStr">
-        <is>
-          <t>SETTINGS-003
-#SETTINGS-PASSWORD</t>
-        </is>
-      </c>
-      <c r="B130" s="3" t="inlineStr">
-        <is>
-          <t>설정</t>
-        </is>
-      </c>
-      <c r="C130" s="3" t="inlineStr">
-        <is>
-          <t>비밀번호 변경</t>
-        </is>
-      </c>
-      <c r="D130" s="3" t="inlineStr">
-        <is>
-          <t>설명</t>
-        </is>
-      </c>
-      <c r="E130" s="3" t="inlineStr">
-        <is>
-          <t>현재 비밀번호 검증 → 새 비밀번호 변경. 변경 후 다른 디바이스는 강제 로그아웃 (보안 우선)</t>
-        </is>
-      </c>
-      <c r="F130" s="3" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G130" s="3" t="inlineStr">
-        <is>
-          <t>비밀번호 변경 API
-리프레시 토큰 무효화 API</t>
-        </is>
-      </c>
-      <c r="H130" s="3" t="inlineStr">
-        <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="I130" s="3" t="inlineStr">
-        <is>
-          <t>기획완료</t>
-        </is>
-      </c>
-      <c r="J130" s="3" t="inlineStr">
-        <is>
-          <t>결정: 변경 시 다른 디바이스 강제 로그아웃 + 화면 안내 문구 추가</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="3" t="inlineStr"/>
-      <c r="B131" s="3" t="inlineStr"/>
-      <c r="C131" s="3" t="inlineStr"/>
-      <c r="D131" s="3" t="inlineStr">
-        <is>
-          <t>입력</t>
-        </is>
-      </c>
-      <c r="E131" s="3" t="inlineStr">
-        <is>
-          <t>current_password, new_password (8~64자, 영문+숫자)</t>
-        </is>
-      </c>
-      <c r="F131" s="3" t="inlineStr"/>
-      <c r="G131" s="3" t="inlineStr"/>
-      <c r="H131" s="3" t="inlineStr"/>
-      <c r="I131" s="3" t="inlineStr"/>
-      <c r="J131" s="3" t="inlineStr"/>
-    </row>
-    <row r="132">
-      <c r="A132" s="3" t="inlineStr"/>
-      <c r="B132" s="3" t="inlineStr"/>
-      <c r="C132" s="3" t="inlineStr"/>
-      <c r="D132" s="3" t="inlineStr">
-        <is>
-          <t>출력</t>
-        </is>
-      </c>
-      <c r="E132" s="3" t="inlineStr">
-        <is>
-          <t>비밀번호 변경 + 모든 다른 디바이스 리프레시 토큰 invalidate + 토스트 "변경됐어요. 다른 기기에서는 다시 로그인해주세요"</t>
-        </is>
-      </c>
-      <c r="F132" s="3" t="inlineStr"/>
-      <c r="G132" s="3" t="inlineStr"/>
-      <c r="H132" s="3" t="inlineStr"/>
-      <c r="I132" s="3" t="inlineStr"/>
-      <c r="J132" s="3" t="inlineStr"/>
-    </row>
-    <row r="133">
-      <c r="A133" s="3" t="inlineStr"/>
-      <c r="B133" s="3" t="inlineStr"/>
-      <c r="C133" s="3" t="inlineStr"/>
-      <c r="D133" s="3" t="inlineStr">
-        <is>
-          <t>정책</t>
-        </is>
-      </c>
-      <c r="E133" s="3" t="inlineStr">
-        <is>
-          <t>[보안] 현재 비밀번호 검증 필수
-[강제 로그아웃] 변경 즉시 서버에서 모든 다른 활성 리프레시 토큰 invalidate
-[화면 안내] 비밀번호 변경 화면 상단에 안내 카피: "비밀번호를 바꾸면 로그인된 다른 기기들에서 자동으로 로그아웃돼요. 보안을 위한 조치예요."</t>
-        </is>
-      </c>
-      <c r="F133" s="3" t="inlineStr"/>
-      <c r="G133" s="3" t="inlineStr"/>
-      <c r="H133" s="3" t="inlineStr"/>
-      <c r="I133" s="3" t="inlineStr"/>
-      <c r="J133" s="3" t="inlineStr"/>
-    </row>
-    <row r="134">
-      <c r="A134" s="3" t="inlineStr"/>
-      <c r="B134" s="3" t="inlineStr"/>
-      <c r="C134" s="3" t="inlineStr"/>
-      <c r="D134" s="3" t="inlineStr">
-        <is>
-          <t>예외</t>
-        </is>
-      </c>
-      <c r="E134" s="3" t="inlineStr">
-        <is>
-          <t>- 현재 PW 불일치: '현재 비밀번호가 일치하지 않아요'
-- 새 PW 정책 미충족: 안내
-- 5회 실패: 잠시 차단</t>
-        </is>
-      </c>
-      <c r="F134" s="3" t="inlineStr"/>
-      <c r="G134" s="3" t="inlineStr"/>
-      <c r="H134" s="3" t="inlineStr"/>
-      <c r="I134" s="3" t="inlineStr"/>
-      <c r="J134" s="3" t="inlineStr"/>
-    </row>
-    <row r="135">
-      <c r="A135" s="3" t="inlineStr">
-        <is>
-          <t>SETTINGS-004
-#SETTINGS-RESET</t>
-        </is>
-      </c>
-      <c r="B135" s="3" t="inlineStr">
-        <is>
-          <t>설정</t>
-        </is>
-      </c>
-      <c r="C135" s="3" t="inlineStr">
-        <is>
-          <t>데이터 초기화</t>
-        </is>
-      </c>
-      <c r="D135" s="3" t="inlineStr">
-        <is>
-          <t>설명</t>
-        </is>
-      </c>
-      <c r="E135" s="3" t="inlineStr">
-        <is>
-          <t>본인 데이터(폴더·링크·공유 멤버십) 전체 영구 삭제. 이중 확인 모달. 모든 디바이스에서 즉시 빈 상태</t>
-        </is>
-      </c>
-      <c r="F135" s="3" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G135" s="3" t="inlineStr">
-        <is>
-          <t>데이터 일괄 삭제 API (트랜잭션)</t>
-        </is>
-      </c>
-      <c r="H135" s="3" t="inlineStr">
-        <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="I135" s="3" t="inlineStr">
-        <is>
-          <t>기획완료</t>
-        </is>
-      </c>
-      <c r="J135" s="3" t="inlineStr">
-        <is>
-          <t>결정: 즉시 hard delete (개인정보보호법 OK, 사용자 의도 그대로 존중)</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="3" t="inlineStr"/>
-      <c r="B136" s="3" t="inlineStr"/>
-      <c r="C136" s="3" t="inlineStr"/>
-      <c r="D136" s="3" t="inlineStr">
-        <is>
-          <t>입력</t>
-        </is>
-      </c>
-      <c r="E136" s="3" t="inlineStr">
-        <is>
-          <t>"초기화" 버튼 → 모달 1 → "정말 삭제" → 모달 2 → 사용자 비밀번호 재입력</t>
-        </is>
-      </c>
       <c r="F136" s="3" t="inlineStr"/>
       <c r="G136" s="3" t="inlineStr"/>
       <c r="H136" s="3" t="inlineStr"/>
@@ -5694,140 +5839,101 @@
       <c r="J136" s="3" t="inlineStr"/>
     </row>
     <row r="137">
-      <c r="A137" s="3" t="inlineStr"/>
-      <c r="B137" s="3" t="inlineStr"/>
-      <c r="C137" s="3" t="inlineStr"/>
-      <c r="D137" s="3" t="inlineStr">
-        <is>
-          <t>출력</t>
-        </is>
-      </c>
-      <c r="E137" s="3" t="inlineStr">
-        <is>
-          <t>DELETE folders/links/folder_members(self) + 모든 디바이스 SYNC</t>
-        </is>
-      </c>
-      <c r="F137" s="3" t="inlineStr"/>
-      <c r="G137" s="3" t="inlineStr"/>
-      <c r="H137" s="3" t="inlineStr"/>
-      <c r="I137" s="3" t="inlineStr"/>
-      <c r="J137" s="3" t="inlineStr"/>
-    </row>
-    <row r="138">
-      <c r="A138" s="3" t="inlineStr"/>
-      <c r="B138" s="3" t="inlineStr"/>
-      <c r="C138" s="3" t="inlineStr"/>
-      <c r="D138" s="3" t="inlineStr">
-        <is>
-          <t>정책</t>
-        </is>
-      </c>
-      <c r="E138" s="3" t="inlineStr">
-        <is>
-          <t>[위험 액션] 이중 확인 + 비밀번호 재입력
-[복구 불가] 즉시 hard delete — DB에서 본인 데이터 영구 삭제, 복구 불가
-[고지] 모달 2에 명시: "삭제하면 복구할 수 없어요. 그래도 진행할까요?"
-[동기화] 즉시 모든 디바이스에서 빈 상태</t>
-        </is>
-      </c>
-      <c r="F138" s="3" t="inlineStr"/>
-      <c r="G138" s="3" t="inlineStr"/>
-      <c r="H138" s="3" t="inlineStr"/>
-      <c r="I138" s="3" t="inlineStr"/>
-      <c r="J138" s="3" t="inlineStr"/>
-    </row>
-    <row r="139">
-      <c r="A139" s="3" t="inlineStr"/>
-      <c r="B139" s="3" t="inlineStr"/>
-      <c r="C139" s="3" t="inlineStr"/>
-      <c r="D139" s="3" t="inlineStr">
-        <is>
-          <t>예외</t>
-        </is>
-      </c>
-      <c r="E139" s="3" t="inlineStr">
-        <is>
-          <t>- 비밀번호 불일치: 모달 안에서 '비밀번호가 일치하지 않아요'
-- 처리 중 네트워크 오류: 트랜잭션으로 서버 측 부분 삭제 방지 (전부 실패하거나 전부 성공)</t>
-        </is>
-      </c>
-      <c r="F139" s="3" t="inlineStr"/>
-      <c r="G139" s="3" t="inlineStr"/>
-      <c r="H139" s="3" t="inlineStr"/>
-      <c r="I139" s="3" t="inlineStr"/>
-      <c r="J139" s="3" t="inlineStr"/>
-    </row>
-    <row r="140">
-      <c r="A140" s="3" t="inlineStr">
-        <is>
-          <t>THEME-001
-#SETTINGS-THEME</t>
-        </is>
-      </c>
-      <c r="B140" s="3" t="inlineStr">
-        <is>
-          <t>설정</t>
-        </is>
-      </c>
-      <c r="C140" s="3" t="inlineStr">
-        <is>
-          <t>다크/라이트 + 강조색</t>
-        </is>
-      </c>
-      <c r="D140" s="3" t="inlineStr">
+      <c r="A137" s="4" t="inlineStr">
+        <is>
+          <t>IMPORT-002</t>
+        </is>
+      </c>
+      <c r="B137" s="4" t="inlineStr">
+        <is>
+          <t>플랫폼</t>
+        </is>
+      </c>
+      <c r="C137" s="4" t="inlineStr">
+        <is>
+          <t>Pocket/Raindrop import</t>
+        </is>
+      </c>
+      <c r="D137" s="4" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="E140" s="3" t="inlineStr">
-        <is>
-          <t>다크/라이트 모드 + 강조색 3종(핑크·블루·그레이). 사용자별 저장. 로그인 화면은 항상 라이트+핑크(브랜드)</t>
-        </is>
-      </c>
-      <c r="F140" s="3" t="inlineStr">
+      <c r="E137" s="4" t="inlineStr">
+        <is>
+          <t>Pocket·Raindrop·Goodlinks 등 export 파일 import</t>
+        </is>
+      </c>
+      <c r="F137" s="4" t="inlineStr">
+        <is>
+          <t>Could</t>
+        </is>
+      </c>
+      <c r="G137" s="4" t="inlineStr"/>
+      <c r="H137" s="4" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="I137" s="4" t="inlineStr">
+        <is>
+          <t>기획중</t>
+        </is>
+      </c>
+      <c r="J137" s="4" t="inlineStr">
+        <is>
+          <t>v1.x 추가 예정</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="3" t="inlineStr">
+        <is>
+          <t>SHARE-001
+#FOLDER-DETAIL
+#SHARE-INVITE</t>
+        </is>
+      </c>
+      <c r="B141" s="3" t="inlineStr">
+        <is>
+          <t>공유 폴더</t>
+        </is>
+      </c>
+      <c r="C141" s="3" t="inlineStr">
+        <is>
+          <t>공유 폴더 만들기</t>
+        </is>
+      </c>
+      <c r="D141" s="3" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+      <c r="E141" s="3" t="inlineStr">
+        <is>
+          <t>폴더의 shared 플래그를 true로 전환 → folder_invites에 토큰 INSERT → OS 공유 시트로 링크 발송</t>
+        </is>
+      </c>
+      <c r="F141" s="3" t="inlineStr">
         <is>
           <t>Should</t>
         </is>
       </c>
-      <c r="G140" s="3" t="inlineStr">
-        <is>
-          <t>프로필 업데이트 API</t>
-        </is>
-      </c>
-      <c r="H140" s="3" t="inlineStr">
+      <c r="G141" s="3" t="inlineStr">
+        <is>
+          <t>초대 토큰 생성 API</t>
+        </is>
+      </c>
+      <c r="H141" s="3" t="inlineStr">
         <is>
           <t>일부포함</t>
         </is>
       </c>
-      <c r="I140" s="3" t="inlineStr">
+      <c r="I141" s="3" t="inlineStr">
         <is>
           <t>기획완료</t>
         </is>
       </c>
-      <c r="J140" s="3" t="inlineStr">
-        <is>
-          <t>결정: 다크/라이트 모드 + 강조색 3종(핑크/블루/그레이)</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="3" t="inlineStr"/>
-      <c r="B141" s="3" t="inlineStr"/>
-      <c r="C141" s="3" t="inlineStr"/>
-      <c r="D141" s="3" t="inlineStr">
-        <is>
-          <t>입력</t>
-        </is>
-      </c>
-      <c r="E141" s="3" t="inlineStr">
-        <is>
-          <t>mode (`light`/`dark`), accent (`pink`/`blue`/`gray`)</t>
-        </is>
-      </c>
-      <c r="F141" s="3" t="inlineStr"/>
-      <c r="G141" s="3" t="inlineStr"/>
-      <c r="H141" s="3" t="inlineStr"/>
-      <c r="I141" s="3" t="inlineStr"/>
       <c r="J141" s="3" t="inlineStr"/>
     </row>
     <row r="142">
@@ -5836,12 +5942,12 @@
       <c r="C142" s="3" t="inlineStr"/>
       <c r="D142" s="3" t="inlineStr">
         <is>
-          <t>출력</t>
+          <t>입력</t>
         </is>
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
-          <t>profiles.theme UPDATE + CSS 변수 즉시 반영 + SYNC</t>
+          <t>folder_id (오너만)</t>
         </is>
       </c>
       <c r="F142" s="3" t="inlineStr"/>
@@ -5856,13 +5962,12 @@
       <c r="C143" s="3" t="inlineStr"/>
       <c r="D143" s="3" t="inlineStr">
         <is>
-          <t>정책</t>
+          <t>출력</t>
         </is>
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>[동기화] SYNC-001로 모든 디바이스 즉시 반영
-[기본값] 신규 가입자 light + pink</t>
+          <t>folders.shared=true / folder_invites INSERT / 공유 URL 생성 (https://qlink.app/invite/{token})</t>
         </is>
       </c>
       <c r="F143" s="3" t="inlineStr"/>
@@ -5872,299 +5977,700 @@
       <c r="J143" s="3" t="inlineStr"/>
     </row>
     <row r="144">
-      <c r="A144" s="4" t="inlineStr">
-        <is>
-          <t>AI-001</t>
-        </is>
-      </c>
-      <c r="B144" s="4" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="C144" s="4" t="inlineStr">
-        <is>
-          <t>Chrome 확장 (외부 AI 세션)</t>
-        </is>
-      </c>
-      <c r="D144" s="4" t="inlineStr">
+      <c r="A144" s="3" t="inlineStr"/>
+      <c r="B144" s="3" t="inlineStr"/>
+      <c r="C144" s="3" t="inlineStr"/>
+      <c r="D144" s="3" t="inlineStr">
+        <is>
+          <t>정책</t>
+        </is>
+      </c>
+      <c r="E144" s="3" t="inlineStr">
+        <is>
+          <t>POLICY-SHARED 참고
+[기본값] 토큰 유효 7일
+[권한] 오너만 발급
+[재발급] 새 토큰 발급 시 이전 토큰은 만료 전까지 유효</t>
+        </is>
+      </c>
+      <c r="F144" s="3" t="inlineStr"/>
+      <c r="G144" s="3" t="inlineStr"/>
+      <c r="H144" s="3" t="inlineStr"/>
+      <c r="I144" s="3" t="inlineStr"/>
+      <c r="J144" s="3" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="3" t="inlineStr"/>
+      <c r="B145" s="3" t="inlineStr"/>
+      <c r="C145" s="3" t="inlineStr"/>
+      <c r="D145" s="3" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="E145" s="3" t="inlineStr">
+        <is>
+          <t>- 비오너 시도: '오너만 공유할 수 있어요'
+- 미분류 폴더 공유 시도: '미분류 폴더는 공유할 수 없어요'</t>
+        </is>
+      </c>
+      <c r="F145" s="3" t="inlineStr"/>
+      <c r="G145" s="3" t="inlineStr"/>
+      <c r="H145" s="3" t="inlineStr"/>
+      <c r="I145" s="3" t="inlineStr"/>
+      <c r="J145" s="3" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="3" t="inlineStr">
+        <is>
+          <t>SHARE-002
+#SHARE-ACCEPT</t>
+        </is>
+      </c>
+      <c r="B146" s="3" t="inlineStr">
+        <is>
+          <t>공유 폴더</t>
+        </is>
+      </c>
+      <c r="C146" s="3" t="inlineStr">
+        <is>
+          <t>공유 폴더 초대 수락</t>
+        </is>
+      </c>
+      <c r="D146" s="3" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="E144" s="4" t="inlineStr">
-        <is>
-          <t>Chrome MV3 확장이 사용자 본인의 웹 Gemini/ChatGPT/Claude 세션에 프롬프트 주입 → 응답 파싱 → QLink 앱으로 postMessage</t>
-        </is>
-      </c>
-      <c r="F144" s="4" t="inlineStr">
-        <is>
-          <t>Could</t>
-        </is>
-      </c>
-      <c r="G144" s="4" t="inlineStr"/>
-      <c r="H144" s="4" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="I144" s="4" t="inlineStr">
+      <c r="E146" s="3" t="inlineStr">
+        <is>
+          <t>초대 링크 클릭 → 토큰 검증 → 사용자가 "참여" 클릭 → folder_members INSERT</t>
+        </is>
+      </c>
+      <c r="F146" s="3" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G146" s="3" t="inlineStr">
+        <is>
+          <t>accept_folder_invite RPC</t>
+        </is>
+      </c>
+      <c r="H146" s="3" t="inlineStr">
+        <is>
+          <t>일부포함</t>
+        </is>
+      </c>
+      <c r="I146" s="3" t="inlineStr">
+        <is>
+          <t>기획완료</t>
+        </is>
+      </c>
+      <c r="J146" s="3" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="3" t="inlineStr"/>
+      <c r="B147" s="3" t="inlineStr"/>
+      <c r="C147" s="3" t="inlineStr"/>
+      <c r="D147" s="3" t="inlineStr">
+        <is>
+          <t>입력</t>
+        </is>
+      </c>
+      <c r="E147" s="3" t="inlineStr">
+        <is>
+          <t>invite_token (URL 파라미터)</t>
+        </is>
+      </c>
+      <c r="F147" s="3" t="inlineStr"/>
+      <c r="G147" s="3" t="inlineStr"/>
+      <c r="H147" s="3" t="inlineStr"/>
+      <c r="I147" s="3" t="inlineStr"/>
+      <c r="J147" s="3" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="3" t="inlineStr"/>
+      <c r="B148" s="3" t="inlineStr"/>
+      <c r="C148" s="3" t="inlineStr"/>
+      <c r="D148" s="3" t="inlineStr">
+        <is>
+          <t>출력</t>
+        </is>
+      </c>
+      <c r="E148" s="3" t="inlineStr">
+        <is>
+          <t>folder_members INSERT (role='member') / 폴더 진입</t>
+        </is>
+      </c>
+      <c r="F148" s="3" t="inlineStr"/>
+      <c r="G148" s="3" t="inlineStr"/>
+      <c r="H148" s="3" t="inlineStr"/>
+      <c r="I148" s="3" t="inlineStr"/>
+      <c r="J148" s="3" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="3" t="inlineStr"/>
+      <c r="B149" s="3" t="inlineStr"/>
+      <c r="C149" s="3" t="inlineStr"/>
+      <c r="D149" s="3" t="inlineStr">
+        <is>
+          <t>정책</t>
+        </is>
+      </c>
+      <c r="E149" s="3" t="inlineStr">
+        <is>
+          <t>POLICY-SHARED 참고
+[처리 순서] 미로그인 시 토큰 임시 보관 → 로그인 후 자동 수락 화면
+[멤버 한도] 50명</t>
+        </is>
+      </c>
+      <c r="F149" s="3" t="inlineStr"/>
+      <c r="G149" s="3" t="inlineStr"/>
+      <c r="H149" s="3" t="inlineStr"/>
+      <c r="I149" s="3" t="inlineStr"/>
+      <c r="J149" s="3" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="3" t="inlineStr"/>
+      <c r="B150" s="3" t="inlineStr"/>
+      <c r="C150" s="3" t="inlineStr"/>
+      <c r="D150" s="3" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="E150" s="3" t="inlineStr">
+        <is>
+          <t>- 토큰 만료: '유효하지 않거나 만료된 초대 링크입니다'
+- 이미 멤버: 토스트 + 폴더 이동
+- 본인이 오너: '본인의 폴더예요'
+- 멤버 한도 50명 초과: '이 폴더는 50명까지만 참여할 수 있어요. 오너에게 문의하세요'</t>
+        </is>
+      </c>
+      <c r="F150" s="3" t="inlineStr"/>
+      <c r="G150" s="3" t="inlineStr"/>
+      <c r="H150" s="3" t="inlineStr"/>
+      <c r="I150" s="3" t="inlineStr"/>
+      <c r="J150" s="3" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="3" t="inlineStr">
+        <is>
+          <t>SHARE-003
+#FOLDER-MEMBERS</t>
+        </is>
+      </c>
+      <c r="B151" s="3" t="inlineStr">
+        <is>
+          <t>공유 폴더</t>
+        </is>
+      </c>
+      <c r="C151" s="3" t="inlineStr">
+        <is>
+          <t>공유 폴더 멤버 관리</t>
+        </is>
+      </c>
+      <c r="D151" s="3" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+      <c r="E151" s="3" t="inlineStr">
+        <is>
+          <t>멤버 목록 + 역할 변경(owner만) + 제거(owner) / 나가기(self)</t>
+        </is>
+      </c>
+      <c r="F151" s="3" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G151" s="3" t="inlineStr">
+        <is>
+          <t>멤버 조회/수정/삭제 API</t>
+        </is>
+      </c>
+      <c r="H151" s="3" t="inlineStr">
+        <is>
+          <t>일부포함</t>
+        </is>
+      </c>
+      <c r="I151" s="3" t="inlineStr">
         <is>
           <t>기획중</t>
         </is>
       </c>
-      <c r="J144" s="4" t="inlineStr">
-        <is>
-          <t>ToS 회색 영역 — 신중 검토</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="4" t="inlineStr">
-        <is>
-          <t>BACKUP-001</t>
-        </is>
-      </c>
-      <c r="B148" s="4" t="inlineStr">
+      <c r="J151" s="3" t="inlineStr">
+        <is>
+          <t>v1.0 가벼운 형태로</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="3" t="inlineStr">
+        <is>
+          <t>VIEW-001
+#LINK-DETAIL</t>
+        </is>
+      </c>
+      <c r="B152" s="3" t="inlineStr">
+        <is>
+          <t>콘텐츠</t>
+        </is>
+      </c>
+      <c r="C152" s="3" t="inlineStr">
+        <is>
+          <t>YouTube 임베드 미리보기</t>
+        </is>
+      </c>
+      <c r="D152" s="3" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+      <c r="E152" s="3" t="inlineStr">
+        <is>
+          <t>URL이 youtube.com/youtu.be 도메인이면 상세 화면에서 iframe 임베드. 자동재생 X, 사용자 클릭 시 재생</t>
+        </is>
+      </c>
+      <c r="F152" s="3" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G152" s="3" t="inlineStr">
+        <is>
+          <t>(클라이언트, iframe)</t>
+        </is>
+      </c>
+      <c r="H152" s="3" t="inlineStr">
+        <is>
+          <t>일부포함</t>
+        </is>
+      </c>
+      <c r="I152" s="3" t="inlineStr">
+        <is>
+          <t>기획중</t>
+        </is>
+      </c>
+      <c r="J152" s="3" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="3" t="inlineStr">
+        <is>
+          <t>SETTINGS-001
+#SETTINGS-AI</t>
+        </is>
+      </c>
+      <c r="B153" s="3" t="inlineStr">
         <is>
           <t>설정</t>
         </is>
       </c>
-      <c r="C148" s="4" t="inlineStr">
-        <is>
-          <t>데이터 내보내기</t>
-        </is>
-      </c>
-      <c r="D148" s="4" t="inlineStr">
+      <c r="C153" s="3" t="inlineStr">
+        <is>
+          <t>AI 제공자 선택</t>
+        </is>
+      </c>
+      <c r="D153" s="3" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="E148" s="4" t="inlineStr">
-        <is>
-          <t>JSON·CSV 다운로드. IMPORT-001과 대칭</t>
-        </is>
-      </c>
-      <c r="F148" s="4" t="inlineStr">
-        <is>
-          <t>Could</t>
-        </is>
-      </c>
-      <c r="G148" s="4" t="inlineStr"/>
-      <c r="H148" s="4" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="I148" s="4" t="inlineStr">
-        <is>
-          <t>기획중</t>
-        </is>
-      </c>
-      <c r="J148" s="4" t="inlineStr"/>
-    </row>
-    <row r="152">
-      <c r="A152" s="4" t="inlineStr">
-        <is>
-          <t>HIGHLIGHT-001</t>
-        </is>
-      </c>
-      <c r="B152" s="4" t="inlineStr">
-        <is>
-          <t>콘텐츠</t>
-        </is>
-      </c>
-      <c r="C152" s="4" t="inlineStr">
-        <is>
-          <t>본문 하이라이트</t>
-        </is>
-      </c>
-      <c r="D152" s="4" t="inlineStr">
+      <c r="E153" s="3" t="inlineStr">
+        <is>
+          <t>6종 중 선택: ChatGPT / Gemini / Claude / Perplexity / 큐링크 기본(mock) / 사용자 API 키. SETTINGS-001 변경은 LINK-004의 provider 입력으로 즉시 반영</t>
+        </is>
+      </c>
+      <c r="F153" s="3" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G153" s="3" t="inlineStr">
+        <is>
+          <t>프로필 업데이트 API</t>
+        </is>
+      </c>
+      <c r="H153" s="3" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="I153" s="3" t="inlineStr">
+        <is>
+          <t>기획완료</t>
+        </is>
+      </c>
+      <c r="J153" s="3" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="3" t="inlineStr"/>
+      <c r="B154" s="3" t="inlineStr"/>
+      <c r="C154" s="3" t="inlineStr"/>
+      <c r="D154" s="3" t="inlineStr">
+        <is>
+          <t>입력</t>
+        </is>
+      </c>
+      <c r="E154" s="3" t="inlineStr">
+        <is>
+          <t>provider 식별자</t>
+        </is>
+      </c>
+      <c r="F154" s="3" t="inlineStr"/>
+      <c r="G154" s="3" t="inlineStr"/>
+      <c r="H154" s="3" t="inlineStr"/>
+      <c r="I154" s="3" t="inlineStr"/>
+      <c r="J154" s="3" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="3" t="inlineStr"/>
+      <c r="B155" s="3" t="inlineStr"/>
+      <c r="C155" s="3" t="inlineStr"/>
+      <c r="D155" s="3" t="inlineStr">
+        <is>
+          <t>출력</t>
+        </is>
+      </c>
+      <c r="E155" s="3" t="inlineStr">
+        <is>
+          <t>profiles.ai_provider UPDATE + 토스트</t>
+        </is>
+      </c>
+      <c r="F155" s="3" t="inlineStr"/>
+      <c r="G155" s="3" t="inlineStr"/>
+      <c r="H155" s="3" t="inlineStr"/>
+      <c r="I155" s="3" t="inlineStr"/>
+      <c r="J155" s="3" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="3" t="inlineStr"/>
+      <c r="B156" s="3" t="inlineStr"/>
+      <c r="C156" s="3" t="inlineStr"/>
+      <c r="D156" s="3" t="inlineStr">
+        <is>
+          <t>정책</t>
+        </is>
+      </c>
+      <c r="E156" s="3" t="inlineStr">
+        <is>
+          <t>[기본값] 'mock' (앱 진입 시)
+[동기화] 모든 디바이스에 SYNC-001로 반영
+[API 키] 사용자 API 키 선택 시 키 입력 화면 추가 노출, 서버 KMS 암호화 저장</t>
+        </is>
+      </c>
+      <c r="F156" s="3" t="inlineStr"/>
+      <c r="G156" s="3" t="inlineStr"/>
+      <c r="H156" s="3" t="inlineStr"/>
+      <c r="I156" s="3" t="inlineStr"/>
+      <c r="J156" s="3" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="3" t="inlineStr"/>
+      <c r="B157" s="3" t="inlineStr"/>
+      <c r="C157" s="3" t="inlineStr"/>
+      <c r="D157" s="3" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="E157" s="3" t="inlineStr">
+        <is>
+          <t>- 외부 세션 provider 선택했지만 Chrome 확장 미설치: '확장 프로그램 설치가 필요해요' + 안내 링크
+- API 키 무효: 다음 호출 시 '키를 확인해주세요' 안내</t>
+        </is>
+      </c>
+      <c r="F157" s="3" t="inlineStr"/>
+      <c r="G157" s="3" t="inlineStr"/>
+      <c r="H157" s="3" t="inlineStr"/>
+      <c r="I157" s="3" t="inlineStr"/>
+      <c r="J157" s="3" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="3" t="inlineStr">
+        <is>
+          <t>SETTINGS-002
+#SETTINGS-PROFILE</t>
+        </is>
+      </c>
+      <c r="B158" s="3" t="inlineStr">
+        <is>
+          <t>설정</t>
+        </is>
+      </c>
+      <c r="C158" s="3" t="inlineStr">
+        <is>
+          <t>프로필 변경</t>
+        </is>
+      </c>
+      <c r="D158" s="3" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="E152" s="4" t="inlineStr">
-        <is>
-          <t>링크 본문 텍스트 일부 강조 저장</t>
-        </is>
-      </c>
-      <c r="F152" s="4" t="inlineStr">
-        <is>
-          <t>Could</t>
-        </is>
-      </c>
-      <c r="G152" s="4" t="inlineStr"/>
-      <c r="H152" s="4" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="I152" s="4" t="inlineStr">
-        <is>
-          <t>기획중</t>
-        </is>
-      </c>
-      <c r="J152" s="4" t="inlineStr"/>
-    </row>
-    <row r="156">
-      <c r="A156" s="4" t="inlineStr">
-        <is>
-          <t>OFFLINE-001</t>
-        </is>
-      </c>
-      <c r="B156" s="4" t="inlineStr">
-        <is>
-          <t>PWA</t>
-        </is>
-      </c>
-      <c r="C156" s="4" t="inlineStr">
-        <is>
-          <t>풀 오프라인 모드</t>
-        </is>
-      </c>
-      <c r="D156" s="4" t="inlineStr">
+      <c r="E158" s="3" t="inlineStr">
+        <is>
+          <t>닉네임·아바타 이모지 변경</t>
+        </is>
+      </c>
+      <c r="F158" s="3" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G158" s="3" t="inlineStr">
+        <is>
+          <t>프로필 업데이트 API</t>
+        </is>
+      </c>
+      <c r="H158" s="3" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="I158" s="3" t="inlineStr">
+        <is>
+          <t>기획완료</t>
+        </is>
+      </c>
+      <c r="J158" s="3" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="3" t="inlineStr"/>
+      <c r="B159" s="3" t="inlineStr"/>
+      <c r="C159" s="3" t="inlineStr"/>
+      <c r="D159" s="3" t="inlineStr">
+        <is>
+          <t>입력</t>
+        </is>
+      </c>
+      <c r="E159" s="3" t="inlineStr">
+        <is>
+          <t>display_name (1~20자), avatar (이모지 단일 문자)</t>
+        </is>
+      </c>
+      <c r="F159" s="3" t="inlineStr"/>
+      <c r="G159" s="3" t="inlineStr"/>
+      <c r="H159" s="3" t="inlineStr"/>
+      <c r="I159" s="3" t="inlineStr"/>
+      <c r="J159" s="3" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="3" t="inlineStr"/>
+      <c r="B160" s="3" t="inlineStr"/>
+      <c r="C160" s="3" t="inlineStr"/>
+      <c r="D160" s="3" t="inlineStr">
+        <is>
+          <t>출력</t>
+        </is>
+      </c>
+      <c r="E160" s="3" t="inlineStr">
+        <is>
+          <t>profiles UPDATE + 헤더 즉시 반영</t>
+        </is>
+      </c>
+      <c r="F160" s="3" t="inlineStr"/>
+      <c r="G160" s="3" t="inlineStr"/>
+      <c r="H160" s="3" t="inlineStr"/>
+      <c r="I160" s="3" t="inlineStr"/>
+      <c r="J160" s="3" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="3" t="inlineStr"/>
+      <c r="B161" s="3" t="inlineStr"/>
+      <c r="C161" s="3" t="inlineStr"/>
+      <c r="D161" s="3" t="inlineStr">
+        <is>
+          <t>정책</t>
+        </is>
+      </c>
+      <c r="E161" s="3" t="inlineStr">
+        <is>
+          <t>[동기화] 즉시 모든 디바이스 반영</t>
+        </is>
+      </c>
+      <c r="F161" s="3" t="inlineStr"/>
+      <c r="G161" s="3" t="inlineStr"/>
+      <c r="H161" s="3" t="inlineStr"/>
+      <c r="I161" s="3" t="inlineStr"/>
+      <c r="J161" s="3" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="3" t="inlineStr"/>
+      <c r="B162" s="3" t="inlineStr"/>
+      <c r="C162" s="3" t="inlineStr"/>
+      <c r="D162" s="3" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="E162" s="3" t="inlineStr">
+        <is>
+          <t>- 빈 닉네임: '닉네임을 입력해주세요'
+- 20자 초과: 입력 차단</t>
+        </is>
+      </c>
+      <c r="F162" s="3" t="inlineStr"/>
+      <c r="G162" s="3" t="inlineStr"/>
+      <c r="H162" s="3" t="inlineStr"/>
+      <c r="I162" s="3" t="inlineStr"/>
+      <c r="J162" s="3" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="3" t="inlineStr">
+        <is>
+          <t>SETTINGS-003
+#SETTINGS-PASSWORD</t>
+        </is>
+      </c>
+      <c r="B163" s="3" t="inlineStr">
+        <is>
+          <t>설정</t>
+        </is>
+      </c>
+      <c r="C163" s="3" t="inlineStr">
+        <is>
+          <t>비밀번호 변경</t>
+        </is>
+      </c>
+      <c r="D163" s="3" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="E156" s="4" t="inlineStr">
-        <is>
-          <t>네트워크 없이 모든 기능 동작 — 동기화 충돌 복잡도, v2 백로그</t>
-        </is>
-      </c>
-      <c r="F156" s="4" t="inlineStr">
-        <is>
-          <t>Won't</t>
-        </is>
-      </c>
-      <c r="G156" s="4" t="inlineStr"/>
-      <c r="H156" s="4" t="inlineStr">
-        <is>
-          <t>미포함</t>
-        </is>
-      </c>
-      <c r="I156" s="4" t="inlineStr">
-        <is>
-          <t>기획중</t>
-        </is>
-      </c>
-      <c r="J156" s="4" t="inlineStr">
-        <is>
-          <t>이번 릴리즈 제외</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="4" t="inlineStr">
-        <is>
-          <t>NATIVE-001</t>
-        </is>
-      </c>
-      <c r="B160" s="4" t="inlineStr">
-        <is>
-          <t>PWA</t>
-        </is>
-      </c>
-      <c r="C160" s="4" t="inlineStr">
-        <is>
-          <t>네이티브 앱</t>
-        </is>
-      </c>
-      <c r="D160" s="4" t="inlineStr">
-        <is>
-          <t>설명</t>
-        </is>
-      </c>
-      <c r="E160" s="4" t="inlineStr">
-        <is>
-          <t>iOS/Android 스토어 등록 — PWA로 충분</t>
-        </is>
-      </c>
-      <c r="F160" s="4" t="inlineStr">
-        <is>
-          <t>Won't</t>
-        </is>
-      </c>
-      <c r="G160" s="4" t="inlineStr"/>
-      <c r="H160" s="4" t="inlineStr">
-        <is>
-          <t>미포함</t>
-        </is>
-      </c>
-      <c r="I160" s="4" t="inlineStr">
-        <is>
-          <t>기획중</t>
-        </is>
-      </c>
-      <c r="J160" s="4" t="inlineStr">
-        <is>
-          <t>이번 릴리즈 제외</t>
+      <c r="E163" s="3" t="inlineStr">
+        <is>
+          <t>현재 비밀번호 검증 → 새 비밀번호 변경. 변경 후 다른 디바이스는 강제 로그아웃 (보안 우선)</t>
+        </is>
+      </c>
+      <c r="F163" s="3" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G163" s="3" t="inlineStr">
+        <is>
+          <t>비밀번호 변경 API
+리프레시 토큰 무효화 API</t>
+        </is>
+      </c>
+      <c r="H163" s="3" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="I163" s="3" t="inlineStr">
+        <is>
+          <t>기획완료</t>
+        </is>
+      </c>
+      <c r="J163" s="3" t="inlineStr">
+        <is>
+          <t>결정: 변경 시 다른 디바이스 강제 로그아웃 + 화면 안내 문구 추가</t>
         </is>
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="4" t="inlineStr">
-        <is>
-          <t>BILLING-001</t>
-        </is>
-      </c>
-      <c r="B164" s="4" t="inlineStr">
-        <is>
-          <t>계정</t>
-        </is>
-      </c>
-      <c r="C164" s="4" t="inlineStr">
-        <is>
-          <t>유료 플랜</t>
-        </is>
-      </c>
-      <c r="D164" s="4" t="inlineStr">
-        <is>
-          <t>설명</t>
-        </is>
-      </c>
-      <c r="E164" s="4" t="inlineStr">
-        <is>
-          <t>결제·구독 — MVP는 무료 우선</t>
-        </is>
-      </c>
-      <c r="F164" s="4" t="inlineStr">
-        <is>
-          <t>Won't</t>
-        </is>
-      </c>
-      <c r="G164" s="4" t="inlineStr"/>
-      <c r="H164" s="4" t="inlineStr">
-        <is>
-          <t>미포함</t>
-        </is>
-      </c>
-      <c r="I164" s="4" t="inlineStr">
-        <is>
-          <t>기획중</t>
-        </is>
-      </c>
-      <c r="J164" s="4" t="inlineStr">
-        <is>
-          <t>이번 릴리즈 제외</t>
-        </is>
-      </c>
+      <c r="A164" s="3" t="inlineStr"/>
+      <c r="B164" s="3" t="inlineStr"/>
+      <c r="C164" s="3" t="inlineStr"/>
+      <c r="D164" s="3" t="inlineStr">
+        <is>
+          <t>입력</t>
+        </is>
+      </c>
+      <c r="E164" s="3" t="inlineStr">
+        <is>
+          <t>current_password, new_password (8~64자, 영문+숫자)</t>
+        </is>
+      </c>
+      <c r="F164" s="3" t="inlineStr"/>
+      <c r="G164" s="3" t="inlineStr"/>
+      <c r="H164" s="3" t="inlineStr"/>
+      <c r="I164" s="3" t="inlineStr"/>
+      <c r="J164" s="3" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="3" t="inlineStr"/>
+      <c r="B165" s="3" t="inlineStr"/>
+      <c r="C165" s="3" t="inlineStr"/>
+      <c r="D165" s="3" t="inlineStr">
+        <is>
+          <t>출력</t>
+        </is>
+      </c>
+      <c r="E165" s="3" t="inlineStr">
+        <is>
+          <t>비밀번호 변경 + 모든 다른 디바이스 리프레시 토큰 invalidate + 토스트 "변경됐어요. 다른 기기에서는 다시 로그인해주세요"</t>
+        </is>
+      </c>
+      <c r="F165" s="3" t="inlineStr"/>
+      <c r="G165" s="3" t="inlineStr"/>
+      <c r="H165" s="3" t="inlineStr"/>
+      <c r="I165" s="3" t="inlineStr"/>
+      <c r="J165" s="3" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="3" t="inlineStr"/>
+      <c r="B166" s="3" t="inlineStr"/>
+      <c r="C166" s="3" t="inlineStr"/>
+      <c r="D166" s="3" t="inlineStr">
+        <is>
+          <t>정책</t>
+        </is>
+      </c>
+      <c r="E166" s="3" t="inlineStr">
+        <is>
+          <t>[보안] 현재 비밀번호 검증 필수
+[강제 로그아웃] 변경 즉시 서버에서 모든 다른 활성 리프레시 토큰 invalidate
+[화면 안내] 비밀번호 변경 화면 상단에 안내 카피: "비밀번호를 바꾸면 로그인된 다른 기기들에서 자동으로 로그아웃돼요. 보안을 위한 조치예요."</t>
+        </is>
+      </c>
+      <c r="F166" s="3" t="inlineStr"/>
+      <c r="G166" s="3" t="inlineStr"/>
+      <c r="H166" s="3" t="inlineStr"/>
+      <c r="I166" s="3" t="inlineStr"/>
+      <c r="J166" s="3" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="3" t="inlineStr"/>
+      <c r="B167" s="3" t="inlineStr"/>
+      <c r="C167" s="3" t="inlineStr"/>
+      <c r="D167" s="3" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="E167" s="3" t="inlineStr">
+        <is>
+          <t>- 현재 PW 불일치: '현재 비밀번호가 일치하지 않아요'
+- 새 PW 정책 미충족: 안내
+- 5회 실패: 잠시 차단</t>
+        </is>
+      </c>
+      <c r="F167" s="3" t="inlineStr"/>
+      <c r="G167" s="3" t="inlineStr"/>
+      <c r="H167" s="3" t="inlineStr"/>
+      <c r="I167" s="3" t="inlineStr"/>
+      <c r="J167" s="3" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="3" t="inlineStr">
         <is>
-          <t>POLICY-AUTH</t>
+          <t>SETTINGS-004
+#SETTINGS-RESET</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
         <is>
-          <t>정책</t>
+          <t>설정</t>
         </is>
       </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
-          <t>토큰 만료/갱신 정책</t>
+          <t>데이터 초기화</t>
         </is>
       </c>
       <c r="D168" s="3" t="inlineStr">
@@ -6174,7 +6680,7 @@
       </c>
       <c r="E168" s="3" t="inlineStr">
         <is>
-          <t>모든 인증 흐름의 공통 토큰 정책. 다른 기능에서는 "POLICY-AUTH 참고"로 1줄 참조</t>
+          <t>본인 데이터(폴더·링크·공유 멤버십) 전체 영구 삭제. 이중 확인 모달. 모든 디바이스에서 즉시 빈 상태</t>
         </is>
       </c>
       <c r="F168" s="3" t="inlineStr">
@@ -6182,7 +6688,11 @@
           <t>Must</t>
         </is>
       </c>
-      <c r="G168" s="3" t="inlineStr"/>
+      <c r="G168" s="3" t="inlineStr">
+        <is>
+          <t>데이터 일괄 삭제 API (트랜잭션)</t>
+        </is>
+      </c>
       <c r="H168" s="3" t="inlineStr">
         <is>
           <t>MVP</t>
@@ -6195,7 +6705,7 @@
       </c>
       <c r="J168" s="3" t="inlineStr">
         <is>
-          <t>공통 참조 정책</t>
+          <t>결정: 즉시 hard delete (개인정보보호법 OK, 사용자 의도 그대로 존중)</t>
         </is>
       </c>
     </row>
@@ -6205,15 +6715,12 @@
       <c r="C169" s="3" t="inlineStr"/>
       <c r="D169" s="3" t="inlineStr">
         <is>
-          <t>정책</t>
+          <t>입력</t>
         </is>
       </c>
       <c r="E169" s="3" t="inlineStr">
         <is>
-          <t>[시간] 액세스 토큰 15분, 리프레시 토큰 30일
-[처리 순서] 401 응답 시 자동 갱신 1회 후 원래 요청 재시도
-[저장] 토큰은 secure storage 또는 httpOnly 쿠키
-[무효화] 비밀번호 변경 시 모든 리프레시 토큰 무효화 옵션 (TBD)</t>
+          <t>"초기화" 버튼 → 모달 1 → "정말 삭제" → 모달 2 → 사용자 비밀번호 재입력</t>
         </is>
       </c>
       <c r="F169" s="3" t="inlineStr"/>
@@ -6228,12 +6735,12 @@
       <c r="C170" s="3" t="inlineStr"/>
       <c r="D170" s="3" t="inlineStr">
         <is>
-          <t>예외</t>
+          <t>출력</t>
         </is>
       </c>
       <c r="E170" s="3" t="inlineStr">
         <is>
-          <t>갱신 실패 시 강제 로그아웃 + #AUTH-LOGIN</t>
+          <t>DELETE folders/links/folder_members(self) + 모든 디바이스 SYNC</t>
         </is>
       </c>
       <c r="F170" s="3" t="inlineStr"/>
@@ -6243,52 +6750,27 @@
       <c r="J170" s="3" t="inlineStr"/>
     </row>
     <row r="171">
-      <c r="A171" s="3" t="inlineStr">
-        <is>
-          <t>POLICY-AI</t>
-        </is>
-      </c>
-      <c r="B171" s="3" t="inlineStr">
+      <c r="A171" s="3" t="inlineStr"/>
+      <c r="B171" s="3" t="inlineStr"/>
+      <c r="C171" s="3" t="inlineStr"/>
+      <c r="D171" s="3" t="inlineStr">
         <is>
           <t>정책</t>
         </is>
       </c>
-      <c r="C171" s="3" t="inlineStr">
-        <is>
-          <t>AI 요약 호출 정책</t>
-        </is>
-      </c>
-      <c r="D171" s="3" t="inlineStr">
-        <is>
-          <t>설명</t>
-        </is>
-      </c>
       <c r="E171" s="3" t="inlineStr">
         <is>
-          <t>LINK-004와 IMPORT-001이 공통 사용. 사다리 폴백 정책</t>
-        </is>
-      </c>
-      <c r="F171" s="3" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
+          <t>[위험 액션] 이중 확인 + 비밀번호 재입력
+[복구 불가] 즉시 hard delete — DB에서 본인 데이터 영구 삭제, 복구 불가
+[고지] 모달 2에 명시: "삭제하면 복구할 수 없어요. 그래도 진행할까요?"
+[동기화] 즉시 모든 디바이스에서 빈 상태</t>
+        </is>
+      </c>
+      <c r="F171" s="3" t="inlineStr"/>
       <c r="G171" s="3" t="inlineStr"/>
-      <c r="H171" s="3" t="inlineStr">
-        <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="I171" s="3" t="inlineStr">
-        <is>
-          <t>기획완료</t>
-        </is>
-      </c>
-      <c r="J171" s="3" t="inlineStr">
-        <is>
-          <t>공통 참조 정책</t>
-        </is>
-      </c>
+      <c r="H171" s="3" t="inlineStr"/>
+      <c r="I171" s="3" t="inlineStr"/>
+      <c r="J171" s="3" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="3" t="inlineStr"/>
@@ -6296,15 +6778,13 @@
       <c r="C172" s="3" t="inlineStr"/>
       <c r="D172" s="3" t="inlineStr">
         <is>
-          <t>정책</t>
+          <t>예외</t>
         </is>
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
-          <t>[폴백 사다리] (1) Chrome 확장 외부 세션(설치된 경우) → (2) 사용자 API 키(설정된 경우) → (3) 서버 mock
-[시간] 단건 요약 1.4초 timeout, 일괄 요약 비동기 큐
-[재시도] 1회 자동, 실패 시 빈 요약으로 저장 + 수동 재시도 버튼
-[데이터·채점] raw_response는 ai_jobs 테이블에 jsonb 보존</t>
+          <t>- 비밀번호 불일치: 모달 안에서 '비밀번호가 일치하지 않아요'
+- 처리 중 네트워크 오류: 트랜잭션으로 서버 측 부분 삭제 방지 (전부 실패하거나 전부 성공)</t>
         </is>
       </c>
       <c r="F172" s="3" t="inlineStr"/>
@@ -6314,72 +6794,77 @@
       <c r="J172" s="3" t="inlineStr"/>
     </row>
     <row r="173">
-      <c r="A173" s="3" t="inlineStr"/>
-      <c r="B173" s="3" t="inlineStr"/>
-      <c r="C173" s="3" t="inlineStr"/>
+      <c r="A173" s="3" t="inlineStr">
+        <is>
+          <t>THEME-001
+#SETTINGS-THEME</t>
+        </is>
+      </c>
+      <c r="B173" s="3" t="inlineStr">
+        <is>
+          <t>설정</t>
+        </is>
+      </c>
+      <c r="C173" s="3" t="inlineStr">
+        <is>
+          <t>다크/라이트 + 강조색</t>
+        </is>
+      </c>
       <c r="D173" s="3" t="inlineStr">
         <is>
-          <t>예외</t>
+          <t>설명</t>
         </is>
       </c>
       <c r="E173" s="3" t="inlineStr">
         <is>
-          <t>모든 폴백 실패 시 빈 요약. 사용자에게 토스트 안내</t>
-        </is>
-      </c>
-      <c r="F173" s="3" t="inlineStr"/>
-      <c r="G173" s="3" t="inlineStr"/>
-      <c r="H173" s="3" t="inlineStr"/>
-      <c r="I173" s="3" t="inlineStr"/>
-      <c r="J173" s="3" t="inlineStr"/>
+          <t>다크/라이트 모드 + 강조색 3종(핑크·블루·그레이). 사용자별 저장. 로그인 화면은 항상 라이트+핑크(브랜드)</t>
+        </is>
+      </c>
+      <c r="F173" s="3" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G173" s="3" t="inlineStr">
+        <is>
+          <t>프로필 업데이트 API</t>
+        </is>
+      </c>
+      <c r="H173" s="3" t="inlineStr">
+        <is>
+          <t>일부포함</t>
+        </is>
+      </c>
+      <c r="I173" s="3" t="inlineStr">
+        <is>
+          <t>기획완료</t>
+        </is>
+      </c>
+      <c r="J173" s="3" t="inlineStr">
+        <is>
+          <t>결정: 다크/라이트 모드 + 강조색 3종(핑크/블루/그레이)</t>
+        </is>
+      </c>
     </row>
     <row r="174">
-      <c r="A174" s="3" t="inlineStr">
-        <is>
-          <t>POLICY-LOCAL</t>
-        </is>
-      </c>
-      <c r="B174" s="3" t="inlineStr">
-        <is>
-          <t>정책</t>
-        </is>
-      </c>
-      <c r="C174" s="3" t="inlineStr">
-        <is>
-          <t>로컬·서버 저장 분리</t>
-        </is>
-      </c>
+      <c r="A174" s="3" t="inlineStr"/>
+      <c r="B174" s="3" t="inlineStr"/>
+      <c r="C174" s="3" t="inlineStr"/>
       <c r="D174" s="3" t="inlineStr">
         <is>
-          <t>설명</t>
+          <t>입력</t>
         </is>
       </c>
       <c r="E174" s="3" t="inlineStr">
         <is>
-          <t>게스트와 정식 사용자의 데이터 위치 분리. 오프라인 시 큐잉</t>
-        </is>
-      </c>
-      <c r="F174" s="3" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
+          <t>mode (`light`/`dark`), accent (`pink`/`blue`/`gray`)</t>
+        </is>
+      </c>
+      <c r="F174" s="3" t="inlineStr"/>
       <c r="G174" s="3" t="inlineStr"/>
-      <c r="H174" s="3" t="inlineStr">
-        <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="I174" s="3" t="inlineStr">
-        <is>
-          <t>기획완료</t>
-        </is>
-      </c>
-      <c r="J174" s="3" t="inlineStr">
-        <is>
-          <t>공통 참조 정책</t>
-        </is>
-      </c>
+      <c r="H174" s="3" t="inlineStr"/>
+      <c r="I174" s="3" t="inlineStr"/>
+      <c r="J174" s="3" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="3" t="inlineStr"/>
@@ -6387,15 +6872,12 @@
       <c r="C175" s="3" t="inlineStr"/>
       <c r="D175" s="3" t="inlineStr">
         <is>
-          <t>정책</t>
+          <t>출력</t>
         </is>
       </c>
       <c r="E175" s="3" t="inlineStr">
         <is>
-          <t>[로컬 저장 대상] 게스트 모드 전체 데이터 / 클립보드 자동 채움 임시값 / 화면 캐시 (PWA Service Worker)
-[서버 저장 대상] 정식 사용자의 모든 데이터
-[오프라인 큐잉] 정식 사용자가 오프라인에서 저장 시 IndexedDB 큐 → 재연결 시 자동 동기화
-[충돌] last-write-wins by updated_at</t>
+          <t>profiles.theme UPDATE + CSS 변수 즉시 반영 + SYNC</t>
         </is>
       </c>
       <c r="F175" s="3" t="inlineStr"/>
@@ -6410,12 +6892,13 @@
       <c r="C176" s="3" t="inlineStr"/>
       <c r="D176" s="3" t="inlineStr">
         <is>
-          <t>예외</t>
+          <t>정책</t>
         </is>
       </c>
       <c r="E176" s="3" t="inlineStr">
         <is>
-          <t>로컬 큐 5MB 초과 시 사용자에게 안내</t>
+          <t>[동기화] SYNC-001로 모든 디바이스 즉시 반영
+[기본값] 신규 가입자 light + pink</t>
         </is>
       </c>
       <c r="F176" s="3" t="inlineStr"/>
@@ -6425,63 +6908,616 @@
       <c r="J176" s="3" t="inlineStr"/>
     </row>
     <row r="177">
-      <c r="A177" s="3" t="inlineStr">
+      <c r="A177" s="4" t="inlineStr">
+        <is>
+          <t>AI-001</t>
+        </is>
+      </c>
+      <c r="B177" s="4" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="C177" s="4" t="inlineStr">
+        <is>
+          <t>Chrome 확장 (외부 AI 세션)</t>
+        </is>
+      </c>
+      <c r="D177" s="4" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+      <c r="E177" s="4" t="inlineStr">
+        <is>
+          <t>Chrome MV3 확장이 사용자 본인의 웹 Gemini/ChatGPT/Claude 세션에 프롬프트 주입 → 응답 파싱 → QLink 앱으로 postMessage</t>
+        </is>
+      </c>
+      <c r="F177" s="4" t="inlineStr">
+        <is>
+          <t>Could</t>
+        </is>
+      </c>
+      <c r="G177" s="4" t="inlineStr"/>
+      <c r="H177" s="4" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="I177" s="4" t="inlineStr">
+        <is>
+          <t>기획중</t>
+        </is>
+      </c>
+      <c r="J177" s="4" t="inlineStr">
+        <is>
+          <t>ToS 회색 영역 — 신중 검토</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="4" t="inlineStr">
+        <is>
+          <t>BACKUP-001</t>
+        </is>
+      </c>
+      <c r="B181" s="4" t="inlineStr">
+        <is>
+          <t>설정</t>
+        </is>
+      </c>
+      <c r="C181" s="4" t="inlineStr">
+        <is>
+          <t>데이터 내보내기</t>
+        </is>
+      </c>
+      <c r="D181" s="4" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+      <c r="E181" s="4" t="inlineStr">
+        <is>
+          <t>JSON·CSV 다운로드. IMPORT-001과 대칭</t>
+        </is>
+      </c>
+      <c r="F181" s="4" t="inlineStr">
+        <is>
+          <t>Could</t>
+        </is>
+      </c>
+      <c r="G181" s="4" t="inlineStr"/>
+      <c r="H181" s="4" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="I181" s="4" t="inlineStr">
+        <is>
+          <t>기획중</t>
+        </is>
+      </c>
+      <c r="J181" s="4" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="4" t="inlineStr">
+        <is>
+          <t>HIGHLIGHT-001</t>
+        </is>
+      </c>
+      <c r="B185" s="4" t="inlineStr">
+        <is>
+          <t>콘텐츠</t>
+        </is>
+      </c>
+      <c r="C185" s="4" t="inlineStr">
+        <is>
+          <t>본문 하이라이트</t>
+        </is>
+      </c>
+      <c r="D185" s="4" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+      <c r="E185" s="4" t="inlineStr">
+        <is>
+          <t>링크 본문 텍스트 일부 강조 저장</t>
+        </is>
+      </c>
+      <c r="F185" s="4" t="inlineStr">
+        <is>
+          <t>Could</t>
+        </is>
+      </c>
+      <c r="G185" s="4" t="inlineStr"/>
+      <c r="H185" s="4" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="I185" s="4" t="inlineStr">
+        <is>
+          <t>기획중</t>
+        </is>
+      </c>
+      <c r="J185" s="4" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="4" t="inlineStr">
+        <is>
+          <t>OFFLINE-001</t>
+        </is>
+      </c>
+      <c r="B189" s="4" t="inlineStr">
+        <is>
+          <t>PWA</t>
+        </is>
+      </c>
+      <c r="C189" s="4" t="inlineStr">
+        <is>
+          <t>풀 오프라인 모드</t>
+        </is>
+      </c>
+      <c r="D189" s="4" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+      <c r="E189" s="4" t="inlineStr">
+        <is>
+          <t>네트워크 없이 모든 기능 동작 — 동기화 충돌 복잡도, v2 백로그</t>
+        </is>
+      </c>
+      <c r="F189" s="4" t="inlineStr">
+        <is>
+          <t>Won't</t>
+        </is>
+      </c>
+      <c r="G189" s="4" t="inlineStr"/>
+      <c r="H189" s="4" t="inlineStr">
+        <is>
+          <t>미포함</t>
+        </is>
+      </c>
+      <c r="I189" s="4" t="inlineStr">
+        <is>
+          <t>기획중</t>
+        </is>
+      </c>
+      <c r="J189" s="4" t="inlineStr">
+        <is>
+          <t>이번 릴리즈 제외</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="4" t="inlineStr">
+        <is>
+          <t>NATIVE-001</t>
+        </is>
+      </c>
+      <c r="B193" s="4" t="inlineStr">
+        <is>
+          <t>PWA</t>
+        </is>
+      </c>
+      <c r="C193" s="4" t="inlineStr">
+        <is>
+          <t>네이티브 앱</t>
+        </is>
+      </c>
+      <c r="D193" s="4" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+      <c r="E193" s="4" t="inlineStr">
+        <is>
+          <t>iOS/Android 스토어 등록 — PWA로 충분</t>
+        </is>
+      </c>
+      <c r="F193" s="4" t="inlineStr">
+        <is>
+          <t>Won't</t>
+        </is>
+      </c>
+      <c r="G193" s="4" t="inlineStr"/>
+      <c r="H193" s="4" t="inlineStr">
+        <is>
+          <t>미포함</t>
+        </is>
+      </c>
+      <c r="I193" s="4" t="inlineStr">
+        <is>
+          <t>기획중</t>
+        </is>
+      </c>
+      <c r="J193" s="4" t="inlineStr">
+        <is>
+          <t>이번 릴리즈 제외</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="4" t="inlineStr">
+        <is>
+          <t>BILLING-001</t>
+        </is>
+      </c>
+      <c r="B197" s="4" t="inlineStr">
+        <is>
+          <t>계정</t>
+        </is>
+      </c>
+      <c r="C197" s="4" t="inlineStr">
+        <is>
+          <t>유료 플랜</t>
+        </is>
+      </c>
+      <c r="D197" s="4" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+      <c r="E197" s="4" t="inlineStr">
+        <is>
+          <t>결제·구독 — MVP는 무료 우선</t>
+        </is>
+      </c>
+      <c r="F197" s="4" t="inlineStr">
+        <is>
+          <t>Won't</t>
+        </is>
+      </c>
+      <c r="G197" s="4" t="inlineStr"/>
+      <c r="H197" s="4" t="inlineStr">
+        <is>
+          <t>미포함</t>
+        </is>
+      </c>
+      <c r="I197" s="4" t="inlineStr">
+        <is>
+          <t>기획중</t>
+        </is>
+      </c>
+      <c r="J197" s="4" t="inlineStr">
+        <is>
+          <t>이번 릴리즈 제외</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="3" t="inlineStr">
+        <is>
+          <t>POLICY-AUTH</t>
+        </is>
+      </c>
+      <c r="B201" s="3" t="inlineStr">
+        <is>
+          <t>정책</t>
+        </is>
+      </c>
+      <c r="C201" s="3" t="inlineStr">
+        <is>
+          <t>토큰 만료/갱신 정책</t>
+        </is>
+      </c>
+      <c r="D201" s="3" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+      <c r="E201" s="3" t="inlineStr">
+        <is>
+          <t>모든 인증 흐름의 공통 토큰 정책. 다른 기능에서는 "POLICY-AUTH 참고"로 1줄 참조</t>
+        </is>
+      </c>
+      <c r="F201" s="3" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G201" s="3" t="inlineStr"/>
+      <c r="H201" s="3" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="I201" s="3" t="inlineStr">
+        <is>
+          <t>기획완료</t>
+        </is>
+      </c>
+      <c r="J201" s="3" t="inlineStr">
+        <is>
+          <t>공통 참조 정책</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="3" t="inlineStr"/>
+      <c r="B202" s="3" t="inlineStr"/>
+      <c r="C202" s="3" t="inlineStr"/>
+      <c r="D202" s="3" t="inlineStr">
+        <is>
+          <t>정책</t>
+        </is>
+      </c>
+      <c r="E202" s="3" t="inlineStr">
+        <is>
+          <t>[시간] 액세스 토큰 15분, 리프레시 토큰 30일
+[처리 순서] 401 응답 시 자동 갱신 1회 후 원래 요청 재시도
+[저장] 토큰은 secure storage 또는 httpOnly 쿠키
+[무효화] 비밀번호 변경 시 모든 리프레시 토큰 무효화 옵션 (TBD)</t>
+        </is>
+      </c>
+      <c r="F202" s="3" t="inlineStr"/>
+      <c r="G202" s="3" t="inlineStr"/>
+      <c r="H202" s="3" t="inlineStr"/>
+      <c r="I202" s="3" t="inlineStr"/>
+      <c r="J202" s="3" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="3" t="inlineStr"/>
+      <c r="B203" s="3" t="inlineStr"/>
+      <c r="C203" s="3" t="inlineStr"/>
+      <c r="D203" s="3" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="E203" s="3" t="inlineStr">
+        <is>
+          <t>갱신 실패 시 강제 로그아웃 + #AUTH-LOGIN</t>
+        </is>
+      </c>
+      <c r="F203" s="3" t="inlineStr"/>
+      <c r="G203" s="3" t="inlineStr"/>
+      <c r="H203" s="3" t="inlineStr"/>
+      <c r="I203" s="3" t="inlineStr"/>
+      <c r="J203" s="3" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="3" t="inlineStr">
+        <is>
+          <t>POLICY-AI</t>
+        </is>
+      </c>
+      <c r="B204" s="3" t="inlineStr">
+        <is>
+          <t>정책</t>
+        </is>
+      </c>
+      <c r="C204" s="3" t="inlineStr">
+        <is>
+          <t>AI 요약 호출 정책</t>
+        </is>
+      </c>
+      <c r="D204" s="3" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+      <c r="E204" s="3" t="inlineStr">
+        <is>
+          <t>LINK-004와 IMPORT-001이 공통 사용. 사다리 폴백 정책</t>
+        </is>
+      </c>
+      <c r="F204" s="3" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G204" s="3" t="inlineStr"/>
+      <c r="H204" s="3" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="I204" s="3" t="inlineStr">
+        <is>
+          <t>기획완료</t>
+        </is>
+      </c>
+      <c r="J204" s="3" t="inlineStr">
+        <is>
+          <t>공통 참조 정책</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="3" t="inlineStr"/>
+      <c r="B205" s="3" t="inlineStr"/>
+      <c r="C205" s="3" t="inlineStr"/>
+      <c r="D205" s="3" t="inlineStr">
+        <is>
+          <t>정책</t>
+        </is>
+      </c>
+      <c r="E205" s="3" t="inlineStr">
+        <is>
+          <t>[폴백 사다리] (1) Chrome 확장 외부 세션(설치된 경우) → (2) 사용자 API 키(설정된 경우) → (3) 서버 mock
+[시간] 단건 요약 1.4초 timeout, 일괄 요약 비동기 큐
+[재시도] 1회 자동, 실패 시 빈 요약으로 저장 + 수동 재시도 버튼
+[데이터·채점] raw_response는 ai_jobs 테이블에 jsonb 보존</t>
+        </is>
+      </c>
+      <c r="F205" s="3" t="inlineStr"/>
+      <c r="G205" s="3" t="inlineStr"/>
+      <c r="H205" s="3" t="inlineStr"/>
+      <c r="I205" s="3" t="inlineStr"/>
+      <c r="J205" s="3" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="3" t="inlineStr"/>
+      <c r="B206" s="3" t="inlineStr"/>
+      <c r="C206" s="3" t="inlineStr"/>
+      <c r="D206" s="3" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="E206" s="3" t="inlineStr">
+        <is>
+          <t>모든 폴백 실패 시 빈 요약. 사용자에게 토스트 안내</t>
+        </is>
+      </c>
+      <c r="F206" s="3" t="inlineStr"/>
+      <c r="G206" s="3" t="inlineStr"/>
+      <c r="H206" s="3" t="inlineStr"/>
+      <c r="I206" s="3" t="inlineStr"/>
+      <c r="J206" s="3" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="3" t="inlineStr">
+        <is>
+          <t>POLICY-LOCAL</t>
+        </is>
+      </c>
+      <c r="B207" s="3" t="inlineStr">
+        <is>
+          <t>정책</t>
+        </is>
+      </c>
+      <c r="C207" s="3" t="inlineStr">
+        <is>
+          <t>로컬·서버 저장 분리</t>
+        </is>
+      </c>
+      <c r="D207" s="3" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+      <c r="E207" s="3" t="inlineStr">
+        <is>
+          <t>게스트와 정식 사용자의 데이터 위치 분리. 오프라인 시 큐잉</t>
+        </is>
+      </c>
+      <c r="F207" s="3" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G207" s="3" t="inlineStr"/>
+      <c r="H207" s="3" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="I207" s="3" t="inlineStr">
+        <is>
+          <t>기획완료</t>
+        </is>
+      </c>
+      <c r="J207" s="3" t="inlineStr">
+        <is>
+          <t>공통 참조 정책</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="3" t="inlineStr"/>
+      <c r="B208" s="3" t="inlineStr"/>
+      <c r="C208" s="3" t="inlineStr"/>
+      <c r="D208" s="3" t="inlineStr">
+        <is>
+          <t>정책</t>
+        </is>
+      </c>
+      <c r="E208" s="3" t="inlineStr">
+        <is>
+          <t>[로컬 저장 대상] 게스트 모드 전체 데이터 / 클립보드 자동 채움 임시값 / 화면 캐시 (PWA Service Worker)
+[서버 저장 대상] 정식 사용자의 모든 데이터
+[오프라인 큐잉] 정식 사용자가 오프라인에서 저장 시 IndexedDB 큐 → 재연결 시 자동 동기화
+[충돌] last-write-wins by updated_at</t>
+        </is>
+      </c>
+      <c r="F208" s="3" t="inlineStr"/>
+      <c r="G208" s="3" t="inlineStr"/>
+      <c r="H208" s="3" t="inlineStr"/>
+      <c r="I208" s="3" t="inlineStr"/>
+      <c r="J208" s="3" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="3" t="inlineStr"/>
+      <c r="B209" s="3" t="inlineStr"/>
+      <c r="C209" s="3" t="inlineStr"/>
+      <c r="D209" s="3" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="E209" s="3" t="inlineStr">
+        <is>
+          <t>로컬 큐 5MB 초과 시 사용자에게 안내</t>
+        </is>
+      </c>
+      <c r="F209" s="3" t="inlineStr"/>
+      <c r="G209" s="3" t="inlineStr"/>
+      <c r="H209" s="3" t="inlineStr"/>
+      <c r="I209" s="3" t="inlineStr"/>
+      <c r="J209" s="3" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="3" t="inlineStr">
         <is>
           <t>POLICY-SHARED</t>
         </is>
       </c>
-      <c r="B177" s="3" t="inlineStr">
+      <c r="B210" s="3" t="inlineStr">
         <is>
           <t>정책</t>
         </is>
       </c>
-      <c r="C177" s="3" t="inlineStr">
+      <c r="C210" s="3" t="inlineStr">
         <is>
           <t>공유 폴더 권한 정책</t>
         </is>
       </c>
-      <c r="D177" s="3" t="inlineStr">
+      <c r="D210" s="3" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="E177" s="3" t="inlineStr">
+      <c r="E210" s="3" t="inlineStr">
         <is>
           <t>SHARE-001/002/003 공통 권한 모델</t>
         </is>
       </c>
-      <c r="F177" s="3" t="inlineStr">
+      <c r="F210" s="3" t="inlineStr">
         <is>
           <t>Should</t>
         </is>
       </c>
-      <c r="G177" s="3" t="inlineStr"/>
-      <c r="H177" s="3" t="inlineStr">
+      <c r="G210" s="3" t="inlineStr"/>
+      <c r="H210" s="3" t="inlineStr">
         <is>
           <t>일부포함</t>
         </is>
       </c>
-      <c r="I177" s="3" t="inlineStr">
+      <c r="I210" s="3" t="inlineStr">
         <is>
           <t>기획완료</t>
         </is>
       </c>
-      <c r="J177" s="3" t="inlineStr">
+      <c r="J210" s="3" t="inlineStr">
         <is>
           <t>공통 참조 정책</t>
         </is>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" s="3" t="inlineStr"/>
-      <c r="B178" s="3" t="inlineStr"/>
-      <c r="C178" s="3" t="inlineStr"/>
-      <c r="D178" s="3" t="inlineStr">
+    <row r="211">
+      <c r="A211" s="3" t="inlineStr"/>
+      <c r="B211" s="3" t="inlineStr"/>
+      <c r="C211" s="3" t="inlineStr"/>
+      <c r="D211" s="3" t="inlineStr">
         <is>
           <t>정책</t>
         </is>
       </c>
-      <c r="E178" s="3" t="inlineStr">
+      <c r="E211" s="3" t="inlineStr">
         <is>
           <t>[역할] owner: 폴더·링크·멤버 전체 권한 / member: 링크 추가·읽기·자기 추가한 링크 삭제 / viewer: 읽기만
 [기본] 초대 수락 시 role='member'
@@ -6489,31 +7525,31 @@
 [멤버 한도] 50명</t>
         </is>
       </c>
-      <c r="F178" s="3" t="inlineStr"/>
-      <c r="G178" s="3" t="inlineStr"/>
-      <c r="H178" s="3" t="inlineStr"/>
-      <c r="I178" s="3" t="inlineStr"/>
-      <c r="J178" s="3" t="inlineStr"/>
-    </row>
-    <row r="179">
-      <c r="A179" s="3" t="inlineStr"/>
-      <c r="B179" s="3" t="inlineStr"/>
-      <c r="C179" s="3" t="inlineStr"/>
-      <c r="D179" s="3" t="inlineStr">
+      <c r="F211" s="3" t="inlineStr"/>
+      <c r="G211" s="3" t="inlineStr"/>
+      <c r="H211" s="3" t="inlineStr"/>
+      <c r="I211" s="3" t="inlineStr"/>
+      <c r="J211" s="3" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="3" t="inlineStr"/>
+      <c r="B212" s="3" t="inlineStr"/>
+      <c r="C212" s="3" t="inlineStr"/>
+      <c r="D212" s="3" t="inlineStr">
         <is>
           <t>예외</t>
         </is>
       </c>
-      <c r="E179" s="3" t="inlineStr">
+      <c r="E212" s="3" t="inlineStr">
         <is>
           <t>권한 부족 액션은 UI에서 비활성 + 툴팁. 백엔드는 항상 재검증 (Lambda 핸들러)</t>
         </is>
       </c>
-      <c r="F179" s="3" t="inlineStr"/>
-      <c r="G179" s="3" t="inlineStr"/>
-      <c r="H179" s="3" t="inlineStr"/>
-      <c r="I179" s="3" t="inlineStr"/>
-      <c r="J179" s="3" t="inlineStr"/>
+      <c r="F212" s="3" t="inlineStr"/>
+      <c r="G212" s="3" t="inlineStr"/>
+      <c r="H212" s="3" t="inlineStr"/>
+      <c r="I212" s="3" t="inlineStr"/>
+      <c r="J212" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/docs/planning/05_상세기능명세서.xlsx
+++ b/docs/planning/05_상세기능명세서.xlsx
@@ -1044,12 +1044,12 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>할 일 완료 체크</t>
+          <t>할 일 완료 체크 (회차별 + 누적)</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>개별 토글, 낙관적 UI</t>
+          <t>반복은 회차별 완료, 누적 이력 토글로 접기·펼치기</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>할 일 완료 체크</t>
+          <t>할 일 완료 체크 (회차별 + 누적)</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
@@ -4138,7 +4138,7 @@
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>할 일 카드 좌측 체크박스 또는 상세에서 토글. 낙관적 UI로 즉시 ✓ 표시 후 서버 UPDATE</t>
+          <t>반복 모드는 회차별 완료(이번 주 완료해도 다음 주에 또 활성). 1회/시간없음 모드는 todo 자체 완료. 누적 완료 이력은 토글로 접기·펼치기 (default 접힘). "✓ 완료한 N회 · 이번 달 M회 ▼" 형태로 요약, 펼치면 회차별 완료 시각 노출 (max-height 200px + 스크롤)</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
@@ -4148,7 +4148,8 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>POST /todos/:id/complete</t>
+          <t>POST /todos/:id/complete
+GET /todos/:id/occurrences</t>
         </is>
       </c>
       <c r="H68" s="3" t="inlineStr">
@@ -4163,7 +4164,7 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>낙관적 UI</t>
+          <t>결정(TBD-13): 회차별 완료 채택. 매주 강의 → 이번 주 ✓ → 다음 주 또 활성. 누적 이력은 토글 접기/펼치기</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4179,7 @@
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>todoId, completed: boolean</t>
+          <t>todoId, completed: bool, (반복 모드) occurrenceDate: 'YYYY-MM-DD' (생략 시 오늘 KST)</t>
         </is>
       </c>
       <c r="F69" s="3" t="inlineStr"/>
@@ -4198,7 +4199,9 @@
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>link_todos.completed_at UPDATE + Realtime</t>
+          <t>- 반복: todo_occurrences INSERT/DELETE
+- 그 외: link_todos.completed_at UPDATE
+- Realtime TODO_UPDATED publish</t>
         </is>
       </c>
       <c r="F70" s="3" t="inlineStr"/>
@@ -4218,8 +4221,10 @@
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>[낙관적 UI] 즉시 ✓ 후 UPDATE 호출, 실패 시 롤백
-[반복 알림] MVP는 "전체 종료"만(EventBridge Rule 일괄 제거). 회차별 완료는 v1.x</t>
+          <t>[회차별 완료] 반복 todo는 오늘 회차만 토글. 토글 후 카드의 "활성 회차"가 다음 예정일로 자동 이동
+[누적 표시] 토글 default 접힘. 펼치면 시간 역순
+[낙관적 UI] 즉시 ✓ 후 UPDATE, 실패 시 롤백
+[반복 종료] 사용자가 명시 액션 시에만 EventBridge Rule 일괄 제거</t>
         </is>
       </c>
       <c r="F71" s="3" t="inlineStr"/>
@@ -4240,7 +4245,8 @@
       <c r="E72" s="3" t="inlineStr">
         <is>
           <t>- 네트워크 오류: 로컬 큐잉, 재연결 시 동기화
-- 동시 토글: last-write-wins</t>
+- 동시 토글: last-write-wins
+- 같은 날짜 중복: PK (todo_id, occurrence_date) 자동 dedupe</t>
         </is>
       </c>
       <c r="F72" s="3" t="inlineStr"/>

--- a/docs/planning/05_상세기능명세서.xlsx
+++ b/docs/planning/05_상세기능명세서.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1145,170 +1145,170 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
+          <t>TODO-009</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>할일</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>할 일 가시성 (공유 폴더)</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>🔒나만 / 👥공유 선택. 메모는 항상 비공개 + 안내 문구</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>US-021</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>TODO-010</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>할일</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>공개 할 일 수락 흐름</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>수락해야 본인 알림 등록. 미수락은 표시만</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>US-022</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
           <t>TODO-006</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>할일</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>캘린더 .ics 내보내기</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>외부 캘린더 앱 연동</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="E22" s="3" t="inlineStr">
         <is>
           <t>일부포함</t>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="F22" s="3" t="inlineStr">
         <is>
           <t>Should</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="G22" s="3" t="inlineStr">
         <is>
           <t>US-008</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>TODO-007</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>할일</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>채용 마감일 자동 추출</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>AI가 채용 공고 마감일 파싱 → 할 일 제안</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E23" s="4" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="F23" s="4" t="inlineStr">
         <is>
           <t>Could</t>
         </is>
       </c>
-      <c r="G21" s="4" t="inlineStr">
+      <c r="G23" s="4" t="inlineStr">
         <is>
           <t>US-009</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>TODO-008</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>할일</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>AI 할 일 추천</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>본문 분석 → 할 일 제안</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>Could</t>
-        </is>
-      </c>
-      <c r="G22" s="4" t="inlineStr">
-        <is>
-          <t>US-007</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>QR-001</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>링크</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>카메라 QR 스캔 (모바일)</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>카메라로 QR 인식 → URL 추출</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>US-005</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>QR-002</t>
+          <t>TODO-008</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>링크</t>
+          <t>할일</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>갤러리 QR 인식</t>
+          <t>AI 할 일 추천</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>사진첩 이미지에서 QR 추출</t>
+          <t>본문 분석 → 할 일 제안</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
@@ -1323,29 +1323,29 @@
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>US-005</t>
+          <t>US-007</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>FOLDER-001</t>
+          <t>QR-001</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>폴더</t>
+          <t>링크</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>폴더 생성/수정/삭제</t>
+          <t>카메라 QR 스캔 (모바일)</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>이모지+이름. 삭제 시 링크 미분류로</t>
+          <t>카메라로 QR 인식 → URL 추출</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -1360,66 +1360,66 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>US-003</t>
+          <t>US-005</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>FOLDER-002</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>폴더</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>폴더 이동</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>링크 상세에서 폴더 변경</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>US-003</t>
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>QR-002</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>링크</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>갤러리 QR 인식</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>사진첩 이미지에서 QR 추출</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>Could</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>US-005</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>HOME-001</t>
+          <t>FOLDER-001</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>홈</t>
+          <t>폴더</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>홈 피드</t>
+          <t>폴더 생성/수정/삭제</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>최신순 무한 스크롤, Empty State</t>
+          <t>이모지+이름. 삭제 시 링크 미분류로</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -1434,29 +1434,29 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>US-001</t>
+          <t>US-003</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>SEARCH-001</t>
+          <t>FOLDER-002</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>검색</t>
+          <t>폴더</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>키워드 검색</t>
+          <t>폴더 이동</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>제목·요약·태그 통합 검색, 디바운스</t>
+          <t>링크 상세에서 폴더 변경</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -1471,29 +1471,29 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>US-004</t>
+          <t>US-003</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>WEB-001</t>
+          <t>HOME-001</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>플랫폼</t>
+          <t>홈</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>데스크톱 웹 레이아웃</t>
+          <t>홈 피드</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>1024px+ 사이드바·다중컬럼·키보드 단축키</t>
+          <t>최신순 무한 스크롤, Empty State</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -1508,29 +1508,29 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>US-006</t>
+          <t>US-001</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>SYNC-001</t>
+          <t>SEARCH-001</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>플랫폼</t>
+          <t>검색</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>모바일↔웹 자동 동기화</t>
+          <t>키워드 검색</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>한 계정 = 한 데이터, Realtime 1~2초</t>
+          <t>제목·요약·태그 통합 검색, 디바운스</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -1545,14 +1545,14 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>US-006</t>
+          <t>US-004</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>IMPORT-001</t>
+          <t>WEB-001</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -1562,86 +1562,86 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>크롬 즐겨찾기 가져오기</t>
+          <t>데스크톱 웹 레이아웃</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>bookmarks.html 업로드 → 일괄 import + AI 요약</t>
+          <t>1024px+ 사이드바·다중컬럼·키보드 단축키</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>일부포함</t>
+          <t>MVP</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>US-007</t>
+          <t>US-006</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>IMPORT-002</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>SYNC-001</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>플랫폼</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>Pocket/Raindrop import</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>타 서비스 export 파일 import</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>Could</t>
-        </is>
-      </c>
-      <c r="G32" s="4" t="inlineStr">
-        <is>
-          <t>US-007</t>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>모바일↔웹 자동 동기화</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>한 계정 = 한 데이터, Realtime 1~2초</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>US-006</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>SHARE-001</t>
+          <t>IMPORT-001</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>공유 폴더</t>
+          <t>플랫폼</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>공유 폴더 만들기</t>
+          <t>크롬 즐겨찾기 가져오기</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>shared 모드 + 초대 토큰</t>
+          <t>bookmarks.html 업로드 → 일괄 import + AI 요약</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -1656,51 +1656,51 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>US-008</t>
+          <t>US-007</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>SHARE-002</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>공유 폴더</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>공유 폴더 초대 수락</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>토큰 검증 + 멤버 가입</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t>일부포함</t>
-        </is>
-      </c>
-      <c r="F34" s="3" t="inlineStr">
-        <is>
-          <t>Should</t>
-        </is>
-      </c>
-      <c r="G34" s="3" t="inlineStr">
-        <is>
-          <t>US-008</t>
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>IMPORT-002</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>플랫폼</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>Pocket/Raindrop import</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>타 서비스 export 파일 import</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>Could</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>US-007</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>SHARE-003</t>
+          <t>SHARE-001</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>공유 폴더 멤버 관리</t>
+          <t>공유 폴더 만들기</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>역할·제거·나가기</t>
+          <t>shared 모드 + 초대 토큰</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -1737,22 +1737,22 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>VIEW-001</t>
+          <t>SHARE-002</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>콘텐츠</t>
+          <t>공유 폴더</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>YouTube 임베드 미리보기</t>
+          <t>공유 폴더 초대 수락</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>URL 자동 인식 → 상세 임베드</t>
+          <t>토큰 검증 + 멤버 가입</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
@@ -1767,88 +1767,88 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>US-009</t>
+          <t>US-008</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>SETTINGS-001</t>
+          <t>SHARE-003</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>설정</t>
+          <t>공유 폴더</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>AI 제공자 선택</t>
+          <t>공유 폴더 멤버 관리</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>Gemini/ChatGPT/Claude/Perplexity 등</t>
+          <t>역할·제거·나가기</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>MVP</t>
+          <t>일부포함</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>US-002</t>
+          <t>US-008</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>SETTINGS-002</t>
+          <t>VIEW-001</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>설정</t>
+          <t>콘텐츠</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>프로필 변경</t>
+          <t>YouTube 임베드 미리보기</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>닉네임·아바타 이모지</t>
+          <t>URL 자동 인식 → 상세 임베드</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>MVP</t>
+          <t>일부포함</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>US-001</t>
+          <t>US-009</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>SETTINGS-003</t>
+          <t>SETTINGS-001</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -1858,12 +1858,12 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>비밀번호 변경</t>
+          <t>AI 제공자 선택</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>현재 PW 검증 후 변경</t>
+          <t>Gemini/ChatGPT/Claude/Perplexity 등</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -1878,14 +1878,14 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>US-001</t>
+          <t>US-002</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>SETTINGS-004</t>
+          <t>SETTINGS-002</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -1895,12 +1895,12 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>데이터 초기화</t>
+          <t>프로필 변경</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>본인 데이터 전체 삭제</t>
+          <t>닉네임·아바타 이모지</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
@@ -1922,133 +1922,133 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
+          <t>SETTINGS-003</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>설정</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>비밀번호 변경</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>현재 PW 검증 후 변경</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>US-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>SETTINGS-004</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>설정</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>데이터 초기화</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>본인 데이터 전체 삭제</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>US-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
           <t>THEME-001</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t>설정</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr">
+      <c r="C43" s="3" t="inlineStr">
         <is>
           <t>다크/라이트 + 강조색</t>
         </is>
       </c>
-      <c r="D41" s="3" t="inlineStr">
+      <c r="D43" s="3" t="inlineStr">
         <is>
           <t>다크/라이트 + 강조색 3종(핑크/블루/그레이)</t>
         </is>
       </c>
-      <c r="E41" s="3" t="inlineStr">
+      <c r="E43" s="3" t="inlineStr">
         <is>
           <t>일부포함</t>
         </is>
       </c>
-      <c r="F41" s="3" t="inlineStr">
+      <c r="F43" s="3" t="inlineStr">
         <is>
           <t>Should</t>
         </is>
       </c>
-      <c r="G41" s="3" t="inlineStr">
+      <c r="G43" s="3" t="inlineStr">
         <is>
           <t>US-012</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>AI-001</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="inlineStr">
-        <is>
-          <t>Chrome 확장 (외부 AI 세션)</t>
-        </is>
-      </c>
-      <c r="D42" s="4" t="inlineStr">
-        <is>
-          <t>사용자 웹 AI 세션 활용</t>
-        </is>
-      </c>
-      <c r="E42" s="4" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="F42" s="4" t="inlineStr">
-        <is>
-          <t>Could</t>
-        </is>
-      </c>
-      <c r="G42" s="4" t="inlineStr">
-        <is>
-          <t>US-013</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>BACKUP-001</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>설정</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="inlineStr">
-        <is>
-          <t>데이터 내보내기</t>
-        </is>
-      </c>
-      <c r="D43" s="4" t="inlineStr">
-        <is>
-          <t>JSON/CSV 다운로드</t>
-        </is>
-      </c>
-      <c r="E43" s="4" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="F43" s="4" t="inlineStr">
-        <is>
-          <t>Could</t>
-        </is>
-      </c>
-      <c r="G43" s="4" t="inlineStr">
-        <is>
-          <t>US-014</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>HIGHLIGHT-001</t>
+          <t>AI-001</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>콘텐츠</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>본문 하이라이트</t>
+          <t>Chrome 확장 (외부 AI 세션)</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>텍스트 일부 강조 저장</t>
+          <t>사용자 웹 AI 세션 활용</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
@@ -2061,185 +2061,193 @@
           <t>Could</t>
         </is>
       </c>
-      <c r="G44" s="4" t="inlineStr"/>
+      <c r="G44" s="4" t="inlineStr">
+        <is>
+          <t>US-013</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>OFFLINE-001</t>
+          <t>BACKUP-001</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>PWA</t>
+          <t>설정</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>풀 오프라인 모드</t>
+          <t>데이터 내보내기</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>네트워크 없이 모든 기능</t>
+          <t>JSON/CSV 다운로드</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>미포함</t>
+          <t>보류</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>Won't</t>
+          <t>Could</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>US-015</t>
+          <t>US-014</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>NATIVE-001</t>
+          <t>HIGHLIGHT-001</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>PWA</t>
+          <t>콘텐츠</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>네이티브 앱</t>
+          <t>본문 하이라이트</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>iOS/Android 스토어</t>
+          <t>텍스트 일부 강조 저장</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>미포함</t>
+          <t>보류</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>Won't</t>
-        </is>
-      </c>
-      <c r="G46" s="4" t="inlineStr">
-        <is>
-          <t>US-016</t>
-        </is>
-      </c>
+          <t>Could</t>
+        </is>
+      </c>
+      <c r="G46" s="4" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
+          <t>OFFLINE-001</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>PWA</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>풀 오프라인 모드</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>네트워크 없이 모든 기능</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>미포함</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>Won't</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="inlineStr">
+        <is>
+          <t>US-015</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>NATIVE-001</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>PWA</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>네이티브 앱</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>iOS/Android 스토어</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>미포함</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>Won't</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="inlineStr">
+        <is>
+          <t>US-016</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
           <t>BILLING-001</t>
         </is>
       </c>
-      <c r="B47" s="4" t="inlineStr">
+      <c r="B49" s="4" t="inlineStr">
         <is>
           <t>계정</t>
         </is>
       </c>
-      <c r="C47" s="4" t="inlineStr">
+      <c r="C49" s="4" t="inlineStr">
         <is>
           <t>유료 플랜</t>
         </is>
       </c>
-      <c r="D47" s="4" t="inlineStr">
+      <c r="D49" s="4" t="inlineStr">
         <is>
           <t>결제·구독</t>
         </is>
       </c>
-      <c r="E47" s="4" t="inlineStr">
+      <c r="E49" s="4" t="inlineStr">
         <is>
           <t>미포함</t>
         </is>
       </c>
-      <c r="F47" s="4" t="inlineStr">
+      <c r="F49" s="4" t="inlineStr">
         <is>
           <t>Won't</t>
         </is>
       </c>
-      <c r="G47" s="4" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>POLICY-AUTH</t>
-        </is>
-      </c>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>정책</t>
-        </is>
-      </c>
-      <c r="C48" s="3" t="inlineStr">
-        <is>
-          <t>토큰 만료/갱신</t>
-        </is>
-      </c>
-      <c r="D48" s="3" t="inlineStr">
-        <is>
-          <t>JWT 액세스 15분 + 리프레시 30일</t>
-        </is>
-      </c>
-      <c r="E48" s="3" t="inlineStr">
-        <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="F48" s="3" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G48" s="3" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>POLICY-AI</t>
-        </is>
-      </c>
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t>정책</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="inlineStr">
-        <is>
-          <t>AI 요약 호출</t>
-        </is>
-      </c>
-      <c r="D49" s="3" t="inlineStr">
-        <is>
-          <t>외부 세션→API→mock 폴백 사다리</t>
-        </is>
-      </c>
-      <c r="E49" s="3" t="inlineStr">
-        <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="F49" s="3" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G49" s="3" t="inlineStr"/>
+      <c r="G49" s="4" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>POLICY-LOCAL</t>
+          <t>POLICY-AUTH</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -2249,12 +2257,12 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>로컬·서버 저장 분리</t>
+          <t>토큰 만료/갱신</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>게스트 로컬 / 정식 서버+캐시, 오프라인 큐잉</t>
+          <t>JWT 액세스 15분 + 리프레시 30일</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
@@ -2272,35 +2280,101 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
+          <t>POLICY-AI</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>정책</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>AI 요약 호출</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>외부 세션→API→mock 폴백 사다리</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>POLICY-LOCAL</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>정책</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>로컬·서버 저장 분리</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>게스트 로컬 / 정식 서버+캐시, 오프라인 큐잉</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
           <t>POLICY-SHARED</t>
         </is>
       </c>
-      <c r="B51" s="3" t="inlineStr">
+      <c r="B53" s="3" t="inlineStr">
         <is>
           <t>정책</t>
         </is>
       </c>
-      <c r="C51" s="3" t="inlineStr">
+      <c r="C53" s="3" t="inlineStr">
         <is>
           <t>공유 폴더 권한</t>
         </is>
       </c>
-      <c r="D51" s="3" t="inlineStr">
+      <c r="D53" s="3" t="inlineStr">
         <is>
           <t>owner/member/viewer + 토큰 7일</t>
         </is>
       </c>
-      <c r="E51" s="3" t="inlineStr">
+      <c r="E53" s="3" t="inlineStr">
         <is>
           <t>일부포함</t>
         </is>
       </c>
-      <c r="F51" s="3" t="inlineStr">
+      <c r="F53" s="3" t="inlineStr">
         <is>
           <t>Should</t>
         </is>
       </c>
-      <c r="G51" s="3" t="inlineStr"/>
+      <c r="G53" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2316,7 +2390,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J212"/>
+  <dimension ref="A1:J222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4529,402 +4603,476 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
+          <t>TODO-009
+#TODO-CREATE
+#TODO-EDIT
+#LINK-DETAIL</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>할일</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>할 일 가시성 (공유 폴더)</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="inlineStr">
+        <is>
+          <t>공유 폴더 link의 할 일은 🔒 나만 보기(default) / 👥 공유자에게 공유 선택. 개인 폴더는 옵션 비노출, 자동 private. 메모는 가시성 옵션 없음, 항상 작성자 전용 + '🔒 나만 볼 수 있는 내용입니다' 안내</t>
+        </is>
+      </c>
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G83" s="3" t="inlineStr">
+        <is>
+          <t>POST /links/:id/todos (visibility)
+PATCH /todos/:id (visibility)</t>
+        </is>
+      </c>
+      <c r="H83" s="3" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="I83" s="3" t="inlineStr">
+        <is>
+          <t>기획완료</t>
+        </is>
+      </c>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>메모는 항상 private + 안내 문구. 공유 폴더에서만 가시성 chip 노출</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr"/>
+      <c r="B84" s="3" t="inlineStr"/>
+      <c r="C84" s="3" t="inlineStr"/>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>입력</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="inlineStr">
+        <is>
+          <t>visibility: 'private' | 'public'</t>
+        </is>
+      </c>
+      <c r="F84" s="3" t="inlineStr"/>
+      <c r="G84" s="3" t="inlineStr"/>
+      <c r="H84" s="3" t="inlineStr"/>
+      <c r="I84" s="3" t="inlineStr"/>
+      <c r="J84" s="3" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr"/>
+      <c r="B85" s="3" t="inlineStr"/>
+      <c r="C85" s="3" t="inlineStr"/>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>출력</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>link_todos.visibility UPDATE + 공개로 변경 시 멤버에게 Realtime 노출</t>
+        </is>
+      </c>
+      <c r="F85" s="3" t="inlineStr"/>
+      <c r="G85" s="3" t="inlineStr"/>
+      <c r="H85" s="3" t="inlineStr"/>
+      <c r="I85" s="3" t="inlineStr"/>
+      <c r="J85" s="3" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="inlineStr"/>
+      <c r="B86" s="3" t="inlineStr"/>
+      <c r="C86" s="3" t="inlineStr"/>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>정책</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="inlineStr">
+        <is>
+          <t>[기본값] private
+[개인 폴더] visibility 자동 private, UI에 노출 안 함
+[메모] 가시성 변경 불가
+[작성자 표시] public todo는 멤버 화면에 '👥 {닉네임}이 공유한 할 일' 라벨</t>
+        </is>
+      </c>
+      <c r="F86" s="3" t="inlineStr"/>
+      <c r="G86" s="3" t="inlineStr"/>
+      <c r="H86" s="3" t="inlineStr"/>
+      <c r="I86" s="3" t="inlineStr"/>
+      <c r="J86" s="3" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="inlineStr"/>
+      <c r="B87" s="3" t="inlineStr"/>
+      <c r="C87" s="3" t="inlineStr"/>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="inlineStr">
+        <is>
+          <t>- 비멤버 공유 todo 조회: 403
+- 메모를 공개로 변경 시도: API에서 차단</t>
+        </is>
+      </c>
+      <c r="F87" s="3" t="inlineStr"/>
+      <c r="G87" s="3" t="inlineStr"/>
+      <c r="H87" s="3" t="inlineStr"/>
+      <c r="I87" s="3" t="inlineStr"/>
+      <c r="J87" s="3" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t>TODO-010
+#TODO-LIST
+#LINK-DETAIL</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>할일</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>공개 할 일 수락 흐름</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="inlineStr">
+        <is>
+          <t>공유 폴더에서 멤버 A가 public todo 등록 → 멤버 B는 화면에서 보지만 '내 할 일에 추가' 수락해야 본인 알림으로 등록. 미수락은 표시만 (정보 공유 수준)</t>
+        </is>
+      </c>
+      <c r="F88" s="3" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G88" s="3" t="inlineStr">
+        <is>
+          <t>POST /todos/:id/accept
+DELETE /todos/:id/accept
+GET /todos/:id/acceptances</t>
+        </is>
+      </c>
+      <c r="H88" s="3" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="I88" s="3" t="inlineStr">
+        <is>
+          <t>기획완료</t>
+        </is>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>의도치 않은 알림 폭탄 방지. 작성자에게 누가 수락했는지 카운터 표시</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr"/>
+      <c r="B89" s="3" t="inlineStr"/>
+      <c r="C89" s="3" t="inlineStr"/>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t>입력</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="inlineStr">
+        <is>
+          <t>todoId (수락 또는 취소)</t>
+        </is>
+      </c>
+      <c r="F89" s="3" t="inlineStr"/>
+      <c r="G89" s="3" t="inlineStr"/>
+      <c r="H89" s="3" t="inlineStr"/>
+      <c r="I89" s="3" t="inlineStr"/>
+      <c r="J89" s="3" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="inlineStr"/>
+      <c r="B90" s="3" t="inlineStr"/>
+      <c r="C90" s="3" t="inlineStr"/>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t>출력</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="inlineStr">
+        <is>
+          <t>todo_acceptances INSERT/DELETE + WebSocket TODO_ACCEPTED</t>
+        </is>
+      </c>
+      <c r="F90" s="3" t="inlineStr"/>
+      <c r="G90" s="3" t="inlineStr"/>
+      <c r="H90" s="3" t="inlineStr"/>
+      <c r="I90" s="3" t="inlineStr"/>
+      <c r="J90" s="3" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="inlineStr"/>
+      <c r="B91" s="3" t="inlineStr"/>
+      <c r="C91" s="3" t="inlineStr"/>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t>정책</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="inlineStr">
+        <is>
+          <t>[수락 UI] 공개 todo 카드에 '내 할 일에 추가' 버튼. 수락 후 '✓ 추가됨'
+[작성자] '👥 N명 수락' 카운터
+[알림 발송] 작성자 + 수락 멤버에게만 FCM
+[회차별 완료] 수락 멤버는 본인 occurrences 따로 관리</t>
+        </is>
+      </c>
+      <c r="F91" s="3" t="inlineStr"/>
+      <c r="G91" s="3" t="inlineStr"/>
+      <c r="H91" s="3" t="inlineStr"/>
+      <c r="I91" s="3" t="inlineStr"/>
+      <c r="J91" s="3" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="inlineStr"/>
+      <c r="B92" s="3" t="inlineStr"/>
+      <c r="C92" s="3" t="inlineStr"/>
+      <c r="D92" s="3" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="inlineStr">
+        <is>
+          <t>- 본인이 작성자: 수락 버튼 비활성
+- 비멤버: 403
+- 이미 수락: '이미 추가됨'</t>
+        </is>
+      </c>
+      <c r="F92" s="3" t="inlineStr"/>
+      <c r="G92" s="3" t="inlineStr"/>
+      <c r="H92" s="3" t="inlineStr"/>
+      <c r="I92" s="3" t="inlineStr"/>
+      <c r="J92" s="3" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="inlineStr">
+        <is>
           <t>TODO-006</t>
         </is>
       </c>
-      <c r="B83" s="3" t="inlineStr">
+      <c r="B93" s="3" t="inlineStr">
         <is>
           <t>할일</t>
         </is>
       </c>
-      <c r="C83" s="3" t="inlineStr">
+      <c r="C93" s="3" t="inlineStr">
         <is>
           <t>캘린더 .ics 내보내기</t>
         </is>
       </c>
-      <c r="D83" s="3" t="inlineStr">
+      <c r="D93" s="3" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="E83" s="3" t="inlineStr">
+      <c r="E93" s="3" t="inlineStr">
         <is>
           <t>할 일 → .ics 파일로 다운로드. 외부 캘린더 import. 반복 알림은 RRULE로 변환</t>
         </is>
       </c>
-      <c r="F83" s="3" t="inlineStr">
+      <c r="F93" s="3" t="inlineStr">
         <is>
           <t>Should</t>
         </is>
       </c>
-      <c r="G83" s="3" t="inlineStr"/>
-      <c r="H83" s="3" t="inlineStr">
+      <c r="G93" s="3" t="inlineStr"/>
+      <c r="H93" s="3" t="inlineStr">
         <is>
           <t>일부포함</t>
         </is>
       </c>
-      <c r="I83" s="3" t="inlineStr">
+      <c r="I93" s="3" t="inlineStr">
         <is>
           <t>기획중</t>
         </is>
       </c>
-      <c r="J83" s="3" t="inlineStr">
+      <c r="J93" s="3" t="inlineStr">
         <is>
           <t>외부 캘린더(Google/Apple/네이버) 연동</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="4" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="4" t="inlineStr">
         <is>
           <t>TODO-007</t>
         </is>
       </c>
-      <c r="B84" s="4" t="inlineStr">
+      <c r="B94" s="4" t="inlineStr">
         <is>
           <t>할일</t>
         </is>
       </c>
-      <c r="C84" s="4" t="inlineStr">
+      <c r="C94" s="4" t="inlineStr">
         <is>
           <t>채용 마감일 자동 추출</t>
         </is>
       </c>
-      <c r="D84" s="4" t="inlineStr">
+      <c r="D94" s="4" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="E84" s="4" t="inlineStr">
+      <c r="E94" s="4" t="inlineStr">
         <is>
           <t>채용 공고 도메인 인식 → AI가 마감일 파싱 → 할 일 제안 (D-3 자소서, D-1 포트폴리오, 당일 지원)</t>
         </is>
       </c>
-      <c r="F84" s="4" t="inlineStr">
+      <c r="F94" s="4" t="inlineStr">
         <is>
           <t>Could</t>
         </is>
       </c>
-      <c r="G84" s="4" t="inlineStr"/>
-      <c r="H84" s="4" t="inlineStr">
+      <c r="G94" s="4" t="inlineStr"/>
+      <c r="H94" s="4" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="I84" s="4" t="inlineStr">
+      <c r="I94" s="4" t="inlineStr">
         <is>
           <t>기획중</t>
         </is>
       </c>
-      <c r="J84" s="4" t="inlineStr">
+      <c r="J94" s="4" t="inlineStr">
         <is>
           <t>v1.x — 채용 도메인(잡코리아/사람인/원티드/링커리어) 패턴 학습</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="4" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t>TODO-008</t>
         </is>
       </c>
-      <c r="B88" s="4" t="inlineStr">
+      <c r="B98" s="4" t="inlineStr">
         <is>
           <t>할일</t>
         </is>
       </c>
-      <c r="C88" s="4" t="inlineStr">
+      <c r="C98" s="4" t="inlineStr">
         <is>
           <t>AI 할 일 추천</t>
         </is>
       </c>
-      <c r="D88" s="4" t="inlineStr">
+      <c r="D98" s="4" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="E88" s="4" t="inlineStr">
+      <c r="E98" s="4" t="inlineStr">
         <is>
           <t>링크 본문 분석 → 액션 아이템 추출 → 할 일 후보로 사용자에게 제안</t>
         </is>
       </c>
-      <c r="F88" s="4" t="inlineStr">
+      <c r="F98" s="4" t="inlineStr">
         <is>
           <t>Could</t>
         </is>
       </c>
-      <c r="G88" s="4" t="inlineStr"/>
-      <c r="H88" s="4" t="inlineStr">
+      <c r="G98" s="4" t="inlineStr"/>
+      <c r="H98" s="4" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="I88" s="4" t="inlineStr">
+      <c r="I98" s="4" t="inlineStr">
         <is>
           <t>기획중</t>
         </is>
       </c>
-      <c r="J88" s="4" t="inlineStr">
+      <c r="J98" s="4" t="inlineStr">
         <is>
           <t>본문 요약 → 할 일 후보 추출</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="3" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="3" t="inlineStr">
         <is>
           <t>QR-001
 #LINK-ADD
 #QR-SCAN</t>
         </is>
       </c>
-      <c r="B92" s="3" t="inlineStr">
+      <c r="B102" s="3" t="inlineStr">
         <is>
           <t>링크</t>
         </is>
       </c>
-      <c r="C92" s="3" t="inlineStr">
+      <c r="C102" s="3" t="inlineStr">
         <is>
           <t>카메라 QR 스캔 (모바일)</t>
         </is>
       </c>
-      <c r="D92" s="3" t="inlineStr">
+      <c r="D102" s="3" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="E92" s="3" t="inlineStr">
+      <c r="E102" s="3" t="inlineStr">
         <is>
           <t>html5-qrcode로 카메라 스트림 인식. URL 형태의 QR이면 #LINK-ADD에 자동 채움. 데스크톱 웹에서는 비활성</t>
         </is>
       </c>
-      <c r="F92" s="3" t="inlineStr">
+      <c r="F102" s="3" t="inlineStr">
         <is>
           <t>Must</t>
         </is>
       </c>
-      <c r="G92" s="3" t="inlineStr">
+      <c r="G102" s="3" t="inlineStr">
         <is>
           <t>(클라이언트, html5-qrcode)</t>
         </is>
       </c>
-      <c r="H92" s="3" t="inlineStr">
+      <c r="H102" s="3" t="inlineStr">
         <is>
           <t>MVP</t>
         </is>
       </c>
-      <c r="I92" s="3" t="inlineStr">
+      <c r="I102" s="3" t="inlineStr">
         <is>
           <t>기획완료</t>
         </is>
       </c>
-      <c r="J92" s="3" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="3" t="inlineStr"/>
-      <c r="B93" s="3" t="inlineStr"/>
-      <c r="C93" s="3" t="inlineStr"/>
-      <c r="D93" s="3" t="inlineStr">
-        <is>
-          <t>입력</t>
-        </is>
-      </c>
-      <c r="E93" s="3" t="inlineStr">
-        <is>
-          <t>(자동) MediaStream
-사용자: QR 비추기</t>
-        </is>
-      </c>
-      <c r="F93" s="3" t="inlineStr"/>
-      <c r="G93" s="3" t="inlineStr"/>
-      <c r="H93" s="3" t="inlineStr"/>
-      <c r="I93" s="3" t="inlineStr"/>
-      <c r="J93" s="3" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="3" t="inlineStr"/>
-      <c r="B94" s="3" t="inlineStr"/>
-      <c r="C94" s="3" t="inlineStr"/>
-      <c r="D94" s="3" t="inlineStr">
-        <is>
-          <t>출력</t>
-        </is>
-      </c>
-      <c r="E94" s="3" t="inlineStr">
-        <is>
-          <t>- URL 추출 → #LINK-ADD 입력창 채움</t>
-        </is>
-      </c>
-      <c r="F94" s="3" t="inlineStr"/>
-      <c r="G94" s="3" t="inlineStr"/>
-      <c r="H94" s="3" t="inlineStr"/>
-      <c r="I94" s="3" t="inlineStr"/>
-      <c r="J94" s="3" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="3" t="inlineStr"/>
-      <c r="B95" s="3" t="inlineStr"/>
-      <c r="C95" s="3" t="inlineStr"/>
-      <c r="D95" s="3" t="inlineStr">
-        <is>
-          <t>정책</t>
-        </is>
-      </c>
-      <c r="E95" s="3" t="inlineStr">
-        <is>
-          <t>[권한] 카메라 권한 거부 시 URL 직접 입력 폴백 + 안내
-[환경] HTTPS 또는 localhost 필수
-[차별 인터랙션] 모바일 전용. 웹에서는 QR 탭 비활성 + 툴팁 "모바일에서 사용 가능해요"</t>
-        </is>
-      </c>
-      <c r="F95" s="3" t="inlineStr"/>
-      <c r="G95" s="3" t="inlineStr"/>
-      <c r="H95" s="3" t="inlineStr"/>
-      <c r="I95" s="3" t="inlineStr"/>
-      <c r="J95" s="3" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="3" t="inlineStr"/>
-      <c r="B96" s="3" t="inlineStr"/>
-      <c r="C96" s="3" t="inlineStr"/>
-      <c r="D96" s="3" t="inlineStr">
-        <is>
-          <t>예외</t>
-        </is>
-      </c>
-      <c r="E96" s="3" t="inlineStr">
-        <is>
-          <t>- 권한 거부: '카메라 권한이 필요해요. 설정에서 허용해주세요'
-- HTTPS 아님: 'QR 스캔은 보안 연결에서만 동작해요'
-- 인식 실패 10초: '다시 비춰주세요' + Mock 입력(개발용)
-- URL이 아닌 QR: 'URL이 아닌 QR이에요'</t>
-        </is>
-      </c>
-      <c r="F96" s="3" t="inlineStr"/>
-      <c r="G96" s="3" t="inlineStr"/>
-      <c r="H96" s="3" t="inlineStr"/>
-      <c r="I96" s="3" t="inlineStr"/>
-      <c r="J96" s="3" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="4" t="inlineStr">
-        <is>
-          <t>QR-002</t>
-        </is>
-      </c>
-      <c r="B97" s="4" t="inlineStr">
-        <is>
-          <t>링크</t>
-        </is>
-      </c>
-      <c r="C97" s="4" t="inlineStr">
-        <is>
-          <t>갤러리 QR 인식</t>
-        </is>
-      </c>
-      <c r="D97" s="4" t="inlineStr">
-        <is>
-          <t>설명</t>
-        </is>
-      </c>
-      <c r="E97" s="4" t="inlineStr">
-        <is>
-          <t>사진첩 이미지에서 QR 추출 (Media Capture + jsQR)</t>
-        </is>
-      </c>
-      <c r="F97" s="4" t="inlineStr">
-        <is>
-          <t>Could</t>
-        </is>
-      </c>
-      <c r="G97" s="4" t="inlineStr"/>
-      <c r="H97" s="4" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="I97" s="4" t="inlineStr">
-        <is>
-          <t>기획중</t>
-        </is>
-      </c>
-      <c r="J97" s="4" t="inlineStr">
-        <is>
-          <t>v1.x 추가 예정</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="3" t="inlineStr">
-        <is>
-          <t>FOLDER-001
-#FOLDER-LIST
-#FOLDER-CREATE
-#FOLDER-DETAIL</t>
-        </is>
-      </c>
-      <c r="B101" s="3" t="inlineStr">
-        <is>
-          <t>폴더</t>
-        </is>
-      </c>
-      <c r="C101" s="3" t="inlineStr">
-        <is>
-          <t>폴더 생성/수정/삭제</t>
-        </is>
-      </c>
-      <c r="D101" s="3" t="inlineStr">
-        <is>
-          <t>설명</t>
-        </is>
-      </c>
-      <c r="E101" s="3" t="inlineStr">
-        <is>
-          <t>이모지 + 이름으로 폴더 관리. 시스템 폴더 "미분류"는 삭제 불가. 공유 폴더는 SHARE-001 참고</t>
-        </is>
-      </c>
-      <c r="F101" s="3" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G101" s="3" t="inlineStr">
-        <is>
-          <t>폴더 CRUD API</t>
-        </is>
-      </c>
-      <c r="H101" s="3" t="inlineStr">
-        <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="I101" s="3" t="inlineStr">
-        <is>
-          <t>기획완료</t>
-        </is>
-      </c>
-      <c r="J101" s="3" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="3" t="inlineStr"/>
-      <c r="B102" s="3" t="inlineStr"/>
-      <c r="C102" s="3" t="inlineStr"/>
-      <c r="D102" s="3" t="inlineStr">
-        <is>
-          <t>입력</t>
-        </is>
-      </c>
-      <c r="E102" s="3" t="inlineStr">
-        <is>
-          <t>(생성) 이름 1~30자, 이모지
-(수정) 이름·이모지 변경
-(삭제) 폴더 ID + 확인</t>
-        </is>
-      </c>
-      <c r="F102" s="3" t="inlineStr"/>
-      <c r="G102" s="3" t="inlineStr"/>
-      <c r="H102" s="3" t="inlineStr"/>
-      <c r="I102" s="3" t="inlineStr"/>
       <c r="J102" s="3" t="inlineStr"/>
     </row>
     <row r="103">
@@ -4933,12 +5081,13 @@
       <c r="C103" s="3" t="inlineStr"/>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t>출력</t>
+          <t>입력</t>
         </is>
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>folders INSERT/UPDATE/DELETE + Realtime</t>
+          <t>(자동) MediaStream
+사용자: QR 비추기</t>
         </is>
       </c>
       <c r="F103" s="3" t="inlineStr"/>
@@ -4953,15 +5102,12 @@
       <c r="C104" s="3" t="inlineStr"/>
       <c r="D104" s="3" t="inlineStr">
         <is>
-          <t>정책</t>
+          <t>출력</t>
         </is>
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
-          <t>[기본값] 이모지=📁
-[제약] 폴더 100개 한도
-[삭제 처리] 폴더 삭제 시 소속 링크는 folder_id=NULL (미분류로 자동 이동)
-[공유 폴더] owner만 이름·이모지 변경 가능</t>
+          <t>- URL 추출 → #LINK-ADD 입력창 채움</t>
         </is>
       </c>
       <c r="F104" s="3" t="inlineStr"/>
@@ -4976,10 +5122,219 @@
       <c r="C105" s="3" t="inlineStr"/>
       <c r="D105" s="3" t="inlineStr">
         <is>
+          <t>정책</t>
+        </is>
+      </c>
+      <c r="E105" s="3" t="inlineStr">
+        <is>
+          <t>[권한] 카메라 권한 거부 시 URL 직접 입력 폴백 + 안내
+[환경] HTTPS 또는 localhost 필수
+[차별 인터랙션] 모바일 전용. 웹에서는 QR 탭 비활성 + 툴팁 "모바일에서 사용 가능해요"</t>
+        </is>
+      </c>
+      <c r="F105" s="3" t="inlineStr"/>
+      <c r="G105" s="3" t="inlineStr"/>
+      <c r="H105" s="3" t="inlineStr"/>
+      <c r="I105" s="3" t="inlineStr"/>
+      <c r="J105" s="3" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="3" t="inlineStr"/>
+      <c r="B106" s="3" t="inlineStr"/>
+      <c r="C106" s="3" t="inlineStr"/>
+      <c r="D106" s="3" t="inlineStr">
+        <is>
           <t>예외</t>
         </is>
       </c>
-      <c r="E105" s="3" t="inlineStr">
+      <c r="E106" s="3" t="inlineStr">
+        <is>
+          <t>- 권한 거부: '카메라 권한이 필요해요. 설정에서 허용해주세요'
+- HTTPS 아님: 'QR 스캔은 보안 연결에서만 동작해요'
+- 인식 실패 10초: '다시 비춰주세요' + Mock 입력(개발용)
+- URL이 아닌 QR: 'URL이 아닌 QR이에요'</t>
+        </is>
+      </c>
+      <c r="F106" s="3" t="inlineStr"/>
+      <c r="G106" s="3" t="inlineStr"/>
+      <c r="H106" s="3" t="inlineStr"/>
+      <c r="I106" s="3" t="inlineStr"/>
+      <c r="J106" s="3" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="4" t="inlineStr">
+        <is>
+          <t>QR-002</t>
+        </is>
+      </c>
+      <c r="B107" s="4" t="inlineStr">
+        <is>
+          <t>링크</t>
+        </is>
+      </c>
+      <c r="C107" s="4" t="inlineStr">
+        <is>
+          <t>갤러리 QR 인식</t>
+        </is>
+      </c>
+      <c r="D107" s="4" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+      <c r="E107" s="4" t="inlineStr">
+        <is>
+          <t>사진첩 이미지에서 QR 추출 (Media Capture + jsQR)</t>
+        </is>
+      </c>
+      <c r="F107" s="4" t="inlineStr">
+        <is>
+          <t>Could</t>
+        </is>
+      </c>
+      <c r="G107" s="4" t="inlineStr"/>
+      <c r="H107" s="4" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="I107" s="4" t="inlineStr">
+        <is>
+          <t>기획중</t>
+        </is>
+      </c>
+      <c r="J107" s="4" t="inlineStr">
+        <is>
+          <t>v1.x 추가 예정</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="3" t="inlineStr">
+        <is>
+          <t>FOLDER-001
+#FOLDER-LIST
+#FOLDER-CREATE
+#FOLDER-DETAIL</t>
+        </is>
+      </c>
+      <c r="B111" s="3" t="inlineStr">
+        <is>
+          <t>폴더</t>
+        </is>
+      </c>
+      <c r="C111" s="3" t="inlineStr">
+        <is>
+          <t>폴더 생성/수정/삭제</t>
+        </is>
+      </c>
+      <c r="D111" s="3" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+      <c r="E111" s="3" t="inlineStr">
+        <is>
+          <t>이모지 + 이름으로 폴더 관리. 시스템 폴더 "미분류"는 삭제 불가. 공유 폴더는 SHARE-001 참고</t>
+        </is>
+      </c>
+      <c r="F111" s="3" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G111" s="3" t="inlineStr">
+        <is>
+          <t>폴더 CRUD API</t>
+        </is>
+      </c>
+      <c r="H111" s="3" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="I111" s="3" t="inlineStr">
+        <is>
+          <t>기획완료</t>
+        </is>
+      </c>
+      <c r="J111" s="3" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="3" t="inlineStr"/>
+      <c r="B112" s="3" t="inlineStr"/>
+      <c r="C112" s="3" t="inlineStr"/>
+      <c r="D112" s="3" t="inlineStr">
+        <is>
+          <t>입력</t>
+        </is>
+      </c>
+      <c r="E112" s="3" t="inlineStr">
+        <is>
+          <t>(생성) 이름 1~30자, 이모지
+(수정) 이름·이모지 변경
+(삭제) 폴더 ID + 확인</t>
+        </is>
+      </c>
+      <c r="F112" s="3" t="inlineStr"/>
+      <c r="G112" s="3" t="inlineStr"/>
+      <c r="H112" s="3" t="inlineStr"/>
+      <c r="I112" s="3" t="inlineStr"/>
+      <c r="J112" s="3" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="3" t="inlineStr"/>
+      <c r="B113" s="3" t="inlineStr"/>
+      <c r="C113" s="3" t="inlineStr"/>
+      <c r="D113" s="3" t="inlineStr">
+        <is>
+          <t>출력</t>
+        </is>
+      </c>
+      <c r="E113" s="3" t="inlineStr">
+        <is>
+          <t>folders INSERT/UPDATE/DELETE + Realtime</t>
+        </is>
+      </c>
+      <c r="F113" s="3" t="inlineStr"/>
+      <c r="G113" s="3" t="inlineStr"/>
+      <c r="H113" s="3" t="inlineStr"/>
+      <c r="I113" s="3" t="inlineStr"/>
+      <c r="J113" s="3" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="3" t="inlineStr"/>
+      <c r="B114" s="3" t="inlineStr"/>
+      <c r="C114" s="3" t="inlineStr"/>
+      <c r="D114" s="3" t="inlineStr">
+        <is>
+          <t>정책</t>
+        </is>
+      </c>
+      <c r="E114" s="3" t="inlineStr">
+        <is>
+          <t>[기본값] 이모지=📁
+[제약] 폴더 100개 한도
+[삭제 처리] 폴더 삭제 시 소속 링크는 folder_id=NULL (미분류로 자동 이동)
+[공유 폴더] owner만 이름·이모지 변경 가능</t>
+        </is>
+      </c>
+      <c r="F114" s="3" t="inlineStr"/>
+      <c r="G114" s="3" t="inlineStr"/>
+      <c r="H114" s="3" t="inlineStr"/>
+      <c r="I114" s="3" t="inlineStr"/>
+      <c r="J114" s="3" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="3" t="inlineStr"/>
+      <c r="B115" s="3" t="inlineStr"/>
+      <c r="C115" s="3" t="inlineStr"/>
+      <c r="D115" s="3" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="E115" s="3" t="inlineStr">
         <is>
           <t>- 빈 이름: '폴더 이름을 입력해주세요'
 - 30자 초과: 입력 자체 차단
@@ -4988,274 +5343,6 @@
 - 100개 한도: '폴더는 최대 100개까지'</t>
         </is>
       </c>
-      <c r="F105" s="3" t="inlineStr"/>
-      <c r="G105" s="3" t="inlineStr"/>
-      <c r="H105" s="3" t="inlineStr"/>
-      <c r="I105" s="3" t="inlineStr"/>
-      <c r="J105" s="3" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="3" t="inlineStr">
-        <is>
-          <t>FOLDER-002
-#LINK-DETAIL
-#FOLDER-PICKER</t>
-        </is>
-      </c>
-      <c r="B106" s="3" t="inlineStr">
-        <is>
-          <t>폴더</t>
-        </is>
-      </c>
-      <c r="C106" s="3" t="inlineStr">
-        <is>
-          <t>폴더 이동</t>
-        </is>
-      </c>
-      <c r="D106" s="3" t="inlineStr">
-        <is>
-          <t>설명</t>
-        </is>
-      </c>
-      <c r="E106" s="3" t="inlineStr">
-        <is>
-          <t>링크 상세에서 폴더 변경. 픽커 모달에 사용자 폴더 + 미분류 노출</t>
-        </is>
-      </c>
-      <c r="F106" s="3" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G106" s="3" t="inlineStr">
-        <is>
-          <t>링크 폴더 이동 API</t>
-        </is>
-      </c>
-      <c r="H106" s="3" t="inlineStr">
-        <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="I106" s="3" t="inlineStr">
-        <is>
-          <t>기획완료</t>
-        </is>
-      </c>
-      <c r="J106" s="3" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="3" t="inlineStr"/>
-      <c r="B107" s="3" t="inlineStr"/>
-      <c r="C107" s="3" t="inlineStr"/>
-      <c r="D107" s="3" t="inlineStr">
-        <is>
-          <t>입력</t>
-        </is>
-      </c>
-      <c r="E107" s="3" t="inlineStr">
-        <is>
-          <t>link_id, target_folder_id</t>
-        </is>
-      </c>
-      <c r="F107" s="3" t="inlineStr"/>
-      <c r="G107" s="3" t="inlineStr"/>
-      <c r="H107" s="3" t="inlineStr"/>
-      <c r="I107" s="3" t="inlineStr"/>
-      <c r="J107" s="3" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="3" t="inlineStr"/>
-      <c r="B108" s="3" t="inlineStr"/>
-      <c r="C108" s="3" t="inlineStr"/>
-      <c r="D108" s="3" t="inlineStr">
-        <is>
-          <t>출력</t>
-        </is>
-      </c>
-      <c r="E108" s="3" t="inlineStr">
-        <is>
-          <t>links.folder_id UPDATE + Realtime</t>
-        </is>
-      </c>
-      <c r="F108" s="3" t="inlineStr"/>
-      <c r="G108" s="3" t="inlineStr"/>
-      <c r="H108" s="3" t="inlineStr"/>
-      <c r="I108" s="3" t="inlineStr"/>
-      <c r="J108" s="3" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="3" t="inlineStr"/>
-      <c r="B109" s="3" t="inlineStr"/>
-      <c r="C109" s="3" t="inlineStr"/>
-      <c r="D109" s="3" t="inlineStr">
-        <is>
-          <t>정책</t>
-        </is>
-      </c>
-      <c r="E109" s="3" t="inlineStr">
-        <is>
-          <t>[동기화] 다른 디바이스에서 카드가 다른 폴더로 부드럽게 이동</t>
-        </is>
-      </c>
-      <c r="F109" s="3" t="inlineStr"/>
-      <c r="G109" s="3" t="inlineStr"/>
-      <c r="H109" s="3" t="inlineStr"/>
-      <c r="I109" s="3" t="inlineStr"/>
-      <c r="J109" s="3" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="3" t="inlineStr"/>
-      <c r="B110" s="3" t="inlineStr"/>
-      <c r="C110" s="3" t="inlineStr"/>
-      <c r="D110" s="3" t="inlineStr">
-        <is>
-          <t>예외</t>
-        </is>
-      </c>
-      <c r="E110" s="3" t="inlineStr">
-        <is>
-          <t>- 공유 폴더(viewer 권한)로 이동 시도: '읽기 권한 폴더에는 옮길 수 없어요'
-- 삭제된 폴더 ID: 미분류로 자동 fallback</t>
-        </is>
-      </c>
-      <c r="F110" s="3" t="inlineStr"/>
-      <c r="G110" s="3" t="inlineStr"/>
-      <c r="H110" s="3" t="inlineStr"/>
-      <c r="I110" s="3" t="inlineStr"/>
-      <c r="J110" s="3" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="3" t="inlineStr">
-        <is>
-          <t>HOME-001
-#HOME
-#HOME-EMPTY</t>
-        </is>
-      </c>
-      <c r="B111" s="3" t="inlineStr">
-        <is>
-          <t>홈</t>
-        </is>
-      </c>
-      <c r="C111" s="3" t="inlineStr">
-        <is>
-          <t>홈 피드</t>
-        </is>
-      </c>
-      <c r="D111" s="3" t="inlineStr">
-        <is>
-          <t>설명</t>
-        </is>
-      </c>
-      <c r="E111" s="3" t="inlineStr">
-        <is>
-          <t>사용자의 모든 링크를 created_at desc로 무한 스크롤. 페이지당 30개. 게스트 시드 데이터 또는 Empty State</t>
-        </is>
-      </c>
-      <c r="F111" s="3" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G111" s="3" t="inlineStr">
-        <is>
-          <t>링크 목록 API (cursor)</t>
-        </is>
-      </c>
-      <c r="H111" s="3" t="inlineStr">
-        <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="I111" s="3" t="inlineStr">
-        <is>
-          <t>기획완료</t>
-        </is>
-      </c>
-      <c r="J111" s="3" t="inlineStr">
-        <is>
-          <t>TBD: 사용자 설정으로 인기/오래된순 추가?</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="3" t="inlineStr"/>
-      <c r="B112" s="3" t="inlineStr"/>
-      <c r="C112" s="3" t="inlineStr"/>
-      <c r="D112" s="3" t="inlineStr">
-        <is>
-          <t>입력</t>
-        </is>
-      </c>
-      <c r="E112" s="3" t="inlineStr">
-        <is>
-          <t>(자동) cursor (last_created_at)</t>
-        </is>
-      </c>
-      <c r="F112" s="3" t="inlineStr"/>
-      <c r="G112" s="3" t="inlineStr"/>
-      <c r="H112" s="3" t="inlineStr"/>
-      <c r="I112" s="3" t="inlineStr"/>
-      <c r="J112" s="3" t="inlineStr"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="3" t="inlineStr"/>
-      <c r="B113" s="3" t="inlineStr"/>
-      <c r="C113" s="3" t="inlineStr"/>
-      <c r="D113" s="3" t="inlineStr">
-        <is>
-          <t>출력</t>
-        </is>
-      </c>
-      <c r="E113" s="3" t="inlineStr">
-        <is>
-          <t>링크 카드 리스트 / Empty State 일러스트+CTA</t>
-        </is>
-      </c>
-      <c r="F113" s="3" t="inlineStr"/>
-      <c r="G113" s="3" t="inlineStr"/>
-      <c r="H113" s="3" t="inlineStr"/>
-      <c r="I113" s="3" t="inlineStr"/>
-      <c r="J113" s="3" t="inlineStr"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="3" t="inlineStr"/>
-      <c r="B114" s="3" t="inlineStr"/>
-      <c r="C114" s="3" t="inlineStr"/>
-      <c r="D114" s="3" t="inlineStr">
-        <is>
-          <t>정책</t>
-        </is>
-      </c>
-      <c r="E114" s="3" t="inlineStr">
-        <is>
-          <t>[기본값] 정렬: 최신순
-[페이지네이션] cursor 기반 30개
-[차별 인터랙션] 모바일=1열, 웹 1024px+=2열, 1440px+=3열, 1920px+=4열 (WEB-001)</t>
-        </is>
-      </c>
-      <c r="F114" s="3" t="inlineStr"/>
-      <c r="G114" s="3" t="inlineStr"/>
-      <c r="H114" s="3" t="inlineStr"/>
-      <c r="I114" s="3" t="inlineStr"/>
-      <c r="J114" s="3" t="inlineStr"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="3" t="inlineStr"/>
-      <c r="B115" s="3" t="inlineStr"/>
-      <c r="C115" s="3" t="inlineStr"/>
-      <c r="D115" s="3" t="inlineStr">
-        <is>
-          <t>예외</t>
-        </is>
-      </c>
-      <c r="E115" s="3" t="inlineStr">
-        <is>
-          <t>- 첫 진입 + 데이터 0개: Empty State "+ 버튼으로 첫 링크를 저장해보세요"
-- 네트워크 오류: 캐시된 마지막 페이지 + "오프라인이에요" 배너</t>
-        </is>
-      </c>
       <c r="F115" s="3" t="inlineStr"/>
       <c r="G115" s="3" t="inlineStr"/>
       <c r="H115" s="3" t="inlineStr"/>
@@ -5265,19 +5352,19 @@
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
         <is>
-          <t>SEARCH-001
-#SEARCH
-#SEARCH-EMPTY</t>
+          <t>FOLDER-002
+#LINK-DETAIL
+#FOLDER-PICKER</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>검색</t>
+          <t>폴더</t>
         </is>
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>키워드 검색</t>
+          <t>폴더 이동</t>
         </is>
       </c>
       <c r="D116" s="3" t="inlineStr">
@@ -5287,7 +5374,7 @@
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
-          <t>제목·요약·태그 통합 검색. 디바운스 200ms. 결과 카드에 키워드 하이라이트. 데스크톱 웹은 ⌘K/Ctrl+K 단축키</t>
+          <t>링크 상세에서 폴더 변경. 픽커 모달에 사용자 폴더 + 미분류 노출</t>
         </is>
       </c>
       <c r="F116" s="3" t="inlineStr">
@@ -5297,7 +5384,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>검색 API (ILIKE → tsvector)</t>
+          <t>링크 폴더 이동 API</t>
         </is>
       </c>
       <c r="H116" s="3" t="inlineStr">
@@ -5323,7 +5410,7 @@
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
-          <t>키워드 (2자 이상)</t>
+          <t>link_id, target_folder_id</t>
         </is>
       </c>
       <c r="F117" s="3" t="inlineStr"/>
@@ -5343,7 +5430,7 @@
       </c>
       <c r="E118" s="3" t="inlineStr">
         <is>
-          <t>매칭 링크 카드 리스트 + 키워드 강조</t>
+          <t>links.folder_id UPDATE + Realtime</t>
         </is>
       </c>
       <c r="F118" s="3" t="inlineStr"/>
@@ -5363,9 +5450,7 @@
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>[기본값] 검색 대상=제목/요약/태그 동시
-[구현] v1: ILIKE '%kw%' (Postgres) / v2: tsvector + gin 인덱스
-[동기화] 새로 저장된 링크도 즉시 검색 가능</t>
+          <t>[동기화] 다른 디바이스에서 카드가 다른 폴더로 부드럽게 이동</t>
         </is>
       </c>
       <c r="F119" s="3" t="inlineStr"/>
@@ -5385,9 +5470,8 @@
       </c>
       <c r="E120" s="3" t="inlineStr">
         <is>
-          <t>- 1자: 트리거 안 함, '2자 이상 입력해주세요'
-- 결과 0개: "'{키워드}' 결과가 없어요" + 최근 검색어 추천
-- 네트워크 오류: 로컬 캐시 결과 + '오프라인 결과를 보여드려요'</t>
+          <t>- 공유 폴더(viewer 권한)로 이동 시도: '읽기 권한 폴더에는 옮길 수 없어요'
+- 삭제된 폴더 ID: 미분류로 자동 fallback</t>
         </is>
       </c>
       <c r="F120" s="3" t="inlineStr"/>
@@ -5399,18 +5483,19 @@
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>WEB-001
-(전 화면 반응형)</t>
+          <t>HOME-001
+#HOME
+#HOME-EMPTY</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>플랫폼</t>
+          <t>홈</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>데스크톱 웹 레이아웃 (반응형 PWA)</t>
+          <t>홈 피드</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr">
@@ -5420,7 +5505,7 @@
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>단일 React PWA 코드베이스가 화면 폭에 따라 모바일·태블릿·데스크톱 레이아웃을 자동 전환. 데스크톱은 좌측 사이드바(폴더 트리) + 메인 그리드(2~4컬럼) + 우측 상세 패널 구조</t>
+          <t>사용자의 모든 링크를 created_at desc로 무한 스크롤. 페이지당 30개. 게스트 시드 데이터 또는 Empty State</t>
         </is>
       </c>
       <c r="F121" s="3" t="inlineStr">
@@ -5430,7 +5515,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>(클라이언트 레이아웃)</t>
+          <t>링크 목록 API (cursor)</t>
         </is>
       </c>
       <c r="H121" s="3" t="inlineStr">
@@ -5445,7 +5530,7 @@
       </c>
       <c r="J121" s="3" t="inlineStr">
         <is>
-          <t>TBD: 사이드바 폭(고정 240px vs 가변), 다크모드 색상 토큰은 THEME-001과 연동</t>
+          <t>TBD: 사용자 설정으로 인기/오래된순 추가?</t>
         </is>
       </c>
     </row>
@@ -5460,7 +5545,7 @@
       </c>
       <c r="E122" s="3" t="inlineStr">
         <is>
-          <t>window.innerWidth (브레이크포인트 매칭)</t>
+          <t>(자동) cursor (last_created_at)</t>
         </is>
       </c>
       <c r="F122" s="3" t="inlineStr"/>
@@ -5480,10 +5565,7 @@
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>- &lt;1024px: 모바일 레이아웃(단일 컬럼 + 하단 탭바)
-- 1024~1439px: 사이드바 + 2컬럼 그리드
-- 1440~1919px: 사이드바 + 3컬럼
-- 1920px+: 사이드바 + 4컬럼 + 우측 상세 패널</t>
+          <t>링크 카드 리스트 / Empty State 일러스트+CTA</t>
         </is>
       </c>
       <c r="F123" s="3" t="inlineStr"/>
@@ -5503,9 +5585,9 @@
       </c>
       <c r="E124" s="3" t="inlineStr">
         <is>
-          <t>[차별 인터랙션] 데스크톱: 키보드 단축키 ⌘K(검색) / N(새 링크) / J·K(카드 이동) / Enter(상세) / Del(삭제)
-[차별 인터랙션] 데스크톱: 카드 hover 시 액션 버튼 노출
-[모바일 전용] QR-001은 데스크톱에서 비활성</t>
+          <t>[기본값] 정렬: 최신순
+[페이지네이션] cursor 기반 30개
+[차별 인터랙션] 모바일=1열, 웹 1024px+=2열, 1440px+=3열, 1920px+=4열 (WEB-001)</t>
         </is>
       </c>
       <c r="F124" s="3" t="inlineStr"/>
@@ -5525,8 +5607,8 @@
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>- 화면 폭 변경(창 리사이즈): 즉시 레이아웃 재계산, 스크롤 위치 보존
-- PWA 설치 데스크톱: 단축키 충돌 회피(브라우저 단축키 존중)</t>
+          <t>- 첫 진입 + 데이터 0개: Empty State "+ 버튼으로 첫 링크를 저장해보세요"
+- 네트워크 오류: 캐시된 마지막 페이지 + "오프라인이에요" 배너</t>
         </is>
       </c>
       <c r="F125" s="3" t="inlineStr"/>
@@ -5538,18 +5620,19 @@
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
         <is>
-          <t>SYNC-001
-(전 화면 백그라운드)</t>
+          <t>SEARCH-001
+#SEARCH
+#SEARCH-EMPTY</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>플랫폼</t>
+          <t>검색</t>
         </is>
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>모바일↔웹 자동 동기화</t>
+          <t>키워드 검색</t>
         </is>
       </c>
       <c r="D126" s="3" t="inlineStr">
@@ -5559,7 +5642,7 @@
       </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
-          <t>한 계정 = 단일 백엔드(AWS RDS) → 디바이스 간 데이터 자동 동기화. AWS API Gateway WebSocket으로 1~2초 내 반영. 멀티탭/멀티디바이스 동시 사용 가정</t>
+          <t>제목·요약·태그 통합 검색. 디바운스 200ms. 결과 카드에 키워드 하이라이트. 데스크톱 웹은 ⌘K/Ctrl+K 단축키</t>
         </is>
       </c>
       <c r="F126" s="3" t="inlineStr">
@@ -5569,8 +5652,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>AWS API Gateway WebSocket
-sync delta API</t>
+          <t>검색 API (ILIKE → tsvector)</t>
         </is>
       </c>
       <c r="H126" s="3" t="inlineStr">
@@ -5583,11 +5665,7 @@
           <t>기획완료</t>
         </is>
       </c>
-      <c r="J126" s="3" t="inlineStr">
-        <is>
-          <t>결정: AWS API Gateway WebSocket 채택 (단순·비용 효율). 끊김 시 5s polling 폴백. last-write-wins. CRDT는 v2 백로그</t>
-        </is>
-      </c>
+      <c r="J126" s="3" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="3" t="inlineStr"/>
@@ -5600,7 +5678,7 @@
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>(자동) 사용자 인증 + 활성 세션</t>
+          <t>키워드 (2자 이상)</t>
         </is>
       </c>
       <c r="F127" s="3" t="inlineStr"/>
@@ -5620,8 +5698,7 @@
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
-          <t>- 각 디바이스가 links/folders/folder_members 변경 이벤트 구독
-- 변경 발생 → 모든 활성 디바이스에 publish → UI에 fade 애니메이션</t>
+          <t>매칭 링크 카드 리스트 + 키워드 강조</t>
         </is>
       </c>
       <c r="F128" s="3" t="inlineStr"/>
@@ -5641,6 +5718,284 @@
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
+          <t>[기본값] 검색 대상=제목/요약/태그 동시
+[구현] v1: ILIKE '%kw%' (Postgres) / v2: tsvector + gin 인덱스
+[동기화] 새로 저장된 링크도 즉시 검색 가능</t>
+        </is>
+      </c>
+      <c r="F129" s="3" t="inlineStr"/>
+      <c r="G129" s="3" t="inlineStr"/>
+      <c r="H129" s="3" t="inlineStr"/>
+      <c r="I129" s="3" t="inlineStr"/>
+      <c r="J129" s="3" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="3" t="inlineStr"/>
+      <c r="B130" s="3" t="inlineStr"/>
+      <c r="C130" s="3" t="inlineStr"/>
+      <c r="D130" s="3" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="E130" s="3" t="inlineStr">
+        <is>
+          <t>- 1자: 트리거 안 함, '2자 이상 입력해주세요'
+- 결과 0개: "'{키워드}' 결과가 없어요" + 최근 검색어 추천
+- 네트워크 오류: 로컬 캐시 결과 + '오프라인 결과를 보여드려요'</t>
+        </is>
+      </c>
+      <c r="F130" s="3" t="inlineStr"/>
+      <c r="G130" s="3" t="inlineStr"/>
+      <c r="H130" s="3" t="inlineStr"/>
+      <c r="I130" s="3" t="inlineStr"/>
+      <c r="J130" s="3" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="3" t="inlineStr">
+        <is>
+          <t>WEB-001
+(전 화면 반응형)</t>
+        </is>
+      </c>
+      <c r="B131" s="3" t="inlineStr">
+        <is>
+          <t>플랫폼</t>
+        </is>
+      </c>
+      <c r="C131" s="3" t="inlineStr">
+        <is>
+          <t>데스크톱 웹 레이아웃 (반응형 PWA)</t>
+        </is>
+      </c>
+      <c r="D131" s="3" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+      <c r="E131" s="3" t="inlineStr">
+        <is>
+          <t>단일 React PWA 코드베이스가 화면 폭에 따라 모바일·태블릿·데스크톱 레이아웃을 자동 전환. 데스크톱은 좌측 사이드바(폴더 트리) + 메인 그리드(2~4컬럼) + 우측 상세 패널 구조</t>
+        </is>
+      </c>
+      <c r="F131" s="3" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G131" s="3" t="inlineStr">
+        <is>
+          <t>(클라이언트 레이아웃)</t>
+        </is>
+      </c>
+      <c r="H131" s="3" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="I131" s="3" t="inlineStr">
+        <is>
+          <t>기획완료</t>
+        </is>
+      </c>
+      <c r="J131" s="3" t="inlineStr">
+        <is>
+          <t>TBD: 사이드바 폭(고정 240px vs 가변), 다크모드 색상 토큰은 THEME-001과 연동</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="3" t="inlineStr"/>
+      <c r="B132" s="3" t="inlineStr"/>
+      <c r="C132" s="3" t="inlineStr"/>
+      <c r="D132" s="3" t="inlineStr">
+        <is>
+          <t>입력</t>
+        </is>
+      </c>
+      <c r="E132" s="3" t="inlineStr">
+        <is>
+          <t>window.innerWidth (브레이크포인트 매칭)</t>
+        </is>
+      </c>
+      <c r="F132" s="3" t="inlineStr"/>
+      <c r="G132" s="3" t="inlineStr"/>
+      <c r="H132" s="3" t="inlineStr"/>
+      <c r="I132" s="3" t="inlineStr"/>
+      <c r="J132" s="3" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="3" t="inlineStr"/>
+      <c r="B133" s="3" t="inlineStr"/>
+      <c r="C133" s="3" t="inlineStr"/>
+      <c r="D133" s="3" t="inlineStr">
+        <is>
+          <t>출력</t>
+        </is>
+      </c>
+      <c r="E133" s="3" t="inlineStr">
+        <is>
+          <t>- &lt;1024px: 모바일 레이아웃(단일 컬럼 + 하단 탭바)
+- 1024~1439px: 사이드바 + 2컬럼 그리드
+- 1440~1919px: 사이드바 + 3컬럼
+- 1920px+: 사이드바 + 4컬럼 + 우측 상세 패널</t>
+        </is>
+      </c>
+      <c r="F133" s="3" t="inlineStr"/>
+      <c r="G133" s="3" t="inlineStr"/>
+      <c r="H133" s="3" t="inlineStr"/>
+      <c r="I133" s="3" t="inlineStr"/>
+      <c r="J133" s="3" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="3" t="inlineStr"/>
+      <c r="B134" s="3" t="inlineStr"/>
+      <c r="C134" s="3" t="inlineStr"/>
+      <c r="D134" s="3" t="inlineStr">
+        <is>
+          <t>정책</t>
+        </is>
+      </c>
+      <c r="E134" s="3" t="inlineStr">
+        <is>
+          <t>[차별 인터랙션] 데스크톱: 키보드 단축키 ⌘K(검색) / N(새 링크) / J·K(카드 이동) / Enter(상세) / Del(삭제)
+[차별 인터랙션] 데스크톱: 카드 hover 시 액션 버튼 노출
+[모바일 전용] QR-001은 데스크톱에서 비활성</t>
+        </is>
+      </c>
+      <c r="F134" s="3" t="inlineStr"/>
+      <c r="G134" s="3" t="inlineStr"/>
+      <c r="H134" s="3" t="inlineStr"/>
+      <c r="I134" s="3" t="inlineStr"/>
+      <c r="J134" s="3" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="3" t="inlineStr"/>
+      <c r="B135" s="3" t="inlineStr"/>
+      <c r="C135" s="3" t="inlineStr"/>
+      <c r="D135" s="3" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="E135" s="3" t="inlineStr">
+        <is>
+          <t>- 화면 폭 변경(창 리사이즈): 즉시 레이아웃 재계산, 스크롤 위치 보존
+- PWA 설치 데스크톱: 단축키 충돌 회피(브라우저 단축키 존중)</t>
+        </is>
+      </c>
+      <c r="F135" s="3" t="inlineStr"/>
+      <c r="G135" s="3" t="inlineStr"/>
+      <c r="H135" s="3" t="inlineStr"/>
+      <c r="I135" s="3" t="inlineStr"/>
+      <c r="J135" s="3" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="3" t="inlineStr">
+        <is>
+          <t>SYNC-001
+(전 화면 백그라운드)</t>
+        </is>
+      </c>
+      <c r="B136" s="3" t="inlineStr">
+        <is>
+          <t>플랫폼</t>
+        </is>
+      </c>
+      <c r="C136" s="3" t="inlineStr">
+        <is>
+          <t>모바일↔웹 자동 동기화</t>
+        </is>
+      </c>
+      <c r="D136" s="3" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+      <c r="E136" s="3" t="inlineStr">
+        <is>
+          <t>한 계정 = 단일 백엔드(AWS RDS) → 디바이스 간 데이터 자동 동기화. AWS API Gateway WebSocket으로 1~2초 내 반영. 멀티탭/멀티디바이스 동시 사용 가정</t>
+        </is>
+      </c>
+      <c r="F136" s="3" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G136" s="3" t="inlineStr">
+        <is>
+          <t>AWS API Gateway WebSocket
+sync delta API</t>
+        </is>
+      </c>
+      <c r="H136" s="3" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="I136" s="3" t="inlineStr">
+        <is>
+          <t>기획완료</t>
+        </is>
+      </c>
+      <c r="J136" s="3" t="inlineStr">
+        <is>
+          <t>결정: AWS API Gateway WebSocket 채택 (단순·비용 효율). 끊김 시 5s polling 폴백. last-write-wins. CRDT는 v2 백로그</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="3" t="inlineStr"/>
+      <c r="B137" s="3" t="inlineStr"/>
+      <c r="C137" s="3" t="inlineStr"/>
+      <c r="D137" s="3" t="inlineStr">
+        <is>
+          <t>입력</t>
+        </is>
+      </c>
+      <c r="E137" s="3" t="inlineStr">
+        <is>
+          <t>(자동) 사용자 인증 + 활성 세션</t>
+        </is>
+      </c>
+      <c r="F137" s="3" t="inlineStr"/>
+      <c r="G137" s="3" t="inlineStr"/>
+      <c r="H137" s="3" t="inlineStr"/>
+      <c r="I137" s="3" t="inlineStr"/>
+      <c r="J137" s="3" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="3" t="inlineStr"/>
+      <c r="B138" s="3" t="inlineStr"/>
+      <c r="C138" s="3" t="inlineStr"/>
+      <c r="D138" s="3" t="inlineStr">
+        <is>
+          <t>출력</t>
+        </is>
+      </c>
+      <c r="E138" s="3" t="inlineStr">
+        <is>
+          <t>- 각 디바이스가 links/folders/folder_members 변경 이벤트 구독
+- 변경 발생 → 모든 활성 디바이스에 publish → UI에 fade 애니메이션</t>
+        </is>
+      </c>
+      <c r="F138" s="3" t="inlineStr"/>
+      <c r="G138" s="3" t="inlineStr"/>
+      <c r="H138" s="3" t="inlineStr"/>
+      <c r="I138" s="3" t="inlineStr"/>
+      <c r="J138" s="3" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="3" t="inlineStr"/>
+      <c r="B139" s="3" t="inlineStr"/>
+      <c r="C139" s="3" t="inlineStr"/>
+      <c r="D139" s="3" t="inlineStr">
+        <is>
+          <t>정책</t>
+        </is>
+      </c>
+      <c r="E139" s="3" t="inlineStr">
+        <is>
           <t>[기본] AWS API Gateway WebSocket (재연결 시 backoff 1s,2s,4s,8s,30s)
 [폴백] 1차 5s polling, 2차 60s polling
 [충돌] last-write-wins by `updated_at` (CRDT는 v2 백로그)
@@ -5648,22 +6003,22 @@
 [동시 편집] 같은 필드 동시 편집 시 토스트 알림</t>
         </is>
       </c>
-      <c r="F129" s="3" t="inlineStr"/>
-      <c r="G129" s="3" t="inlineStr"/>
-      <c r="H129" s="3" t="inlineStr"/>
-      <c r="I129" s="3" t="inlineStr"/>
-      <c r="J129" s="3" t="inlineStr"/>
-    </row>
-    <row r="130">
-      <c r="A130" s="3" t="inlineStr"/>
-      <c r="B130" s="3" t="inlineStr"/>
-      <c r="C130" s="3" t="inlineStr"/>
-      <c r="D130" s="3" t="inlineStr">
+      <c r="F139" s="3" t="inlineStr"/>
+      <c r="G139" s="3" t="inlineStr"/>
+      <c r="H139" s="3" t="inlineStr"/>
+      <c r="I139" s="3" t="inlineStr"/>
+      <c r="J139" s="3" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="3" t="inlineStr"/>
+      <c r="B140" s="3" t="inlineStr"/>
+      <c r="C140" s="3" t="inlineStr"/>
+      <c r="D140" s="3" t="inlineStr">
         <is>
           <t>예외</t>
         </is>
       </c>
-      <c r="E130" s="3" t="inlineStr">
+      <c r="E140" s="3" t="inlineStr">
         <is>
           <t>- WebSocket 끊김: 자동 재연결 + 마지막 sync timestamp 이후 변경분 일괄 fetch
 - 디바이스 시계 어긋남: 서버 timestamp만 사용
@@ -5671,14 +6026,14 @@
 - 데이터 초기화(SETTINGS-004): 모든 디바이스에서 즉시 빈 상태</t>
         </is>
       </c>
-      <c r="F130" s="3" t="inlineStr"/>
-      <c r="G130" s="3" t="inlineStr"/>
-      <c r="H130" s="3" t="inlineStr"/>
-      <c r="I130" s="3" t="inlineStr"/>
-      <c r="J130" s="3" t="inlineStr"/>
-    </row>
-    <row r="131">
-      <c r="A131" s="3" t="inlineStr">
+      <c r="F140" s="3" t="inlineStr"/>
+      <c r="G140" s="3" t="inlineStr"/>
+      <c r="H140" s="3" t="inlineStr"/>
+      <c r="I140" s="3" t="inlineStr"/>
+      <c r="J140" s="3" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="3" t="inlineStr">
         <is>
           <t>IMPORT-001
 #SETTINGS-IMPORT
@@ -5687,103 +6042,103 @@
 #IMPORT-PROGRESS</t>
         </is>
       </c>
-      <c r="B131" s="3" t="inlineStr">
+      <c r="B141" s="3" t="inlineStr">
         <is>
           <t>플랫폼</t>
         </is>
       </c>
-      <c r="C131" s="3" t="inlineStr">
+      <c r="C141" s="3" t="inlineStr">
         <is>
           <t>크롬 즐겨찾기 가져오기 (웹 전용)</t>
         </is>
       </c>
-      <c r="D131" s="3" t="inlineStr">
+      <c r="D141" s="3" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="E131" s="3" t="inlineStr">
+      <c r="E141" s="3" t="inlineStr">
         <is>
           <t>크롬 북마크 관리자 → 내보내기 → bookmarks.html 파일 업로드. 파싱 후 폴더 구조와 함께 미리보기 → 사용자가 폴더 선택/제외 → 일괄 INSERT + AI 요약 SQS 큐잉</t>
         </is>
       </c>
-      <c r="F131" s="3" t="inlineStr">
+      <c r="F141" s="3" t="inlineStr">
         <is>
           <t>Should</t>
         </is>
       </c>
-      <c r="G131" s="3" t="inlineStr">
+      <c r="G141" s="3" t="inlineStr">
         <is>
           <t>북마크 import API (배치)
 AI 요약 큐 publish</t>
         </is>
       </c>
-      <c r="H131" s="3" t="inlineStr">
+      <c r="H141" s="3" t="inlineStr">
         <is>
           <t>일부포함</t>
         </is>
       </c>
-      <c r="I131" s="3" t="inlineStr">
+      <c r="I141" s="3" t="inlineStr">
         <is>
           <t>기획완료</t>
         </is>
       </c>
-      <c r="J131" s="3" t="inlineStr">
+      <c r="J141" s="3" t="inlineStr">
         <is>
           <t>결정: MVP는 비용 동의 모달 미표시 (mock·API키만 가정, 사용자가 본인 API 키 사용 시 본인 부담). 외부 세션 도입(v1.x) 시 모달 추가</t>
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="3" t="inlineStr"/>
-      <c r="B132" s="3" t="inlineStr"/>
-      <c r="C132" s="3" t="inlineStr"/>
-      <c r="D132" s="3" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="3" t="inlineStr"/>
+      <c r="B142" s="3" t="inlineStr"/>
+      <c r="C142" s="3" t="inlineStr"/>
+      <c r="D142" s="3" t="inlineStr">
         <is>
           <t>플로우</t>
         </is>
       </c>
-      <c r="E132" s="3" t="inlineStr">
+      <c r="E142" s="3" t="inlineStr">
         <is>
           <t>(1) 안내(크롬 메뉴 → 북마크 관리자 → ⋮ → 북마크 내보내기) → (2) bookmarks.html 업로드 → (3) 파싱 + 미리보기(폴더 트리 + 링크 카운트) → (4) 폴더 선택/제외 → (5) "가져오기" → (6) 진행률 + 백그라운드 AI 요약</t>
         </is>
       </c>
-      <c r="F132" s="3" t="inlineStr"/>
-      <c r="G132" s="3" t="inlineStr"/>
-      <c r="H132" s="3" t="inlineStr"/>
-      <c r="I132" s="3" t="inlineStr"/>
-      <c r="J132" s="3" t="inlineStr"/>
-    </row>
-    <row r="133">
-      <c r="A133" s="3" t="inlineStr"/>
-      <c r="B133" s="3" t="inlineStr"/>
-      <c r="C133" s="3" t="inlineStr"/>
-      <c r="D133" s="3" t="inlineStr">
+      <c r="F142" s="3" t="inlineStr"/>
+      <c r="G142" s="3" t="inlineStr"/>
+      <c r="H142" s="3" t="inlineStr"/>
+      <c r="I142" s="3" t="inlineStr"/>
+      <c r="J142" s="3" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="3" t="inlineStr"/>
+      <c r="B143" s="3" t="inlineStr"/>
+      <c r="C143" s="3" t="inlineStr"/>
+      <c r="D143" s="3" t="inlineStr">
         <is>
           <t>입력</t>
         </is>
       </c>
-      <c r="E133" s="3" t="inlineStr">
+      <c r="E143" s="3" t="inlineStr">
         <is>
           <t>- bookmarks.html (≤5MB, Netscape Bookmark Format)</t>
         </is>
       </c>
-      <c r="F133" s="3" t="inlineStr"/>
-      <c r="G133" s="3" t="inlineStr"/>
-      <c r="H133" s="3" t="inlineStr"/>
-      <c r="I133" s="3" t="inlineStr"/>
-      <c r="J133" s="3" t="inlineStr"/>
-    </row>
-    <row r="134">
-      <c r="A134" s="3" t="inlineStr"/>
-      <c r="B134" s="3" t="inlineStr"/>
-      <c r="C134" s="3" t="inlineStr"/>
-      <c r="D134" s="3" t="inlineStr">
+      <c r="F143" s="3" t="inlineStr"/>
+      <c r="G143" s="3" t="inlineStr"/>
+      <c r="H143" s="3" t="inlineStr"/>
+      <c r="I143" s="3" t="inlineStr"/>
+      <c r="J143" s="3" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="3" t="inlineStr"/>
+      <c r="B144" s="3" t="inlineStr"/>
+      <c r="C144" s="3" t="inlineStr"/>
+      <c r="D144" s="3" t="inlineStr">
         <is>
           <t>출력</t>
         </is>
       </c>
-      <c r="E134" s="3" t="inlineStr">
+      <c r="E144" s="3" t="inlineStr">
         <is>
           <t>- 폴더 N개 INSERT
 - 링크 M개 INSERT
@@ -5791,22 +6146,22 @@
 - "N개 가져왔어요. AI 요약은 백그라운드에서 진행 중이에요"</t>
         </is>
       </c>
-      <c r="F134" s="3" t="inlineStr"/>
-      <c r="G134" s="3" t="inlineStr"/>
-      <c r="H134" s="3" t="inlineStr"/>
-      <c r="I134" s="3" t="inlineStr"/>
-      <c r="J134" s="3" t="inlineStr"/>
-    </row>
-    <row r="135">
-      <c r="A135" s="3" t="inlineStr"/>
-      <c r="B135" s="3" t="inlineStr"/>
-      <c r="C135" s="3" t="inlineStr"/>
-      <c r="D135" s="3" t="inlineStr">
+      <c r="F144" s="3" t="inlineStr"/>
+      <c r="G144" s="3" t="inlineStr"/>
+      <c r="H144" s="3" t="inlineStr"/>
+      <c r="I144" s="3" t="inlineStr"/>
+      <c r="J144" s="3" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="3" t="inlineStr"/>
+      <c r="B145" s="3" t="inlineStr"/>
+      <c r="C145" s="3" t="inlineStr"/>
+      <c r="D145" s="3" t="inlineStr">
         <is>
           <t>정책</t>
         </is>
       </c>
-      <c r="E135" s="3" t="inlineStr">
+      <c r="E145" s="3" t="inlineStr">
         <is>
           <t>[차별 인터랙션] 데스크톱 웹 전용 (모바일은 안내만)
 [중복 처리] 기본=스킵, 옵션=덮어쓰기
@@ -5814,22 +6169,22 @@
 [한도] 폴더 100개·링크 10000개 한도 사전 검증, 초과 시 일부 선택 강제</t>
         </is>
       </c>
-      <c r="F135" s="3" t="inlineStr"/>
-      <c r="G135" s="3" t="inlineStr"/>
-      <c r="H135" s="3" t="inlineStr"/>
-      <c r="I135" s="3" t="inlineStr"/>
-      <c r="J135" s="3" t="inlineStr"/>
-    </row>
-    <row r="136">
-      <c r="A136" s="3" t="inlineStr"/>
-      <c r="B136" s="3" t="inlineStr"/>
-      <c r="C136" s="3" t="inlineStr"/>
-      <c r="D136" s="3" t="inlineStr">
+      <c r="F145" s="3" t="inlineStr"/>
+      <c r="G145" s="3" t="inlineStr"/>
+      <c r="H145" s="3" t="inlineStr"/>
+      <c r="I145" s="3" t="inlineStr"/>
+      <c r="J145" s="3" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="3" t="inlineStr"/>
+      <c r="B146" s="3" t="inlineStr"/>
+      <c r="C146" s="3" t="inlineStr"/>
+      <c r="D146" s="3" t="inlineStr">
         <is>
           <t>예외</t>
         </is>
       </c>
-      <c r="E136" s="3" t="inlineStr">
+      <c r="E146" s="3" t="inlineStr">
         <is>
           <t>- 형식 오류: '크롬 즐겨찾기 HTML 파일만 가능해요'
 - 5MB 초과: '파일이 너무 커요. 5MB 이하로 잘라서 다시 시도해주세요'
@@ -5838,477 +6193,148 @@
 - 모바일 진입: '데스크톱 웹에서 사용 가능한 기능이에요'</t>
         </is>
       </c>
-      <c r="F136" s="3" t="inlineStr"/>
-      <c r="G136" s="3" t="inlineStr"/>
-      <c r="H136" s="3" t="inlineStr"/>
-      <c r="I136" s="3" t="inlineStr"/>
-      <c r="J136" s="3" t="inlineStr"/>
-    </row>
-    <row r="137">
-      <c r="A137" s="4" t="inlineStr">
+      <c r="F146" s="3" t="inlineStr"/>
+      <c r="G146" s="3" t="inlineStr"/>
+      <c r="H146" s="3" t="inlineStr"/>
+      <c r="I146" s="3" t="inlineStr"/>
+      <c r="J146" s="3" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="4" t="inlineStr">
         <is>
           <t>IMPORT-002</t>
         </is>
       </c>
-      <c r="B137" s="4" t="inlineStr">
+      <c r="B147" s="4" t="inlineStr">
         <is>
           <t>플랫폼</t>
         </is>
       </c>
-      <c r="C137" s="4" t="inlineStr">
+      <c r="C147" s="4" t="inlineStr">
         <is>
           <t>Pocket/Raindrop import</t>
         </is>
       </c>
-      <c r="D137" s="4" t="inlineStr">
+      <c r="D147" s="4" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="E137" s="4" t="inlineStr">
+      <c r="E147" s="4" t="inlineStr">
         <is>
           <t>Pocket·Raindrop·Goodlinks 등 export 파일 import</t>
         </is>
       </c>
-      <c r="F137" s="4" t="inlineStr">
+      <c r="F147" s="4" t="inlineStr">
         <is>
           <t>Could</t>
         </is>
       </c>
-      <c r="G137" s="4" t="inlineStr"/>
-      <c r="H137" s="4" t="inlineStr">
+      <c r="G147" s="4" t="inlineStr"/>
+      <c r="H147" s="4" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="I137" s="4" t="inlineStr">
+      <c r="I147" s="4" t="inlineStr">
         <is>
           <t>기획중</t>
         </is>
       </c>
-      <c r="J137" s="4" t="inlineStr">
+      <c r="J147" s="4" t="inlineStr">
         <is>
           <t>v1.x 추가 예정</t>
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="3" t="inlineStr">
+    <row r="151">
+      <c r="A151" s="3" t="inlineStr">
         <is>
           <t>SHARE-001
 #FOLDER-DETAIL
 #SHARE-INVITE</t>
         </is>
       </c>
-      <c r="B141" s="3" t="inlineStr">
+      <c r="B151" s="3" t="inlineStr">
         <is>
           <t>공유 폴더</t>
         </is>
       </c>
-      <c r="C141" s="3" t="inlineStr">
+      <c r="C151" s="3" t="inlineStr">
         <is>
           <t>공유 폴더 만들기</t>
         </is>
       </c>
-      <c r="D141" s="3" t="inlineStr">
+      <c r="D151" s="3" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="E141" s="3" t="inlineStr">
+      <c r="E151" s="3" t="inlineStr">
         <is>
           <t>폴더의 shared 플래그를 true로 전환 → folder_invites에 토큰 INSERT → OS 공유 시트로 링크 발송</t>
         </is>
       </c>
-      <c r="F141" s="3" t="inlineStr">
+      <c r="F151" s="3" t="inlineStr">
         <is>
           <t>Should</t>
         </is>
       </c>
-      <c r="G141" s="3" t="inlineStr">
+      <c r="G151" s="3" t="inlineStr">
         <is>
           <t>초대 토큰 생성 API</t>
         </is>
       </c>
-      <c r="H141" s="3" t="inlineStr">
+      <c r="H151" s="3" t="inlineStr">
         <is>
           <t>일부포함</t>
         </is>
       </c>
-      <c r="I141" s="3" t="inlineStr">
+      <c r="I151" s="3" t="inlineStr">
         <is>
           <t>기획완료</t>
         </is>
       </c>
-      <c r="J141" s="3" t="inlineStr"/>
-    </row>
-    <row r="142">
-      <c r="A142" s="3" t="inlineStr"/>
-      <c r="B142" s="3" t="inlineStr"/>
-      <c r="C142" s="3" t="inlineStr"/>
-      <c r="D142" s="3" t="inlineStr">
+      <c r="J151" s="3" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="3" t="inlineStr"/>
+      <c r="B152" s="3" t="inlineStr"/>
+      <c r="C152" s="3" t="inlineStr"/>
+      <c r="D152" s="3" t="inlineStr">
         <is>
           <t>입력</t>
         </is>
       </c>
-      <c r="E142" s="3" t="inlineStr">
+      <c r="E152" s="3" t="inlineStr">
         <is>
           <t>folder_id (오너만)</t>
         </is>
       </c>
-      <c r="F142" s="3" t="inlineStr"/>
-      <c r="G142" s="3" t="inlineStr"/>
-      <c r="H142" s="3" t="inlineStr"/>
-      <c r="I142" s="3" t="inlineStr"/>
-      <c r="J142" s="3" t="inlineStr"/>
-    </row>
-    <row r="143">
-      <c r="A143" s="3" t="inlineStr"/>
-      <c r="B143" s="3" t="inlineStr"/>
-      <c r="C143" s="3" t="inlineStr"/>
-      <c r="D143" s="3" t="inlineStr">
+      <c r="F152" s="3" t="inlineStr"/>
+      <c r="G152" s="3" t="inlineStr"/>
+      <c r="H152" s="3" t="inlineStr"/>
+      <c r="I152" s="3" t="inlineStr"/>
+      <c r="J152" s="3" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="3" t="inlineStr"/>
+      <c r="B153" s="3" t="inlineStr"/>
+      <c r="C153" s="3" t="inlineStr"/>
+      <c r="D153" s="3" t="inlineStr">
         <is>
           <t>출력</t>
         </is>
       </c>
-      <c r="E143" s="3" t="inlineStr">
+      <c r="E153" s="3" t="inlineStr">
         <is>
           <t>folders.shared=true / folder_invites INSERT / 공유 URL 생성 (https://qlink.app/invite/{token})</t>
         </is>
       </c>
-      <c r="F143" s="3" t="inlineStr"/>
-      <c r="G143" s="3" t="inlineStr"/>
-      <c r="H143" s="3" t="inlineStr"/>
-      <c r="I143" s="3" t="inlineStr"/>
-      <c r="J143" s="3" t="inlineStr"/>
-    </row>
-    <row r="144">
-      <c r="A144" s="3" t="inlineStr"/>
-      <c r="B144" s="3" t="inlineStr"/>
-      <c r="C144" s="3" t="inlineStr"/>
-      <c r="D144" s="3" t="inlineStr">
-        <is>
-          <t>정책</t>
-        </is>
-      </c>
-      <c r="E144" s="3" t="inlineStr">
-        <is>
-          <t>POLICY-SHARED 참고
-[기본값] 토큰 유효 7일
-[권한] 오너만 발급
-[재발급] 새 토큰 발급 시 이전 토큰은 만료 전까지 유효</t>
-        </is>
-      </c>
-      <c r="F144" s="3" t="inlineStr"/>
-      <c r="G144" s="3" t="inlineStr"/>
-      <c r="H144" s="3" t="inlineStr"/>
-      <c r="I144" s="3" t="inlineStr"/>
-      <c r="J144" s="3" t="inlineStr"/>
-    </row>
-    <row r="145">
-      <c r="A145" s="3" t="inlineStr"/>
-      <c r="B145" s="3" t="inlineStr"/>
-      <c r="C145" s="3" t="inlineStr"/>
-      <c r="D145" s="3" t="inlineStr">
-        <is>
-          <t>예외</t>
-        </is>
-      </c>
-      <c r="E145" s="3" t="inlineStr">
-        <is>
-          <t>- 비오너 시도: '오너만 공유할 수 있어요'
-- 미분류 폴더 공유 시도: '미분류 폴더는 공유할 수 없어요'</t>
-        </is>
-      </c>
-      <c r="F145" s="3" t="inlineStr"/>
-      <c r="G145" s="3" t="inlineStr"/>
-      <c r="H145" s="3" t="inlineStr"/>
-      <c r="I145" s="3" t="inlineStr"/>
-      <c r="J145" s="3" t="inlineStr"/>
-    </row>
-    <row r="146">
-      <c r="A146" s="3" t="inlineStr">
-        <is>
-          <t>SHARE-002
-#SHARE-ACCEPT</t>
-        </is>
-      </c>
-      <c r="B146" s="3" t="inlineStr">
-        <is>
-          <t>공유 폴더</t>
-        </is>
-      </c>
-      <c r="C146" s="3" t="inlineStr">
-        <is>
-          <t>공유 폴더 초대 수락</t>
-        </is>
-      </c>
-      <c r="D146" s="3" t="inlineStr">
-        <is>
-          <t>설명</t>
-        </is>
-      </c>
-      <c r="E146" s="3" t="inlineStr">
-        <is>
-          <t>초대 링크 클릭 → 토큰 검증 → 사용자가 "참여" 클릭 → folder_members INSERT</t>
-        </is>
-      </c>
-      <c r="F146" s="3" t="inlineStr">
-        <is>
-          <t>Should</t>
-        </is>
-      </c>
-      <c r="G146" s="3" t="inlineStr">
-        <is>
-          <t>accept_folder_invite RPC</t>
-        </is>
-      </c>
-      <c r="H146" s="3" t="inlineStr">
-        <is>
-          <t>일부포함</t>
-        </is>
-      </c>
-      <c r="I146" s="3" t="inlineStr">
-        <is>
-          <t>기획완료</t>
-        </is>
-      </c>
-      <c r="J146" s="3" t="inlineStr"/>
-    </row>
-    <row r="147">
-      <c r="A147" s="3" t="inlineStr"/>
-      <c r="B147" s="3" t="inlineStr"/>
-      <c r="C147" s="3" t="inlineStr"/>
-      <c r="D147" s="3" t="inlineStr">
-        <is>
-          <t>입력</t>
-        </is>
-      </c>
-      <c r="E147" s="3" t="inlineStr">
-        <is>
-          <t>invite_token (URL 파라미터)</t>
-        </is>
-      </c>
-      <c r="F147" s="3" t="inlineStr"/>
-      <c r="G147" s="3" t="inlineStr"/>
-      <c r="H147" s="3" t="inlineStr"/>
-      <c r="I147" s="3" t="inlineStr"/>
-      <c r="J147" s="3" t="inlineStr"/>
-    </row>
-    <row r="148">
-      <c r="A148" s="3" t="inlineStr"/>
-      <c r="B148" s="3" t="inlineStr"/>
-      <c r="C148" s="3" t="inlineStr"/>
-      <c r="D148" s="3" t="inlineStr">
-        <is>
-          <t>출력</t>
-        </is>
-      </c>
-      <c r="E148" s="3" t="inlineStr">
-        <is>
-          <t>folder_members INSERT (role='member') / 폴더 진입</t>
-        </is>
-      </c>
-      <c r="F148" s="3" t="inlineStr"/>
-      <c r="G148" s="3" t="inlineStr"/>
-      <c r="H148" s="3" t="inlineStr"/>
-      <c r="I148" s="3" t="inlineStr"/>
-      <c r="J148" s="3" t="inlineStr"/>
-    </row>
-    <row r="149">
-      <c r="A149" s="3" t="inlineStr"/>
-      <c r="B149" s="3" t="inlineStr"/>
-      <c r="C149" s="3" t="inlineStr"/>
-      <c r="D149" s="3" t="inlineStr">
-        <is>
-          <t>정책</t>
-        </is>
-      </c>
-      <c r="E149" s="3" t="inlineStr">
-        <is>
-          <t>POLICY-SHARED 참고
-[처리 순서] 미로그인 시 토큰 임시 보관 → 로그인 후 자동 수락 화면
-[멤버 한도] 50명</t>
-        </is>
-      </c>
-      <c r="F149" s="3" t="inlineStr"/>
-      <c r="G149" s="3" t="inlineStr"/>
-      <c r="H149" s="3" t="inlineStr"/>
-      <c r="I149" s="3" t="inlineStr"/>
-      <c r="J149" s="3" t="inlineStr"/>
-    </row>
-    <row r="150">
-      <c r="A150" s="3" t="inlineStr"/>
-      <c r="B150" s="3" t="inlineStr"/>
-      <c r="C150" s="3" t="inlineStr"/>
-      <c r="D150" s="3" t="inlineStr">
-        <is>
-          <t>예외</t>
-        </is>
-      </c>
-      <c r="E150" s="3" t="inlineStr">
-        <is>
-          <t>- 토큰 만료: '유효하지 않거나 만료된 초대 링크입니다'
-- 이미 멤버: 토스트 + 폴더 이동
-- 본인이 오너: '본인의 폴더예요'
-- 멤버 한도 50명 초과: '이 폴더는 50명까지만 참여할 수 있어요. 오너에게 문의하세요'</t>
-        </is>
-      </c>
-      <c r="F150" s="3" t="inlineStr"/>
-      <c r="G150" s="3" t="inlineStr"/>
-      <c r="H150" s="3" t="inlineStr"/>
-      <c r="I150" s="3" t="inlineStr"/>
-      <c r="J150" s="3" t="inlineStr"/>
-    </row>
-    <row r="151">
-      <c r="A151" s="3" t="inlineStr">
-        <is>
-          <t>SHARE-003
-#FOLDER-MEMBERS</t>
-        </is>
-      </c>
-      <c r="B151" s="3" t="inlineStr">
-        <is>
-          <t>공유 폴더</t>
-        </is>
-      </c>
-      <c r="C151" s="3" t="inlineStr">
-        <is>
-          <t>공유 폴더 멤버 관리</t>
-        </is>
-      </c>
-      <c r="D151" s="3" t="inlineStr">
-        <is>
-          <t>설명</t>
-        </is>
-      </c>
-      <c r="E151" s="3" t="inlineStr">
-        <is>
-          <t>멤버 목록 + 역할 변경(owner만) + 제거(owner) / 나가기(self)</t>
-        </is>
-      </c>
-      <c r="F151" s="3" t="inlineStr">
-        <is>
-          <t>Should</t>
-        </is>
-      </c>
-      <c r="G151" s="3" t="inlineStr">
-        <is>
-          <t>멤버 조회/수정/삭제 API</t>
-        </is>
-      </c>
-      <c r="H151" s="3" t="inlineStr">
-        <is>
-          <t>일부포함</t>
-        </is>
-      </c>
-      <c r="I151" s="3" t="inlineStr">
-        <is>
-          <t>기획중</t>
-        </is>
-      </c>
-      <c r="J151" s="3" t="inlineStr">
-        <is>
-          <t>v1.0 가벼운 형태로</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="3" t="inlineStr">
-        <is>
-          <t>VIEW-001
-#LINK-DETAIL</t>
-        </is>
-      </c>
-      <c r="B152" s="3" t="inlineStr">
-        <is>
-          <t>콘텐츠</t>
-        </is>
-      </c>
-      <c r="C152" s="3" t="inlineStr">
-        <is>
-          <t>YouTube 임베드 미리보기</t>
-        </is>
-      </c>
-      <c r="D152" s="3" t="inlineStr">
-        <is>
-          <t>설명</t>
-        </is>
-      </c>
-      <c r="E152" s="3" t="inlineStr">
-        <is>
-          <t>URL이 youtube.com/youtu.be 도메인이면 상세 화면에서 iframe 임베드. 자동재생 X, 사용자 클릭 시 재생</t>
-        </is>
-      </c>
-      <c r="F152" s="3" t="inlineStr">
-        <is>
-          <t>Should</t>
-        </is>
-      </c>
-      <c r="G152" s="3" t="inlineStr">
-        <is>
-          <t>(클라이언트, iframe)</t>
-        </is>
-      </c>
-      <c r="H152" s="3" t="inlineStr">
-        <is>
-          <t>일부포함</t>
-        </is>
-      </c>
-      <c r="I152" s="3" t="inlineStr">
-        <is>
-          <t>기획중</t>
-        </is>
-      </c>
-      <c r="J152" s="3" t="inlineStr"/>
-    </row>
-    <row r="153">
-      <c r="A153" s="3" t="inlineStr">
-        <is>
-          <t>SETTINGS-001
-#SETTINGS-AI</t>
-        </is>
-      </c>
-      <c r="B153" s="3" t="inlineStr">
-        <is>
-          <t>설정</t>
-        </is>
-      </c>
-      <c r="C153" s="3" t="inlineStr">
-        <is>
-          <t>AI 제공자 선택</t>
-        </is>
-      </c>
-      <c r="D153" s="3" t="inlineStr">
-        <is>
-          <t>설명</t>
-        </is>
-      </c>
-      <c r="E153" s="3" t="inlineStr">
-        <is>
-          <t>6종 중 선택: ChatGPT / Gemini / Claude / Perplexity / 큐링크 기본(mock) / 사용자 API 키. SETTINGS-001 변경은 LINK-004의 provider 입력으로 즉시 반영</t>
-        </is>
-      </c>
-      <c r="F153" s="3" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G153" s="3" t="inlineStr">
-        <is>
-          <t>프로필 업데이트 API</t>
-        </is>
-      </c>
-      <c r="H153" s="3" t="inlineStr">
-        <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="I153" s="3" t="inlineStr">
-        <is>
-          <t>기획완료</t>
-        </is>
-      </c>
+      <c r="F153" s="3" t="inlineStr"/>
+      <c r="G153" s="3" t="inlineStr"/>
+      <c r="H153" s="3" t="inlineStr"/>
+      <c r="I153" s="3" t="inlineStr"/>
       <c r="J153" s="3" t="inlineStr"/>
     </row>
     <row r="154">
@@ -6317,12 +6343,15 @@
       <c r="C154" s="3" t="inlineStr"/>
       <c r="D154" s="3" t="inlineStr">
         <is>
-          <t>입력</t>
+          <t>정책</t>
         </is>
       </c>
       <c r="E154" s="3" t="inlineStr">
         <is>
-          <t>provider 식별자</t>
+          <t>POLICY-SHARED 참고
+[기본값] 토큰 유효 7일
+[권한] 오너만 발급
+[재발급] 새 토큰 발급 시 이전 토큰은 만료 전까지 유효</t>
         </is>
       </c>
       <c r="F154" s="3" t="inlineStr"/>
@@ -6337,12 +6366,13 @@
       <c r="C155" s="3" t="inlineStr"/>
       <c r="D155" s="3" t="inlineStr">
         <is>
-          <t>출력</t>
+          <t>예외</t>
         </is>
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
-          <t>profiles.ai_provider UPDATE + 토스트</t>
+          <t>- 비오너 시도: '오너만 공유할 수 있어요'
+- 미분류 폴더 공유 시도: '미분류 폴더는 공유할 수 없어요'</t>
         </is>
       </c>
       <c r="F155" s="3" t="inlineStr"/>
@@ -6352,25 +6382,52 @@
       <c r="J155" s="3" t="inlineStr"/>
     </row>
     <row r="156">
-      <c r="A156" s="3" t="inlineStr"/>
-      <c r="B156" s="3" t="inlineStr"/>
-      <c r="C156" s="3" t="inlineStr"/>
+      <c r="A156" s="3" t="inlineStr">
+        <is>
+          <t>SHARE-002
+#SHARE-ACCEPT</t>
+        </is>
+      </c>
+      <c r="B156" s="3" t="inlineStr">
+        <is>
+          <t>공유 폴더</t>
+        </is>
+      </c>
+      <c r="C156" s="3" t="inlineStr">
+        <is>
+          <t>공유 폴더 초대 수락</t>
+        </is>
+      </c>
       <c r="D156" s="3" t="inlineStr">
         <is>
-          <t>정책</t>
+          <t>설명</t>
         </is>
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
-          <t>[기본값] 'mock' (앱 진입 시)
-[동기화] 모든 디바이스에 SYNC-001로 반영
-[API 키] 사용자 API 키 선택 시 키 입력 화면 추가 노출, 서버 KMS 암호화 저장</t>
-        </is>
-      </c>
-      <c r="F156" s="3" t="inlineStr"/>
-      <c r="G156" s="3" t="inlineStr"/>
-      <c r="H156" s="3" t="inlineStr"/>
-      <c r="I156" s="3" t="inlineStr"/>
+          <t>초대 링크 클릭 → 토큰 검증 → 사용자가 "참여" 클릭 → folder_members INSERT</t>
+        </is>
+      </c>
+      <c r="F156" s="3" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G156" s="3" t="inlineStr">
+        <is>
+          <t>accept_folder_invite RPC</t>
+        </is>
+      </c>
+      <c r="H156" s="3" t="inlineStr">
+        <is>
+          <t>일부포함</t>
+        </is>
+      </c>
+      <c r="I156" s="3" t="inlineStr">
+        <is>
+          <t>기획완료</t>
+        </is>
+      </c>
       <c r="J156" s="3" t="inlineStr"/>
     </row>
     <row r="157">
@@ -6379,13 +6436,12 @@
       <c r="C157" s="3" t="inlineStr"/>
       <c r="D157" s="3" t="inlineStr">
         <is>
-          <t>예외</t>
+          <t>입력</t>
         </is>
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>- 외부 세션 provider 선택했지만 Chrome 확장 미설치: '확장 프로그램 설치가 필요해요' + 안내 링크
-- API 키 무효: 다음 호출 시 '키를 확인해주세요' 안내</t>
+          <t>invite_token (URL 파라미터)</t>
         </is>
       </c>
       <c r="F157" s="3" t="inlineStr"/>
@@ -6395,52 +6451,23 @@
       <c r="J157" s="3" t="inlineStr"/>
     </row>
     <row r="158">
-      <c r="A158" s="3" t="inlineStr">
-        <is>
-          <t>SETTINGS-002
-#SETTINGS-PROFILE</t>
-        </is>
-      </c>
-      <c r="B158" s="3" t="inlineStr">
-        <is>
-          <t>설정</t>
-        </is>
-      </c>
-      <c r="C158" s="3" t="inlineStr">
-        <is>
-          <t>프로필 변경</t>
-        </is>
-      </c>
+      <c r="A158" s="3" t="inlineStr"/>
+      <c r="B158" s="3" t="inlineStr"/>
+      <c r="C158" s="3" t="inlineStr"/>
       <c r="D158" s="3" t="inlineStr">
         <is>
-          <t>설명</t>
+          <t>출력</t>
         </is>
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>닉네임·아바타 이모지 변경</t>
-        </is>
-      </c>
-      <c r="F158" s="3" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G158" s="3" t="inlineStr">
-        <is>
-          <t>프로필 업데이트 API</t>
-        </is>
-      </c>
-      <c r="H158" s="3" t="inlineStr">
-        <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="I158" s="3" t="inlineStr">
-        <is>
-          <t>기획완료</t>
-        </is>
-      </c>
+          <t>folder_members INSERT (role='member') / 폴더 진입</t>
+        </is>
+      </c>
+      <c r="F158" s="3" t="inlineStr"/>
+      <c r="G158" s="3" t="inlineStr"/>
+      <c r="H158" s="3" t="inlineStr"/>
+      <c r="I158" s="3" t="inlineStr"/>
       <c r="J158" s="3" t="inlineStr"/>
     </row>
     <row r="159">
@@ -6449,12 +6476,14 @@
       <c r="C159" s="3" t="inlineStr"/>
       <c r="D159" s="3" t="inlineStr">
         <is>
-          <t>입력</t>
+          <t>정책</t>
         </is>
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>display_name (1~20자), avatar (이모지 단일 문자)</t>
+          <t>POLICY-SHARED 참고
+[처리 순서] 미로그인 시 토큰 임시 보관 → 로그인 후 자동 수락 화면
+[멤버 한도] 50명</t>
         </is>
       </c>
       <c r="F159" s="3" t="inlineStr"/>
@@ -6469,12 +6498,15 @@
       <c r="C160" s="3" t="inlineStr"/>
       <c r="D160" s="3" t="inlineStr">
         <is>
-          <t>출력</t>
+          <t>예외</t>
         </is>
       </c>
       <c r="E160" s="3" t="inlineStr">
         <is>
-          <t>profiles UPDATE + 헤더 즉시 반영</t>
+          <t>- 토큰 만료: '유효하지 않거나 만료된 초대 링크입니다'
+- 이미 멤버: 토스트 + 폴더 이동
+- 본인이 오너: '본인의 폴더예요'
+- 멤버 한도 50명 초과: '이 폴더는 50명까지만 참여할 수 있어요. 오너에게 문의하세요'</t>
         </is>
       </c>
       <c r="F160" s="3" t="inlineStr"/>
@@ -6484,51 +6516,112 @@
       <c r="J160" s="3" t="inlineStr"/>
     </row>
     <row r="161">
-      <c r="A161" s="3" t="inlineStr"/>
-      <c r="B161" s="3" t="inlineStr"/>
-      <c r="C161" s="3" t="inlineStr"/>
+      <c r="A161" s="3" t="inlineStr">
+        <is>
+          <t>SHARE-003
+#FOLDER-MEMBERS</t>
+        </is>
+      </c>
+      <c r="B161" s="3" t="inlineStr">
+        <is>
+          <t>공유 폴더</t>
+        </is>
+      </c>
+      <c r="C161" s="3" t="inlineStr">
+        <is>
+          <t>공유 폴더 멤버 관리</t>
+        </is>
+      </c>
       <c r="D161" s="3" t="inlineStr">
         <is>
-          <t>정책</t>
+          <t>설명</t>
         </is>
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
-          <t>[동기화] 즉시 모든 디바이스 반영</t>
-        </is>
-      </c>
-      <c r="F161" s="3" t="inlineStr"/>
-      <c r="G161" s="3" t="inlineStr"/>
-      <c r="H161" s="3" t="inlineStr"/>
-      <c r="I161" s="3" t="inlineStr"/>
-      <c r="J161" s="3" t="inlineStr"/>
+          <t>멤버 목록 + 역할 변경(owner만) + 제거(owner) / 나가기(self)</t>
+        </is>
+      </c>
+      <c r="F161" s="3" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G161" s="3" t="inlineStr">
+        <is>
+          <t>멤버 조회/수정/삭제 API</t>
+        </is>
+      </c>
+      <c r="H161" s="3" t="inlineStr">
+        <is>
+          <t>일부포함</t>
+        </is>
+      </c>
+      <c r="I161" s="3" t="inlineStr">
+        <is>
+          <t>기획중</t>
+        </is>
+      </c>
+      <c r="J161" s="3" t="inlineStr">
+        <is>
+          <t>v1.0 가벼운 형태로</t>
+        </is>
+      </c>
     </row>
     <row r="162">
-      <c r="A162" s="3" t="inlineStr"/>
-      <c r="B162" s="3" t="inlineStr"/>
-      <c r="C162" s="3" t="inlineStr"/>
+      <c r="A162" s="3" t="inlineStr">
+        <is>
+          <t>VIEW-001
+#LINK-DETAIL</t>
+        </is>
+      </c>
+      <c r="B162" s="3" t="inlineStr">
+        <is>
+          <t>콘텐츠</t>
+        </is>
+      </c>
+      <c r="C162" s="3" t="inlineStr">
+        <is>
+          <t>YouTube 임베드 미리보기</t>
+        </is>
+      </c>
       <c r="D162" s="3" t="inlineStr">
         <is>
-          <t>예외</t>
+          <t>설명</t>
         </is>
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
-          <t>- 빈 닉네임: '닉네임을 입력해주세요'
-- 20자 초과: 입력 차단</t>
-        </is>
-      </c>
-      <c r="F162" s="3" t="inlineStr"/>
-      <c r="G162" s="3" t="inlineStr"/>
-      <c r="H162" s="3" t="inlineStr"/>
-      <c r="I162" s="3" t="inlineStr"/>
+          <t>URL이 youtube.com/youtu.be 도메인이면 상세 화면에서 iframe 임베드. 자동재생 X, 사용자 클릭 시 재생</t>
+        </is>
+      </c>
+      <c r="F162" s="3" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G162" s="3" t="inlineStr">
+        <is>
+          <t>(클라이언트, iframe)</t>
+        </is>
+      </c>
+      <c r="H162" s="3" t="inlineStr">
+        <is>
+          <t>일부포함</t>
+        </is>
+      </c>
+      <c r="I162" s="3" t="inlineStr">
+        <is>
+          <t>기획중</t>
+        </is>
+      </c>
       <c r="J162" s="3" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="3" t="inlineStr">
         <is>
-          <t>SETTINGS-003
-#SETTINGS-PASSWORD</t>
+          <t>SETTINGS-001
+#SETTINGS-AI</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
@@ -6538,7 +6631,7 @@
       </c>
       <c r="C163" s="3" t="inlineStr">
         <is>
-          <t>비밀번호 변경</t>
+          <t>AI 제공자 선택</t>
         </is>
       </c>
       <c r="D163" s="3" t="inlineStr">
@@ -6548,7 +6641,7 @@
       </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
-          <t>현재 비밀번호 검증 → 새 비밀번호 변경. 변경 후 다른 디바이스는 강제 로그아웃 (보안 우선)</t>
+          <t>6종 중 선택: ChatGPT / Gemini / Claude / Perplexity / 큐링크 기본(mock) / 사용자 API 키. SETTINGS-001 변경은 LINK-004의 provider 입력으로 즉시 반영</t>
         </is>
       </c>
       <c r="F163" s="3" t="inlineStr">
@@ -6558,8 +6651,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>비밀번호 변경 API
-리프레시 토큰 무효화 API</t>
+          <t>프로필 업데이트 API</t>
         </is>
       </c>
       <c r="H163" s="3" t="inlineStr">
@@ -6572,11 +6664,7 @@
           <t>기획완료</t>
         </is>
       </c>
-      <c r="J163" s="3" t="inlineStr">
-        <is>
-          <t>결정: 변경 시 다른 디바이스 강제 로그아웃 + 화면 안내 문구 추가</t>
-        </is>
-      </c>
+      <c r="J163" s="3" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="3" t="inlineStr"/>
@@ -6589,7 +6677,7 @@
       </c>
       <c r="E164" s="3" t="inlineStr">
         <is>
-          <t>current_password, new_password (8~64자, 영문+숫자)</t>
+          <t>provider 식별자</t>
         </is>
       </c>
       <c r="F164" s="3" t="inlineStr"/>
@@ -6609,7 +6697,7 @@
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
-          <t>비밀번호 변경 + 모든 다른 디바이스 리프레시 토큰 invalidate + 토스트 "변경됐어요. 다른 기기에서는 다시 로그인해주세요"</t>
+          <t>profiles.ai_provider UPDATE + 토스트</t>
         </is>
       </c>
       <c r="F165" s="3" t="inlineStr"/>
@@ -6629,9 +6717,9 @@
       </c>
       <c r="E166" s="3" t="inlineStr">
         <is>
-          <t>[보안] 현재 비밀번호 검증 필수
-[강제 로그아웃] 변경 즉시 서버에서 모든 다른 활성 리프레시 토큰 invalidate
-[화면 안내] 비밀번호 변경 화면 상단에 안내 카피: "비밀번호를 바꾸면 로그인된 다른 기기들에서 자동으로 로그아웃돼요. 보안을 위한 조치예요."</t>
+          <t>[기본값] 'mock' (앱 진입 시)
+[동기화] 모든 디바이스에 SYNC-001로 반영
+[API 키] 사용자 API 키 선택 시 키 입력 화면 추가 노출, 서버 KMS 암호화 저장</t>
         </is>
       </c>
       <c r="F166" s="3" t="inlineStr"/>
@@ -6651,9 +6739,8 @@
       </c>
       <c r="E167" s="3" t="inlineStr">
         <is>
-          <t>- 현재 PW 불일치: '현재 비밀번호가 일치하지 않아요'
-- 새 PW 정책 미충족: 안내
-- 5회 실패: 잠시 차단</t>
+          <t>- 외부 세션 provider 선택했지만 Chrome 확장 미설치: '확장 프로그램 설치가 필요해요' + 안내 링크
+- API 키 무효: 다음 호출 시 '키를 확인해주세요' 안내</t>
         </is>
       </c>
       <c r="F167" s="3" t="inlineStr"/>
@@ -6665,8 +6752,8 @@
     <row r="168">
       <c r="A168" s="3" t="inlineStr">
         <is>
-          <t>SETTINGS-004
-#SETTINGS-RESET</t>
+          <t>SETTINGS-002
+#SETTINGS-PROFILE</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
@@ -6676,7 +6763,7 @@
       </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
-          <t>데이터 초기화</t>
+          <t>프로필 변경</t>
         </is>
       </c>
       <c r="D168" s="3" t="inlineStr">
@@ -6686,7 +6773,7 @@
       </c>
       <c r="E168" s="3" t="inlineStr">
         <is>
-          <t>본인 데이터(폴더·링크·공유 멤버십) 전체 영구 삭제. 이중 확인 모달. 모든 디바이스에서 즉시 빈 상태</t>
+          <t>닉네임·아바타 이모지 변경</t>
         </is>
       </c>
       <c r="F168" s="3" t="inlineStr">
@@ -6696,7 +6783,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>데이터 일괄 삭제 API (트랜잭션)</t>
+          <t>프로필 업데이트 API</t>
         </is>
       </c>
       <c r="H168" s="3" t="inlineStr">
@@ -6709,11 +6796,7 @@
           <t>기획완료</t>
         </is>
       </c>
-      <c r="J168" s="3" t="inlineStr">
-        <is>
-          <t>결정: 즉시 hard delete (개인정보보호법 OK, 사용자 의도 그대로 존중)</t>
-        </is>
-      </c>
+      <c r="J168" s="3" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="3" t="inlineStr"/>
@@ -6726,7 +6809,7 @@
       </c>
       <c r="E169" s="3" t="inlineStr">
         <is>
-          <t>"초기화" 버튼 → 모달 1 → "정말 삭제" → 모달 2 → 사용자 비밀번호 재입력</t>
+          <t>display_name (1~20자), avatar (이모지 단일 문자)</t>
         </is>
       </c>
       <c r="F169" s="3" t="inlineStr"/>
@@ -6746,7 +6829,7 @@
       </c>
       <c r="E170" s="3" t="inlineStr">
         <is>
-          <t>DELETE folders/links/folder_members(self) + 모든 디바이스 SYNC</t>
+          <t>profiles UPDATE + 헤더 즉시 반영</t>
         </is>
       </c>
       <c r="F170" s="3" t="inlineStr"/>
@@ -6766,10 +6849,7 @@
       </c>
       <c r="E171" s="3" t="inlineStr">
         <is>
-          <t>[위험 액션] 이중 확인 + 비밀번호 재입력
-[복구 불가] 즉시 hard delete — DB에서 본인 데이터 영구 삭제, 복구 불가
-[고지] 모달 2에 명시: "삭제하면 복구할 수 없어요. 그래도 진행할까요?"
-[동기화] 즉시 모든 디바이스에서 빈 상태</t>
+          <t>[동기화] 즉시 모든 디바이스 반영</t>
         </is>
       </c>
       <c r="F171" s="3" t="inlineStr"/>
@@ -6789,8 +6869,8 @@
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
-          <t>- 비밀번호 불일치: 모달 안에서 '비밀번호가 일치하지 않아요'
-- 처리 중 네트워크 오류: 트랜잭션으로 서버 측 부분 삭제 방지 (전부 실패하거나 전부 성공)</t>
+          <t>- 빈 닉네임: '닉네임을 입력해주세요'
+- 20자 초과: 입력 차단</t>
         </is>
       </c>
       <c r="F172" s="3" t="inlineStr"/>
@@ -6802,8 +6882,8 @@
     <row r="173">
       <c r="A173" s="3" t="inlineStr">
         <is>
-          <t>THEME-001
-#SETTINGS-THEME</t>
+          <t>SETTINGS-003
+#SETTINGS-PASSWORD</t>
         </is>
       </c>
       <c r="B173" s="3" t="inlineStr">
@@ -6813,7 +6893,7 @@
       </c>
       <c r="C173" s="3" t="inlineStr">
         <is>
-          <t>다크/라이트 + 강조색</t>
+          <t>비밀번호 변경</t>
         </is>
       </c>
       <c r="D173" s="3" t="inlineStr">
@@ -6823,22 +6903,23 @@
       </c>
       <c r="E173" s="3" t="inlineStr">
         <is>
-          <t>다크/라이트 모드 + 강조색 3종(핑크·블루·그레이). 사용자별 저장. 로그인 화면은 항상 라이트+핑크(브랜드)</t>
+          <t>현재 비밀번호 검증 → 새 비밀번호 변경. 변경 후 다른 디바이스는 강제 로그아웃 (보안 우선)</t>
         </is>
       </c>
       <c r="F173" s="3" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>프로필 업데이트 API</t>
+          <t>비밀번호 변경 API
+리프레시 토큰 무효화 API</t>
         </is>
       </c>
       <c r="H173" s="3" t="inlineStr">
         <is>
-          <t>일부포함</t>
+          <t>MVP</t>
         </is>
       </c>
       <c r="I173" s="3" t="inlineStr">
@@ -6848,7 +6929,7 @@
       </c>
       <c r="J173" s="3" t="inlineStr">
         <is>
-          <t>결정: 다크/라이트 모드 + 강조색 3종(핑크/블루/그레이)</t>
+          <t>결정: 변경 시 다른 디바이스 강제 로그아웃 + 화면 안내 문구 추가</t>
         </is>
       </c>
     </row>
@@ -6863,7 +6944,7 @@
       </c>
       <c r="E174" s="3" t="inlineStr">
         <is>
-          <t>mode (`light`/`dark`), accent (`pink`/`blue`/`gray`)</t>
+          <t>current_password, new_password (8~64자, 영문+숫자)</t>
         </is>
       </c>
       <c r="F174" s="3" t="inlineStr"/>
@@ -6883,7 +6964,7 @@
       </c>
       <c r="E175" s="3" t="inlineStr">
         <is>
-          <t>profiles.theme UPDATE + CSS 변수 즉시 반영 + SYNC</t>
+          <t>비밀번호 변경 + 모든 다른 디바이스 리프레시 토큰 invalidate + 토스트 "변경됐어요. 다른 기기에서는 다시 로그인해주세요"</t>
         </is>
       </c>
       <c r="F175" s="3" t="inlineStr"/>
@@ -6903,8 +6984,9 @@
       </c>
       <c r="E176" s="3" t="inlineStr">
         <is>
-          <t>[동기화] SYNC-001로 모든 디바이스 즉시 반영
-[기본값] 신규 가입자 light + pink</t>
+          <t>[보안] 현재 비밀번호 검증 필수
+[강제 로그아웃] 변경 즉시 서버에서 모든 다른 활성 리프레시 토큰 invalidate
+[화면 안내] 비밀번호 변경 화면 상단에 안내 카피: "비밀번호를 바꾸면 로그인된 다른 기기들에서 자동으로 로그아웃돼요. 보안을 위한 조치예요."</t>
         </is>
       </c>
       <c r="F176" s="3" t="inlineStr"/>
@@ -6914,628 +6996,605 @@
       <c r="J176" s="3" t="inlineStr"/>
     </row>
     <row r="177">
-      <c r="A177" s="4" t="inlineStr">
+      <c r="A177" s="3" t="inlineStr"/>
+      <c r="B177" s="3" t="inlineStr"/>
+      <c r="C177" s="3" t="inlineStr"/>
+      <c r="D177" s="3" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="E177" s="3" t="inlineStr">
+        <is>
+          <t>- 현재 PW 불일치: '현재 비밀번호가 일치하지 않아요'
+- 새 PW 정책 미충족: 안내
+- 5회 실패: 잠시 차단</t>
+        </is>
+      </c>
+      <c r="F177" s="3" t="inlineStr"/>
+      <c r="G177" s="3" t="inlineStr"/>
+      <c r="H177" s="3" t="inlineStr"/>
+      <c r="I177" s="3" t="inlineStr"/>
+      <c r="J177" s="3" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="3" t="inlineStr">
+        <is>
+          <t>SETTINGS-004
+#SETTINGS-RESET</t>
+        </is>
+      </c>
+      <c r="B178" s="3" t="inlineStr">
+        <is>
+          <t>설정</t>
+        </is>
+      </c>
+      <c r="C178" s="3" t="inlineStr">
+        <is>
+          <t>데이터 초기화</t>
+        </is>
+      </c>
+      <c r="D178" s="3" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+      <c r="E178" s="3" t="inlineStr">
+        <is>
+          <t>본인 데이터(폴더·링크·공유 멤버십) 전체 영구 삭제. 이중 확인 모달. 모든 디바이스에서 즉시 빈 상태</t>
+        </is>
+      </c>
+      <c r="F178" s="3" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G178" s="3" t="inlineStr">
+        <is>
+          <t>데이터 일괄 삭제 API (트랜잭션)</t>
+        </is>
+      </c>
+      <c r="H178" s="3" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="I178" s="3" t="inlineStr">
+        <is>
+          <t>기획완료</t>
+        </is>
+      </c>
+      <c r="J178" s="3" t="inlineStr">
+        <is>
+          <t>결정: 즉시 hard delete (개인정보보호법 OK, 사용자 의도 그대로 존중)</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="3" t="inlineStr"/>
+      <c r="B179" s="3" t="inlineStr"/>
+      <c r="C179" s="3" t="inlineStr"/>
+      <c r="D179" s="3" t="inlineStr">
+        <is>
+          <t>입력</t>
+        </is>
+      </c>
+      <c r="E179" s="3" t="inlineStr">
+        <is>
+          <t>"초기화" 버튼 → 모달 1 → "정말 삭제" → 모달 2 → 사용자 비밀번호 재입력</t>
+        </is>
+      </c>
+      <c r="F179" s="3" t="inlineStr"/>
+      <c r="G179" s="3" t="inlineStr"/>
+      <c r="H179" s="3" t="inlineStr"/>
+      <c r="I179" s="3" t="inlineStr"/>
+      <c r="J179" s="3" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="3" t="inlineStr"/>
+      <c r="B180" s="3" t="inlineStr"/>
+      <c r="C180" s="3" t="inlineStr"/>
+      <c r="D180" s="3" t="inlineStr">
+        <is>
+          <t>출력</t>
+        </is>
+      </c>
+      <c r="E180" s="3" t="inlineStr">
+        <is>
+          <t>DELETE folders/links/folder_members(self) + 모든 디바이스 SYNC</t>
+        </is>
+      </c>
+      <c r="F180" s="3" t="inlineStr"/>
+      <c r="G180" s="3" t="inlineStr"/>
+      <c r="H180" s="3" t="inlineStr"/>
+      <c r="I180" s="3" t="inlineStr"/>
+      <c r="J180" s="3" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="3" t="inlineStr"/>
+      <c r="B181" s="3" t="inlineStr"/>
+      <c r="C181" s="3" t="inlineStr"/>
+      <c r="D181" s="3" t="inlineStr">
+        <is>
+          <t>정책</t>
+        </is>
+      </c>
+      <c r="E181" s="3" t="inlineStr">
+        <is>
+          <t>[위험 액션] 이중 확인 + 비밀번호 재입력
+[복구 불가] 즉시 hard delete — DB에서 본인 데이터 영구 삭제, 복구 불가
+[고지] 모달 2에 명시: "삭제하면 복구할 수 없어요. 그래도 진행할까요?"
+[동기화] 즉시 모든 디바이스에서 빈 상태</t>
+        </is>
+      </c>
+      <c r="F181" s="3" t="inlineStr"/>
+      <c r="G181" s="3" t="inlineStr"/>
+      <c r="H181" s="3" t="inlineStr"/>
+      <c r="I181" s="3" t="inlineStr"/>
+      <c r="J181" s="3" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="3" t="inlineStr"/>
+      <c r="B182" s="3" t="inlineStr"/>
+      <c r="C182" s="3" t="inlineStr"/>
+      <c r="D182" s="3" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="E182" s="3" t="inlineStr">
+        <is>
+          <t>- 비밀번호 불일치: 모달 안에서 '비밀번호가 일치하지 않아요'
+- 처리 중 네트워크 오류: 트랜잭션으로 서버 측 부분 삭제 방지 (전부 실패하거나 전부 성공)</t>
+        </is>
+      </c>
+      <c r="F182" s="3" t="inlineStr"/>
+      <c r="G182" s="3" t="inlineStr"/>
+      <c r="H182" s="3" t="inlineStr"/>
+      <c r="I182" s="3" t="inlineStr"/>
+      <c r="J182" s="3" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="3" t="inlineStr">
+        <is>
+          <t>THEME-001
+#SETTINGS-THEME</t>
+        </is>
+      </c>
+      <c r="B183" s="3" t="inlineStr">
+        <is>
+          <t>설정</t>
+        </is>
+      </c>
+      <c r="C183" s="3" t="inlineStr">
+        <is>
+          <t>다크/라이트 + 강조색</t>
+        </is>
+      </c>
+      <c r="D183" s="3" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+      <c r="E183" s="3" t="inlineStr">
+        <is>
+          <t>다크/라이트 모드 + 강조색 3종(핑크·블루·그레이). 사용자별 저장. 로그인 화면은 항상 라이트+핑크(브랜드)</t>
+        </is>
+      </c>
+      <c r="F183" s="3" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G183" s="3" t="inlineStr">
+        <is>
+          <t>프로필 업데이트 API</t>
+        </is>
+      </c>
+      <c r="H183" s="3" t="inlineStr">
+        <is>
+          <t>일부포함</t>
+        </is>
+      </c>
+      <c r="I183" s="3" t="inlineStr">
+        <is>
+          <t>기획완료</t>
+        </is>
+      </c>
+      <c r="J183" s="3" t="inlineStr">
+        <is>
+          <t>결정: 다크/라이트 모드 + 강조색 3종(핑크/블루/그레이)</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="3" t="inlineStr"/>
+      <c r="B184" s="3" t="inlineStr"/>
+      <c r="C184" s="3" t="inlineStr"/>
+      <c r="D184" s="3" t="inlineStr">
+        <is>
+          <t>입력</t>
+        </is>
+      </c>
+      <c r="E184" s="3" t="inlineStr">
+        <is>
+          <t>mode (`light`/`dark`), accent (`pink`/`blue`/`gray`)</t>
+        </is>
+      </c>
+      <c r="F184" s="3" t="inlineStr"/>
+      <c r="G184" s="3" t="inlineStr"/>
+      <c r="H184" s="3" t="inlineStr"/>
+      <c r="I184" s="3" t="inlineStr"/>
+      <c r="J184" s="3" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="3" t="inlineStr"/>
+      <c r="B185" s="3" t="inlineStr"/>
+      <c r="C185" s="3" t="inlineStr"/>
+      <c r="D185" s="3" t="inlineStr">
+        <is>
+          <t>출력</t>
+        </is>
+      </c>
+      <c r="E185" s="3" t="inlineStr">
+        <is>
+          <t>profiles.theme UPDATE + CSS 변수 즉시 반영 + SYNC</t>
+        </is>
+      </c>
+      <c r="F185" s="3" t="inlineStr"/>
+      <c r="G185" s="3" t="inlineStr"/>
+      <c r="H185" s="3" t="inlineStr"/>
+      <c r="I185" s="3" t="inlineStr"/>
+      <c r="J185" s="3" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="3" t="inlineStr"/>
+      <c r="B186" s="3" t="inlineStr"/>
+      <c r="C186" s="3" t="inlineStr"/>
+      <c r="D186" s="3" t="inlineStr">
+        <is>
+          <t>정책</t>
+        </is>
+      </c>
+      <c r="E186" s="3" t="inlineStr">
+        <is>
+          <t>[동기화] SYNC-001로 모든 디바이스 즉시 반영
+[기본값] 신규 가입자 light + pink</t>
+        </is>
+      </c>
+      <c r="F186" s="3" t="inlineStr"/>
+      <c r="G186" s="3" t="inlineStr"/>
+      <c r="H186" s="3" t="inlineStr"/>
+      <c r="I186" s="3" t="inlineStr"/>
+      <c r="J186" s="3" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="4" t="inlineStr">
         <is>
           <t>AI-001</t>
         </is>
       </c>
-      <c r="B177" s="4" t="inlineStr">
+      <c r="B187" s="4" t="inlineStr">
         <is>
           <t>AI</t>
         </is>
       </c>
-      <c r="C177" s="4" t="inlineStr">
+      <c r="C187" s="4" t="inlineStr">
         <is>
           <t>Chrome 확장 (외부 AI 세션)</t>
         </is>
       </c>
-      <c r="D177" s="4" t="inlineStr">
+      <c r="D187" s="4" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="E177" s="4" t="inlineStr">
+      <c r="E187" s="4" t="inlineStr">
         <is>
           <t>Chrome MV3 확장이 사용자 본인의 웹 Gemini/ChatGPT/Claude 세션에 프롬프트 주입 → 응답 파싱 → QLink 앱으로 postMessage</t>
         </is>
       </c>
-      <c r="F177" s="4" t="inlineStr">
+      <c r="F187" s="4" t="inlineStr">
         <is>
           <t>Could</t>
         </is>
       </c>
-      <c r="G177" s="4" t="inlineStr"/>
-      <c r="H177" s="4" t="inlineStr">
+      <c r="G187" s="4" t="inlineStr"/>
+      <c r="H187" s="4" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="I177" s="4" t="inlineStr">
+      <c r="I187" s="4" t="inlineStr">
         <is>
           <t>기획중</t>
         </is>
       </c>
-      <c r="J177" s="4" t="inlineStr">
+      <c r="J187" s="4" t="inlineStr">
         <is>
           <t>ToS 회색 영역 — 신중 검토</t>
         </is>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" s="4" t="inlineStr">
+    <row r="191">
+      <c r="A191" s="4" t="inlineStr">
         <is>
           <t>BACKUP-001</t>
         </is>
       </c>
-      <c r="B181" s="4" t="inlineStr">
+      <c r="B191" s="4" t="inlineStr">
         <is>
           <t>설정</t>
         </is>
       </c>
-      <c r="C181" s="4" t="inlineStr">
+      <c r="C191" s="4" t="inlineStr">
         <is>
           <t>데이터 내보내기</t>
         </is>
       </c>
-      <c r="D181" s="4" t="inlineStr">
+      <c r="D191" s="4" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="E181" s="4" t="inlineStr">
+      <c r="E191" s="4" t="inlineStr">
         <is>
           <t>JSON·CSV 다운로드. IMPORT-001과 대칭</t>
         </is>
       </c>
-      <c r="F181" s="4" t="inlineStr">
+      <c r="F191" s="4" t="inlineStr">
         <is>
           <t>Could</t>
         </is>
       </c>
-      <c r="G181" s="4" t="inlineStr"/>
-      <c r="H181" s="4" t="inlineStr">
+      <c r="G191" s="4" t="inlineStr"/>
+      <c r="H191" s="4" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="I181" s="4" t="inlineStr">
+      <c r="I191" s="4" t="inlineStr">
         <is>
           <t>기획중</t>
         </is>
       </c>
-      <c r="J181" s="4" t="inlineStr"/>
-    </row>
-    <row r="185">
-      <c r="A185" s="4" t="inlineStr">
+      <c r="J191" s="4" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="4" t="inlineStr">
         <is>
           <t>HIGHLIGHT-001</t>
         </is>
       </c>
-      <c r="B185" s="4" t="inlineStr">
+      <c r="B195" s="4" t="inlineStr">
         <is>
           <t>콘텐츠</t>
         </is>
       </c>
-      <c r="C185" s="4" t="inlineStr">
+      <c r="C195" s="4" t="inlineStr">
         <is>
           <t>본문 하이라이트</t>
         </is>
       </c>
-      <c r="D185" s="4" t="inlineStr">
+      <c r="D195" s="4" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="E185" s="4" t="inlineStr">
+      <c r="E195" s="4" t="inlineStr">
         <is>
           <t>링크 본문 텍스트 일부 강조 저장</t>
         </is>
       </c>
-      <c r="F185" s="4" t="inlineStr">
+      <c r="F195" s="4" t="inlineStr">
         <is>
           <t>Could</t>
         </is>
       </c>
-      <c r="G185" s="4" t="inlineStr"/>
-      <c r="H185" s="4" t="inlineStr">
+      <c r="G195" s="4" t="inlineStr"/>
+      <c r="H195" s="4" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="I185" s="4" t="inlineStr">
+      <c r="I195" s="4" t="inlineStr">
         <is>
           <t>기획중</t>
         </is>
       </c>
-      <c r="J185" s="4" t="inlineStr"/>
-    </row>
-    <row r="189">
-      <c r="A189" s="4" t="inlineStr">
+      <c r="J195" s="4" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="4" t="inlineStr">
         <is>
           <t>OFFLINE-001</t>
         </is>
       </c>
-      <c r="B189" s="4" t="inlineStr">
+      <c r="B199" s="4" t="inlineStr">
         <is>
           <t>PWA</t>
         </is>
       </c>
-      <c r="C189" s="4" t="inlineStr">
+      <c r="C199" s="4" t="inlineStr">
         <is>
           <t>풀 오프라인 모드</t>
         </is>
       </c>
-      <c r="D189" s="4" t="inlineStr">
+      <c r="D199" s="4" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="E189" s="4" t="inlineStr">
+      <c r="E199" s="4" t="inlineStr">
         <is>
           <t>네트워크 없이 모든 기능 동작 — 동기화 충돌 복잡도, v2 백로그</t>
         </is>
       </c>
-      <c r="F189" s="4" t="inlineStr">
+      <c r="F199" s="4" t="inlineStr">
         <is>
           <t>Won't</t>
         </is>
       </c>
-      <c r="G189" s="4" t="inlineStr"/>
-      <c r="H189" s="4" t="inlineStr">
+      <c r="G199" s="4" t="inlineStr"/>
+      <c r="H199" s="4" t="inlineStr">
         <is>
           <t>미포함</t>
         </is>
       </c>
-      <c r="I189" s="4" t="inlineStr">
+      <c r="I199" s="4" t="inlineStr">
         <is>
           <t>기획중</t>
         </is>
       </c>
-      <c r="J189" s="4" t="inlineStr">
+      <c r="J199" s="4" t="inlineStr">
         <is>
           <t>이번 릴리즈 제외</t>
         </is>
       </c>
     </row>
-    <row r="193">
-      <c r="A193" s="4" t="inlineStr">
+    <row r="203">
+      <c r="A203" s="4" t="inlineStr">
         <is>
           <t>NATIVE-001</t>
         </is>
       </c>
-      <c r="B193" s="4" t="inlineStr">
+      <c r="B203" s="4" t="inlineStr">
         <is>
           <t>PWA</t>
         </is>
       </c>
-      <c r="C193" s="4" t="inlineStr">
+      <c r="C203" s="4" t="inlineStr">
         <is>
           <t>네이티브 앱</t>
         </is>
       </c>
-      <c r="D193" s="4" t="inlineStr">
+      <c r="D203" s="4" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="E193" s="4" t="inlineStr">
+      <c r="E203" s="4" t="inlineStr">
         <is>
           <t>iOS/Android 스토어 등록 — PWA로 충분</t>
         </is>
       </c>
-      <c r="F193" s="4" t="inlineStr">
+      <c r="F203" s="4" t="inlineStr">
         <is>
           <t>Won't</t>
         </is>
       </c>
-      <c r="G193" s="4" t="inlineStr"/>
-      <c r="H193" s="4" t="inlineStr">
+      <c r="G203" s="4" t="inlineStr"/>
+      <c r="H203" s="4" t="inlineStr">
         <is>
           <t>미포함</t>
         </is>
       </c>
-      <c r="I193" s="4" t="inlineStr">
+      <c r="I203" s="4" t="inlineStr">
         <is>
           <t>기획중</t>
         </is>
       </c>
-      <c r="J193" s="4" t="inlineStr">
+      <c r="J203" s="4" t="inlineStr">
         <is>
           <t>이번 릴리즈 제외</t>
         </is>
       </c>
     </row>
-    <row r="197">
-      <c r="A197" s="4" t="inlineStr">
+    <row r="207">
+      <c r="A207" s="4" t="inlineStr">
         <is>
           <t>BILLING-001</t>
         </is>
       </c>
-      <c r="B197" s="4" t="inlineStr">
+      <c r="B207" s="4" t="inlineStr">
         <is>
           <t>계정</t>
         </is>
       </c>
-      <c r="C197" s="4" t="inlineStr">
+      <c r="C207" s="4" t="inlineStr">
         <is>
           <t>유료 플랜</t>
         </is>
       </c>
-      <c r="D197" s="4" t="inlineStr">
+      <c r="D207" s="4" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="E197" s="4" t="inlineStr">
+      <c r="E207" s="4" t="inlineStr">
         <is>
           <t>결제·구독 — MVP는 무료 우선</t>
         </is>
       </c>
-      <c r="F197" s="4" t="inlineStr">
+      <c r="F207" s="4" t="inlineStr">
         <is>
           <t>Won't</t>
         </is>
       </c>
-      <c r="G197" s="4" t="inlineStr"/>
-      <c r="H197" s="4" t="inlineStr">
+      <c r="G207" s="4" t="inlineStr"/>
+      <c r="H207" s="4" t="inlineStr">
         <is>
           <t>미포함</t>
         </is>
       </c>
-      <c r="I197" s="4" t="inlineStr">
+      <c r="I207" s="4" t="inlineStr">
         <is>
           <t>기획중</t>
         </is>
       </c>
-      <c r="J197" s="4" t="inlineStr">
+      <c r="J207" s="4" t="inlineStr">
         <is>
           <t>이번 릴리즈 제외</t>
         </is>
       </c>
     </row>
-    <row r="201">
-      <c r="A201" s="3" t="inlineStr">
+    <row r="211">
+      <c r="A211" s="3" t="inlineStr">
         <is>
           <t>POLICY-AUTH</t>
         </is>
       </c>
-      <c r="B201" s="3" t="inlineStr">
+      <c r="B211" s="3" t="inlineStr">
         <is>
           <t>정책</t>
         </is>
       </c>
-      <c r="C201" s="3" t="inlineStr">
+      <c r="C211" s="3" t="inlineStr">
         <is>
           <t>토큰 만료/갱신 정책</t>
         </is>
       </c>
-      <c r="D201" s="3" t="inlineStr">
+      <c r="D211" s="3" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="E201" s="3" t="inlineStr">
+      <c r="E211" s="3" t="inlineStr">
         <is>
           <t>모든 인증 흐름의 공통 토큰 정책. 다른 기능에서는 "POLICY-AUTH 참고"로 1줄 참조</t>
         </is>
       </c>
-      <c r="F201" s="3" t="inlineStr">
+      <c r="F211" s="3" t="inlineStr">
         <is>
           <t>Must</t>
         </is>
       </c>
-      <c r="G201" s="3" t="inlineStr"/>
-      <c r="H201" s="3" t="inlineStr">
+      <c r="G211" s="3" t="inlineStr"/>
+      <c r="H211" s="3" t="inlineStr">
         <is>
           <t>MVP</t>
         </is>
       </c>
-      <c r="I201" s="3" t="inlineStr">
+      <c r="I211" s="3" t="inlineStr">
         <is>
           <t>기획완료</t>
         </is>
       </c>
-      <c r="J201" s="3" t="inlineStr">
+      <c r="J211" s="3" t="inlineStr">
         <is>
           <t>공통 참조 정책</t>
         </is>
       </c>
-    </row>
-    <row r="202">
-      <c r="A202" s="3" t="inlineStr"/>
-      <c r="B202" s="3" t="inlineStr"/>
-      <c r="C202" s="3" t="inlineStr"/>
-      <c r="D202" s="3" t="inlineStr">
-        <is>
-          <t>정책</t>
-        </is>
-      </c>
-      <c r="E202" s="3" t="inlineStr">
-        <is>
-          <t>[시간] 액세스 토큰 15분, 리프레시 토큰 30일
-[처리 순서] 401 응답 시 자동 갱신 1회 후 원래 요청 재시도
-[저장] 토큰은 secure storage 또는 httpOnly 쿠키
-[무효화] 비밀번호 변경 시 모든 리프레시 토큰 무효화 옵션 (TBD)</t>
-        </is>
-      </c>
-      <c r="F202" s="3" t="inlineStr"/>
-      <c r="G202" s="3" t="inlineStr"/>
-      <c r="H202" s="3" t="inlineStr"/>
-      <c r="I202" s="3" t="inlineStr"/>
-      <c r="J202" s="3" t="inlineStr"/>
-    </row>
-    <row r="203">
-      <c r="A203" s="3" t="inlineStr"/>
-      <c r="B203" s="3" t="inlineStr"/>
-      <c r="C203" s="3" t="inlineStr"/>
-      <c r="D203" s="3" t="inlineStr">
-        <is>
-          <t>예외</t>
-        </is>
-      </c>
-      <c r="E203" s="3" t="inlineStr">
-        <is>
-          <t>갱신 실패 시 강제 로그아웃 + #AUTH-LOGIN</t>
-        </is>
-      </c>
-      <c r="F203" s="3" t="inlineStr"/>
-      <c r="G203" s="3" t="inlineStr"/>
-      <c r="H203" s="3" t="inlineStr"/>
-      <c r="I203" s="3" t="inlineStr"/>
-      <c r="J203" s="3" t="inlineStr"/>
-    </row>
-    <row r="204">
-      <c r="A204" s="3" t="inlineStr">
-        <is>
-          <t>POLICY-AI</t>
-        </is>
-      </c>
-      <c r="B204" s="3" t="inlineStr">
-        <is>
-          <t>정책</t>
-        </is>
-      </c>
-      <c r="C204" s="3" t="inlineStr">
-        <is>
-          <t>AI 요약 호출 정책</t>
-        </is>
-      </c>
-      <c r="D204" s="3" t="inlineStr">
-        <is>
-          <t>설명</t>
-        </is>
-      </c>
-      <c r="E204" s="3" t="inlineStr">
-        <is>
-          <t>LINK-004와 IMPORT-001이 공통 사용. 사다리 폴백 정책</t>
-        </is>
-      </c>
-      <c r="F204" s="3" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G204" s="3" t="inlineStr"/>
-      <c r="H204" s="3" t="inlineStr">
-        <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="I204" s="3" t="inlineStr">
-        <is>
-          <t>기획완료</t>
-        </is>
-      </c>
-      <c r="J204" s="3" t="inlineStr">
-        <is>
-          <t>공통 참조 정책</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" s="3" t="inlineStr"/>
-      <c r="B205" s="3" t="inlineStr"/>
-      <c r="C205" s="3" t="inlineStr"/>
-      <c r="D205" s="3" t="inlineStr">
-        <is>
-          <t>정책</t>
-        </is>
-      </c>
-      <c r="E205" s="3" t="inlineStr">
-        <is>
-          <t>[폴백 사다리] (1) Chrome 확장 외부 세션(설치된 경우) → (2) 사용자 API 키(설정된 경우) → (3) 서버 mock
-[시간] 단건 요약 1.4초 timeout, 일괄 요약 비동기 큐
-[재시도] 1회 자동, 실패 시 빈 요약으로 저장 + 수동 재시도 버튼
-[데이터·채점] raw_response는 ai_jobs 테이블에 jsonb 보존</t>
-        </is>
-      </c>
-      <c r="F205" s="3" t="inlineStr"/>
-      <c r="G205" s="3" t="inlineStr"/>
-      <c r="H205" s="3" t="inlineStr"/>
-      <c r="I205" s="3" t="inlineStr"/>
-      <c r="J205" s="3" t="inlineStr"/>
-    </row>
-    <row r="206">
-      <c r="A206" s="3" t="inlineStr"/>
-      <c r="B206" s="3" t="inlineStr"/>
-      <c r="C206" s="3" t="inlineStr"/>
-      <c r="D206" s="3" t="inlineStr">
-        <is>
-          <t>예외</t>
-        </is>
-      </c>
-      <c r="E206" s="3" t="inlineStr">
-        <is>
-          <t>모든 폴백 실패 시 빈 요약. 사용자에게 토스트 안내</t>
-        </is>
-      </c>
-      <c r="F206" s="3" t="inlineStr"/>
-      <c r="G206" s="3" t="inlineStr"/>
-      <c r="H206" s="3" t="inlineStr"/>
-      <c r="I206" s="3" t="inlineStr"/>
-      <c r="J206" s="3" t="inlineStr"/>
-    </row>
-    <row r="207">
-      <c r="A207" s="3" t="inlineStr">
-        <is>
-          <t>POLICY-LOCAL</t>
-        </is>
-      </c>
-      <c r="B207" s="3" t="inlineStr">
-        <is>
-          <t>정책</t>
-        </is>
-      </c>
-      <c r="C207" s="3" t="inlineStr">
-        <is>
-          <t>로컬·서버 저장 분리</t>
-        </is>
-      </c>
-      <c r="D207" s="3" t="inlineStr">
-        <is>
-          <t>설명</t>
-        </is>
-      </c>
-      <c r="E207" s="3" t="inlineStr">
-        <is>
-          <t>게스트와 정식 사용자의 데이터 위치 분리. 오프라인 시 큐잉</t>
-        </is>
-      </c>
-      <c r="F207" s="3" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G207" s="3" t="inlineStr"/>
-      <c r="H207" s="3" t="inlineStr">
-        <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="I207" s="3" t="inlineStr">
-        <is>
-          <t>기획완료</t>
-        </is>
-      </c>
-      <c r="J207" s="3" t="inlineStr">
-        <is>
-          <t>공통 참조 정책</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" s="3" t="inlineStr"/>
-      <c r="B208" s="3" t="inlineStr"/>
-      <c r="C208" s="3" t="inlineStr"/>
-      <c r="D208" s="3" t="inlineStr">
-        <is>
-          <t>정책</t>
-        </is>
-      </c>
-      <c r="E208" s="3" t="inlineStr">
-        <is>
-          <t>[로컬 저장 대상] 게스트 모드 전체 데이터 / 클립보드 자동 채움 임시값 / 화면 캐시 (PWA Service Worker)
-[서버 저장 대상] 정식 사용자의 모든 데이터
-[오프라인 큐잉] 정식 사용자가 오프라인에서 저장 시 IndexedDB 큐 → 재연결 시 자동 동기화
-[충돌] last-write-wins by updated_at</t>
-        </is>
-      </c>
-      <c r="F208" s="3" t="inlineStr"/>
-      <c r="G208" s="3" t="inlineStr"/>
-      <c r="H208" s="3" t="inlineStr"/>
-      <c r="I208" s="3" t="inlineStr"/>
-      <c r="J208" s="3" t="inlineStr"/>
-    </row>
-    <row r="209">
-      <c r="A209" s="3" t="inlineStr"/>
-      <c r="B209" s="3" t="inlineStr"/>
-      <c r="C209" s="3" t="inlineStr"/>
-      <c r="D209" s="3" t="inlineStr">
-        <is>
-          <t>예외</t>
-        </is>
-      </c>
-      <c r="E209" s="3" t="inlineStr">
-        <is>
-          <t>로컬 큐 5MB 초과 시 사용자에게 안내</t>
-        </is>
-      </c>
-      <c r="F209" s="3" t="inlineStr"/>
-      <c r="G209" s="3" t="inlineStr"/>
-      <c r="H209" s="3" t="inlineStr"/>
-      <c r="I209" s="3" t="inlineStr"/>
-      <c r="J209" s="3" t="inlineStr"/>
-    </row>
-    <row r="210">
-      <c r="A210" s="3" t="inlineStr">
-        <is>
-          <t>POLICY-SHARED</t>
-        </is>
-      </c>
-      <c r="B210" s="3" t="inlineStr">
-        <is>
-          <t>정책</t>
-        </is>
-      </c>
-      <c r="C210" s="3" t="inlineStr">
-        <is>
-          <t>공유 폴더 권한 정책</t>
-        </is>
-      </c>
-      <c r="D210" s="3" t="inlineStr">
-        <is>
-          <t>설명</t>
-        </is>
-      </c>
-      <c r="E210" s="3" t="inlineStr">
-        <is>
-          <t>SHARE-001/002/003 공통 권한 모델</t>
-        </is>
-      </c>
-      <c r="F210" s="3" t="inlineStr">
-        <is>
-          <t>Should</t>
-        </is>
-      </c>
-      <c r="G210" s="3" t="inlineStr"/>
-      <c r="H210" s="3" t="inlineStr">
-        <is>
-          <t>일부포함</t>
-        </is>
-      </c>
-      <c r="I210" s="3" t="inlineStr">
-        <is>
-          <t>기획완료</t>
-        </is>
-      </c>
-      <c r="J210" s="3" t="inlineStr">
-        <is>
-          <t>공통 참조 정책</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" s="3" t="inlineStr"/>
-      <c r="B211" s="3" t="inlineStr"/>
-      <c r="C211" s="3" t="inlineStr"/>
-      <c r="D211" s="3" t="inlineStr">
-        <is>
-          <t>정책</t>
-        </is>
-      </c>
-      <c r="E211" s="3" t="inlineStr">
-        <is>
-          <t>[역할] owner: 폴더·링크·멤버 전체 권한 / member: 링크 추가·읽기·자기 추가한 링크 삭제 / viewer: 읽기만
-[기본] 초대 수락 시 role='member'
-[토큰] 유효 7일, 1회용 아님(여러 명 사용 가능)
-[멤버 한도] 50명</t>
-        </is>
-      </c>
-      <c r="F211" s="3" t="inlineStr"/>
-      <c r="G211" s="3" t="inlineStr"/>
-      <c r="H211" s="3" t="inlineStr"/>
-      <c r="I211" s="3" t="inlineStr"/>
-      <c r="J211" s="3" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" s="3" t="inlineStr"/>
@@ -7543,12 +7602,15 @@
       <c r="C212" s="3" t="inlineStr"/>
       <c r="D212" s="3" t="inlineStr">
         <is>
-          <t>예외</t>
+          <t>정책</t>
         </is>
       </c>
       <c r="E212" s="3" t="inlineStr">
         <is>
-          <t>권한 부족 액션은 UI에서 비활성 + 툴팁. 백엔드는 항상 재검증 (Lambda 핸들러)</t>
+          <t>[시간] 액세스 토큰 15분, 리프레시 토큰 30일
+[처리 순서] 401 응답 시 자동 갱신 1회 후 원래 요청 재시도
+[저장] 토큰은 secure storage 또는 httpOnly 쿠키
+[무효화] 비밀번호 변경 시 모든 리프레시 토큰 무효화 옵션 (TBD)</t>
         </is>
       </c>
       <c r="F212" s="3" t="inlineStr"/>
@@ -7556,6 +7618,299 @@
       <c r="H212" s="3" t="inlineStr"/>
       <c r="I212" s="3" t="inlineStr"/>
       <c r="J212" s="3" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="3" t="inlineStr"/>
+      <c r="B213" s="3" t="inlineStr"/>
+      <c r="C213" s="3" t="inlineStr"/>
+      <c r="D213" s="3" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="E213" s="3" t="inlineStr">
+        <is>
+          <t>갱신 실패 시 강제 로그아웃 + #AUTH-LOGIN</t>
+        </is>
+      </c>
+      <c r="F213" s="3" t="inlineStr"/>
+      <c r="G213" s="3" t="inlineStr"/>
+      <c r="H213" s="3" t="inlineStr"/>
+      <c r="I213" s="3" t="inlineStr"/>
+      <c r="J213" s="3" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="3" t="inlineStr">
+        <is>
+          <t>POLICY-AI</t>
+        </is>
+      </c>
+      <c r="B214" s="3" t="inlineStr">
+        <is>
+          <t>정책</t>
+        </is>
+      </c>
+      <c r="C214" s="3" t="inlineStr">
+        <is>
+          <t>AI 요약 호출 정책</t>
+        </is>
+      </c>
+      <c r="D214" s="3" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+      <c r="E214" s="3" t="inlineStr">
+        <is>
+          <t>LINK-004와 IMPORT-001이 공통 사용. 사다리 폴백 정책</t>
+        </is>
+      </c>
+      <c r="F214" s="3" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G214" s="3" t="inlineStr"/>
+      <c r="H214" s="3" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="I214" s="3" t="inlineStr">
+        <is>
+          <t>기획완료</t>
+        </is>
+      </c>
+      <c r="J214" s="3" t="inlineStr">
+        <is>
+          <t>공통 참조 정책</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="3" t="inlineStr"/>
+      <c r="B215" s="3" t="inlineStr"/>
+      <c r="C215" s="3" t="inlineStr"/>
+      <c r="D215" s="3" t="inlineStr">
+        <is>
+          <t>정책</t>
+        </is>
+      </c>
+      <c r="E215" s="3" t="inlineStr">
+        <is>
+          <t>[폴백 사다리] (1) Chrome 확장 외부 세션(설치된 경우) → (2) 사용자 API 키(설정된 경우) → (3) 서버 mock
+[시간] 단건 요약 1.4초 timeout, 일괄 요약 비동기 큐
+[재시도] 1회 자동, 실패 시 빈 요약으로 저장 + 수동 재시도 버튼
+[데이터·채점] raw_response는 ai_jobs 테이블에 jsonb 보존</t>
+        </is>
+      </c>
+      <c r="F215" s="3" t="inlineStr"/>
+      <c r="G215" s="3" t="inlineStr"/>
+      <c r="H215" s="3" t="inlineStr"/>
+      <c r="I215" s="3" t="inlineStr"/>
+      <c r="J215" s="3" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="3" t="inlineStr"/>
+      <c r="B216" s="3" t="inlineStr"/>
+      <c r="C216" s="3" t="inlineStr"/>
+      <c r="D216" s="3" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="E216" s="3" t="inlineStr">
+        <is>
+          <t>모든 폴백 실패 시 빈 요약. 사용자에게 토스트 안내</t>
+        </is>
+      </c>
+      <c r="F216" s="3" t="inlineStr"/>
+      <c r="G216" s="3" t="inlineStr"/>
+      <c r="H216" s="3" t="inlineStr"/>
+      <c r="I216" s="3" t="inlineStr"/>
+      <c r="J216" s="3" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="3" t="inlineStr">
+        <is>
+          <t>POLICY-LOCAL</t>
+        </is>
+      </c>
+      <c r="B217" s="3" t="inlineStr">
+        <is>
+          <t>정책</t>
+        </is>
+      </c>
+      <c r="C217" s="3" t="inlineStr">
+        <is>
+          <t>로컬·서버 저장 분리</t>
+        </is>
+      </c>
+      <c r="D217" s="3" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+      <c r="E217" s="3" t="inlineStr">
+        <is>
+          <t>게스트와 정식 사용자의 데이터 위치 분리. 오프라인 시 큐잉</t>
+        </is>
+      </c>
+      <c r="F217" s="3" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G217" s="3" t="inlineStr"/>
+      <c r="H217" s="3" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="I217" s="3" t="inlineStr">
+        <is>
+          <t>기획완료</t>
+        </is>
+      </c>
+      <c r="J217" s="3" t="inlineStr">
+        <is>
+          <t>공통 참조 정책</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="3" t="inlineStr"/>
+      <c r="B218" s="3" t="inlineStr"/>
+      <c r="C218" s="3" t="inlineStr"/>
+      <c r="D218" s="3" t="inlineStr">
+        <is>
+          <t>정책</t>
+        </is>
+      </c>
+      <c r="E218" s="3" t="inlineStr">
+        <is>
+          <t>[로컬 저장 대상] 게스트 모드 전체 데이터 / 클립보드 자동 채움 임시값 / 화면 캐시 (PWA Service Worker)
+[서버 저장 대상] 정식 사용자의 모든 데이터
+[오프라인 큐잉] 정식 사용자가 오프라인에서 저장 시 IndexedDB 큐 → 재연결 시 자동 동기화
+[충돌] last-write-wins by updated_at</t>
+        </is>
+      </c>
+      <c r="F218" s="3" t="inlineStr"/>
+      <c r="G218" s="3" t="inlineStr"/>
+      <c r="H218" s="3" t="inlineStr"/>
+      <c r="I218" s="3" t="inlineStr"/>
+      <c r="J218" s="3" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="3" t="inlineStr"/>
+      <c r="B219" s="3" t="inlineStr"/>
+      <c r="C219" s="3" t="inlineStr"/>
+      <c r="D219" s="3" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="E219" s="3" t="inlineStr">
+        <is>
+          <t>로컬 큐 5MB 초과 시 사용자에게 안내</t>
+        </is>
+      </c>
+      <c r="F219" s="3" t="inlineStr"/>
+      <c r="G219" s="3" t="inlineStr"/>
+      <c r="H219" s="3" t="inlineStr"/>
+      <c r="I219" s="3" t="inlineStr"/>
+      <c r="J219" s="3" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="3" t="inlineStr">
+        <is>
+          <t>POLICY-SHARED</t>
+        </is>
+      </c>
+      <c r="B220" s="3" t="inlineStr">
+        <is>
+          <t>정책</t>
+        </is>
+      </c>
+      <c r="C220" s="3" t="inlineStr">
+        <is>
+          <t>공유 폴더 권한 정책</t>
+        </is>
+      </c>
+      <c r="D220" s="3" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+      <c r="E220" s="3" t="inlineStr">
+        <is>
+          <t>SHARE-001/002/003 공통 권한 모델</t>
+        </is>
+      </c>
+      <c r="F220" s="3" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G220" s="3" t="inlineStr"/>
+      <c r="H220" s="3" t="inlineStr">
+        <is>
+          <t>일부포함</t>
+        </is>
+      </c>
+      <c r="I220" s="3" t="inlineStr">
+        <is>
+          <t>기획완료</t>
+        </is>
+      </c>
+      <c r="J220" s="3" t="inlineStr">
+        <is>
+          <t>공통 참조 정책</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="3" t="inlineStr"/>
+      <c r="B221" s="3" t="inlineStr"/>
+      <c r="C221" s="3" t="inlineStr"/>
+      <c r="D221" s="3" t="inlineStr">
+        <is>
+          <t>정책</t>
+        </is>
+      </c>
+      <c r="E221" s="3" t="inlineStr">
+        <is>
+          <t>[역할] owner: 폴더·링크·멤버 전체 권한 / member: 링크 추가·읽기·자기 추가한 링크 삭제 / viewer: 읽기만
+[기본] 초대 수락 시 role='member'
+[토큰] 유효 7일, 1회용 아님(여러 명 사용 가능)
+[멤버 한도] 50명</t>
+        </is>
+      </c>
+      <c r="F221" s="3" t="inlineStr"/>
+      <c r="G221" s="3" t="inlineStr"/>
+      <c r="H221" s="3" t="inlineStr"/>
+      <c r="I221" s="3" t="inlineStr"/>
+      <c r="J221" s="3" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="3" t="inlineStr"/>
+      <c r="B222" s="3" t="inlineStr"/>
+      <c r="C222" s="3" t="inlineStr"/>
+      <c r="D222" s="3" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="E222" s="3" t="inlineStr">
+        <is>
+          <t>권한 부족 액션은 UI에서 비활성 + 툴팁. 백엔드는 항상 재검증 (Lambda 핸들러)</t>
+        </is>
+      </c>
+      <c r="F222" s="3" t="inlineStr"/>
+      <c r="G222" s="3" t="inlineStr"/>
+      <c r="H222" s="3" t="inlineStr"/>
+      <c r="I222" s="3" t="inlineStr"/>
+      <c r="J222" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/docs/planning/05_상세기능명세서.xlsx
+++ b/docs/planning/05_상세기능명세서.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G53"/>
+  <dimension ref="A1:G54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2361,7 +2361,7 @@
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>owner/member/viewer + 토큰 7일</t>
+          <t>owner/member/viewer + 토큰 7일 + 멤버 50명</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
@@ -2375,6 +2375,39 @@
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>POLICY-VISIBILITY</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>정책</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>공유 폴더 콘텐츠 가시성</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>할 일 private/public 선택 + 메모 항상 private + 수락 필요 모델</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2390,7 +2423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J222"/>
+  <dimension ref="A1:J226"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -7911,6 +7944,121 @@
       <c r="H222" s="3" t="inlineStr"/>
       <c r="I222" s="3" t="inlineStr"/>
       <c r="J222" s="3" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="3" t="inlineStr">
+        <is>
+          <t>POLICY-VISIBILITY</t>
+        </is>
+      </c>
+      <c r="B223" s="3" t="inlineStr">
+        <is>
+          <t>정책</t>
+        </is>
+      </c>
+      <c r="C223" s="3" t="inlineStr">
+        <is>
+          <t>공유 폴더 콘텐츠 가시성</t>
+        </is>
+      </c>
+      <c r="D223" s="3" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+      <c r="E223" s="3" t="inlineStr">
+        <is>
+          <t>공유 폴더 link의 부속 콘텐츠(할 일·메모) 노출 규칙. TODO-009/010 공통 사용</t>
+        </is>
+      </c>
+      <c r="F223" s="3" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G223" s="3" t="inlineStr"/>
+      <c r="H223" s="3" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="I223" s="3" t="inlineStr">
+        <is>
+          <t>기획완료</t>
+        </is>
+      </c>
+      <c r="J223" s="3" t="inlineStr">
+        <is>
+          <t>TODO-009/010 공통 정책. 메모와 할 일의 가시성 규칙이 다름</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="3" t="inlineStr"/>
+      <c r="B224" s="3" t="inlineStr"/>
+      <c r="C224" s="3" t="inlineStr"/>
+      <c r="D224" s="3" t="inlineStr">
+        <is>
+          <t>정책</t>
+        </is>
+      </c>
+      <c r="E224" s="3" t="inlineStr">
+        <is>
+          <t>[할 일] visibility: 'private'(default) | 'public'. 사용자 선택
+[메모] visibility 컬럼 없음. 항상 private. UI에 '🔒 나만 볼 수 있는 내용입니다' 안내
+[작성자 표시] public todo는 멤버에게 '👥 {닉네임}이 공유한 할 일'
+[수락 모델] public todo는 명시적 수락(POST /todos/:id/accept)해야 본인 알림 등록
+[DB 일관성] 메모 public 변경 API 호출은 백엔드 차단(400)</t>
+        </is>
+      </c>
+      <c r="F224" s="3" t="inlineStr"/>
+      <c r="G224" s="3" t="inlineStr"/>
+      <c r="H224" s="3" t="inlineStr"/>
+      <c r="I224" s="3" t="inlineStr"/>
+      <c r="J224" s="3" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="3" t="inlineStr"/>
+      <c r="B225" s="3" t="inlineStr"/>
+      <c r="C225" s="3" t="inlineStr"/>
+      <c r="D225" s="3" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="E225" s="3" t="inlineStr">
+        <is>
+          <t>- 비멤버 조회: 403
+- 자기 todo 수락 시도: UI 비활성, API CONFLICT
+- public→private 전환: 기존 수락자 알림 즉시 제거 + Realtime publish
+- 작성자가 public 삭제: 수락 멤버 알림 일괄 제거 (이중 확인 모달)</t>
+        </is>
+      </c>
+      <c r="F225" s="3" t="inlineStr"/>
+      <c r="G225" s="3" t="inlineStr"/>
+      <c r="H225" s="3" t="inlineStr"/>
+      <c r="I225" s="3" t="inlineStr"/>
+      <c r="J225" s="3" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="3" t="inlineStr"/>
+      <c r="B226" s="3" t="inlineStr"/>
+      <c r="C226" s="3" t="inlineStr"/>
+      <c r="D226" s="3" t="inlineStr">
+        <is>
+          <t>마이그레이션</t>
+        </is>
+      </c>
+      <c r="E226" s="3" t="inlineStr">
+        <is>
+          <t>개인 폴더 → 공유 폴더 전환(SHARE-001) 시 기존 todo 자동 'private'. 사용자가 개별 변경</t>
+        </is>
+      </c>
+      <c r="F226" s="3" t="inlineStr"/>
+      <c r="G226" s="3" t="inlineStr"/>
+      <c r="H226" s="3" t="inlineStr"/>
+      <c r="I226" s="3" t="inlineStr"/>
+      <c r="J226" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -8248,7 +8396,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -8314,10 +8462,32 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>결정 12건 반영: 이메일 6자리·게스트 출시 제거(Won't)·AI 폴백(MVP=mock+API키, v1.x=외부세션)·FCM Topic 분배+모바일/PC 채널 분리·비밀번호 변경 시 강제 로그아웃·즉시 hard delete·AWS API Gateway WebSocket·last-write-wins·공유멤버 50명·강조색 3색(핑크/블루/그레이)·단건 외부세션 미사용</t>
+          <t>결정 12건 반영 + 할 일 = 1차 USP 격상: TODO-001~005 Must 추가, 페르소나 시나리오 3개(직장인 PM·취준생·자격증), 다중 할 일·반복 알림(요일+시간) UX, 회차별 완료 + 누적 이력 토글</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>인우</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>v1.0.2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>공유 폴더 가시성·수락 흐름: TODO-009(할 일 private/public 선택), TODO-010(공개 할 일 수락), POLICY-VISIBILITY 신규, 메모 항상 비공개 + 안내 문구. FLOW-017 추가, 색상 가독성 전면 개선(--qlink-primary 기반)</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>인우</t>
         </is>
